--- a/아이템 도감.xlsx
+++ b/아이템 도감.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hcw97\Desktop\CapstoneProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\CapstoneProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1D6BE8A-CC92-4354-8C3C-B3EFA9BD581D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C68618-CD66-43CB-9A36-6022D4E3CACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{AEFF7BDA-CB51-4C25-A75C-46A97EA8EBD6}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{AEFF7BDA-CB51-4C25-A75C-46A97EA8EBD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -176,9 +176,6 @@
     <t>아이스크림</t>
   </si>
   <si>
-    <t>곰팡이 캐릭터 빵</t>
-  </si>
-  <si>
     <t>먹다 남은 나쵸</t>
   </si>
   <si>
@@ -467,10 +464,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>귀여운 캐릭터 빵. 띠부 씰과 곰팡이 포함.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>누군가 먹다 남긴 치즈맛 나쵸.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -771,20 +764,28 @@
     <t>Food_yogurt</t>
   </si>
   <si>
-    <t>곰팡이 식빵</t>
+    <t>Food_cheese</t>
+  </si>
+  <si>
+    <t>Food_cocoa</t>
+  </si>
+  <si>
+    <t>Food_drumstick</t>
+  </si>
+  <si>
+    <t>Food_melonpan</t>
+  </si>
+  <si>
+    <t>멜론 빵</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Food_cheese</t>
-  </si>
-  <si>
-    <t>Food_cocoa</t>
-  </si>
-  <si>
-    <t>Food_drumstick</t>
-  </si>
-  <si>
-    <t>Food_melonpan</t>
+    <t>귀여운 멜론 모양의 맛있는 빵.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(삭제할 아이템)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1049,9 +1050,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1089,7 +1090,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1195,7 +1196,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1337,7 +1338,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1346,27 +1347,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176CEBE0-28C6-4629-A760-C52146228B7D}">
   <dimension ref="A1:Q433"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12.875" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="18.08203125" customWidth="1"/>
+    <col min="3" max="3" width="18.125" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" customWidth="1"/>
-    <col min="6" max="6" width="21.08203125" customWidth="1"/>
-    <col min="7" max="8" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.375" customWidth="1"/>
+    <col min="6" max="6" width="21.125" customWidth="1"/>
+    <col min="7" max="8" width="14.875" customWidth="1"/>
     <col min="9" max="9" width="14.25" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="15.58203125" customWidth="1"/>
-    <col min="12" max="12" width="19.08203125" customWidth="1"/>
+    <col min="10" max="10" width="12.875" customWidth="1"/>
+    <col min="11" max="11" width="15.625" customWidth="1"/>
+    <col min="12" max="12" width="19.125" customWidth="1"/>
     <col min="13" max="13" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="54.58203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="35.1640625" customWidth="1"/>
+    <col min="14" max="14" width="54.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="35.125" customWidth="1"/>
     <col min="16" max="16" width="56.25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="59.58203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="59.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1395,7 +1396,7 @@
         <v>6</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>7</v>
@@ -1410,13 +1411,13 @@
         <v>10</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="P1" s="11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1460,13 +1461,13 @@
         <v>1</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="P2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1511,10 +1512,10 @@
       </c>
       <c r="O3" s="6"/>
       <c r="P3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1559,10 +1560,10 @@
       </c>
       <c r="O4" s="6"/>
       <c r="P4" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1607,10 +1608,10 @@
       </c>
       <c r="O5" s="6"/>
       <c r="P5" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1654,13 +1655,13 @@
         <v>1</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="P6" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1705,10 +1706,10 @@
       </c>
       <c r="O7" s="6"/>
       <c r="P7" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1753,10 +1754,10 @@
       </c>
       <c r="O8" s="6"/>
       <c r="P8" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1801,10 +1802,10 @@
       </c>
       <c r="O9" s="6"/>
       <c r="P9" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1848,13 +1849,13 @@
         <v>1</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="P10" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1899,10 +1900,10 @@
       </c>
       <c r="O11" s="6"/>
       <c r="P11" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1947,10 +1948,10 @@
       </c>
       <c r="O12" s="6"/>
       <c r="P12" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1995,10 +1996,10 @@
       </c>
       <c r="O13" s="6"/>
       <c r="P13" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2043,10 +2044,10 @@
       </c>
       <c r="O14" s="6"/>
       <c r="P14" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2057,7 +2058,7 @@
         <v>150</v>
       </c>
       <c r="D15" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -2090,13 +2091,13 @@
         <v>1</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="P15" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2140,13 +2141,13 @@
         <v>1</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="P16" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.45">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2191,10 +2192,10 @@
       </c>
       <c r="O17" s="6"/>
       <c r="P17" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.45">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2238,13 +2239,13 @@
         <v>1</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="P18" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.45">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2289,10 +2290,10 @@
       </c>
       <c r="O19" s="6"/>
       <c r="P19" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.45">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2336,13 +2337,13 @@
         <v>1</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="P20" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.45">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -2356,7 +2357,7 @@
       <c r="M21" s="6"/>
       <c r="O21" s="6"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>20</v>
       </c>
@@ -2400,13 +2401,13 @@
         <v>1</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="P22" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.45">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>21</v>
       </c>
@@ -2450,13 +2451,13 @@
         <v>1</v>
       </c>
       <c r="O23" s="6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="P23" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.45">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>22</v>
       </c>
@@ -2500,13 +2501,13 @@
         <v>1</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="P24" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.45">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>23</v>
       </c>
@@ -2550,13 +2551,13 @@
         <v>1</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="P25" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.45">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>24</v>
       </c>
@@ -2600,16 +2601,16 @@
         <v>1</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="P26" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q26" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.45">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25</v>
       </c>
@@ -2653,16 +2654,16 @@
         <v>1</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="P27" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q27" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.45">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26</v>
       </c>
@@ -2706,13 +2707,13 @@
         <v>1</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="P28" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.45">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>27</v>
       </c>
@@ -2756,13 +2757,13 @@
         <v>1</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="P29" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.45">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>28</v>
       </c>
@@ -2773,7 +2774,7 @@
         <v>200</v>
       </c>
       <c r="D30" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -2807,10 +2808,10 @@
       </c>
       <c r="O30" s="6"/>
       <c r="P30" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.45">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>29</v>
       </c>
@@ -2854,13 +2855,13 @@
         <v>1</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="P31" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.45">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>30</v>
       </c>
@@ -2904,13 +2905,13 @@
         <v>1</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="P32" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.45">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>31</v>
       </c>
@@ -2954,13 +2955,13 @@
         <v>1</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="P33" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.45">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>32</v>
       </c>
@@ -3004,13 +3005,13 @@
         <v>1</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="P34" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.45">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>33</v>
       </c>
@@ -3054,16 +3055,16 @@
         <v>1</v>
       </c>
       <c r="O35" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="P35" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q35" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.45">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>34</v>
       </c>
@@ -3107,16 +3108,16 @@
         <v>1</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P36" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Q36" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.45">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>35</v>
       </c>
@@ -3127,7 +3128,7 @@
         <v>202</v>
       </c>
       <c r="D37" t="s">
-        <v>46</v>
+        <v>224</v>
       </c>
       <c r="E37">
         <v>1</v>
@@ -3160,13 +3161,13 @@
         <v>1</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="P37" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.45">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>36</v>
       </c>
@@ -3177,7 +3178,7 @@
         <v>202</v>
       </c>
       <c r="D38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -3210,13 +3211,13 @@
         <v>1</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="P38" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.45">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>37</v>
       </c>
@@ -3227,7 +3228,7 @@
         <v>203</v>
       </c>
       <c r="D39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -3260,16 +3261,16 @@
         <v>1</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="P39" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="Q39" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.45">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>38</v>
       </c>
@@ -3280,7 +3281,7 @@
         <v>202</v>
       </c>
       <c r="D40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -3313,13 +3314,13 @@
         <v>1</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="P40" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.45">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>39</v>
       </c>
@@ -3330,7 +3331,7 @@
         <v>202</v>
       </c>
       <c r="D41" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -3363,13 +3364,13 @@
         <v>1</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P41" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.45">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>40</v>
       </c>
@@ -3380,7 +3381,7 @@
         <v>202</v>
       </c>
       <c r="D42" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E42">
         <v>1</v>
@@ -3413,13 +3414,13 @@
         <v>1</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="P42" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.45">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>41</v>
       </c>
@@ -3430,7 +3431,7 @@
         <v>202</v>
       </c>
       <c r="D43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E43">
         <v>1</v>
@@ -3463,13 +3464,13 @@
         <v>1</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="P43" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.45">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>42</v>
       </c>
@@ -3480,7 +3481,7 @@
         <v>203</v>
       </c>
       <c r="D44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3513,16 +3514,16 @@
         <v>1</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="P44" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="Q44" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.45">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>43</v>
       </c>
@@ -3533,7 +3534,7 @@
         <v>202</v>
       </c>
       <c r="D45" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E45">
         <v>1</v>
@@ -3566,13 +3567,13 @@
         <v>1</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="P45" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>44</v>
       </c>
@@ -3583,7 +3584,7 @@
         <v>202</v>
       </c>
       <c r="D46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E46">
         <v>1</v>
@@ -3616,13 +3617,13 @@
         <v>1</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="P46" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.45">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>45</v>
       </c>
@@ -3633,7 +3634,7 @@
         <v>202</v>
       </c>
       <c r="D47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E47">
         <v>1</v>
@@ -3666,13 +3667,13 @@
         <v>1</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="P47" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.45">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>46</v>
       </c>
@@ -3683,7 +3684,7 @@
         <v>202</v>
       </c>
       <c r="D48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3716,16 +3717,16 @@
         <v>1</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="P48" s="9" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.45">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="O49" s="6"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>47</v>
       </c>
@@ -3736,7 +3737,7 @@
         <v>302</v>
       </c>
       <c r="D50" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E50">
         <v>1</v>
@@ -3770,13 +3771,13 @@
       </c>
       <c r="O50" s="6"/>
       <c r="P50" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Q50" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.45">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>48</v>
       </c>
@@ -3787,7 +3788,7 @@
         <v>301</v>
       </c>
       <c r="D51" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E51">
         <v>1</v>
@@ -3821,13 +3822,13 @@
       </c>
       <c r="O51" s="6"/>
       <c r="P51" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Q51" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.45">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>49</v>
       </c>
@@ -3838,7 +3839,7 @@
         <v>301</v>
       </c>
       <c r="D52" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E52">
         <v>1</v>
@@ -3872,13 +3873,13 @@
       </c>
       <c r="O52" s="6"/>
       <c r="P52" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="Q52" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.45">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>50</v>
       </c>
@@ -3889,7 +3890,7 @@
         <v>303</v>
       </c>
       <c r="D53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -3923,13 +3924,13 @@
       </c>
       <c r="O53" s="6"/>
       <c r="P53" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="Q53" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.45">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>51</v>
       </c>
@@ -3940,7 +3941,7 @@
         <v>300</v>
       </c>
       <c r="D54" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E54">
         <v>1</v>
@@ -3974,10 +3975,10 @@
       </c>
       <c r="O54" s="6"/>
       <c r="P54" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.45">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>52</v>
       </c>
@@ -3988,7 +3989,7 @@
         <v>300</v>
       </c>
       <c r="D55" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E55">
         <v>1</v>
@@ -4022,10 +4023,10 @@
       </c>
       <c r="O55" s="6"/>
       <c r="P55" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.45">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>53</v>
       </c>
@@ -4036,7 +4037,7 @@
         <v>300</v>
       </c>
       <c r="D56" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E56">
         <v>1</v>
@@ -4070,10 +4071,10 @@
       </c>
       <c r="O56" s="6"/>
       <c r="P56" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.45">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>54</v>
       </c>
@@ -4084,7 +4085,7 @@
         <v>300</v>
       </c>
       <c r="D57" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E57">
         <v>1</v>
@@ -4118,13 +4119,13 @@
       </c>
       <c r="O57" s="6"/>
       <c r="P57" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="Q57" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.45">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>55</v>
       </c>
@@ -4135,7 +4136,7 @@
         <v>303</v>
       </c>
       <c r="D58" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E58">
         <v>1</v>
@@ -4169,13 +4170,13 @@
       </c>
       <c r="O58" s="6"/>
       <c r="P58" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="Q58" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.45">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>56</v>
       </c>
@@ -4186,7 +4187,7 @@
         <v>303</v>
       </c>
       <c r="D59" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E59">
         <v>1</v>
@@ -4220,16 +4221,16 @@
       </c>
       <c r="O59" s="6"/>
       <c r="P59" s="9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="Q59" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.45">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="O60" s="6"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>57</v>
       </c>
@@ -4237,7 +4238,7 @@
         <v>3</v>
       </c>
       <c r="D61" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -4271,7 +4272,7 @@
       </c>
       <c r="O61" s="6"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>58</v>
       </c>
@@ -4279,7 +4280,7 @@
         <v>3</v>
       </c>
       <c r="D62" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E62">
         <v>3</v>
@@ -4313,7 +4314,7 @@
       </c>
       <c r="O62" s="6"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>59</v>
       </c>
@@ -4321,7 +4322,7 @@
         <v>3</v>
       </c>
       <c r="D63" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E63">
         <v>4</v>
@@ -4355,7 +4356,7 @@
       </c>
       <c r="O63" s="6"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>60</v>
       </c>
@@ -4363,7 +4364,7 @@
         <v>3</v>
       </c>
       <c r="D64" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E64">
         <v>3</v>
@@ -4397,7 +4398,7 @@
       </c>
       <c r="O64" s="6"/>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>61</v>
       </c>
@@ -4405,7 +4406,7 @@
         <v>3</v>
       </c>
       <c r="D65" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E65">
         <v>4</v>
@@ -4439,7 +4440,7 @@
       </c>
       <c r="O65" s="6"/>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>62</v>
       </c>
@@ -4447,7 +4448,7 @@
         <v>3</v>
       </c>
       <c r="D66" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -4481,7 +4482,7 @@
       </c>
       <c r="O66" s="6"/>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>63</v>
       </c>
@@ -4489,7 +4490,7 @@
         <v>3</v>
       </c>
       <c r="D67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E67">
         <v>10</v>
@@ -4523,7 +4524,7 @@
       </c>
       <c r="O67" s="6"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>64</v>
       </c>
@@ -4531,7 +4532,7 @@
         <v>3</v>
       </c>
       <c r="D68" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E68">
         <v>1</v>
@@ -4565,7 +4566,7 @@
       </c>
       <c r="O68" s="6"/>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>65</v>
       </c>
@@ -4573,7 +4574,7 @@
         <v>3</v>
       </c>
       <c r="D69" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E69">
         <v>2</v>
@@ -4607,7 +4608,7 @@
       </c>
       <c r="O69" s="6"/>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>66</v>
       </c>
@@ -4615,7 +4616,7 @@
         <v>3</v>
       </c>
       <c r="D70" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E70">
         <v>5</v>
@@ -4649,7 +4650,7 @@
       </c>
       <c r="O70" s="6"/>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>67</v>
       </c>
@@ -4657,7 +4658,7 @@
         <v>3</v>
       </c>
       <c r="D71" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E71">
         <v>40</v>
@@ -4691,7 +4692,7 @@
       </c>
       <c r="O71" s="6"/>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>68</v>
       </c>
@@ -4699,7 +4700,7 @@
         <v>3</v>
       </c>
       <c r="D72" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E72">
         <v>32</v>
@@ -4733,7 +4734,7 @@
       </c>
       <c r="O72" s="6"/>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>69</v>
       </c>
@@ -4741,7 +4742,7 @@
         <v>3</v>
       </c>
       <c r="D73" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E73">
         <v>1</v>
@@ -4775,7 +4776,7 @@
       </c>
       <c r="O73" s="6"/>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>70</v>
       </c>
@@ -4783,7 +4784,7 @@
         <v>3</v>
       </c>
       <c r="D74" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E74">
         <v>2</v>
@@ -4817,7 +4818,7 @@
       </c>
       <c r="O74" s="6"/>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>71</v>
       </c>
@@ -4825,7 +4826,7 @@
         <v>3</v>
       </c>
       <c r="D75" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E75">
         <v>3</v>
@@ -4859,7 +4860,7 @@
       </c>
       <c r="O75" s="6"/>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>72</v>
       </c>
@@ -4867,7 +4868,7 @@
         <v>3</v>
       </c>
       <c r="D76" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E76">
         <v>15</v>
@@ -4901,7 +4902,7 @@
       </c>
       <c r="O76" s="6"/>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>73</v>
       </c>
@@ -4909,7 +4910,7 @@
         <v>3</v>
       </c>
       <c r="D77" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E77">
         <v>6</v>
@@ -4943,7 +4944,7 @@
       </c>
       <c r="O77" s="6"/>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>74</v>
       </c>
@@ -4951,7 +4952,7 @@
         <v>3</v>
       </c>
       <c r="D78" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E78">
         <v>8</v>
@@ -4985,7 +4986,7 @@
       </c>
       <c r="O78" s="6"/>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>75</v>
       </c>
@@ -4993,7 +4994,7 @@
         <v>3</v>
       </c>
       <c r="D79" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E79">
         <v>20</v>
@@ -5027,7 +5028,7 @@
       </c>
       <c r="O79" s="6"/>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>76</v>
       </c>
@@ -5035,7 +5036,7 @@
         <v>3</v>
       </c>
       <c r="D80" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E80">
         <v>5</v>
@@ -5069,7 +5070,7 @@
       </c>
       <c r="O80" s="6"/>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>77</v>
       </c>
@@ -5077,7 +5078,7 @@
         <v>3</v>
       </c>
       <c r="D81" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E81">
         <v>4</v>
@@ -5111,7 +5112,7 @@
       </c>
       <c r="O81" s="6"/>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>78</v>
       </c>
@@ -5119,7 +5120,7 @@
         <v>3</v>
       </c>
       <c r="D82" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E82">
         <v>3</v>
@@ -5153,7 +5154,7 @@
       </c>
       <c r="O82" s="6"/>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>79</v>
       </c>
@@ -5161,7 +5162,7 @@
         <v>3</v>
       </c>
       <c r="D83" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E83">
         <v>20</v>
@@ -5195,7 +5196,7 @@
       </c>
       <c r="O83" s="6"/>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>80</v>
       </c>
@@ -5203,7 +5204,7 @@
         <v>3</v>
       </c>
       <c r="D84" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E84">
         <v>10</v>
@@ -5237,7 +5238,7 @@
       </c>
       <c r="O84" s="6"/>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>81</v>
       </c>
@@ -5245,7 +5246,7 @@
         <v>3</v>
       </c>
       <c r="D85" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E85">
         <v>12</v>
@@ -5279,7 +5280,7 @@
       </c>
       <c r="O85" s="6"/>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>82</v>
       </c>
@@ -5287,7 +5288,7 @@
         <v>3</v>
       </c>
       <c r="D86" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E86">
         <v>17</v>
@@ -5321,7 +5322,7 @@
       </c>
       <c r="O86" s="6"/>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>83</v>
       </c>
@@ -5329,7 +5330,7 @@
         <v>3</v>
       </c>
       <c r="D87" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E87">
         <v>8</v>
@@ -5363,7 +5364,7 @@
       </c>
       <c r="O87" s="6"/>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>84</v>
       </c>
@@ -5371,7 +5372,7 @@
         <v>3</v>
       </c>
       <c r="D88" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E88">
         <v>10</v>
@@ -5405,7 +5406,7 @@
       </c>
       <c r="O88" s="6"/>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>85</v>
       </c>
@@ -5413,7 +5414,7 @@
         <v>3</v>
       </c>
       <c r="D89" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E89">
         <v>17</v>
@@ -5447,7 +5448,7 @@
       </c>
       <c r="O89" s="6"/>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>86</v>
       </c>
@@ -5455,7 +5456,7 @@
         <v>3</v>
       </c>
       <c r="D90" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E90">
         <v>30</v>
@@ -5489,7 +5490,7 @@
       </c>
       <c r="O90" s="6"/>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>87</v>
       </c>
@@ -5497,7 +5498,7 @@
         <v>3</v>
       </c>
       <c r="D91" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E91">
         <v>14</v>
@@ -5531,7 +5532,7 @@
       </c>
       <c r="O91" s="6"/>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>88</v>
       </c>
@@ -5539,7 +5540,7 @@
         <v>3</v>
       </c>
       <c r="D92" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E92">
         <v>8</v>
@@ -5573,7 +5574,7 @@
       </c>
       <c r="O92" s="6"/>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>89</v>
       </c>
@@ -5581,7 +5582,7 @@
         <v>3</v>
       </c>
       <c r="D93" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E93">
         <v>15</v>
@@ -5615,7 +5616,7 @@
       </c>
       <c r="O93" s="6"/>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>90</v>
       </c>
@@ -5623,7 +5624,7 @@
         <v>3</v>
       </c>
       <c r="D94" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E94">
         <v>25</v>
@@ -5657,7 +5658,7 @@
       </c>
       <c r="O94" s="6"/>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>91</v>
       </c>
@@ -5665,7 +5666,7 @@
         <v>3</v>
       </c>
       <c r="D95" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E95">
         <v>5</v>
@@ -5699,7 +5700,7 @@
       </c>
       <c r="O95" s="6"/>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>92</v>
       </c>
@@ -5707,7 +5708,7 @@
         <v>3</v>
       </c>
       <c r="D96" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E96">
         <v>3</v>
@@ -5741,7 +5742,7 @@
       </c>
       <c r="O96" s="6"/>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>93</v>
       </c>
@@ -5749,7 +5750,7 @@
         <v>3</v>
       </c>
       <c r="D97" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E97">
         <v>30</v>
@@ -5783,7 +5784,7 @@
       </c>
       <c r="O97" s="6"/>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>94</v>
       </c>
@@ -5791,7 +5792,7 @@
         <v>3</v>
       </c>
       <c r="D98" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E98">
         <v>20</v>
@@ -5825,7 +5826,7 @@
       </c>
       <c r="O98" s="6"/>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>95</v>
       </c>
@@ -5833,7 +5834,7 @@
         <v>3</v>
       </c>
       <c r="D99" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E99">
         <v>18</v>
@@ -5867,7 +5868,7 @@
       </c>
       <c r="O99" s="6"/>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>96</v>
       </c>
@@ -5875,7 +5876,7 @@
         <v>3</v>
       </c>
       <c r="D100" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E100">
         <v>8</v>
@@ -5909,7 +5910,7 @@
       </c>
       <c r="O100" s="6"/>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>97</v>
       </c>
@@ -5917,7 +5918,7 @@
         <v>3</v>
       </c>
       <c r="D101" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E101">
         <v>2</v>
@@ -5951,7 +5952,7 @@
       </c>
       <c r="O101" s="6"/>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>98</v>
       </c>
@@ -5959,7 +5960,7 @@
         <v>3</v>
       </c>
       <c r="D102" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E102">
         <v>40</v>
@@ -5993,7 +5994,7 @@
       </c>
       <c r="O102" s="6"/>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>99</v>
       </c>
@@ -6001,7 +6002,7 @@
         <v>3</v>
       </c>
       <c r="D103" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E103">
         <v>15</v>
@@ -6035,7 +6036,7 @@
       </c>
       <c r="O103" s="6"/>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>100</v>
       </c>
@@ -6043,7 +6044,7 @@
         <v>3</v>
       </c>
       <c r="D104" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E104">
         <v>5</v>
@@ -6077,7 +6078,7 @@
       </c>
       <c r="O104" s="6"/>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>101</v>
       </c>
@@ -6085,7 +6086,7 @@
         <v>3</v>
       </c>
       <c r="D105" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E105">
         <v>25</v>
@@ -6119,7 +6120,7 @@
       </c>
       <c r="O105" s="6"/>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>102</v>
       </c>
@@ -6127,7 +6128,7 @@
         <v>3</v>
       </c>
       <c r="D106" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E106">
         <v>30</v>
@@ -6161,7 +6162,7 @@
       </c>
       <c r="O106" s="6"/>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>103</v>
       </c>
@@ -6169,7 +6170,7 @@
         <v>3</v>
       </c>
       <c r="D107" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E107">
         <v>50</v>
@@ -6203,7 +6204,7 @@
       </c>
       <c r="O107" s="6"/>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>104</v>
       </c>
@@ -6211,7 +6212,7 @@
         <v>3</v>
       </c>
       <c r="D108" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E108">
         <v>45</v>
@@ -6245,7 +6246,7 @@
       </c>
       <c r="O108" s="6"/>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>105</v>
       </c>
@@ -6253,7 +6254,7 @@
         <v>3</v>
       </c>
       <c r="D109" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E109">
         <v>40</v>
@@ -6287,7 +6288,7 @@
       </c>
       <c r="O109" s="6"/>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>106</v>
       </c>
@@ -6295,7 +6296,7 @@
         <v>3</v>
       </c>
       <c r="D110" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E110">
         <v>80</v>
@@ -6329,7 +6330,7 @@
       </c>
       <c r="O110" s="6"/>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>107</v>
       </c>
@@ -6337,7 +6338,7 @@
         <v>3</v>
       </c>
       <c r="D111" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E111">
         <v>1</v>
@@ -6371,7 +6372,7 @@
       </c>
       <c r="O111" s="6"/>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>108</v>
       </c>
@@ -6379,7 +6380,7 @@
         <v>3</v>
       </c>
       <c r="D112" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E112">
         <v>70</v>
@@ -6413,7 +6414,7 @@
       </c>
       <c r="O112" s="6"/>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>109</v>
       </c>
@@ -6421,7 +6422,7 @@
         <v>3</v>
       </c>
       <c r="D113" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E113">
         <v>62</v>
@@ -6455,7 +6456,7 @@
       </c>
       <c r="O113" s="6"/>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>110</v>
       </c>
@@ -6463,7 +6464,7 @@
         <v>3</v>
       </c>
       <c r="D114" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E114">
         <v>150</v>
@@ -6497,7 +6498,7 @@
       </c>
       <c r="O114" s="6"/>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>111</v>
       </c>
@@ -6505,7 +6506,7 @@
         <v>3</v>
       </c>
       <c r="D115" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E115">
         <v>70</v>
@@ -6539,958 +6540,958 @@
       </c>
       <c r="O115" s="6"/>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O116" s="6"/>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O117" s="6"/>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O118" s="6"/>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O119" s="6"/>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O120" s="6"/>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O121" s="6"/>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O122" s="6"/>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O123" s="6"/>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O124" s="6"/>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O125" s="6"/>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O126" s="6"/>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O127" s="6"/>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O128" s="6"/>
     </row>
-    <row r="129" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="129" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O129" s="6"/>
     </row>
-    <row r="130" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="130" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O130" s="6"/>
     </row>
-    <row r="131" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="131" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O131" s="6"/>
     </row>
-    <row r="132" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="132" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O132" s="6"/>
     </row>
-    <row r="133" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="133" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O133" s="6"/>
     </row>
-    <row r="134" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="134" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O134" s="6"/>
     </row>
-    <row r="135" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="135" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O135" s="6"/>
     </row>
-    <row r="136" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="136" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O136" s="6"/>
     </row>
-    <row r="137" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="137" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O137" s="6"/>
     </row>
-    <row r="138" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="138" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O138" s="6"/>
     </row>
-    <row r="139" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="139" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O139" s="6"/>
     </row>
-    <row r="140" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="140" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O140" s="6"/>
     </row>
-    <row r="141" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="141" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O141" s="6"/>
     </row>
-    <row r="142" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="142" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O142" s="6"/>
     </row>
-    <row r="143" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="143" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O143" s="6"/>
     </row>
-    <row r="144" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="144" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O144" s="6"/>
     </row>
-    <row r="145" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="145" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O145" s="6"/>
     </row>
-    <row r="146" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="146" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O146" s="6"/>
     </row>
-    <row r="147" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="147" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O147" s="6"/>
     </row>
-    <row r="148" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="148" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O148" s="6"/>
     </row>
-    <row r="149" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="149" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O149" s="6"/>
     </row>
-    <row r="150" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="150" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O150" s="6"/>
     </row>
-    <row r="151" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="151" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O151" s="6"/>
     </row>
-    <row r="152" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="152" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O152" s="6"/>
     </row>
-    <row r="153" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="153" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O153" s="6"/>
     </row>
-    <row r="154" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="154" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O154" s="6"/>
     </row>
-    <row r="155" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="155" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O155" s="6"/>
     </row>
-    <row r="156" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="156" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O156" s="6"/>
     </row>
-    <row r="157" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="157" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O157" s="6"/>
     </row>
-    <row r="158" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="158" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O158" s="6"/>
     </row>
-    <row r="159" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="159" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O159" s="6"/>
     </row>
-    <row r="160" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="160" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O160" s="6"/>
     </row>
-    <row r="161" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="161" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O161" s="6"/>
     </row>
-    <row r="162" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="162" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O162" s="6"/>
     </row>
-    <row r="163" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="163" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O163" s="6"/>
     </row>
-    <row r="164" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="164" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O164" s="6"/>
     </row>
-    <row r="165" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="165" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O165" s="6"/>
     </row>
-    <row r="166" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="166" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O166" s="6"/>
     </row>
-    <row r="167" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="167" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O167" s="6"/>
     </row>
-    <row r="168" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="168" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O168" s="6"/>
     </row>
-    <row r="169" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="169" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O169" s="6"/>
     </row>
-    <row r="170" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="170" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O170" s="6"/>
     </row>
-    <row r="171" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="171" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O171" s="6"/>
     </row>
-    <row r="172" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="172" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O172" s="6"/>
     </row>
-    <row r="173" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="173" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O173" s="6"/>
     </row>
-    <row r="174" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="174" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O174" s="6"/>
     </row>
-    <row r="175" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="175" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O175" s="6"/>
     </row>
-    <row r="176" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="176" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O176" s="6"/>
     </row>
-    <row r="177" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="177" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O177" s="6"/>
     </row>
-    <row r="178" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="178" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O178" s="6"/>
     </row>
-    <row r="179" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="179" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O179" s="6"/>
     </row>
-    <row r="180" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="180" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O180" s="6"/>
     </row>
-    <row r="181" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="181" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O181" s="6"/>
     </row>
-    <row r="182" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="182" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O182" s="6"/>
     </row>
-    <row r="183" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="183" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O183" s="6"/>
     </row>
-    <row r="184" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="184" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O184" s="6"/>
     </row>
-    <row r="185" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="185" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O185" s="6"/>
     </row>
-    <row r="186" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="186" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O186" s="6"/>
     </row>
-    <row r="187" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="187" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O187" s="6"/>
     </row>
-    <row r="188" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="188" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O188" s="6"/>
     </row>
-    <row r="189" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="189" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O189" s="6"/>
     </row>
-    <row r="190" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="190" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O190" s="6"/>
     </row>
-    <row r="191" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="191" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O191" s="6"/>
     </row>
-    <row r="192" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="192" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O192" s="6"/>
     </row>
-    <row r="193" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="193" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O193" s="6"/>
     </row>
-    <row r="194" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="194" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O194" s="6"/>
     </row>
-    <row r="195" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="195" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O195" s="6"/>
     </row>
-    <row r="196" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="196" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O196" s="6"/>
     </row>
-    <row r="197" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="197" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O197" s="6"/>
     </row>
-    <row r="198" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="198" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O198" s="6"/>
     </row>
-    <row r="199" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="199" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O199" s="6"/>
     </row>
-    <row r="200" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="200" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O200" s="6"/>
     </row>
-    <row r="201" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="201" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O201" s="6"/>
     </row>
-    <row r="202" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="202" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O202" s="6"/>
     </row>
-    <row r="203" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="203" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O203" s="6"/>
     </row>
-    <row r="204" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="204" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O204" s="6"/>
     </row>
-    <row r="205" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="205" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O205" s="6"/>
     </row>
-    <row r="206" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="206" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O206" s="6"/>
     </row>
-    <row r="207" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="207" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O207" s="6"/>
     </row>
-    <row r="208" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="208" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O208" s="6"/>
     </row>
-    <row r="209" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="209" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O209" s="6"/>
     </row>
-    <row r="210" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="210" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O210" s="6"/>
     </row>
-    <row r="211" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="211" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O211" s="6"/>
     </row>
-    <row r="212" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="212" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O212" s="6"/>
     </row>
-    <row r="213" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="213" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O213" s="6"/>
     </row>
-    <row r="214" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="214" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O214" s="6"/>
     </row>
-    <row r="215" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="215" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O215" s="6"/>
     </row>
-    <row r="216" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="216" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O216" s="6"/>
     </row>
-    <row r="217" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="217" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O217" s="6"/>
     </row>
-    <row r="218" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="218" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O218" s="6"/>
     </row>
-    <row r="219" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="219" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O219" s="6"/>
     </row>
-    <row r="220" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="220" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O220" s="6"/>
     </row>
-    <row r="221" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="221" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O221" s="6"/>
     </row>
-    <row r="222" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="222" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O222" s="6"/>
     </row>
-    <row r="223" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="223" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O223" s="6"/>
     </row>
-    <row r="224" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="224" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O224" s="6"/>
     </row>
-    <row r="225" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="225" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O225" s="6"/>
     </row>
-    <row r="226" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="226" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O226" s="6"/>
     </row>
-    <row r="227" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="227" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O227" s="6"/>
     </row>
-    <row r="228" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="228" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O228" s="6"/>
     </row>
-    <row r="229" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="229" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O229" s="6"/>
     </row>
-    <row r="230" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="230" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O230" s="6"/>
     </row>
-    <row r="231" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="231" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O231" s="6"/>
     </row>
-    <row r="232" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="232" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O232" s="6"/>
     </row>
-    <row r="233" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="233" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O233" s="6"/>
     </row>
-    <row r="234" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="234" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O234" s="6"/>
     </row>
-    <row r="235" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="235" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O235" s="6"/>
     </row>
-    <row r="236" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="236" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O236" s="6"/>
     </row>
-    <row r="237" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="237" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O237" s="6"/>
     </row>
-    <row r="238" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="238" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O238" s="6"/>
     </row>
-    <row r="239" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="239" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O239" s="6"/>
     </row>
-    <row r="240" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="240" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O240" s="6"/>
     </row>
-    <row r="241" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="241" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O241" s="6"/>
     </row>
-    <row r="242" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="242" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O242" s="6"/>
     </row>
-    <row r="243" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="243" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O243" s="6"/>
     </row>
-    <row r="244" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="244" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O244" s="6"/>
     </row>
-    <row r="245" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="245" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O245" s="6"/>
     </row>
-    <row r="246" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="246" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O246" s="6"/>
     </row>
-    <row r="247" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="247" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O247" s="6"/>
     </row>
-    <row r="248" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="248" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O248" s="6"/>
     </row>
-    <row r="249" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="249" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O249" s="6"/>
     </row>
-    <row r="250" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="250" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O250" s="6"/>
     </row>
-    <row r="251" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="251" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O251" s="6"/>
     </row>
-    <row r="252" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="252" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O252" s="6"/>
     </row>
-    <row r="253" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="253" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O253" s="6"/>
     </row>
-    <row r="254" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="254" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O254" s="6"/>
     </row>
-    <row r="255" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="255" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O255" s="6"/>
     </row>
-    <row r="256" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="256" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O256" s="6"/>
     </row>
-    <row r="257" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="257" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O257" s="6"/>
     </row>
-    <row r="258" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="258" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O258" s="6"/>
     </row>
-    <row r="259" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="259" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O259" s="6"/>
     </row>
-    <row r="260" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="260" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O260" s="6"/>
     </row>
-    <row r="261" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="261" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O261" s="6"/>
     </row>
-    <row r="262" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="262" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O262" s="6"/>
     </row>
-    <row r="263" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="263" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O263" s="6"/>
     </row>
-    <row r="264" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="264" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O264" s="6"/>
     </row>
-    <row r="265" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="265" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O265" s="6"/>
     </row>
-    <row r="266" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="266" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O266" s="6"/>
     </row>
-    <row r="267" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="267" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O267" s="6"/>
     </row>
-    <row r="268" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="268" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O268" s="6"/>
     </row>
-    <row r="269" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="269" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O269" s="6"/>
     </row>
-    <row r="270" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="270" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O270" s="6"/>
     </row>
-    <row r="271" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="271" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O271" s="6"/>
     </row>
-    <row r="272" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="272" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O272" s="6"/>
     </row>
-    <row r="273" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="273" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O273" s="6"/>
     </row>
-    <row r="274" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="274" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O274" s="6"/>
     </row>
-    <row r="275" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="275" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O275" s="6"/>
     </row>
-    <row r="276" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="276" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O276" s="6"/>
     </row>
-    <row r="277" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="277" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O277" s="6"/>
     </row>
-    <row r="278" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="278" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O278" s="6"/>
     </row>
-    <row r="279" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="279" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O279" s="6"/>
     </row>
-    <row r="280" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="280" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O280" s="6"/>
     </row>
-    <row r="281" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="281" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O281" s="6"/>
     </row>
-    <row r="282" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="282" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O282" s="6"/>
     </row>
-    <row r="283" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="283" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O283" s="6"/>
     </row>
-    <row r="284" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="284" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O284" s="6"/>
     </row>
-    <row r="285" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="285" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O285" s="6"/>
     </row>
-    <row r="286" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="286" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O286" s="6"/>
     </row>
-    <row r="287" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="287" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O287" s="6"/>
     </row>
-    <row r="288" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="288" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O288" s="6"/>
     </row>
-    <row r="289" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="289" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O289" s="6"/>
     </row>
-    <row r="290" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="290" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O290" s="6"/>
     </row>
-    <row r="291" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="291" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O291" s="6"/>
     </row>
-    <row r="292" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="292" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O292" s="6"/>
     </row>
-    <row r="293" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="293" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O293" s="6"/>
     </row>
-    <row r="294" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="294" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O294" s="6"/>
     </row>
-    <row r="295" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="295" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O295" s="6"/>
     </row>
-    <row r="296" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="296" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O296" s="6"/>
     </row>
-    <row r="297" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="297" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O297" s="6"/>
     </row>
-    <row r="298" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="298" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O298" s="6"/>
     </row>
-    <row r="299" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="299" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O299" s="6"/>
     </row>
-    <row r="300" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="300" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O300" s="6"/>
     </row>
-    <row r="301" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="301" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O301" s="6"/>
     </row>
-    <row r="302" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="302" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O302" s="6"/>
     </row>
-    <row r="303" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="303" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O303" s="6"/>
     </row>
-    <row r="304" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="304" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O304" s="6"/>
     </row>
-    <row r="305" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="305" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O305" s="6"/>
     </row>
-    <row r="306" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="306" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O306" s="6"/>
     </row>
-    <row r="307" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="307" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O307" s="6"/>
     </row>
-    <row r="308" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="308" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O308" s="6"/>
     </row>
-    <row r="309" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="309" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O309" s="6"/>
     </row>
-    <row r="310" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="310" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O310" s="6"/>
     </row>
-    <row r="311" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="311" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O311" s="6"/>
     </row>
-    <row r="312" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="312" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O312" s="6"/>
     </row>
-    <row r="313" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="313" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O313" s="6"/>
     </row>
-    <row r="314" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="314" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O314" s="6"/>
     </row>
-    <row r="315" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="315" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O315" s="6"/>
     </row>
-    <row r="316" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="316" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O316" s="6"/>
     </row>
-    <row r="317" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="317" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O317" s="6"/>
     </row>
-    <row r="318" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="318" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O318" s="6"/>
     </row>
-    <row r="319" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="319" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O319" s="6"/>
     </row>
-    <row r="320" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="320" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O320" s="6"/>
     </row>
-    <row r="321" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="321" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O321" s="6"/>
     </row>
-    <row r="322" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="322" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O322" s="6"/>
     </row>
-    <row r="323" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="323" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O323" s="6"/>
     </row>
-    <row r="324" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="324" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O324" s="6"/>
     </row>
-    <row r="325" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="325" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O325" s="6"/>
     </row>
-    <row r="326" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="326" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O326" s="6"/>
     </row>
-    <row r="327" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="327" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O327" s="6"/>
     </row>
-    <row r="328" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="328" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O328" s="6"/>
     </row>
-    <row r="329" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="329" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O329" s="6"/>
     </row>
-    <row r="330" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="330" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O330" s="6"/>
     </row>
-    <row r="331" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="331" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O331" s="6"/>
     </row>
-    <row r="332" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="332" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O332" s="6"/>
     </row>
-    <row r="333" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="333" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O333" s="6"/>
     </row>
-    <row r="334" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="334" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O334" s="6"/>
     </row>
-    <row r="335" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="335" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O335" s="6"/>
     </row>
-    <row r="336" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="336" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O336" s="6"/>
     </row>
-    <row r="337" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="337" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O337" s="6"/>
     </row>
-    <row r="338" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="338" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O338" s="6"/>
     </row>
-    <row r="339" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="339" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O339" s="6"/>
     </row>
-    <row r="340" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="340" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O340" s="6"/>
     </row>
-    <row r="341" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="341" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O341" s="6"/>
     </row>
-    <row r="342" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="342" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O342" s="6"/>
     </row>
-    <row r="343" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="343" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O343" s="6"/>
     </row>
-    <row r="344" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="344" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O344" s="6"/>
     </row>
-    <row r="345" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="345" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O345" s="6"/>
     </row>
-    <row r="346" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="346" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O346" s="6"/>
     </row>
-    <row r="347" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="347" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O347" s="6"/>
     </row>
-    <row r="348" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="348" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O348" s="6"/>
     </row>
-    <row r="349" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="349" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O349" s="6"/>
     </row>
-    <row r="350" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="350" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O350" s="6"/>
     </row>
-    <row r="351" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="351" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O351" s="6"/>
     </row>
-    <row r="352" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="352" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O352" s="6"/>
     </row>
-    <row r="353" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="353" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O353" s="6"/>
     </row>
-    <row r="354" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="354" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O354" s="6"/>
     </row>
-    <row r="355" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="355" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O355" s="6"/>
     </row>
-    <row r="356" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="356" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O356" s="6"/>
     </row>
-    <row r="357" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="357" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O357" s="6"/>
     </row>
-    <row r="358" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="358" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O358" s="6"/>
     </row>
-    <row r="359" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="359" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O359" s="6"/>
     </row>
-    <row r="360" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="360" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O360" s="6"/>
     </row>
-    <row r="361" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="361" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O361" s="6"/>
     </row>
-    <row r="362" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="362" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O362" s="6"/>
     </row>
-    <row r="363" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="363" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O363" s="6"/>
     </row>
-    <row r="364" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="364" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O364" s="6"/>
     </row>
-    <row r="365" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="365" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O365" s="6"/>
     </row>
-    <row r="366" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="366" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O366" s="6"/>
     </row>
-    <row r="367" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="367" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O367" s="6"/>
     </row>
-    <row r="368" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="368" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O368" s="6"/>
     </row>
-    <row r="369" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="369" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O369" s="6"/>
     </row>
-    <row r="370" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="370" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O370" s="6"/>
     </row>
-    <row r="371" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="371" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O371" s="6"/>
     </row>
-    <row r="372" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="372" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O372" s="6"/>
     </row>
-    <row r="373" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="373" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O373" s="6"/>
     </row>
-    <row r="374" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="374" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O374" s="6"/>
     </row>
-    <row r="375" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="375" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O375" s="6"/>
     </row>
-    <row r="376" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="376" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O376" s="6"/>
     </row>
-    <row r="377" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="377" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O377" s="6"/>
     </row>
-    <row r="378" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="378" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O378" s="6"/>
     </row>
-    <row r="379" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="379" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O379" s="6"/>
     </row>
-    <row r="380" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="380" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O380" s="6"/>
     </row>
-    <row r="381" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="381" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O381" s="6"/>
     </row>
-    <row r="382" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="382" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O382" s="6"/>
     </row>
-    <row r="383" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="383" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O383" s="6"/>
     </row>
-    <row r="384" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="384" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O384" s="6"/>
     </row>
-    <row r="385" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="385" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O385" s="6"/>
     </row>
-    <row r="386" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="386" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O386" s="6"/>
     </row>
-    <row r="387" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="387" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O387" s="6"/>
     </row>
-    <row r="388" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="388" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O388" s="6"/>
     </row>
-    <row r="389" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="389" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O389" s="6"/>
     </row>
-    <row r="390" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="390" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O390" s="6"/>
     </row>
-    <row r="391" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="391" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O391" s="6"/>
     </row>
-    <row r="392" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="392" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O392" s="6"/>
     </row>
-    <row r="393" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="393" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O393" s="6"/>
     </row>
-    <row r="394" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="394" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O394" s="6"/>
     </row>
-    <row r="395" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="395" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O395" s="6"/>
     </row>
-    <row r="396" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="396" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O396" s="6"/>
     </row>
-    <row r="397" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="397" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O397" s="6"/>
     </row>
-    <row r="398" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="398" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O398" s="6"/>
     </row>
-    <row r="399" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="399" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O399" s="6"/>
     </row>
-    <row r="400" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="400" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O400" s="6"/>
     </row>
-    <row r="401" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="401" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O401" s="6"/>
     </row>
-    <row r="402" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="402" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O402" s="6"/>
     </row>
-    <row r="403" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="403" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O403" s="6"/>
     </row>
-    <row r="404" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="404" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O404" s="6"/>
     </row>
-    <row r="405" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="405" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O405" s="6"/>
     </row>
-    <row r="406" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="406" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O406" s="6"/>
     </row>
-    <row r="407" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="407" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O407" s="6"/>
     </row>
-    <row r="408" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="408" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O408" s="6"/>
     </row>
-    <row r="409" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="409" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O409" s="6"/>
     </row>
-    <row r="410" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="410" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O410" s="6"/>
     </row>
-    <row r="411" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="411" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O411" s="6"/>
     </row>
-    <row r="412" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="412" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O412" s="6"/>
     </row>
-    <row r="413" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="413" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O413" s="6"/>
     </row>
-    <row r="414" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="414" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O414" s="6"/>
     </row>
-    <row r="415" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="415" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O415" s="6"/>
     </row>
-    <row r="416" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="416" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O416" s="6"/>
     </row>
-    <row r="417" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="417" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O417" s="6"/>
     </row>
-    <row r="418" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="418" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O418" s="6"/>
     </row>
-    <row r="419" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="419" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O419" s="6"/>
     </row>
-    <row r="420" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="420" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O420" s="6"/>
     </row>
-    <row r="421" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="421" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O421" s="6"/>
     </row>
-    <row r="422" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="422" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O422" s="6"/>
     </row>
-    <row r="423" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="423" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O423" s="6"/>
     </row>
-    <row r="424" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="424" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O424" s="6"/>
     </row>
-    <row r="425" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="425" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O425" s="6"/>
     </row>
-    <row r="426" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="426" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O426" s="6"/>
     </row>
-    <row r="427" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="427" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O427" s="6"/>
     </row>
-    <row r="428" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="428" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O428" s="6"/>
     </row>
-    <row r="429" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="429" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O429" s="6"/>
     </row>
-    <row r="430" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="430" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O430" s="6"/>
     </row>
-    <row r="431" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="431" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O431" s="6"/>
     </row>
-    <row r="432" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="432" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O432" s="6"/>
     </row>
-    <row r="433" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="433" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O433" s="6"/>
     </row>
   </sheetData>

--- a/아이템 도감.xlsx
+++ b/아이템 도감.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\CapstoneProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hcw97\Desktop\CapstoneProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C68618-CD66-43CB-9A36-6022D4E3CACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F2B7715-A92D-4DF9-9E9F-A9F820930778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{AEFF7BDA-CB51-4C25-A75C-46A97EA8EBD6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{AEFF7BDA-CB51-4C25-A75C-46A97EA8EBD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="226">
   <si>
     <t>item_id</t>
   </si>
@@ -781,10 +781,6 @@
   </si>
   <si>
     <t>귀여운 멜론 모양의 맛있는 빵.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>(삭제할 아이템)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1050,9 +1046,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1090,7 +1086,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1196,7 +1192,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1338,7 +1334,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1347,27 +1343,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176CEBE0-28C6-4629-A760-C52146228B7D}">
   <dimension ref="A1:Q433"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.875" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="18.125" customWidth="1"/>
+    <col min="3" max="3" width="18.08203125" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
-    <col min="5" max="5" width="14.375" customWidth="1"/>
-    <col min="6" max="6" width="21.125" customWidth="1"/>
-    <col min="7" max="8" width="14.875" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" customWidth="1"/>
+    <col min="6" max="6" width="21.08203125" customWidth="1"/>
+    <col min="7" max="8" width="14.83203125" customWidth="1"/>
     <col min="9" max="9" width="14.25" customWidth="1"/>
-    <col min="10" max="10" width="12.875" customWidth="1"/>
-    <col min="11" max="11" width="15.625" customWidth="1"/>
-    <col min="12" max="12" width="19.125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="15.58203125" customWidth="1"/>
+    <col min="12" max="12" width="19.08203125" customWidth="1"/>
     <col min="13" max="13" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="54.625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="35.125" customWidth="1"/>
+    <col min="14" max="14" width="54.58203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="35.08203125" customWidth="1"/>
     <col min="16" max="16" width="56.25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="59.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="59.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1417,7 +1413,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1467,7 +1463,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1515,7 +1511,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1563,7 +1559,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1611,7 +1607,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1661,7 +1657,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1709,7 +1705,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1757,7 +1753,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1805,7 +1801,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1855,7 +1851,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1903,7 +1899,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1951,7 +1947,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1999,7 +1995,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2047,7 +2043,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2097,7 +2093,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2147,7 +2143,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2195,7 +2191,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2245,7 +2241,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2293,7 +2289,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2343,7 +2339,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -2357,7 +2353,7 @@
       <c r="M21" s="6"/>
       <c r="O21" s="6"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>20</v>
       </c>
@@ -2407,7 +2403,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>21</v>
       </c>
@@ -2457,7 +2453,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>22</v>
       </c>
@@ -2507,7 +2503,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>23</v>
       </c>
@@ -2557,7 +2553,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>24</v>
       </c>
@@ -2610,7 +2606,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>25</v>
       </c>
@@ -2663,7 +2659,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>26</v>
       </c>
@@ -2713,7 +2709,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>27</v>
       </c>
@@ -2763,18 +2759,18 @@
         <v>133</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A30">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D30" t="s">
-        <v>226</v>
+        <v>40</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -2783,10 +2779,10 @@
         <v>-1</v>
       </c>
       <c r="G30">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -2798,7 +2794,7 @@
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="M30">
         <v>99</v>
@@ -2806,14 +2802,16 @@
       <c r="N30" t="b">
         <v>1</v>
       </c>
-      <c r="O30" s="6"/>
+      <c r="O30" s="6" t="s">
+        <v>203</v>
+      </c>
       <c r="P30" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A31">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -2822,7 +2820,7 @@
         <v>202</v>
       </c>
       <c r="D31" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -2831,7 +2829,7 @@
         <v>-1</v>
       </c>
       <c r="G31">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H31">
         <v>10</v>
@@ -2855,24 +2853,24 @@
         <v>1</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="P31" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A32">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
       <c r="C32">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D32" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -2881,10 +2879,10 @@
         <v>-1</v>
       </c>
       <c r="G32">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H32">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -2905,24 +2903,24 @@
         <v>1</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="P32" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A33">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33">
         <v>1</v>
       </c>
       <c r="C33">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D33" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -2931,10 +2929,10 @@
         <v>-1</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H33">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -2946,7 +2944,7 @@
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>100</v>
+        <v>220</v>
       </c>
       <c r="M33">
         <v>99</v>
@@ -2955,24 +2953,24 @@
         <v>1</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="P33" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A34">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34">
         <v>1</v>
       </c>
       <c r="C34">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D34" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -2981,22 +2979,22 @@
         <v>-1</v>
       </c>
       <c r="G34">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H34">
+        <v>15</v>
+      </c>
+      <c r="I34">
+        <v>30</v>
+      </c>
+      <c r="J34">
         <v>10</v>
       </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
-        <v>-1</v>
-      </c>
       <c r="K34">
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>220</v>
+        <v>100</v>
       </c>
       <c r="M34">
         <v>99</v>
@@ -3005,15 +3003,18 @@
         <v>1</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="P34" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A35">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -3022,7 +3023,7 @@
         <v>203</v>
       </c>
       <c r="D35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -3034,10 +3035,10 @@
         <v>10</v>
       </c>
       <c r="H35">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I35">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J35">
         <v>10</v>
@@ -3046,7 +3047,7 @@
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M35">
         <v>99</v>
@@ -3055,27 +3056,27 @@
         <v>1</v>
       </c>
       <c r="O35" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="P35" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36">
         <v>202</v>
       </c>
-      <c r="P35" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <v>34</v>
-      </c>
-      <c r="B36">
-        <v>1</v>
-      </c>
-      <c r="C36">
-        <v>203</v>
-      </c>
       <c r="D36" t="s">
-        <v>45</v>
+        <v>224</v>
       </c>
       <c r="E36">
         <v>1</v>
@@ -3084,16 +3085,16 @@
         <v>-1</v>
       </c>
       <c r="G36">
+        <v>50</v>
+      </c>
+      <c r="H36">
         <v>10</v>
       </c>
-      <c r="H36">
-        <v>25</v>
-      </c>
       <c r="I36">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J36">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="K36">
         <v>-1</v>
@@ -3108,18 +3109,15 @@
         <v>1</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="P36" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A37">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -3128,7 +3126,7 @@
         <v>202</v>
       </c>
       <c r="D37" t="s">
-        <v>224</v>
+        <v>46</v>
       </c>
       <c r="E37">
         <v>1</v>
@@ -3137,7 +3135,7 @@
         <v>-1</v>
       </c>
       <c r="G37">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H37">
         <v>10</v>
@@ -3161,24 +3159,24 @@
         <v>1</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="P37" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A38">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
       <c r="C38">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D38" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -3187,16 +3185,16 @@
         <v>-1</v>
       </c>
       <c r="G38">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H38">
         <v>10</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K38">
         <v>-1</v>
@@ -3211,24 +3209,27 @@
         <v>1</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="P38" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A39">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B39">
         <v>1</v>
       </c>
       <c r="C39">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D39" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -3237,16 +3238,16 @@
         <v>-1</v>
       </c>
       <c r="G39">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="H39">
         <v>10</v>
       </c>
       <c r="I39">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J39">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="K39">
         <v>-1</v>
@@ -3261,18 +3262,15 @@
         <v>1</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="P39" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A40">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -3281,7 +3279,7 @@
         <v>202</v>
       </c>
       <c r="D40" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -3290,10 +3288,10 @@
         <v>-1</v>
       </c>
       <c r="G40">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H40">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -3314,15 +3312,15 @@
         <v>1</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="P40" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A41">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -3331,7 +3329,7 @@
         <v>202</v>
       </c>
       <c r="D41" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -3340,7 +3338,7 @@
         <v>-1</v>
       </c>
       <c r="G41">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H41">
         <v>5</v>
@@ -3364,15 +3362,15 @@
         <v>1</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P41" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A42">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -3381,7 +3379,7 @@
         <v>202</v>
       </c>
       <c r="D42" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E42">
         <v>1</v>
@@ -3390,10 +3388,10 @@
         <v>-1</v>
       </c>
       <c r="G42">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H42">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -3414,24 +3412,24 @@
         <v>1</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P42" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A43">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
       <c r="C43">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D43" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E43">
         <v>1</v>
@@ -3443,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="H43">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J43">
         <v>-1</v>
@@ -3464,24 +3462,27 @@
         <v>1</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="P43" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A44">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B44">
         <v>1</v>
       </c>
       <c r="C44">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D44" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3490,13 +3491,13 @@
         <v>-1</v>
       </c>
       <c r="G44">
+        <v>5</v>
+      </c>
+      <c r="H44">
+        <v>15</v>
+      </c>
+      <c r="I44">
         <v>0</v>
-      </c>
-      <c r="H44">
-        <v>50</v>
-      </c>
-      <c r="I44">
-        <v>10</v>
       </c>
       <c r="J44">
         <v>-1</v>
@@ -3514,18 +3515,15 @@
         <v>1</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="P44" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A45">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -3534,7 +3532,7 @@
         <v>202</v>
       </c>
       <c r="D45" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E45">
         <v>1</v>
@@ -3543,10 +3541,10 @@
         <v>-1</v>
       </c>
       <c r="G45">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H45">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -3567,15 +3565,15 @@
         <v>1</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P45" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A46">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -3584,7 +3582,7 @@
         <v>202</v>
       </c>
       <c r="D46" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E46">
         <v>1</v>
@@ -3593,10 +3591,10 @@
         <v>-1</v>
       </c>
       <c r="G46">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H46">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -3617,15 +3615,15 @@
         <v>1</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="P46" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A47">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -3634,7 +3632,7 @@
         <v>202</v>
       </c>
       <c r="D47" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E47">
         <v>1</v>
@@ -3643,10 +3641,10 @@
         <v>-1</v>
       </c>
       <c r="G47">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H47">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -3667,66 +3665,16 @@
         <v>1</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="P47" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A48">
-        <v>46</v>
-      </c>
-      <c r="B48">
-        <v>1</v>
-      </c>
-      <c r="C48">
-        <v>202</v>
-      </c>
-      <c r="D48" t="s">
-        <v>56</v>
-      </c>
-      <c r="E48">
-        <v>1</v>
-      </c>
-      <c r="F48">
-        <v>-1</v>
-      </c>
-      <c r="G48">
-        <v>25</v>
-      </c>
-      <c r="H48">
-        <v>30</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-      <c r="J48">
-        <v>-1</v>
-      </c>
-      <c r="K48">
-        <v>-1</v>
-      </c>
-      <c r="L48">
-        <v>200</v>
-      </c>
-      <c r="M48">
-        <v>99</v>
-      </c>
-      <c r="N48" t="b">
-        <v>1</v>
-      </c>
-      <c r="O48" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="P48" s="9" t="s">
+      <c r="P47" s="9" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.45">
       <c r="O49" s="6"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>47</v>
       </c>
@@ -3777,7 +3725,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>48</v>
       </c>
@@ -3828,7 +3776,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>49</v>
       </c>
@@ -3879,7 +3827,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>50</v>
       </c>
@@ -3930,7 +3878,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>51</v>
       </c>
@@ -3978,7 +3926,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>52</v>
       </c>
@@ -4026,7 +3974,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>53</v>
       </c>
@@ -4074,7 +4022,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>54</v>
       </c>
@@ -4125,7 +4073,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>55</v>
       </c>
@@ -4176,7 +4124,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>56</v>
       </c>
@@ -4227,10 +4175,10 @@
         <v>167</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.45">
       <c r="O60" s="6"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>57</v>
       </c>
@@ -4272,7 +4220,7 @@
       </c>
       <c r="O61" s="6"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>58</v>
       </c>
@@ -4314,7 +4262,7 @@
       </c>
       <c r="O62" s="6"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>59</v>
       </c>
@@ -4356,7 +4304,7 @@
       </c>
       <c r="O63" s="6"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>60</v>
       </c>
@@ -4398,7 +4346,7 @@
       </c>
       <c r="O64" s="6"/>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>61</v>
       </c>
@@ -4440,7 +4388,7 @@
       </c>
       <c r="O65" s="6"/>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>62</v>
       </c>
@@ -4482,7 +4430,7 @@
       </c>
       <c r="O66" s="6"/>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>63</v>
       </c>
@@ -4524,7 +4472,7 @@
       </c>
       <c r="O67" s="6"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>64</v>
       </c>
@@ -4566,7 +4514,7 @@
       </c>
       <c r="O68" s="6"/>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>65</v>
       </c>
@@ -4608,7 +4556,7 @@
       </c>
       <c r="O69" s="6"/>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>66</v>
       </c>
@@ -4650,7 +4598,7 @@
       </c>
       <c r="O70" s="6"/>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>67</v>
       </c>
@@ -4692,7 +4640,7 @@
       </c>
       <c r="O71" s="6"/>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>68</v>
       </c>
@@ -4734,7 +4682,7 @@
       </c>
       <c r="O72" s="6"/>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>69</v>
       </c>
@@ -4776,7 +4724,7 @@
       </c>
       <c r="O73" s="6"/>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>70</v>
       </c>
@@ -4818,7 +4766,7 @@
       </c>
       <c r="O74" s="6"/>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>71</v>
       </c>
@@ -4860,7 +4808,7 @@
       </c>
       <c r="O75" s="6"/>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>72</v>
       </c>
@@ -4902,7 +4850,7 @@
       </c>
       <c r="O76" s="6"/>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>73</v>
       </c>
@@ -4944,7 +4892,7 @@
       </c>
       <c r="O77" s="6"/>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>74</v>
       </c>
@@ -4986,7 +4934,7 @@
       </c>
       <c r="O78" s="6"/>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>75</v>
       </c>
@@ -5028,7 +4976,7 @@
       </c>
       <c r="O79" s="6"/>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>76</v>
       </c>
@@ -5070,7 +5018,7 @@
       </c>
       <c r="O80" s="6"/>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>77</v>
       </c>
@@ -5112,7 +5060,7 @@
       </c>
       <c r="O81" s="6"/>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>78</v>
       </c>
@@ -5154,7 +5102,7 @@
       </c>
       <c r="O82" s="6"/>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>79</v>
       </c>
@@ -5196,7 +5144,7 @@
       </c>
       <c r="O83" s="6"/>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>80</v>
       </c>
@@ -5238,7 +5186,7 @@
       </c>
       <c r="O84" s="6"/>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>81</v>
       </c>
@@ -5280,7 +5228,7 @@
       </c>
       <c r="O85" s="6"/>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>82</v>
       </c>
@@ -5322,7 +5270,7 @@
       </c>
       <c r="O86" s="6"/>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>83</v>
       </c>
@@ -5364,7 +5312,7 @@
       </c>
       <c r="O87" s="6"/>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>84</v>
       </c>
@@ -5406,7 +5354,7 @@
       </c>
       <c r="O88" s="6"/>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>85</v>
       </c>
@@ -5448,7 +5396,7 @@
       </c>
       <c r="O89" s="6"/>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>86</v>
       </c>
@@ -5490,7 +5438,7 @@
       </c>
       <c r="O90" s="6"/>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>87</v>
       </c>
@@ -5532,7 +5480,7 @@
       </c>
       <c r="O91" s="6"/>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>88</v>
       </c>
@@ -5574,7 +5522,7 @@
       </c>
       <c r="O92" s="6"/>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>89</v>
       </c>
@@ -5616,7 +5564,7 @@
       </c>
       <c r="O93" s="6"/>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>90</v>
       </c>
@@ -5658,7 +5606,7 @@
       </c>
       <c r="O94" s="6"/>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>91</v>
       </c>
@@ -5700,7 +5648,7 @@
       </c>
       <c r="O95" s="6"/>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>92</v>
       </c>
@@ -5742,7 +5690,7 @@
       </c>
       <c r="O96" s="6"/>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>93</v>
       </c>
@@ -5784,7 +5732,7 @@
       </c>
       <c r="O97" s="6"/>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>94</v>
       </c>
@@ -5826,7 +5774,7 @@
       </c>
       <c r="O98" s="6"/>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>95</v>
       </c>
@@ -5868,7 +5816,7 @@
       </c>
       <c r="O99" s="6"/>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>96</v>
       </c>
@@ -5910,7 +5858,7 @@
       </c>
       <c r="O100" s="6"/>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>97</v>
       </c>
@@ -5952,7 +5900,7 @@
       </c>
       <c r="O101" s="6"/>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A102">
         <v>98</v>
       </c>
@@ -5994,7 +5942,7 @@
       </c>
       <c r="O102" s="6"/>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A103">
         <v>99</v>
       </c>
@@ -6036,7 +5984,7 @@
       </c>
       <c r="O103" s="6"/>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A104">
         <v>100</v>
       </c>
@@ -6078,7 +6026,7 @@
       </c>
       <c r="O104" s="6"/>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A105">
         <v>101</v>
       </c>
@@ -6120,7 +6068,7 @@
       </c>
       <c r="O105" s="6"/>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A106">
         <v>102</v>
       </c>
@@ -6162,7 +6110,7 @@
       </c>
       <c r="O106" s="6"/>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A107">
         <v>103</v>
       </c>
@@ -6204,7 +6152,7 @@
       </c>
       <c r="O107" s="6"/>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A108">
         <v>104</v>
       </c>
@@ -6246,7 +6194,7 @@
       </c>
       <c r="O108" s="6"/>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A109">
         <v>105</v>
       </c>
@@ -6288,7 +6236,7 @@
       </c>
       <c r="O109" s="6"/>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A110">
         <v>106</v>
       </c>
@@ -6330,7 +6278,7 @@
       </c>
       <c r="O110" s="6"/>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A111">
         <v>107</v>
       </c>
@@ -6372,7 +6320,7 @@
       </c>
       <c r="O111" s="6"/>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A112">
         <v>108</v>
       </c>
@@ -6414,7 +6362,7 @@
       </c>
       <c r="O112" s="6"/>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A113">
         <v>109</v>
       </c>
@@ -6456,7 +6404,7 @@
       </c>
       <c r="O113" s="6"/>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A114">
         <v>110</v>
       </c>
@@ -6498,7 +6446,7 @@
       </c>
       <c r="O114" s="6"/>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A115">
         <v>111</v>
       </c>
@@ -6540,958 +6488,958 @@
       </c>
       <c r="O115" s="6"/>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O116" s="6"/>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O117" s="6"/>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O118" s="6"/>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O119" s="6"/>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O120" s="6"/>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O121" s="6"/>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O122" s="6"/>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O123" s="6"/>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O124" s="6"/>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O125" s="6"/>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O126" s="6"/>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O127" s="6"/>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O128" s="6"/>
     </row>
-    <row r="129" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="129" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O129" s="6"/>
     </row>
-    <row r="130" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="130" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O130" s="6"/>
     </row>
-    <row r="131" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="131" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O131" s="6"/>
     </row>
-    <row r="132" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="132" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O132" s="6"/>
     </row>
-    <row r="133" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="133" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O133" s="6"/>
     </row>
-    <row r="134" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="134" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O134" s="6"/>
     </row>
-    <row r="135" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="135" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O135" s="6"/>
     </row>
-    <row r="136" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="136" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O136" s="6"/>
     </row>
-    <row r="137" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="137" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O137" s="6"/>
     </row>
-    <row r="138" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="138" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O138" s="6"/>
     </row>
-    <row r="139" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="139" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O139" s="6"/>
     </row>
-    <row r="140" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="140" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O140" s="6"/>
     </row>
-    <row r="141" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="141" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O141" s="6"/>
     </row>
-    <row r="142" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="142" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O142" s="6"/>
     </row>
-    <row r="143" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="143" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O143" s="6"/>
     </row>
-    <row r="144" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="144" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O144" s="6"/>
     </row>
-    <row r="145" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="145" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O145" s="6"/>
     </row>
-    <row r="146" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="146" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O146" s="6"/>
     </row>
-    <row r="147" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="147" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O147" s="6"/>
     </row>
-    <row r="148" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="148" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O148" s="6"/>
     </row>
-    <row r="149" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="149" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O149" s="6"/>
     </row>
-    <row r="150" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="150" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O150" s="6"/>
     </row>
-    <row r="151" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="151" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O151" s="6"/>
     </row>
-    <row r="152" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="152" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O152" s="6"/>
     </row>
-    <row r="153" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="153" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O153" s="6"/>
     </row>
-    <row r="154" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="154" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O154" s="6"/>
     </row>
-    <row r="155" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="155" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O155" s="6"/>
     </row>
-    <row r="156" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="156" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O156" s="6"/>
     </row>
-    <row r="157" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="157" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O157" s="6"/>
     </row>
-    <row r="158" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="158" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O158" s="6"/>
     </row>
-    <row r="159" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="159" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O159" s="6"/>
     </row>
-    <row r="160" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="160" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O160" s="6"/>
     </row>
-    <row r="161" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="161" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O161" s="6"/>
     </row>
-    <row r="162" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="162" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O162" s="6"/>
     </row>
-    <row r="163" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="163" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O163" s="6"/>
     </row>
-    <row r="164" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="164" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O164" s="6"/>
     </row>
-    <row r="165" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="165" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O165" s="6"/>
     </row>
-    <row r="166" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="166" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O166" s="6"/>
     </row>
-    <row r="167" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="167" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O167" s="6"/>
     </row>
-    <row r="168" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="168" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O168" s="6"/>
     </row>
-    <row r="169" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="169" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O169" s="6"/>
     </row>
-    <row r="170" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="170" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O170" s="6"/>
     </row>
-    <row r="171" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="171" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O171" s="6"/>
     </row>
-    <row r="172" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="172" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O172" s="6"/>
     </row>
-    <row r="173" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="173" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O173" s="6"/>
     </row>
-    <row r="174" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="174" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O174" s="6"/>
     </row>
-    <row r="175" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="175" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O175" s="6"/>
     </row>
-    <row r="176" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="176" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O176" s="6"/>
     </row>
-    <row r="177" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="177" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O177" s="6"/>
     </row>
-    <row r="178" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="178" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O178" s="6"/>
     </row>
-    <row r="179" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="179" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O179" s="6"/>
     </row>
-    <row r="180" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="180" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O180" s="6"/>
     </row>
-    <row r="181" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="181" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O181" s="6"/>
     </row>
-    <row r="182" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="182" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O182" s="6"/>
     </row>
-    <row r="183" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="183" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O183" s="6"/>
     </row>
-    <row r="184" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="184" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O184" s="6"/>
     </row>
-    <row r="185" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="185" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O185" s="6"/>
     </row>
-    <row r="186" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="186" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O186" s="6"/>
     </row>
-    <row r="187" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="187" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O187" s="6"/>
     </row>
-    <row r="188" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="188" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O188" s="6"/>
     </row>
-    <row r="189" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="189" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O189" s="6"/>
     </row>
-    <row r="190" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="190" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O190" s="6"/>
     </row>
-    <row r="191" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="191" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O191" s="6"/>
     </row>
-    <row r="192" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="192" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O192" s="6"/>
     </row>
-    <row r="193" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="193" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O193" s="6"/>
     </row>
-    <row r="194" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="194" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O194" s="6"/>
     </row>
-    <row r="195" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="195" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O195" s="6"/>
     </row>
-    <row r="196" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="196" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O196" s="6"/>
     </row>
-    <row r="197" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="197" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O197" s="6"/>
     </row>
-    <row r="198" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="198" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O198" s="6"/>
     </row>
-    <row r="199" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="199" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O199" s="6"/>
     </row>
-    <row r="200" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="200" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O200" s="6"/>
     </row>
-    <row r="201" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="201" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O201" s="6"/>
     </row>
-    <row r="202" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="202" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O202" s="6"/>
     </row>
-    <row r="203" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="203" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O203" s="6"/>
     </row>
-    <row r="204" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="204" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O204" s="6"/>
     </row>
-    <row r="205" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="205" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O205" s="6"/>
     </row>
-    <row r="206" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="206" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O206" s="6"/>
     </row>
-    <row r="207" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="207" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O207" s="6"/>
     </row>
-    <row r="208" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="208" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O208" s="6"/>
     </row>
-    <row r="209" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="209" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O209" s="6"/>
     </row>
-    <row r="210" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="210" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O210" s="6"/>
     </row>
-    <row r="211" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="211" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O211" s="6"/>
     </row>
-    <row r="212" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="212" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O212" s="6"/>
     </row>
-    <row r="213" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="213" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O213" s="6"/>
     </row>
-    <row r="214" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="214" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O214" s="6"/>
     </row>
-    <row r="215" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="215" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O215" s="6"/>
     </row>
-    <row r="216" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="216" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O216" s="6"/>
     </row>
-    <row r="217" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="217" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O217" s="6"/>
     </row>
-    <row r="218" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="218" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O218" s="6"/>
     </row>
-    <row r="219" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="219" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O219" s="6"/>
     </row>
-    <row r="220" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="220" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O220" s="6"/>
     </row>
-    <row r="221" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="221" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O221" s="6"/>
     </row>
-    <row r="222" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="222" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O222" s="6"/>
     </row>
-    <row r="223" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="223" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O223" s="6"/>
     </row>
-    <row r="224" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="224" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O224" s="6"/>
     </row>
-    <row r="225" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="225" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O225" s="6"/>
     </row>
-    <row r="226" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="226" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O226" s="6"/>
     </row>
-    <row r="227" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="227" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O227" s="6"/>
     </row>
-    <row r="228" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="228" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O228" s="6"/>
     </row>
-    <row r="229" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="229" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O229" s="6"/>
     </row>
-    <row r="230" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="230" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O230" s="6"/>
     </row>
-    <row r="231" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="231" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O231" s="6"/>
     </row>
-    <row r="232" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="232" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O232" s="6"/>
     </row>
-    <row r="233" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="233" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O233" s="6"/>
     </row>
-    <row r="234" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="234" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O234" s="6"/>
     </row>
-    <row r="235" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="235" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O235" s="6"/>
     </row>
-    <row r="236" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="236" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O236" s="6"/>
     </row>
-    <row r="237" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="237" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O237" s="6"/>
     </row>
-    <row r="238" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="238" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O238" s="6"/>
     </row>
-    <row r="239" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="239" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O239" s="6"/>
     </row>
-    <row r="240" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="240" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O240" s="6"/>
     </row>
-    <row r="241" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="241" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O241" s="6"/>
     </row>
-    <row r="242" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="242" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O242" s="6"/>
     </row>
-    <row r="243" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="243" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O243" s="6"/>
     </row>
-    <row r="244" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="244" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O244" s="6"/>
     </row>
-    <row r="245" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="245" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O245" s="6"/>
     </row>
-    <row r="246" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="246" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O246" s="6"/>
     </row>
-    <row r="247" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="247" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O247" s="6"/>
     </row>
-    <row r="248" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="248" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O248" s="6"/>
     </row>
-    <row r="249" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="249" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O249" s="6"/>
     </row>
-    <row r="250" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="250" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O250" s="6"/>
     </row>
-    <row r="251" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="251" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O251" s="6"/>
     </row>
-    <row r="252" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="252" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O252" s="6"/>
     </row>
-    <row r="253" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="253" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O253" s="6"/>
     </row>
-    <row r="254" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="254" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O254" s="6"/>
     </row>
-    <row r="255" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="255" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O255" s="6"/>
     </row>
-    <row r="256" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="256" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O256" s="6"/>
     </row>
-    <row r="257" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="257" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O257" s="6"/>
     </row>
-    <row r="258" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="258" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O258" s="6"/>
     </row>
-    <row r="259" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="259" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O259" s="6"/>
     </row>
-    <row r="260" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="260" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O260" s="6"/>
     </row>
-    <row r="261" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="261" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O261" s="6"/>
     </row>
-    <row r="262" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="262" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O262" s="6"/>
     </row>
-    <row r="263" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="263" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O263" s="6"/>
     </row>
-    <row r="264" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="264" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O264" s="6"/>
     </row>
-    <row r="265" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="265" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O265" s="6"/>
     </row>
-    <row r="266" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="266" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O266" s="6"/>
     </row>
-    <row r="267" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="267" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O267" s="6"/>
     </row>
-    <row r="268" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="268" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O268" s="6"/>
     </row>
-    <row r="269" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="269" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O269" s="6"/>
     </row>
-    <row r="270" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="270" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O270" s="6"/>
     </row>
-    <row r="271" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="271" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O271" s="6"/>
     </row>
-    <row r="272" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="272" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O272" s="6"/>
     </row>
-    <row r="273" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="273" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O273" s="6"/>
     </row>
-    <row r="274" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="274" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O274" s="6"/>
     </row>
-    <row r="275" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="275" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O275" s="6"/>
     </row>
-    <row r="276" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="276" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O276" s="6"/>
     </row>
-    <row r="277" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="277" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O277" s="6"/>
     </row>
-    <row r="278" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="278" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O278" s="6"/>
     </row>
-    <row r="279" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="279" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O279" s="6"/>
     </row>
-    <row r="280" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="280" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O280" s="6"/>
     </row>
-    <row r="281" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="281" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O281" s="6"/>
     </row>
-    <row r="282" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="282" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O282" s="6"/>
     </row>
-    <row r="283" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="283" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O283" s="6"/>
     </row>
-    <row r="284" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="284" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O284" s="6"/>
     </row>
-    <row r="285" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="285" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O285" s="6"/>
     </row>
-    <row r="286" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="286" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O286" s="6"/>
     </row>
-    <row r="287" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="287" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O287" s="6"/>
     </row>
-    <row r="288" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="288" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O288" s="6"/>
     </row>
-    <row r="289" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="289" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O289" s="6"/>
     </row>
-    <row r="290" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="290" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O290" s="6"/>
     </row>
-    <row r="291" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="291" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O291" s="6"/>
     </row>
-    <row r="292" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="292" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O292" s="6"/>
     </row>
-    <row r="293" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="293" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O293" s="6"/>
     </row>
-    <row r="294" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="294" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O294" s="6"/>
     </row>
-    <row r="295" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="295" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O295" s="6"/>
     </row>
-    <row r="296" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="296" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O296" s="6"/>
     </row>
-    <row r="297" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="297" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O297" s="6"/>
     </row>
-    <row r="298" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="298" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O298" s="6"/>
     </row>
-    <row r="299" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="299" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O299" s="6"/>
     </row>
-    <row r="300" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="300" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O300" s="6"/>
     </row>
-    <row r="301" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="301" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O301" s="6"/>
     </row>
-    <row r="302" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="302" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O302" s="6"/>
     </row>
-    <row r="303" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="303" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O303" s="6"/>
     </row>
-    <row r="304" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="304" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O304" s="6"/>
     </row>
-    <row r="305" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="305" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O305" s="6"/>
     </row>
-    <row r="306" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="306" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O306" s="6"/>
     </row>
-    <row r="307" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="307" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O307" s="6"/>
     </row>
-    <row r="308" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="308" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O308" s="6"/>
     </row>
-    <row r="309" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="309" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O309" s="6"/>
     </row>
-    <row r="310" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="310" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O310" s="6"/>
     </row>
-    <row r="311" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="311" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O311" s="6"/>
     </row>
-    <row r="312" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="312" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O312" s="6"/>
     </row>
-    <row r="313" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="313" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O313" s="6"/>
     </row>
-    <row r="314" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="314" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O314" s="6"/>
     </row>
-    <row r="315" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="315" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O315" s="6"/>
     </row>
-    <row r="316" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="316" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O316" s="6"/>
     </row>
-    <row r="317" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="317" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O317" s="6"/>
     </row>
-    <row r="318" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="318" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O318" s="6"/>
     </row>
-    <row r="319" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="319" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O319" s="6"/>
     </row>
-    <row r="320" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="320" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O320" s="6"/>
     </row>
-    <row r="321" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="321" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O321" s="6"/>
     </row>
-    <row r="322" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="322" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O322" s="6"/>
     </row>
-    <row r="323" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="323" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O323" s="6"/>
     </row>
-    <row r="324" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="324" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O324" s="6"/>
     </row>
-    <row r="325" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="325" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O325" s="6"/>
     </row>
-    <row r="326" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="326" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O326" s="6"/>
     </row>
-    <row r="327" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="327" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O327" s="6"/>
     </row>
-    <row r="328" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="328" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O328" s="6"/>
     </row>
-    <row r="329" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="329" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O329" s="6"/>
     </row>
-    <row r="330" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="330" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O330" s="6"/>
     </row>
-    <row r="331" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="331" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O331" s="6"/>
     </row>
-    <row r="332" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="332" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O332" s="6"/>
     </row>
-    <row r="333" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="333" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O333" s="6"/>
     </row>
-    <row r="334" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="334" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O334" s="6"/>
     </row>
-    <row r="335" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="335" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O335" s="6"/>
     </row>
-    <row r="336" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="336" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O336" s="6"/>
     </row>
-    <row r="337" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="337" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O337" s="6"/>
     </row>
-    <row r="338" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="338" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O338" s="6"/>
     </row>
-    <row r="339" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="339" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O339" s="6"/>
     </row>
-    <row r="340" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="340" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O340" s="6"/>
     </row>
-    <row r="341" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="341" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O341" s="6"/>
     </row>
-    <row r="342" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="342" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O342" s="6"/>
     </row>
-    <row r="343" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="343" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O343" s="6"/>
     </row>
-    <row r="344" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="344" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O344" s="6"/>
     </row>
-    <row r="345" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="345" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O345" s="6"/>
     </row>
-    <row r="346" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="346" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O346" s="6"/>
     </row>
-    <row r="347" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="347" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O347" s="6"/>
     </row>
-    <row r="348" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="348" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O348" s="6"/>
     </row>
-    <row r="349" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="349" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O349" s="6"/>
     </row>
-    <row r="350" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="350" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O350" s="6"/>
     </row>
-    <row r="351" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="351" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O351" s="6"/>
     </row>
-    <row r="352" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="352" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O352" s="6"/>
     </row>
-    <row r="353" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="353" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O353" s="6"/>
     </row>
-    <row r="354" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="354" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O354" s="6"/>
     </row>
-    <row r="355" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="355" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O355" s="6"/>
     </row>
-    <row r="356" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="356" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O356" s="6"/>
     </row>
-    <row r="357" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="357" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O357" s="6"/>
     </row>
-    <row r="358" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="358" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O358" s="6"/>
     </row>
-    <row r="359" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="359" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O359" s="6"/>
     </row>
-    <row r="360" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="360" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O360" s="6"/>
     </row>
-    <row r="361" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="361" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O361" s="6"/>
     </row>
-    <row r="362" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="362" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O362" s="6"/>
     </row>
-    <row r="363" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="363" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O363" s="6"/>
     </row>
-    <row r="364" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="364" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O364" s="6"/>
     </row>
-    <row r="365" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="365" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O365" s="6"/>
     </row>
-    <row r="366" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="366" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O366" s="6"/>
     </row>
-    <row r="367" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="367" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O367" s="6"/>
     </row>
-    <row r="368" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="368" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O368" s="6"/>
     </row>
-    <row r="369" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="369" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O369" s="6"/>
     </row>
-    <row r="370" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="370" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O370" s="6"/>
     </row>
-    <row r="371" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="371" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O371" s="6"/>
     </row>
-    <row r="372" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="372" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O372" s="6"/>
     </row>
-    <row r="373" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="373" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O373" s="6"/>
     </row>
-    <row r="374" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="374" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O374" s="6"/>
     </row>
-    <row r="375" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="375" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O375" s="6"/>
     </row>
-    <row r="376" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="376" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O376" s="6"/>
     </row>
-    <row r="377" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="377" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O377" s="6"/>
     </row>
-    <row r="378" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="378" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O378" s="6"/>
     </row>
-    <row r="379" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="379" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O379" s="6"/>
     </row>
-    <row r="380" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="380" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O380" s="6"/>
     </row>
-    <row r="381" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="381" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O381" s="6"/>
     </row>
-    <row r="382" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="382" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O382" s="6"/>
     </row>
-    <row r="383" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="383" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O383" s="6"/>
     </row>
-    <row r="384" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="384" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O384" s="6"/>
     </row>
-    <row r="385" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="385" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O385" s="6"/>
     </row>
-    <row r="386" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="386" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O386" s="6"/>
     </row>
-    <row r="387" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="387" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O387" s="6"/>
     </row>
-    <row r="388" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="388" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O388" s="6"/>
     </row>
-    <row r="389" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="389" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O389" s="6"/>
     </row>
-    <row r="390" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="390" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O390" s="6"/>
     </row>
-    <row r="391" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="391" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O391" s="6"/>
     </row>
-    <row r="392" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="392" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O392" s="6"/>
     </row>
-    <row r="393" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="393" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O393" s="6"/>
     </row>
-    <row r="394" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="394" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O394" s="6"/>
     </row>
-    <row r="395" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="395" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O395" s="6"/>
     </row>
-    <row r="396" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="396" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O396" s="6"/>
     </row>
-    <row r="397" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="397" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O397" s="6"/>
     </row>
-    <row r="398" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="398" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O398" s="6"/>
     </row>
-    <row r="399" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="399" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O399" s="6"/>
     </row>
-    <row r="400" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="400" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O400" s="6"/>
     </row>
-    <row r="401" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="401" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O401" s="6"/>
     </row>
-    <row r="402" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="402" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O402" s="6"/>
     </row>
-    <row r="403" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="403" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O403" s="6"/>
     </row>
-    <row r="404" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="404" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O404" s="6"/>
     </row>
-    <row r="405" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="405" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O405" s="6"/>
     </row>
-    <row r="406" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="406" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O406" s="6"/>
     </row>
-    <row r="407" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="407" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O407" s="6"/>
     </row>
-    <row r="408" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="408" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O408" s="6"/>
     </row>
-    <row r="409" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="409" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O409" s="6"/>
     </row>
-    <row r="410" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="410" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O410" s="6"/>
     </row>
-    <row r="411" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="411" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O411" s="6"/>
     </row>
-    <row r="412" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="412" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O412" s="6"/>
     </row>
-    <row r="413" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="413" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O413" s="6"/>
     </row>
-    <row r="414" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="414" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O414" s="6"/>
     </row>
-    <row r="415" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="415" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O415" s="6"/>
     </row>
-    <row r="416" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="416" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O416" s="6"/>
     </row>
-    <row r="417" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="417" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O417" s="6"/>
     </row>
-    <row r="418" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="418" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O418" s="6"/>
     </row>
-    <row r="419" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="419" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O419" s="6"/>
     </row>
-    <row r="420" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="420" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O420" s="6"/>
     </row>
-    <row r="421" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="421" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O421" s="6"/>
     </row>
-    <row r="422" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="422" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O422" s="6"/>
     </row>
-    <row r="423" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="423" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O423" s="6"/>
     </row>
-    <row r="424" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="424" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O424" s="6"/>
     </row>
-    <row r="425" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="425" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O425" s="6"/>
     </row>
-    <row r="426" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="426" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O426" s="6"/>
     </row>
-    <row r="427" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="427" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O427" s="6"/>
     </row>
-    <row r="428" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="428" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O428" s="6"/>
     </row>
-    <row r="429" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="429" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O429" s="6"/>
     </row>
-    <row r="430" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="430" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O430" s="6"/>
     </row>
-    <row r="431" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="431" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O431" s="6"/>
     </row>
-    <row r="432" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="432" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O432" s="6"/>
     </row>
-    <row r="433" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="433" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O433" s="6"/>
     </row>
   </sheetData>

--- a/아이템 도감.xlsx
+++ b/아이템 도감.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hcw97\Desktop\CapstoneProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F2B7715-A92D-4DF9-9E9F-A9F820930778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED115D2-E3F5-42CA-8B07-5616D2B74197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{AEFF7BDA-CB51-4C25-A75C-46A97EA8EBD6}"/>
   </bookViews>

--- a/아이템 도감.xlsx
+++ b/아이템 도감.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hcw97\Desktop\CapstoneProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED115D2-E3F5-42CA-8B07-5616D2B74197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA5DDECC-3A28-4104-A1C9-59BB85B3D6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{AEFF7BDA-CB51-4C25-A75C-46A97EA8EBD6}"/>
   </bookViews>
@@ -122,9 +122,6 @@
     <t>뿅망치</t>
   </si>
   <si>
-    <t>줄넘기</t>
-  </si>
-  <si>
     <t>마법 지팡이</t>
   </si>
   <si>
@@ -660,10 +657,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>줄에 걸리면 꽤나 아프다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>duration</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -781,6 +774,14 @@
   </si>
   <si>
     <t>귀여운 멜론 모양의 맛있는 빵.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>유령 퇴치 스프레이</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>유령을 퇴치하는 스프레이</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -990,7 +991,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1026,6 +1027,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1392,7 +1399,7 @@
         <v>6</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>7</v>
@@ -1407,7 +1414,7 @@
         <v>10</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="P1" s="11" t="s">
         <v>11</v>
@@ -1457,10 +1464,10 @@
         <v>1</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="P2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.45">
@@ -1508,7 +1515,7 @@
       </c>
       <c r="O3" s="6"/>
       <c r="P3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.45">
@@ -1556,7 +1563,7 @@
       </c>
       <c r="O4" s="6"/>
       <c r="P4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.45">
@@ -1604,7 +1611,7 @@
       </c>
       <c r="O5" s="6"/>
       <c r="P5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.45">
@@ -1651,10 +1658,10 @@
         <v>1</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="P6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.45">
@@ -1702,7 +1709,7 @@
       </c>
       <c r="O7" s="6"/>
       <c r="P7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.45">
@@ -1750,7 +1757,7 @@
       </c>
       <c r="O8" s="6"/>
       <c r="P8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.45">
@@ -1798,7 +1805,7 @@
       </c>
       <c r="O9" s="6"/>
       <c r="P9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.45">
@@ -1845,10 +1852,10 @@
         <v>1</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="P10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.45">
@@ -1896,7 +1903,7 @@
       </c>
       <c r="O11" s="6"/>
       <c r="P11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.45">
@@ -1944,7 +1951,7 @@
       </c>
       <c r="O12" s="6"/>
       <c r="P12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.45">
@@ -1992,7 +1999,7 @@
       </c>
       <c r="O13" s="6"/>
       <c r="P13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.45">
@@ -2040,7 +2047,7 @@
       </c>
       <c r="O14" s="6"/>
       <c r="P14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.45">
@@ -2054,7 +2061,7 @@
         <v>150</v>
       </c>
       <c r="D15" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -2087,10 +2094,10 @@
         <v>1</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="P15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.45">
@@ -2137,24 +2144,24 @@
         <v>1</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="P16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A17">
+      <c r="A17" s="13">
         <v>16</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="13">
         <v>0</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="13">
         <v>150</v>
       </c>
-      <c r="D17" t="s">
-        <v>28</v>
+      <c r="D17" s="12" t="s">
+        <v>224</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -2178,7 +2185,7 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="M17">
         <v>1</v>
@@ -2188,7 +2195,7 @@
       </c>
       <c r="O17" s="6"/>
       <c r="P17" t="s">
-        <v>187</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.45">
@@ -2202,7 +2209,7 @@
         <v>150</v>
       </c>
       <c r="D18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -2235,10 +2242,10 @@
         <v>1</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="P18" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.45">
@@ -2252,7 +2259,7 @@
         <v>150</v>
       </c>
       <c r="D19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E19">
         <v>2</v>
@@ -2286,7 +2293,7 @@
       </c>
       <c r="O19" s="6"/>
       <c r="P19" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.45">
@@ -2300,7 +2307,7 @@
         <v>150</v>
       </c>
       <c r="D20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E20">
         <v>2</v>
@@ -2333,129 +2340,15 @@
         <v>1</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="P20" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-      <c r="O21" s="6"/>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A22">
-        <v>20</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22">
-        <v>201</v>
-      </c>
-      <c r="D22" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="F22">
-        <v>-1</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>30</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>-1</v>
-      </c>
-      <c r="K22">
-        <v>-1</v>
-      </c>
-      <c r="L22">
-        <v>300</v>
-      </c>
-      <c r="M22">
-        <v>99</v>
-      </c>
-      <c r="N22" t="b">
-        <v>1</v>
-      </c>
-      <c r="O22" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="P22" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A23">
-        <v>21</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23">
-        <v>201</v>
-      </c>
-      <c r="D23" t="s">
-        <v>33</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="F23">
-        <v>-1</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>50</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>-1</v>
-      </c>
-      <c r="K23">
-        <v>-1</v>
-      </c>
-      <c r="L23">
-        <v>200</v>
-      </c>
-      <c r="M23">
-        <v>99</v>
-      </c>
-      <c r="N23" t="b">
-        <v>1</v>
-      </c>
-      <c r="O23" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="P23" t="s">
-        <v>127</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A24">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -2464,7 +2357,7 @@
         <v>201</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -2476,7 +2369,7 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -2488,7 +2381,7 @@
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="M24">
         <v>99</v>
@@ -2497,15 +2390,15 @@
         <v>1</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="P24" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A25">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -2514,7 +2407,7 @@
         <v>201</v>
       </c>
       <c r="D25" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -2526,7 +2419,7 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -2538,7 +2431,7 @@
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="M25">
         <v>99</v>
@@ -2550,12 +2443,12 @@
         <v>205</v>
       </c>
       <c r="P25" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A26">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -2564,7 +2457,7 @@
         <v>201</v>
       </c>
       <c r="D26" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -2576,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -2588,7 +2481,7 @@
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="M26">
         <v>99</v>
@@ -2597,27 +2490,24 @@
         <v>1</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P26" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A27">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D27" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -2626,10 +2516,10 @@
         <v>-1</v>
       </c>
       <c r="G27">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H27">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -2641,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="M27">
         <v>99</v>
@@ -2650,27 +2540,24 @@
         <v>1</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="P27" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A28">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D28" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -2679,10 +2566,10 @@
         <v>-1</v>
       </c>
       <c r="G28">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -2694,7 +2581,7 @@
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="M28">
         <v>99</v>
@@ -2703,24 +2590,27 @@
         <v>1</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="P28" t="s">
-        <v>132</v>
+        <v>129</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A29">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D29" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -2729,10 +2619,10 @@
         <v>-1</v>
       </c>
       <c r="G29">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -2744,7 +2634,7 @@
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M29">
         <v>99</v>
@@ -2753,24 +2643,27 @@
         <v>1</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P29" t="s">
-        <v>133</v>
+        <v>130</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A30">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D30" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -2779,10 +2672,10 @@
         <v>-1</v>
       </c>
       <c r="G30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H30">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -2794,7 +2687,7 @@
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M30">
         <v>99</v>
@@ -2803,24 +2696,24 @@
         <v>1</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="P30" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A31">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
       <c r="C31">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D31" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -2832,7 +2725,7 @@
         <v>10</v>
       </c>
       <c r="H31">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -2844,7 +2737,7 @@
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M31">
         <v>99</v>
@@ -2853,24 +2746,24 @@
         <v>1</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="P31" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A32">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
       <c r="C32">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D32" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -2879,10 +2772,10 @@
         <v>-1</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H32">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -2903,15 +2796,15 @@
         <v>1</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="P32" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A33">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -2920,7 +2813,7 @@
         <v>202</v>
       </c>
       <c r="D33" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -2929,7 +2822,7 @@
         <v>-1</v>
       </c>
       <c r="G33">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H33">
         <v>10</v>
@@ -2944,7 +2837,7 @@
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>220</v>
+        <v>100</v>
       </c>
       <c r="M33">
         <v>99</v>
@@ -2953,24 +2846,24 @@
         <v>1</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="P33" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A34">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B34">
         <v>1</v>
       </c>
       <c r="C34">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D34" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -2979,16 +2872,16 @@
         <v>-1</v>
       </c>
       <c r="G34">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H34">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="I34">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J34">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="K34">
         <v>-1</v>
@@ -3003,27 +2896,24 @@
         <v>1</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="P34" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A35">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B35">
         <v>1</v>
       </c>
       <c r="C35">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D35" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -3032,22 +2922,22 @@
         <v>-1</v>
       </c>
       <c r="G35">
+        <v>20</v>
+      </c>
+      <c r="H35">
         <v>10</v>
       </c>
-      <c r="H35">
-        <v>25</v>
-      </c>
       <c r="I35">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J35">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="K35">
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="M35">
         <v>99</v>
@@ -3056,27 +2946,24 @@
         <v>1</v>
       </c>
       <c r="O35" s="6" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="P35" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A36">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B36">
         <v>1</v>
       </c>
       <c r="C36">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D36" t="s">
-        <v>224</v>
+        <v>43</v>
       </c>
       <c r="E36">
         <v>1</v>
@@ -3085,22 +2972,22 @@
         <v>-1</v>
       </c>
       <c r="G36">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H36">
+        <v>15</v>
+      </c>
+      <c r="I36">
+        <v>30</v>
+      </c>
+      <c r="J36">
         <v>10</v>
       </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>-1</v>
-      </c>
       <c r="K36">
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M36">
         <v>99</v>
@@ -3109,24 +2996,27 @@
         <v>1</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="P36" t="s">
-        <v>225</v>
+        <v>136</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A37">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
       <c r="C37">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D37" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E37">
         <v>1</v>
@@ -3135,16 +3025,16 @@
         <v>-1</v>
       </c>
       <c r="G37">
+        <v>10</v>
+      </c>
+      <c r="H37">
         <v>25</v>
       </c>
-      <c r="H37">
+      <c r="I37">
         <v>10</v>
       </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
       <c r="J37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K37">
         <v>-1</v>
@@ -3159,24 +3049,27 @@
         <v>1</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="P37" t="s">
-        <v>138</v>
+        <v>147</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A38">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
       <c r="C38">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D38" t="s">
-        <v>47</v>
+        <v>222</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -3185,16 +3078,16 @@
         <v>-1</v>
       </c>
       <c r="G38">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="H38">
         <v>10</v>
       </c>
       <c r="I38">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J38">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="K38">
         <v>-1</v>
@@ -3209,18 +3102,15 @@
         <v>1</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="P38" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>156</v>
+        <v>223</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A39">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -3229,7 +3119,7 @@
         <v>202</v>
       </c>
       <c r="D39" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -3238,7 +3128,7 @@
         <v>-1</v>
       </c>
       <c r="G39">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H39">
         <v>10</v>
@@ -3262,24 +3152,24 @@
         <v>1</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="P39" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A40">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
       <c r="C40">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D40" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -3288,16 +3178,16 @@
         <v>-1</v>
       </c>
       <c r="G40">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H40">
+        <v>10</v>
+      </c>
+      <c r="I40">
         <v>5</v>
       </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
       <c r="J40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K40">
         <v>-1</v>
@@ -3312,15 +3202,18 @@
         <v>1</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="P40" t="s">
-        <v>141</v>
+        <v>138</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A41">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -3329,7 +3222,7 @@
         <v>202</v>
       </c>
       <c r="D41" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -3338,10 +3231,10 @@
         <v>-1</v>
       </c>
       <c r="G41">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H41">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -3362,15 +3255,15 @@
         <v>1</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P41" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A42">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -3379,7 +3272,7 @@
         <v>202</v>
       </c>
       <c r="D42" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E42">
         <v>1</v>
@@ -3388,10 +3281,10 @@
         <v>-1</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H42">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -3412,24 +3305,24 @@
         <v>1</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="P42" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A43">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
       <c r="C43">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D43" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E43">
         <v>1</v>
@@ -3438,13 +3331,13 @@
         <v>-1</v>
       </c>
       <c r="G43">
+        <v>15</v>
+      </c>
+      <c r="H43">
+        <v>5</v>
+      </c>
+      <c r="I43">
         <v>0</v>
-      </c>
-      <c r="H43">
-        <v>50</v>
-      </c>
-      <c r="I43">
-        <v>10</v>
       </c>
       <c r="J43">
         <v>-1</v>
@@ -3462,18 +3355,15 @@
         <v>1</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="P43" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A44">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -3482,7 +3372,7 @@
         <v>202</v>
       </c>
       <c r="D44" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3491,10 +3381,10 @@
         <v>-1</v>
       </c>
       <c r="G44">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H44">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -3515,24 +3405,24 @@
         <v>1</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P44" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A45">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B45">
         <v>1</v>
       </c>
       <c r="C45">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D45" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E45">
         <v>1</v>
@@ -3541,13 +3431,13 @@
         <v>-1</v>
       </c>
       <c r="G45">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H45">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J45">
         <v>-1</v>
@@ -3565,15 +3455,18 @@
         <v>1</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="P45" t="s">
-        <v>146</v>
+        <v>143</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A46">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -3582,7 +3475,7 @@
         <v>202</v>
       </c>
       <c r="D46" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E46">
         <v>1</v>
@@ -3591,10 +3484,10 @@
         <v>-1</v>
       </c>
       <c r="G46">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H46">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -3615,15 +3508,15 @@
         <v>1</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="P46" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A47">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -3632,7 +3525,7 @@
         <v>202</v>
       </c>
       <c r="D47" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E47">
         <v>1</v>
@@ -3641,7 +3534,7 @@
         <v>-1</v>
       </c>
       <c r="G47">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H47">
         <v>30</v>
@@ -3665,129 +3558,127 @@
         <v>1</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="P47" s="9" t="s">
-        <v>150</v>
+        <v>213</v>
+      </c>
+      <c r="P47" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A48">
+        <v>45</v>
+      </c>
+      <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="C48">
+        <v>202</v>
+      </c>
+      <c r="D48" t="s">
+        <v>54</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+      <c r="F48">
+        <v>-1</v>
+      </c>
+      <c r="G48">
+        <v>20</v>
+      </c>
+      <c r="H48">
+        <v>10</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>-1</v>
+      </c>
+      <c r="K48">
+        <v>-1</v>
+      </c>
+      <c r="L48">
+        <v>200</v>
+      </c>
+      <c r="M48">
+        <v>99</v>
+      </c>
+      <c r="N48" t="b">
+        <v>1</v>
+      </c>
+      <c r="O48" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="P48" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="O49" s="6"/>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A50">
-        <v>47</v>
-      </c>
-      <c r="B50">
-        <v>2</v>
-      </c>
-      <c r="C50">
-        <v>302</v>
-      </c>
-      <c r="D50" t="s">
-        <v>57</v>
-      </c>
-      <c r="E50">
-        <v>1</v>
-      </c>
-      <c r="F50">
-        <v>-1</v>
-      </c>
-      <c r="G50">
-        <v>-1</v>
-      </c>
-      <c r="H50">
-        <v>-1</v>
-      </c>
-      <c r="I50">
-        <v>-1</v>
-      </c>
-      <c r="J50">
-        <v>-1</v>
-      </c>
-      <c r="K50">
-        <v>-1</v>
-      </c>
-      <c r="L50">
-        <v>80</v>
-      </c>
-      <c r="M50">
+      <c r="A49">
+        <v>46</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49">
+        <v>202</v>
+      </c>
+      <c r="D49" t="s">
+        <v>55</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
+      </c>
+      <c r="F49">
+        <v>-1</v>
+      </c>
+      <c r="G49">
+        <v>25</v>
+      </c>
+      <c r="H49">
+        <v>30</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>-1</v>
+      </c>
+      <c r="K49">
+        <v>-1</v>
+      </c>
+      <c r="L49">
+        <v>200</v>
+      </c>
+      <c r="M49">
         <v>99</v>
       </c>
-      <c r="N50" t="b">
-        <v>1</v>
-      </c>
-      <c r="O50" s="6"/>
-      <c r="P50" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>157</v>
+      <c r="N49" t="b">
+        <v>1</v>
+      </c>
+      <c r="O49" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="P49" s="9" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A51">
-        <v>48</v>
-      </c>
-      <c r="B51">
-        <v>2</v>
-      </c>
-      <c r="C51">
-        <v>301</v>
-      </c>
-      <c r="D51" t="s">
-        <v>58</v>
-      </c>
-      <c r="E51">
-        <v>1</v>
-      </c>
-      <c r="F51">
-        <v>-1</v>
-      </c>
-      <c r="G51">
-        <v>-1</v>
-      </c>
-      <c r="H51">
-        <v>-1</v>
-      </c>
-      <c r="I51">
-        <v>-1</v>
-      </c>
-      <c r="J51">
-        <v>-1</v>
-      </c>
-      <c r="K51">
-        <v>-1</v>
-      </c>
-      <c r="L51">
-        <v>150</v>
-      </c>
-      <c r="M51">
-        <v>99</v>
-      </c>
-      <c r="N51" t="b">
-        <v>1</v>
-      </c>
       <c r="O51" s="6"/>
-      <c r="P51" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q51" t="s">
-        <v>59</v>
-      </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A52">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B52">
         <v>2</v>
       </c>
       <c r="C52">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D52" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E52">
         <v>1</v>
@@ -3811,7 +3702,7 @@
         <v>-1</v>
       </c>
       <c r="L52">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M52">
         <v>99</v>
@@ -3821,24 +3712,24 @@
       </c>
       <c r="O52" s="6"/>
       <c r="P52" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="Q52" t="s">
-        <v>61</v>
+        <v>156</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A53">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B53">
         <v>2</v>
       </c>
       <c r="C53">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D53" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -3862,7 +3753,7 @@
         <v>-1</v>
       </c>
       <c r="L53">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="M53">
         <v>99</v>
@@ -3872,24 +3763,24 @@
       </c>
       <c r="O53" s="6"/>
       <c r="P53" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="Q53" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A54">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B54">
         <v>2</v>
       </c>
       <c r="C54">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D54" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E54">
         <v>1</v>
@@ -3913,7 +3804,7 @@
         <v>-1</v>
       </c>
       <c r="L54">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="M54">
         <v>99</v>
@@ -3923,21 +3814,24 @@
       </c>
       <c r="O54" s="6"/>
       <c r="P54" t="s">
-        <v>161</v>
+        <v>158</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A55">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B55">
         <v>2</v>
       </c>
       <c r="C55">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D55" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E55">
         <v>1</v>
@@ -3961,7 +3855,7 @@
         <v>-1</v>
       </c>
       <c r="L55">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="M55">
         <v>99</v>
@@ -3971,12 +3865,15 @@
       </c>
       <c r="O55" s="6"/>
       <c r="P55" t="s">
-        <v>162</v>
+        <v>159</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A56">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B56">
         <v>2</v>
@@ -3985,7 +3882,7 @@
         <v>300</v>
       </c>
       <c r="D56" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E56">
         <v>1</v>
@@ -4009,7 +3906,7 @@
         <v>-1</v>
       </c>
       <c r="L56">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="M56">
         <v>99</v>
@@ -4019,12 +3916,12 @@
       </c>
       <c r="O56" s="6"/>
       <c r="P56" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A57">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B57">
         <v>2</v>
@@ -4033,7 +3930,7 @@
         <v>300</v>
       </c>
       <c r="D57" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E57">
         <v>1</v>
@@ -4057,7 +3954,7 @@
         <v>-1</v>
       </c>
       <c r="L57">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="M57">
         <v>99</v>
@@ -4067,24 +3964,21 @@
       </c>
       <c r="O57" s="6"/>
       <c r="P57" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q57" t="s">
-        <v>68</v>
+        <v>161</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A58">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B58">
         <v>2</v>
       </c>
       <c r="C58">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D58" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E58">
         <v>1</v>
@@ -4108,7 +4002,7 @@
         <v>-1</v>
       </c>
       <c r="L58">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="M58">
         <v>99</v>
@@ -4118,24 +4012,21 @@
       </c>
       <c r="O58" s="6"/>
       <c r="P58" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A59">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B59">
         <v>2</v>
       </c>
       <c r="C59">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D59" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E59">
         <v>1</v>
@@ -4150,16 +4041,16 @@
         <v>-1</v>
       </c>
       <c r="I59">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="J59">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="K59">
         <v>-1</v>
       </c>
       <c r="L59">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="M59">
         <v>99</v>
@@ -4168,28 +4059,79 @@
         <v>1</v>
       </c>
       <c r="O59" s="6"/>
-      <c r="P59" s="9" t="s">
-        <v>166</v>
+      <c r="P59" t="s">
+        <v>163</v>
       </c>
       <c r="Q59" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A60">
+        <v>55</v>
+      </c>
+      <c r="B60">
+        <v>2</v>
+      </c>
+      <c r="C60">
+        <v>303</v>
+      </c>
+      <c r="D60" t="s">
+        <v>68</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+      <c r="F60">
+        <v>-1</v>
+      </c>
+      <c r="G60">
+        <v>-1</v>
+      </c>
+      <c r="H60">
+        <v>-1</v>
+      </c>
+      <c r="I60">
+        <v>-1</v>
+      </c>
+      <c r="J60">
+        <v>-1</v>
+      </c>
+      <c r="K60">
+        <v>-1</v>
+      </c>
+      <c r="L60">
+        <v>80</v>
+      </c>
+      <c r="M60">
+        <v>99</v>
+      </c>
+      <c r="N60" t="b">
+        <v>1</v>
+      </c>
+      <c r="O60" s="6"/>
+      <c r="P60" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q60" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="O60" s="6"/>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A61">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B61">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="C61">
+        <v>303</v>
       </c>
       <c r="D61" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F61">
         <v>-1</v>
@@ -4201,79 +4143,46 @@
         <v>-1</v>
       </c>
       <c r="I61">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J61">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K61">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L61">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="M61">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="N61" t="b">
         <v>1</v>
       </c>
       <c r="O61" s="6"/>
+      <c r="P61" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A62">
-        <v>58</v>
-      </c>
-      <c r="B62">
-        <v>3</v>
-      </c>
-      <c r="D62" t="s">
-        <v>72</v>
-      </c>
-      <c r="E62">
-        <v>3</v>
-      </c>
-      <c r="F62">
-        <v>-1</v>
-      </c>
-      <c r="G62">
-        <v>-1</v>
-      </c>
-      <c r="H62">
-        <v>-1</v>
-      </c>
-      <c r="I62">
-        <v>-1</v>
-      </c>
-      <c r="J62">
-        <v>-1</v>
-      </c>
-      <c r="K62">
-        <v>0</v>
-      </c>
-      <c r="L62">
-        <v>18</v>
-      </c>
-      <c r="M62">
-        <v>1</v>
-      </c>
-      <c r="N62" t="b">
-        <v>1</v>
-      </c>
       <c r="O62" s="6"/>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A63">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B63">
         <v>3</v>
       </c>
       <c r="D63" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E63">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F63">
         <v>-1</v>
@@ -4294,7 +4203,7 @@
         <v>0</v>
       </c>
       <c r="L63">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="M63">
         <v>1</v>
@@ -4306,13 +4215,13 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A64">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B64">
         <v>3</v>
       </c>
       <c r="D64" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E64">
         <v>3</v>
@@ -4336,7 +4245,7 @@
         <v>0</v>
       </c>
       <c r="L64">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M64">
         <v>1</v>
@@ -4348,13 +4257,13 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A65">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B65">
         <v>3</v>
       </c>
       <c r="D65" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E65">
         <v>4</v>
@@ -4378,7 +4287,7 @@
         <v>0</v>
       </c>
       <c r="L65">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M65">
         <v>1</v>
@@ -4390,16 +4299,16 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A66">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B66">
         <v>3</v>
       </c>
       <c r="D66" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F66">
         <v>-1</v>
@@ -4420,7 +4329,7 @@
         <v>0</v>
       </c>
       <c r="L66">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="M66">
         <v>1</v>
@@ -4432,16 +4341,16 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A67">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B67">
         <v>3</v>
       </c>
       <c r="D67" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E67">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F67">
         <v>-1</v>
@@ -4462,7 +4371,7 @@
         <v>0</v>
       </c>
       <c r="L67">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="M67">
         <v>1</v>
@@ -4474,13 +4383,13 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A68">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B68">
         <v>3</v>
       </c>
       <c r="D68" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E68">
         <v>1</v>
@@ -4504,7 +4413,7 @@
         <v>0</v>
       </c>
       <c r="L68">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="M68">
         <v>1</v>
@@ -4516,16 +4425,16 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A69">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B69">
         <v>3</v>
       </c>
       <c r="D69" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E69">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F69">
         <v>-1</v>
@@ -4546,7 +4455,7 @@
         <v>0</v>
       </c>
       <c r="L69">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="M69">
         <v>1</v>
@@ -4558,16 +4467,16 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A70">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B70">
         <v>3</v>
       </c>
       <c r="D70" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E70">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F70">
         <v>-1</v>
@@ -4588,7 +4497,7 @@
         <v>0</v>
       </c>
       <c r="L70">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="M70">
         <v>1</v>
@@ -4600,16 +4509,16 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A71">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B71">
         <v>3</v>
       </c>
       <c r="D71" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E71">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="F71">
         <v>-1</v>
@@ -4630,7 +4539,7 @@
         <v>0</v>
       </c>
       <c r="L71">
-        <v>350</v>
+        <v>16</v>
       </c>
       <c r="M71">
         <v>1</v>
@@ -4642,16 +4551,16 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A72">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B72">
         <v>3</v>
       </c>
       <c r="D72" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E72">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="F72">
         <v>-1</v>
@@ -4672,7 +4581,7 @@
         <v>0</v>
       </c>
       <c r="L72">
-        <v>240</v>
+        <v>26</v>
       </c>
       <c r="M72">
         <v>1</v>
@@ -4684,16 +4593,16 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A73">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B73">
         <v>3</v>
       </c>
       <c r="D73" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E73">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="F73">
         <v>-1</v>
@@ -4714,7 +4623,7 @@
         <v>0</v>
       </c>
       <c r="L73">
-        <v>2</v>
+        <v>350</v>
       </c>
       <c r="M73">
         <v>1</v>
@@ -4726,16 +4635,16 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A74">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B74">
         <v>3</v>
       </c>
       <c r="D74" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E74">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="F74">
         <v>-1</v>
@@ -4756,7 +4665,7 @@
         <v>0</v>
       </c>
       <c r="L74">
-        <v>8</v>
+        <v>240</v>
       </c>
       <c r="M74">
         <v>1</v>
@@ -4768,16 +4677,16 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A75">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B75">
         <v>3</v>
       </c>
       <c r="D75" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F75">
         <v>-1</v>
@@ -4798,7 +4707,7 @@
         <v>0</v>
       </c>
       <c r="L75">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M75">
         <v>1</v>
@@ -4810,16 +4719,16 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A76">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B76">
         <v>3</v>
       </c>
       <c r="D76" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E76">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F76">
         <v>-1</v>
@@ -4840,7 +4749,7 @@
         <v>0</v>
       </c>
       <c r="L76">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="M76">
         <v>1</v>
@@ -4852,16 +4761,16 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A77">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B77">
         <v>3</v>
       </c>
       <c r="D77" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E77">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F77">
         <v>-1</v>
@@ -4882,7 +4791,7 @@
         <v>0</v>
       </c>
       <c r="L77">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="M77">
         <v>1</v>
@@ -4894,16 +4803,16 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A78">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B78">
         <v>3</v>
       </c>
       <c r="D78" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E78">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F78">
         <v>-1</v>
@@ -4924,7 +4833,7 @@
         <v>0</v>
       </c>
       <c r="L78">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M78">
         <v>1</v>
@@ -4936,16 +4845,16 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A79">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B79">
         <v>3</v>
       </c>
       <c r="D79" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E79">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F79">
         <v>-1</v>
@@ -4966,7 +4875,7 @@
         <v>0</v>
       </c>
       <c r="L79">
-        <v>150</v>
+        <v>35</v>
       </c>
       <c r="M79">
         <v>1</v>
@@ -4978,16 +4887,16 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A80">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B80">
         <v>3</v>
       </c>
       <c r="D80" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E80">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F80">
         <v>-1</v>
@@ -5005,10 +4914,10 @@
         <v>-1</v>
       </c>
       <c r="K80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="M80">
         <v>1</v>
@@ -5020,16 +4929,16 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A81">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B81">
         <v>3</v>
       </c>
       <c r="D81" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E81">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F81">
         <v>-1</v>
@@ -5047,10 +4956,10 @@
         <v>-1</v>
       </c>
       <c r="K81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M81">
         <v>1</v>
@@ -5062,16 +4971,16 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A82">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B82">
         <v>3</v>
       </c>
       <c r="D82" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E82">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F82">
         <v>-1</v>
@@ -5092,7 +5001,7 @@
         <v>1</v>
       </c>
       <c r="L82">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="M82">
         <v>1</v>
@@ -5104,16 +5013,16 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A83">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B83">
         <v>3</v>
       </c>
       <c r="D83" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E83">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F83">
         <v>-1</v>
@@ -5134,7 +5043,7 @@
         <v>1</v>
       </c>
       <c r="L83">
-        <v>620</v>
+        <v>100</v>
       </c>
       <c r="M83">
         <v>1</v>
@@ -5146,16 +5055,16 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A84">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B84">
         <v>3</v>
       </c>
       <c r="D84" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E84">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F84">
         <v>-1</v>
@@ -5176,7 +5085,7 @@
         <v>1</v>
       </c>
       <c r="L84">
-        <v>360</v>
+        <v>150</v>
       </c>
       <c r="M84">
         <v>1</v>
@@ -5188,16 +5097,16 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A85">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B85">
         <v>3</v>
       </c>
       <c r="D85" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E85">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F85">
         <v>-1</v>
@@ -5218,7 +5127,7 @@
         <v>1</v>
       </c>
       <c r="L85">
-        <v>500</v>
+        <v>620</v>
       </c>
       <c r="M85">
         <v>1</v>
@@ -5230,16 +5139,16 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A86">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B86">
         <v>3</v>
       </c>
       <c r="D86" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E86">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F86">
         <v>-1</v>
@@ -5260,7 +5169,7 @@
         <v>1</v>
       </c>
       <c r="L86">
-        <v>440</v>
+        <v>360</v>
       </c>
       <c r="M86">
         <v>1</v>
@@ -5272,16 +5181,16 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A87">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B87">
         <v>3</v>
       </c>
       <c r="D87" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E87">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F87">
         <v>-1</v>
@@ -5302,7 +5211,7 @@
         <v>1</v>
       </c>
       <c r="L87">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="M87">
         <v>1</v>
@@ -5314,16 +5223,16 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A88">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B88">
         <v>3</v>
       </c>
       <c r="D88" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E88">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F88">
         <v>-1</v>
@@ -5344,7 +5253,7 @@
         <v>1</v>
       </c>
       <c r="L88">
-        <v>270</v>
+        <v>440</v>
       </c>
       <c r="M88">
         <v>1</v>
@@ -5356,16 +5265,16 @@
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A89">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B89">
         <v>3</v>
       </c>
       <c r="D89" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E89">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F89">
         <v>-1</v>
@@ -5386,7 +5295,7 @@
         <v>1</v>
       </c>
       <c r="L89">
-        <v>530</v>
+        <v>170</v>
       </c>
       <c r="M89">
         <v>1</v>
@@ -5398,16 +5307,16 @@
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A90">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B90">
         <v>3</v>
       </c>
       <c r="D90" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E90">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F90">
         <v>-1</v>
@@ -5428,7 +5337,7 @@
         <v>1</v>
       </c>
       <c r="L90">
-        <v>720</v>
+        <v>270</v>
       </c>
       <c r="M90">
         <v>1</v>
@@ -5440,16 +5349,16 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A91">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B91">
         <v>3</v>
       </c>
       <c r="D91" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E91">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F91">
         <v>-1</v>
@@ -5470,7 +5379,7 @@
         <v>1</v>
       </c>
       <c r="L91">
-        <v>300</v>
+        <v>530</v>
       </c>
       <c r="M91">
         <v>1</v>
@@ -5482,16 +5391,16 @@
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A92">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B92">
         <v>3</v>
       </c>
       <c r="D92" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E92">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F92">
         <v>-1</v>
@@ -5512,7 +5421,7 @@
         <v>1</v>
       </c>
       <c r="L92">
-        <v>360</v>
+        <v>720</v>
       </c>
       <c r="M92">
         <v>1</v>
@@ -5524,16 +5433,16 @@
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A93">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B93">
         <v>3</v>
       </c>
       <c r="D93" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E93">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F93">
         <v>-1</v>
@@ -5554,7 +5463,7 @@
         <v>1</v>
       </c>
       <c r="L93">
-        <v>520</v>
+        <v>300</v>
       </c>
       <c r="M93">
         <v>1</v>
@@ -5566,16 +5475,16 @@
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A94">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B94">
         <v>3</v>
       </c>
       <c r="D94" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E94">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F94">
         <v>-1</v>
@@ -5596,7 +5505,7 @@
         <v>1</v>
       </c>
       <c r="L94">
-        <v>710</v>
+        <v>360</v>
       </c>
       <c r="M94">
         <v>1</v>
@@ -5608,16 +5517,16 @@
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A95">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B95">
         <v>3</v>
       </c>
       <c r="D95" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E95">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F95">
         <v>-1</v>
@@ -5635,10 +5544,10 @@
         <v>-1</v>
       </c>
       <c r="K95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L95">
-        <v>300</v>
+        <v>520</v>
       </c>
       <c r="M95">
         <v>1</v>
@@ -5650,16 +5559,16 @@
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A96">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B96">
         <v>3</v>
       </c>
       <c r="D96" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E96">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="F96">
         <v>-1</v>
@@ -5677,10 +5586,10 @@
         <v>-1</v>
       </c>
       <c r="K96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L96">
-        <v>340</v>
+        <v>710</v>
       </c>
       <c r="M96">
         <v>1</v>
@@ -5692,16 +5601,16 @@
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A97">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B97">
         <v>3</v>
       </c>
       <c r="D97" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E97">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F97">
         <v>-1</v>
@@ -5722,7 +5631,7 @@
         <v>2</v>
       </c>
       <c r="L97">
-        <v>2400</v>
+        <v>300</v>
       </c>
       <c r="M97">
         <v>1</v>
@@ -5734,16 +5643,16 @@
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A98">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B98">
         <v>3</v>
       </c>
       <c r="D98" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E98">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F98">
         <v>-1</v>
@@ -5764,7 +5673,7 @@
         <v>2</v>
       </c>
       <c r="L98">
-        <v>1400</v>
+        <v>340</v>
       </c>
       <c r="M98">
         <v>1</v>
@@ -5776,16 +5685,16 @@
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A99">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B99">
         <v>3</v>
       </c>
       <c r="D99" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E99">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F99">
         <v>-1</v>
@@ -5806,7 +5715,7 @@
         <v>2</v>
       </c>
       <c r="L99">
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="M99">
         <v>1</v>
@@ -5818,16 +5727,16 @@
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A100">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B100">
         <v>3</v>
       </c>
       <c r="D100" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E100">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F100">
         <v>-1</v>
@@ -5848,7 +5757,7 @@
         <v>2</v>
       </c>
       <c r="L100">
-        <v>700</v>
+        <v>1400</v>
       </c>
       <c r="M100">
         <v>1</v>
@@ -5860,16 +5769,16 @@
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A101">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B101">
         <v>3</v>
       </c>
       <c r="D101" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E101">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="F101">
         <v>-1</v>
@@ -5890,7 +5799,7 @@
         <v>2</v>
       </c>
       <c r="L101">
-        <v>240</v>
+        <v>1800</v>
       </c>
       <c r="M101">
         <v>1</v>
@@ -5902,16 +5811,16 @@
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A102">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B102">
         <v>3</v>
       </c>
       <c r="D102" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E102">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F102">
         <v>-1</v>
@@ -5932,7 +5841,7 @@
         <v>2</v>
       </c>
       <c r="L102">
-        <v>2950</v>
+        <v>700</v>
       </c>
       <c r="M102">
         <v>1</v>
@@ -5944,16 +5853,16 @@
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A103">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B103">
         <v>3</v>
       </c>
       <c r="D103" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E103">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F103">
         <v>-1</v>
@@ -5974,7 +5883,7 @@
         <v>2</v>
       </c>
       <c r="L103">
-        <v>1350</v>
+        <v>240</v>
       </c>
       <c r="M103">
         <v>1</v>
@@ -5986,16 +5895,16 @@
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A104">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B104">
         <v>3</v>
       </c>
       <c r="D104" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E104">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="F104">
         <v>-1</v>
@@ -6013,10 +5922,10 @@
         <v>-1</v>
       </c>
       <c r="K104">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L104">
-        <v>1500</v>
+        <v>2950</v>
       </c>
       <c r="M104">
         <v>1</v>
@@ -6028,16 +5937,16 @@
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A105">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B105">
         <v>3</v>
       </c>
       <c r="D105" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E105">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F105">
         <v>-1</v>
@@ -6055,10 +5964,10 @@
         <v>-1</v>
       </c>
       <c r="K105">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L105">
-        <v>5000</v>
+        <v>1350</v>
       </c>
       <c r="M105">
         <v>1</v>
@@ -6070,16 +5979,16 @@
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A106">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B106">
         <v>3</v>
       </c>
       <c r="D106" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E106">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F106">
         <v>-1</v>
@@ -6100,7 +6009,7 @@
         <v>3</v>
       </c>
       <c r="L106">
-        <v>4520</v>
+        <v>1500</v>
       </c>
       <c r="M106">
         <v>1</v>
@@ -6112,16 +6021,16 @@
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A107">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B107">
         <v>3</v>
       </c>
       <c r="D107" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E107">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F107">
         <v>-1</v>
@@ -6142,7 +6051,7 @@
         <v>3</v>
       </c>
       <c r="L107">
-        <v>9800</v>
+        <v>5000</v>
       </c>
       <c r="M107">
         <v>1</v>
@@ -6154,16 +6063,16 @@
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A108">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B108">
         <v>3</v>
       </c>
       <c r="D108" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E108">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F108">
         <v>-1</v>
@@ -6184,7 +6093,7 @@
         <v>3</v>
       </c>
       <c r="L108">
-        <v>12000</v>
+        <v>4520</v>
       </c>
       <c r="M108">
         <v>1</v>
@@ -6196,16 +6105,16 @@
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A109">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B109">
         <v>3</v>
       </c>
       <c r="D109" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E109">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F109">
         <v>-1</v>
@@ -6226,7 +6135,7 @@
         <v>3</v>
       </c>
       <c r="L109">
-        <v>7500</v>
+        <v>9800</v>
       </c>
       <c r="M109">
         <v>1</v>
@@ -6238,16 +6147,16 @@
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A110">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B110">
         <v>3</v>
       </c>
       <c r="D110" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E110">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="F110">
         <v>-1</v>
@@ -6268,7 +6177,7 @@
         <v>3</v>
       </c>
       <c r="L110">
-        <v>19520</v>
+        <v>12000</v>
       </c>
       <c r="M110">
         <v>1</v>
@@ -6280,16 +6189,16 @@
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A111">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B111">
         <v>3</v>
       </c>
       <c r="D111" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E111">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="F111">
         <v>-1</v>
@@ -6307,10 +6216,10 @@
         <v>-1</v>
       </c>
       <c r="K111">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L111">
-        <v>1000</v>
+        <v>7500</v>
       </c>
       <c r="M111">
         <v>1</v>
@@ -6322,16 +6231,16 @@
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A112">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B112">
         <v>3</v>
       </c>
       <c r="D112" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E112">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F112">
         <v>-1</v>
@@ -6349,10 +6258,10 @@
         <v>-1</v>
       </c>
       <c r="K112">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L112">
-        <v>37200</v>
+        <v>19520</v>
       </c>
       <c r="M112">
         <v>1</v>
@@ -6364,16 +6273,16 @@
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A113">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B113">
         <v>3</v>
       </c>
       <c r="D113" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E113">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="F113">
         <v>-1</v>
@@ -6394,7 +6303,7 @@
         <v>4</v>
       </c>
       <c r="L113">
-        <v>42890</v>
+        <v>1000</v>
       </c>
       <c r="M113">
         <v>1</v>
@@ -6406,16 +6315,16 @@
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A114">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B114">
         <v>3</v>
       </c>
       <c r="D114" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E114">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="F114">
         <v>-1</v>
@@ -6436,7 +6345,7 @@
         <v>4</v>
       </c>
       <c r="L114">
-        <v>132460</v>
+        <v>37200</v>
       </c>
       <c r="M114">
         <v>1</v>
@@ -6448,16 +6357,16 @@
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A115">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B115">
         <v>3</v>
       </c>
       <c r="D115" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E115">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F115">
         <v>-1</v>
@@ -6478,20 +6387,98 @@
         <v>4</v>
       </c>
       <c r="L115">
+        <v>42890</v>
+      </c>
+      <c r="M115">
+        <v>1</v>
+      </c>
+      <c r="N115" t="b">
+        <v>1</v>
+      </c>
+      <c r="O115" s="6"/>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A116">
+        <v>110</v>
+      </c>
+      <c r="B116">
+        <v>3</v>
+      </c>
+      <c r="D116" t="s">
+        <v>123</v>
+      </c>
+      <c r="E116">
+        <v>150</v>
+      </c>
+      <c r="F116">
+        <v>-1</v>
+      </c>
+      <c r="G116">
+        <v>-1</v>
+      </c>
+      <c r="H116">
+        <v>-1</v>
+      </c>
+      <c r="I116">
+        <v>-1</v>
+      </c>
+      <c r="J116">
+        <v>-1</v>
+      </c>
+      <c r="K116">
+        <v>4</v>
+      </c>
+      <c r="L116">
+        <v>132460</v>
+      </c>
+      <c r="M116">
+        <v>1</v>
+      </c>
+      <c r="N116" t="b">
+        <v>1</v>
+      </c>
+      <c r="O116" s="6"/>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A117">
+        <v>111</v>
+      </c>
+      <c r="B117">
+        <v>3</v>
+      </c>
+      <c r="D117" t="s">
+        <v>124</v>
+      </c>
+      <c r="E117">
+        <v>70</v>
+      </c>
+      <c r="F117">
+        <v>-1</v>
+      </c>
+      <c r="G117">
+        <v>-1</v>
+      </c>
+      <c r="H117">
+        <v>-1</v>
+      </c>
+      <c r="I117">
+        <v>-1</v>
+      </c>
+      <c r="J117">
+        <v>-1</v>
+      </c>
+      <c r="K117">
+        <v>4</v>
+      </c>
+      <c r="L117">
         <v>52520</v>
       </c>
-      <c r="M115">
-        <v>1</v>
-      </c>
-      <c r="N115" t="b">
-        <v>1</v>
-      </c>
-      <c r="O115" s="6"/>
-    </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="O116" s="6"/>
-    </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="M117">
+        <v>1</v>
+      </c>
+      <c r="N117" t="b">
+        <v>1</v>
+      </c>
       <c r="O117" s="6"/>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.45">

--- a/아이템 도감.xlsx
+++ b/아이템 도감.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hcw97\Desktop\CapstoneProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA5DDECC-3A28-4104-A1C9-59BB85B3D6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA33D05E-CCF4-4CFE-81FF-B60C28787021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{AEFF7BDA-CB51-4C25-A75C-46A97EA8EBD6}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="227">
   <si>
     <t>item_id</t>
   </si>
@@ -782,6 +782,10 @@
   </si>
   <si>
     <t>유령을 퇴치하는 스프레이</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip_ghostspray</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2193,7 +2197,9 @@
       <c r="N17" t="b">
         <v>1</v>
       </c>
-      <c r="O17" s="6"/>
+      <c r="O17" s="6" t="s">
+        <v>226</v>
+      </c>
       <c r="P17" t="s">
         <v>225</v>
       </c>

--- a/아이템 도감.xlsx
+++ b/아이템 도감.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hcw97\Desktop\CapstoneProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA33D05E-CCF4-4CFE-81FF-B60C28787021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{240432D1-1735-4D09-B899-A788316C72D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{AEFF7BDA-CB51-4C25-A75C-46A97EA8EBD6}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="227">
   <si>
     <t>item_id</t>
   </si>
@@ -2354,7 +2354,7 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A24">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -2404,7 +2404,7 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A25">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -2454,7 +2454,7 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A26">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -2504,7 +2504,7 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A27">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -2554,7 +2554,7 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A28">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -2607,7 +2607,7 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A29">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -2660,7 +2660,7 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A30">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -2710,7 +2710,7 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A31">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -2760,7 +2760,7 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A32">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A33">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -2860,7 +2860,7 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A34">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B34">
         <v>1</v>
@@ -2910,7 +2910,7 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A35">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -2960,7 +2960,7 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A36">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -3013,7 +3013,7 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A37">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -3066,7 +3066,7 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A38">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -3116,7 +3116,7 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A39">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -3166,7 +3166,7 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A40">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -3219,7 +3219,7 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A41">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -3269,7 +3269,7 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A42">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -3319,7 +3319,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A43">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -3369,7 +3369,7 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A44">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -3419,7 +3419,7 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A45">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -3472,7 +3472,7 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A46">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -3522,7 +3522,7 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A47">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -3572,7 +3572,7 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A48">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -3622,7 +3622,7 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A49">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -3675,7 +3675,7 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A52">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B52">
         <v>2</v>
@@ -3726,7 +3726,7 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A53">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B53">
         <v>2</v>
@@ -3777,7 +3777,7 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A54">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B54">
         <v>2</v>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A55">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B55">
         <v>2</v>
@@ -3879,7 +3879,7 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A56">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B56">
         <v>2</v>
@@ -3927,7 +3927,7 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A57">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B57">
         <v>2</v>
@@ -3975,7 +3975,7 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A58">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B58">
         <v>2</v>
@@ -4023,7 +4023,7 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A59">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B59">
         <v>2</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A60">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B60">
         <v>2</v>
@@ -4125,7 +4125,7 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A61">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B61">
         <v>2</v>
@@ -4179,7 +4179,7 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A63">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B63">
         <v>3</v>
@@ -4221,7 +4221,7 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A64">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B64">
         <v>3</v>
@@ -4263,7 +4263,7 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A65">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B65">
         <v>3</v>
@@ -4305,7 +4305,7 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A66">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B66">
         <v>3</v>
@@ -4347,7 +4347,7 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A67">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B67">
         <v>3</v>
@@ -4389,7 +4389,7 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A68">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B68">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A69">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B69">
         <v>3</v>
@@ -4473,7 +4473,7 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A70">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B70">
         <v>3</v>
@@ -4515,7 +4515,7 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A71">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B71">
         <v>3</v>
@@ -4557,7 +4557,7 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A72">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B72">
         <v>3</v>
@@ -4599,7 +4599,7 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A73">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B73">
         <v>3</v>
@@ -4641,7 +4641,7 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A74">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B74">
         <v>3</v>
@@ -4683,7 +4683,7 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A75">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B75">
         <v>3</v>
@@ -4725,7 +4725,7 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A76">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B76">
         <v>3</v>
@@ -4767,7 +4767,7 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A77">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B77">
         <v>3</v>
@@ -4809,7 +4809,7 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A78">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B78">
         <v>3</v>
@@ -4851,7 +4851,7 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A79">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B79">
         <v>3</v>
@@ -4893,7 +4893,7 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A80">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B80">
         <v>3</v>
@@ -4935,7 +4935,7 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A81">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B81">
         <v>3</v>
@@ -4977,7 +4977,7 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A82">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B82">
         <v>3</v>
@@ -5019,7 +5019,7 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A83">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B83">
         <v>3</v>
@@ -5061,7 +5061,7 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A84">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B84">
         <v>3</v>
@@ -5103,7 +5103,7 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A85">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B85">
         <v>3</v>
@@ -5145,7 +5145,7 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A86">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B86">
         <v>3</v>
@@ -5187,7 +5187,7 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A87">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B87">
         <v>3</v>
@@ -5229,7 +5229,7 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A88">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B88">
         <v>3</v>
@@ -5271,7 +5271,7 @@
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A89">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B89">
         <v>3</v>
@@ -5313,7 +5313,7 @@
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A90">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B90">
         <v>3</v>
@@ -5355,7 +5355,7 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A91">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B91">
         <v>3</v>
@@ -5397,7 +5397,7 @@
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A92">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B92">
         <v>3</v>
@@ -5439,7 +5439,7 @@
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A93">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B93">
         <v>3</v>
@@ -5481,7 +5481,7 @@
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A94">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B94">
         <v>3</v>
@@ -5523,7 +5523,7 @@
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A95">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B95">
         <v>3</v>
@@ -5565,7 +5565,7 @@
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A96">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B96">
         <v>3</v>
@@ -5607,7 +5607,7 @@
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A97">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B97">
         <v>3</v>
@@ -5649,7 +5649,7 @@
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A98">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B98">
         <v>3</v>
@@ -5691,7 +5691,7 @@
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A99">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B99">
         <v>3</v>
@@ -5733,7 +5733,7 @@
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A100">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B100">
         <v>3</v>
@@ -5775,7 +5775,7 @@
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A101">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B101">
         <v>3</v>
@@ -5817,7 +5817,7 @@
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A102">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B102">
         <v>3</v>
@@ -5859,7 +5859,7 @@
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A103">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B103">
         <v>3</v>
@@ -5901,7 +5901,7 @@
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A104">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B104">
         <v>3</v>
@@ -5943,7 +5943,7 @@
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A105">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B105">
         <v>3</v>
@@ -5985,7 +5985,7 @@
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A106">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B106">
         <v>3</v>
@@ -6027,7 +6027,7 @@
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A107">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B107">
         <v>3</v>
@@ -6069,7 +6069,7 @@
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A108">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B108">
         <v>3</v>
@@ -6111,7 +6111,7 @@
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A109">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B109">
         <v>3</v>
@@ -6153,7 +6153,7 @@
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A110">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B110">
         <v>3</v>
@@ -6195,7 +6195,7 @@
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A111">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B111">
         <v>3</v>
@@ -6237,7 +6237,7 @@
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A112">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B112">
         <v>3</v>
@@ -6279,7 +6279,7 @@
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A113">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B113">
         <v>3</v>
@@ -6321,7 +6321,7 @@
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A114">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B114">
         <v>3</v>
@@ -6363,7 +6363,7 @@
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A115">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B115">
         <v>3</v>
@@ -6405,7 +6405,7 @@
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A116">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B116">
         <v>3</v>
@@ -6447,7 +6447,7 @@
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A117">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B117">
         <v>3</v>

--- a/아이템 도감.xlsx
+++ b/아이템 도감.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hcw97\Desktop\CapstoneProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{240432D1-1735-4D09-B899-A788316C72D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C470385-1376-41BC-B0B1-5D924A4E0198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{AEFF7BDA-CB51-4C25-A75C-46A97EA8EBD6}"/>
   </bookViews>
@@ -2162,7 +2162,7 @@
         <v>0</v>
       </c>
       <c r="C17" s="13">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>224</v>
@@ -2212,7 +2212,7 @@
         <v>0</v>
       </c>
       <c r="C18">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D18" t="s">
         <v>28</v>
@@ -2262,7 +2262,7 @@
         <v>0</v>
       </c>
       <c r="C19">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D19" t="s">
         <v>29</v>

--- a/아이템 도감.xlsx
+++ b/아이템 도감.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hcw97\Desktop\CapstoneProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C470385-1376-41BC-B0B1-5D924A4E0198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5F3C5D-CAFB-420B-8770-80F5DD9B8503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{AEFF7BDA-CB51-4C25-A75C-46A97EA8EBD6}"/>
+    <workbookView xWindow="1600" yWindow="4860" windowWidth="28800" windowHeight="15370" xr2:uid="{AEFF7BDA-CB51-4C25-A75C-46A97EA8EBD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2171,7 +2171,7 @@
         <v>2</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>-1</v>

--- a/아이템 도감.xlsx
+++ b/아이템 도감.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hcw97\Desktop\CapstoneProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\CapstoneProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5F3C5D-CAFB-420B-8770-80F5DD9B8503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F2D1722-D18B-4DC1-9CB2-DCB4FCEA20DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1600" yWindow="4860" windowWidth="28800" windowHeight="15370" xr2:uid="{AEFF7BDA-CB51-4C25-A75C-46A97EA8EBD6}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{AEFF7BDA-CB51-4C25-A75C-46A97EA8EBD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="226">
   <si>
     <t>item_id</t>
   </si>
@@ -335,9 +335,6 @@
     <t>도자기 화병</t>
   </si>
   <si>
-    <t>오크통</t>
-  </si>
-  <si>
     <t>복싱 글러브</t>
   </si>
   <si>
@@ -345,9 +342,6 @@
   </si>
   <si>
     <t>명품 가방</t>
-  </si>
-  <si>
-    <t>여행 가방</t>
   </si>
   <si>
     <t>은 반지</t>
@@ -786,6 +780,10 @@
   </si>
   <si>
     <t>Equip_ghostspray</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>황금 주사위</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1057,9 +1055,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1097,7 +1095,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1203,7 +1201,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1345,7 +1343,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1354,27 +1352,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176CEBE0-28C6-4629-A760-C52146228B7D}">
   <dimension ref="A1:Q433"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12.875" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="18.08203125" customWidth="1"/>
+    <col min="3" max="3" width="18.125" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" customWidth="1"/>
-    <col min="6" max="6" width="21.08203125" customWidth="1"/>
-    <col min="7" max="8" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.375" customWidth="1"/>
+    <col min="6" max="6" width="21.125" customWidth="1"/>
+    <col min="7" max="8" width="14.875" customWidth="1"/>
     <col min="9" max="9" width="14.25" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="15.58203125" customWidth="1"/>
-    <col min="12" max="12" width="19.08203125" customWidth="1"/>
+    <col min="10" max="10" width="12.875" customWidth="1"/>
+    <col min="11" max="11" width="15.625" customWidth="1"/>
+    <col min="12" max="12" width="19.125" customWidth="1"/>
     <col min="13" max="13" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="54.58203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="35.08203125" customWidth="1"/>
+    <col min="14" max="14" width="54.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="35.125" customWidth="1"/>
     <col min="16" max="16" width="56.25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="59.58203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="59.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1403,7 +1401,7 @@
         <v>6</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>7</v>
@@ -1418,13 +1416,13 @@
         <v>10</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="P1" s="11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1468,13 +1466,13 @@
         <v>1</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="P2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1519,10 +1517,10 @@
       </c>
       <c r="O3" s="6"/>
       <c r="P3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1567,10 +1565,10 @@
       </c>
       <c r="O4" s="6"/>
       <c r="P4" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1615,10 +1613,10 @@
       </c>
       <c r="O5" s="6"/>
       <c r="P5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1662,13 +1660,13 @@
         <v>1</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="P6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1713,10 +1711,10 @@
       </c>
       <c r="O7" s="6"/>
       <c r="P7" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1761,10 +1759,10 @@
       </c>
       <c r="O8" s="6"/>
       <c r="P8" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1809,10 +1807,10 @@
       </c>
       <c r="O9" s="6"/>
       <c r="P9" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1856,13 +1854,13 @@
         <v>1</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="P10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1907,10 +1905,10 @@
       </c>
       <c r="O11" s="6"/>
       <c r="P11" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1955,10 +1953,10 @@
       </c>
       <c r="O12" s="6"/>
       <c r="P12" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2003,10 +2001,10 @@
       </c>
       <c r="O13" s="6"/>
       <c r="P13" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2051,10 +2049,10 @@
       </c>
       <c r="O14" s="6"/>
       <c r="P14" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2065,7 +2063,7 @@
         <v>150</v>
       </c>
       <c r="D15" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -2098,13 +2096,13 @@
         <v>1</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="P15" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2148,13 +2146,13 @@
         <v>1</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="P16" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.45">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
         <v>16</v>
       </c>
@@ -2165,7 +2163,7 @@
         <v>151</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -2198,13 +2196,13 @@
         <v>1</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="P17" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.45">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2248,13 +2246,13 @@
         <v>1</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="P18" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.45">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2299,10 +2297,10 @@
       </c>
       <c r="O19" s="6"/>
       <c r="P19" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.45">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2346,13 +2344,13 @@
         <v>1</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="P20" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.45">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>20</v>
       </c>
@@ -2396,13 +2394,13 @@
         <v>1</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="P24" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.45">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>21</v>
       </c>
@@ -2446,13 +2444,13 @@
         <v>1</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="P25" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.45">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>22</v>
       </c>
@@ -2496,13 +2494,13 @@
         <v>1</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="P26" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.45">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>23</v>
       </c>
@@ -2546,13 +2544,13 @@
         <v>1</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="P27" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.45">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>24</v>
       </c>
@@ -2596,16 +2594,16 @@
         <v>1</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="P28" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="Q28" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.45">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>25</v>
       </c>
@@ -2649,16 +2647,16 @@
         <v>1</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="P29" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="Q29" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.45">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26</v>
       </c>
@@ -2702,13 +2700,13 @@
         <v>1</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="P30" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.45">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>27</v>
       </c>
@@ -2752,13 +2750,13 @@
         <v>1</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="P31" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.45">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>28</v>
       </c>
@@ -2802,13 +2800,13 @@
         <v>1</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="P32" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.45">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>29</v>
       </c>
@@ -2852,13 +2850,13 @@
         <v>1</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="P33" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.45">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>30</v>
       </c>
@@ -2902,13 +2900,13 @@
         <v>1</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="P34" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.45">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>31</v>
       </c>
@@ -2952,13 +2950,13 @@
         <v>1</v>
       </c>
       <c r="O35" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="P35" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.45">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>32</v>
       </c>
@@ -3002,16 +3000,16 @@
         <v>1</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="P36" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="Q36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.45">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>33</v>
       </c>
@@ -3055,16 +3053,16 @@
         <v>1</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="P37" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="Q37" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.45">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>34</v>
       </c>
@@ -3075,7 +3073,7 @@
         <v>202</v>
       </c>
       <c r="D38" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -3108,13 +3106,13 @@
         <v>1</v>
       </c>
       <c r="O38" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="P38" t="s">
         <v>221</v>
       </c>
-      <c r="P38" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.45">
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>35</v>
       </c>
@@ -3158,13 +3156,13 @@
         <v>1</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="P39" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.45">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>36</v>
       </c>
@@ -3208,16 +3206,16 @@
         <v>1</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="P40" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="Q40" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.45">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>37</v>
       </c>
@@ -3261,13 +3259,13 @@
         <v>1</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="P41" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.45">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>38</v>
       </c>
@@ -3311,13 +3309,13 @@
         <v>1</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="P42" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.45">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>39</v>
       </c>
@@ -3361,13 +3359,13 @@
         <v>1</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="P43" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.45">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>40</v>
       </c>
@@ -3411,13 +3409,13 @@
         <v>1</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="P44" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.45">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>41</v>
       </c>
@@ -3461,16 +3459,16 @@
         <v>1</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="P45" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="Q45" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.45">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>42</v>
       </c>
@@ -3514,13 +3512,13 @@
         <v>1</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="P46" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.45">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>43</v>
       </c>
@@ -3564,13 +3562,13 @@
         <v>1</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="P47" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.45">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>44</v>
       </c>
@@ -3614,13 +3612,13 @@
         <v>1</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="P48" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.45">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>45</v>
       </c>
@@ -3664,16 +3662,16 @@
         <v>1</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.45">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="O51" s="6"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>46</v>
       </c>
@@ -3718,13 +3716,13 @@
       </c>
       <c r="O52" s="6"/>
       <c r="P52" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Q52" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.45">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>47</v>
       </c>
@@ -3769,13 +3767,13 @@
       </c>
       <c r="O53" s="6"/>
       <c r="P53" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="Q53" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>48</v>
       </c>
@@ -3820,13 +3818,13 @@
       </c>
       <c r="O54" s="6"/>
       <c r="P54" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="Q54" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>49</v>
       </c>
@@ -3871,13 +3869,13 @@
       </c>
       <c r="O55" s="6"/>
       <c r="P55" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q55" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>50</v>
       </c>
@@ -3922,10 +3920,10 @@
       </c>
       <c r="O56" s="6"/>
       <c r="P56" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.45">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>51</v>
       </c>
@@ -3970,10 +3968,10 @@
       </c>
       <c r="O57" s="6"/>
       <c r="P57" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.45">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>52</v>
       </c>
@@ -4018,10 +4016,10 @@
       </c>
       <c r="O58" s="6"/>
       <c r="P58" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.45">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>53</v>
       </c>
@@ -4066,13 +4064,13 @@
       </c>
       <c r="O59" s="6"/>
       <c r="P59" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="Q59" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>54</v>
       </c>
@@ -4117,13 +4115,13 @@
       </c>
       <c r="O60" s="6"/>
       <c r="P60" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Q60" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.45">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>55</v>
       </c>
@@ -4168,16 +4166,16 @@
       </c>
       <c r="O61" s="6"/>
       <c r="P61" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Q61" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.45">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="O62" s="6"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>56</v>
       </c>
@@ -4219,7 +4217,7 @@
       </c>
       <c r="O63" s="6"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>57</v>
       </c>
@@ -4261,7 +4259,7 @@
       </c>
       <c r="O64" s="6"/>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>58</v>
       </c>
@@ -4303,7 +4301,7 @@
       </c>
       <c r="O65" s="6"/>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>59</v>
       </c>
@@ -4345,7 +4343,7 @@
       </c>
       <c r="O66" s="6"/>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>60</v>
       </c>
@@ -4387,7 +4385,7 @@
       </c>
       <c r="O67" s="6"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>61</v>
       </c>
@@ -4429,7 +4427,7 @@
       </c>
       <c r="O68" s="6"/>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>62</v>
       </c>
@@ -4471,7 +4469,7 @@
       </c>
       <c r="O69" s="6"/>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>63</v>
       </c>
@@ -4513,7 +4511,7 @@
       </c>
       <c r="O70" s="6"/>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>64</v>
       </c>
@@ -4555,7 +4553,7 @@
       </c>
       <c r="O71" s="6"/>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>65</v>
       </c>
@@ -4597,7 +4595,7 @@
       </c>
       <c r="O72" s="6"/>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>66</v>
       </c>
@@ -4639,7 +4637,7 @@
       </c>
       <c r="O73" s="6"/>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>67</v>
       </c>
@@ -4681,7 +4679,7 @@
       </c>
       <c r="O74" s="6"/>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>68</v>
       </c>
@@ -4723,7 +4721,7 @@
       </c>
       <c r="O75" s="6"/>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>69</v>
       </c>
@@ -4765,7 +4763,7 @@
       </c>
       <c r="O76" s="6"/>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>70</v>
       </c>
@@ -4807,7 +4805,7 @@
       </c>
       <c r="O77" s="6"/>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>71</v>
       </c>
@@ -4849,7 +4847,7 @@
       </c>
       <c r="O78" s="6"/>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>72</v>
       </c>
@@ -4891,7 +4889,7 @@
       </c>
       <c r="O79" s="6"/>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>73</v>
       </c>
@@ -4933,7 +4931,7 @@
       </c>
       <c r="O80" s="6"/>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>74</v>
       </c>
@@ -4975,7 +4973,7 @@
       </c>
       <c r="O81" s="6"/>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>75</v>
       </c>
@@ -5017,7 +5015,7 @@
       </c>
       <c r="O82" s="6"/>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>76</v>
       </c>
@@ -5059,7 +5057,7 @@
       </c>
       <c r="O83" s="6"/>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>77</v>
       </c>
@@ -5101,7 +5099,7 @@
       </c>
       <c r="O84" s="6"/>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>78</v>
       </c>
@@ -5143,7 +5141,7 @@
       </c>
       <c r="O85" s="6"/>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>79</v>
       </c>
@@ -5185,7 +5183,7 @@
       </c>
       <c r="O86" s="6"/>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>80</v>
       </c>
@@ -5227,7 +5225,7 @@
       </c>
       <c r="O87" s="6"/>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>81</v>
       </c>
@@ -5269,7 +5267,7 @@
       </c>
       <c r="O88" s="6"/>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>82</v>
       </c>
@@ -5311,7 +5309,7 @@
       </c>
       <c r="O89" s="6"/>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>83</v>
       </c>
@@ -5353,7 +5351,7 @@
       </c>
       <c r="O90" s="6"/>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>84</v>
       </c>
@@ -5395,7 +5393,7 @@
       </c>
       <c r="O91" s="6"/>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>85</v>
       </c>
@@ -5403,7 +5401,7 @@
         <v>3</v>
       </c>
       <c r="D92" t="s">
-        <v>99</v>
+        <v>225</v>
       </c>
       <c r="E92">
         <v>30</v>
@@ -5437,7 +5435,7 @@
       </c>
       <c r="O92" s="6"/>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>86</v>
       </c>
@@ -5445,7 +5443,7 @@
         <v>3</v>
       </c>
       <c r="D93" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E93">
         <v>14</v>
@@ -5479,7 +5477,7 @@
       </c>
       <c r="O93" s="6"/>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>87</v>
       </c>
@@ -5487,7 +5485,7 @@
         <v>3</v>
       </c>
       <c r="D94" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E94">
         <v>8</v>
@@ -5521,7 +5519,7 @@
       </c>
       <c r="O94" s="6"/>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>88</v>
       </c>
@@ -5529,7 +5527,7 @@
         <v>3</v>
       </c>
       <c r="D95" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E95">
         <v>15</v>
@@ -5563,7 +5561,7 @@
       </c>
       <c r="O95" s="6"/>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>89</v>
       </c>
@@ -5571,10 +5569,10 @@
         <v>3</v>
       </c>
       <c r="D96" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E96">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F96">
         <v>-1</v>
@@ -5592,10 +5590,10 @@
         <v>-1</v>
       </c>
       <c r="K96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L96">
-        <v>710</v>
+        <v>300</v>
       </c>
       <c r="M96">
         <v>1</v>
@@ -5605,7 +5603,7 @@
       </c>
       <c r="O96" s="6"/>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>90</v>
       </c>
@@ -5613,10 +5611,10 @@
         <v>3</v>
       </c>
       <c r="D97" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E97">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F97">
         <v>-1</v>
@@ -5637,7 +5635,7 @@
         <v>2</v>
       </c>
       <c r="L97">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="M97">
         <v>1</v>
@@ -5647,7 +5645,7 @@
       </c>
       <c r="O97" s="6"/>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>91</v>
       </c>
@@ -5655,10 +5653,10 @@
         <v>3</v>
       </c>
       <c r="D98" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E98">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F98">
         <v>-1</v>
@@ -5679,7 +5677,7 @@
         <v>2</v>
       </c>
       <c r="L98">
-        <v>340</v>
+        <v>2400</v>
       </c>
       <c r="M98">
         <v>1</v>
@@ -5689,7 +5687,7 @@
       </c>
       <c r="O98" s="6"/>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>92</v>
       </c>
@@ -5697,10 +5695,10 @@
         <v>3</v>
       </c>
       <c r="D99" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E99">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F99">
         <v>-1</v>
@@ -5721,7 +5719,7 @@
         <v>2</v>
       </c>
       <c r="L99">
-        <v>2400</v>
+        <v>1400</v>
       </c>
       <c r="M99">
         <v>1</v>
@@ -5731,7 +5729,7 @@
       </c>
       <c r="O99" s="6"/>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>93</v>
       </c>
@@ -5739,10 +5737,10 @@
         <v>3</v>
       </c>
       <c r="D100" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E100">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F100">
         <v>-1</v>
@@ -5763,7 +5761,7 @@
         <v>2</v>
       </c>
       <c r="L100">
-        <v>1400</v>
+        <v>1800</v>
       </c>
       <c r="M100">
         <v>1</v>
@@ -5773,7 +5771,7 @@
       </c>
       <c r="O100" s="6"/>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>94</v>
       </c>
@@ -5781,10 +5779,10 @@
         <v>3</v>
       </c>
       <c r="D101" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E101">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F101">
         <v>-1</v>
@@ -5805,7 +5803,7 @@
         <v>2</v>
       </c>
       <c r="L101">
-        <v>1800</v>
+        <v>700</v>
       </c>
       <c r="M101">
         <v>1</v>
@@ -5815,7 +5813,7 @@
       </c>
       <c r="O101" s="6"/>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>95</v>
       </c>
@@ -5823,10 +5821,10 @@
         <v>3</v>
       </c>
       <c r="D102" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E102">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F102">
         <v>-1</v>
@@ -5847,7 +5845,7 @@
         <v>2</v>
       </c>
       <c r="L102">
-        <v>700</v>
+        <v>240</v>
       </c>
       <c r="M102">
         <v>1</v>
@@ -5857,7 +5855,7 @@
       </c>
       <c r="O102" s="6"/>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>96</v>
       </c>
@@ -5865,10 +5863,10 @@
         <v>3</v>
       </c>
       <c r="D103" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E103">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="F103">
         <v>-1</v>
@@ -5889,7 +5887,7 @@
         <v>2</v>
       </c>
       <c r="L103">
-        <v>240</v>
+        <v>2950</v>
       </c>
       <c r="M103">
         <v>1</v>
@@ -5899,7 +5897,7 @@
       </c>
       <c r="O103" s="6"/>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>97</v>
       </c>
@@ -5907,10 +5905,10 @@
         <v>3</v>
       </c>
       <c r="D104" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E104">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F104">
         <v>-1</v>
@@ -5931,7 +5929,7 @@
         <v>2</v>
       </c>
       <c r="L104">
-        <v>2950</v>
+        <v>1350</v>
       </c>
       <c r="M104">
         <v>1</v>
@@ -5941,7 +5939,7 @@
       </c>
       <c r="O104" s="6"/>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>98</v>
       </c>
@@ -5949,10 +5947,10 @@
         <v>3</v>
       </c>
       <c r="D105" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E105">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F105">
         <v>-1</v>
@@ -5970,10 +5968,10 @@
         <v>-1</v>
       </c>
       <c r="K105">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L105">
-        <v>1350</v>
+        <v>1500</v>
       </c>
       <c r="M105">
         <v>1</v>
@@ -5983,7 +5981,7 @@
       </c>
       <c r="O105" s="6"/>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>99</v>
       </c>
@@ -5991,10 +5989,10 @@
         <v>3</v>
       </c>
       <c r="D106" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E106">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F106">
         <v>-1</v>
@@ -6015,7 +6013,7 @@
         <v>3</v>
       </c>
       <c r="L106">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="M106">
         <v>1</v>
@@ -6025,7 +6023,7 @@
       </c>
       <c r="O106" s="6"/>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>100</v>
       </c>
@@ -6033,10 +6031,10 @@
         <v>3</v>
       </c>
       <c r="D107" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E107">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F107">
         <v>-1</v>
@@ -6057,7 +6055,7 @@
         <v>3</v>
       </c>
       <c r="L107">
-        <v>5000</v>
+        <v>4520</v>
       </c>
       <c r="M107">
         <v>1</v>
@@ -6067,7 +6065,7 @@
       </c>
       <c r="O107" s="6"/>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>101</v>
       </c>
@@ -6075,10 +6073,10 @@
         <v>3</v>
       </c>
       <c r="D108" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E108">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F108">
         <v>-1</v>
@@ -6099,7 +6097,7 @@
         <v>3</v>
       </c>
       <c r="L108">
-        <v>4520</v>
+        <v>9800</v>
       </c>
       <c r="M108">
         <v>1</v>
@@ -6109,7 +6107,7 @@
       </c>
       <c r="O108" s="6"/>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>102</v>
       </c>
@@ -6117,10 +6115,10 @@
         <v>3</v>
       </c>
       <c r="D109" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E109">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F109">
         <v>-1</v>
@@ -6141,7 +6139,7 @@
         <v>3</v>
       </c>
       <c r="L109">
-        <v>9800</v>
+        <v>12000</v>
       </c>
       <c r="M109">
         <v>1</v>
@@ -6151,7 +6149,7 @@
       </c>
       <c r="O109" s="6"/>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>103</v>
       </c>
@@ -6159,10 +6157,10 @@
         <v>3</v>
       </c>
       <c r="D110" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E110">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F110">
         <v>-1</v>
@@ -6183,7 +6181,7 @@
         <v>3</v>
       </c>
       <c r="L110">
-        <v>12000</v>
+        <v>7500</v>
       </c>
       <c r="M110">
         <v>1</v>
@@ -6193,7 +6191,7 @@
       </c>
       <c r="O110" s="6"/>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>104</v>
       </c>
@@ -6201,10 +6199,10 @@
         <v>3</v>
       </c>
       <c r="D111" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E111">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F111">
         <v>-1</v>
@@ -6225,7 +6223,7 @@
         <v>3</v>
       </c>
       <c r="L111">
-        <v>7500</v>
+        <v>19520</v>
       </c>
       <c r="M111">
         <v>1</v>
@@ -6235,7 +6233,7 @@
       </c>
       <c r="O111" s="6"/>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>105</v>
       </c>
@@ -6243,10 +6241,10 @@
         <v>3</v>
       </c>
       <c r="D112" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E112">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="F112">
         <v>-1</v>
@@ -6264,10 +6262,10 @@
         <v>-1</v>
       </c>
       <c r="K112">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L112">
-        <v>19520</v>
+        <v>1000</v>
       </c>
       <c r="M112">
         <v>1</v>
@@ -6277,7 +6275,7 @@
       </c>
       <c r="O112" s="6"/>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>106</v>
       </c>
@@ -6285,10 +6283,10 @@
         <v>3</v>
       </c>
       <c r="D113" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E113">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="F113">
         <v>-1</v>
@@ -6309,7 +6307,7 @@
         <v>4</v>
       </c>
       <c r="L113">
-        <v>1000</v>
+        <v>37200</v>
       </c>
       <c r="M113">
         <v>1</v>
@@ -6319,7 +6317,7 @@
       </c>
       <c r="O113" s="6"/>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>107</v>
       </c>
@@ -6327,10 +6325,10 @@
         <v>3</v>
       </c>
       <c r="D114" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E114">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F114">
         <v>-1</v>
@@ -6351,7 +6349,7 @@
         <v>4</v>
       </c>
       <c r="L114">
-        <v>37200</v>
+        <v>42890</v>
       </c>
       <c r="M114">
         <v>1</v>
@@ -6361,7 +6359,7 @@
       </c>
       <c r="O114" s="6"/>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>108</v>
       </c>
@@ -6369,10 +6367,10 @@
         <v>3</v>
       </c>
       <c r="D115" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E115">
-        <v>62</v>
+        <v>150</v>
       </c>
       <c r="F115">
         <v>-1</v>
@@ -6393,7 +6391,7 @@
         <v>4</v>
       </c>
       <c r="L115">
-        <v>42890</v>
+        <v>132460</v>
       </c>
       <c r="M115">
         <v>1</v>
@@ -6403,7 +6401,7 @@
       </c>
       <c r="O115" s="6"/>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>109</v>
       </c>
@@ -6411,10 +6409,10 @@
         <v>3</v>
       </c>
       <c r="D116" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E116">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="F116">
         <v>-1</v>
@@ -6435,7 +6433,7 @@
         <v>4</v>
       </c>
       <c r="L116">
-        <v>132460</v>
+        <v>52520</v>
       </c>
       <c r="M116">
         <v>1</v>
@@ -6445,994 +6443,955 @@
       </c>
       <c r="O116" s="6"/>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A117">
-        <v>110</v>
-      </c>
-      <c r="B117">
-        <v>3</v>
-      </c>
-      <c r="D117" t="s">
-        <v>124</v>
-      </c>
-      <c r="E117">
-        <v>70</v>
-      </c>
-      <c r="F117">
-        <v>-1</v>
-      </c>
-      <c r="G117">
-        <v>-1</v>
-      </c>
-      <c r="H117">
-        <v>-1</v>
-      </c>
-      <c r="I117">
-        <v>-1</v>
-      </c>
-      <c r="J117">
-        <v>-1</v>
-      </c>
-      <c r="K117">
-        <v>4</v>
-      </c>
-      <c r="L117">
-        <v>52520</v>
-      </c>
-      <c r="M117">
-        <v>1</v>
-      </c>
-      <c r="N117" t="b">
-        <v>1</v>
-      </c>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O117" s="6"/>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O118" s="6"/>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O119" s="6"/>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O120" s="6"/>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O121" s="6"/>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O122" s="6"/>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O123" s="6"/>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O124" s="6"/>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O125" s="6"/>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O126" s="6"/>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O127" s="6"/>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O128" s="6"/>
     </row>
-    <row r="129" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="129" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O129" s="6"/>
     </row>
-    <row r="130" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="130" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O130" s="6"/>
     </row>
-    <row r="131" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="131" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O131" s="6"/>
     </row>
-    <row r="132" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="132" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O132" s="6"/>
     </row>
-    <row r="133" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="133" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O133" s="6"/>
     </row>
-    <row r="134" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="134" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O134" s="6"/>
     </row>
-    <row r="135" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="135" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O135" s="6"/>
     </row>
-    <row r="136" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="136" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O136" s="6"/>
     </row>
-    <row r="137" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="137" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O137" s="6"/>
     </row>
-    <row r="138" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="138" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O138" s="6"/>
     </row>
-    <row r="139" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="139" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O139" s="6"/>
     </row>
-    <row r="140" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="140" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O140" s="6"/>
     </row>
-    <row r="141" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="141" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O141" s="6"/>
     </row>
-    <row r="142" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="142" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O142" s="6"/>
     </row>
-    <row r="143" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="143" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O143" s="6"/>
     </row>
-    <row r="144" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="144" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O144" s="6"/>
     </row>
-    <row r="145" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="145" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O145" s="6"/>
     </row>
-    <row r="146" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="146" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O146" s="6"/>
     </row>
-    <row r="147" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="147" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O147" s="6"/>
     </row>
-    <row r="148" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="148" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O148" s="6"/>
     </row>
-    <row r="149" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="149" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O149" s="6"/>
     </row>
-    <row r="150" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="150" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O150" s="6"/>
     </row>
-    <row r="151" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="151" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O151" s="6"/>
     </row>
-    <row r="152" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="152" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O152" s="6"/>
     </row>
-    <row r="153" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="153" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O153" s="6"/>
     </row>
-    <row r="154" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="154" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O154" s="6"/>
     </row>
-    <row r="155" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="155" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O155" s="6"/>
     </row>
-    <row r="156" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="156" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O156" s="6"/>
     </row>
-    <row r="157" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="157" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O157" s="6"/>
     </row>
-    <row r="158" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="158" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O158" s="6"/>
     </row>
-    <row r="159" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="159" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O159" s="6"/>
     </row>
-    <row r="160" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="160" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O160" s="6"/>
     </row>
-    <row r="161" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="161" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O161" s="6"/>
     </row>
-    <row r="162" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="162" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O162" s="6"/>
     </row>
-    <row r="163" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="163" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O163" s="6"/>
     </row>
-    <row r="164" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="164" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O164" s="6"/>
     </row>
-    <row r="165" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="165" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O165" s="6"/>
     </row>
-    <row r="166" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="166" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O166" s="6"/>
     </row>
-    <row r="167" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="167" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O167" s="6"/>
     </row>
-    <row r="168" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="168" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O168" s="6"/>
     </row>
-    <row r="169" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="169" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O169" s="6"/>
     </row>
-    <row r="170" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="170" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O170" s="6"/>
     </row>
-    <row r="171" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="171" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O171" s="6"/>
     </row>
-    <row r="172" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="172" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O172" s="6"/>
     </row>
-    <row r="173" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="173" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O173" s="6"/>
     </row>
-    <row r="174" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="174" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O174" s="6"/>
     </row>
-    <row r="175" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="175" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O175" s="6"/>
     </row>
-    <row r="176" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="176" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O176" s="6"/>
     </row>
-    <row r="177" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="177" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O177" s="6"/>
     </row>
-    <row r="178" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="178" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O178" s="6"/>
     </row>
-    <row r="179" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="179" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O179" s="6"/>
     </row>
-    <row r="180" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="180" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O180" s="6"/>
     </row>
-    <row r="181" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="181" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O181" s="6"/>
     </row>
-    <row r="182" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="182" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O182" s="6"/>
     </row>
-    <row r="183" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="183" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O183" s="6"/>
     </row>
-    <row r="184" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="184" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O184" s="6"/>
     </row>
-    <row r="185" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="185" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O185" s="6"/>
     </row>
-    <row r="186" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="186" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O186" s="6"/>
     </row>
-    <row r="187" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="187" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O187" s="6"/>
     </row>
-    <row r="188" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="188" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O188" s="6"/>
     </row>
-    <row r="189" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="189" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O189" s="6"/>
     </row>
-    <row r="190" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="190" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O190" s="6"/>
     </row>
-    <row r="191" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="191" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O191" s="6"/>
     </row>
-    <row r="192" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="192" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O192" s="6"/>
     </row>
-    <row r="193" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="193" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O193" s="6"/>
     </row>
-    <row r="194" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="194" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O194" s="6"/>
     </row>
-    <row r="195" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="195" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O195" s="6"/>
     </row>
-    <row r="196" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="196" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O196" s="6"/>
     </row>
-    <row r="197" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="197" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O197" s="6"/>
     </row>
-    <row r="198" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="198" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O198" s="6"/>
     </row>
-    <row r="199" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="199" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O199" s="6"/>
     </row>
-    <row r="200" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="200" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O200" s="6"/>
     </row>
-    <row r="201" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="201" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O201" s="6"/>
     </row>
-    <row r="202" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="202" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O202" s="6"/>
     </row>
-    <row r="203" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="203" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O203" s="6"/>
     </row>
-    <row r="204" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="204" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O204" s="6"/>
     </row>
-    <row r="205" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="205" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O205" s="6"/>
     </row>
-    <row r="206" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="206" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O206" s="6"/>
     </row>
-    <row r="207" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="207" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O207" s="6"/>
     </row>
-    <row r="208" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="208" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O208" s="6"/>
     </row>
-    <row r="209" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="209" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O209" s="6"/>
     </row>
-    <row r="210" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="210" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O210" s="6"/>
     </row>
-    <row r="211" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="211" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O211" s="6"/>
     </row>
-    <row r="212" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="212" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O212" s="6"/>
     </row>
-    <row r="213" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="213" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O213" s="6"/>
     </row>
-    <row r="214" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="214" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O214" s="6"/>
     </row>
-    <row r="215" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="215" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O215" s="6"/>
     </row>
-    <row r="216" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="216" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O216" s="6"/>
     </row>
-    <row r="217" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="217" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O217" s="6"/>
     </row>
-    <row r="218" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="218" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O218" s="6"/>
     </row>
-    <row r="219" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="219" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O219" s="6"/>
     </row>
-    <row r="220" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="220" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O220" s="6"/>
     </row>
-    <row r="221" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="221" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O221" s="6"/>
     </row>
-    <row r="222" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="222" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O222" s="6"/>
     </row>
-    <row r="223" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="223" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O223" s="6"/>
     </row>
-    <row r="224" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="224" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O224" s="6"/>
     </row>
-    <row r="225" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="225" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O225" s="6"/>
     </row>
-    <row r="226" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="226" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O226" s="6"/>
     </row>
-    <row r="227" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="227" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O227" s="6"/>
     </row>
-    <row r="228" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="228" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O228" s="6"/>
     </row>
-    <row r="229" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="229" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O229" s="6"/>
     </row>
-    <row r="230" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="230" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O230" s="6"/>
     </row>
-    <row r="231" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="231" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O231" s="6"/>
     </row>
-    <row r="232" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="232" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O232" s="6"/>
     </row>
-    <row r="233" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="233" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O233" s="6"/>
     </row>
-    <row r="234" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="234" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O234" s="6"/>
     </row>
-    <row r="235" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="235" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O235" s="6"/>
     </row>
-    <row r="236" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="236" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O236" s="6"/>
     </row>
-    <row r="237" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="237" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O237" s="6"/>
     </row>
-    <row r="238" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="238" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O238" s="6"/>
     </row>
-    <row r="239" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="239" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O239" s="6"/>
     </row>
-    <row r="240" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="240" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O240" s="6"/>
     </row>
-    <row r="241" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="241" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O241" s="6"/>
     </row>
-    <row r="242" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="242" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O242" s="6"/>
     </row>
-    <row r="243" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="243" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O243" s="6"/>
     </row>
-    <row r="244" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="244" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O244" s="6"/>
     </row>
-    <row r="245" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="245" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O245" s="6"/>
     </row>
-    <row r="246" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="246" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O246" s="6"/>
     </row>
-    <row r="247" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="247" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O247" s="6"/>
     </row>
-    <row r="248" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="248" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O248" s="6"/>
     </row>
-    <row r="249" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="249" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O249" s="6"/>
     </row>
-    <row r="250" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="250" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O250" s="6"/>
     </row>
-    <row r="251" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="251" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O251" s="6"/>
     </row>
-    <row r="252" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="252" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O252" s="6"/>
     </row>
-    <row r="253" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="253" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O253" s="6"/>
     </row>
-    <row r="254" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="254" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O254" s="6"/>
     </row>
-    <row r="255" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="255" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O255" s="6"/>
     </row>
-    <row r="256" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="256" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O256" s="6"/>
     </row>
-    <row r="257" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="257" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O257" s="6"/>
     </row>
-    <row r="258" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="258" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O258" s="6"/>
     </row>
-    <row r="259" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="259" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O259" s="6"/>
     </row>
-    <row r="260" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="260" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O260" s="6"/>
     </row>
-    <row r="261" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="261" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O261" s="6"/>
     </row>
-    <row r="262" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="262" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O262" s="6"/>
     </row>
-    <row r="263" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="263" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O263" s="6"/>
     </row>
-    <row r="264" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="264" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O264" s="6"/>
     </row>
-    <row r="265" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="265" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O265" s="6"/>
     </row>
-    <row r="266" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="266" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O266" s="6"/>
     </row>
-    <row r="267" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="267" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O267" s="6"/>
     </row>
-    <row r="268" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="268" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O268" s="6"/>
     </row>
-    <row r="269" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="269" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O269" s="6"/>
     </row>
-    <row r="270" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="270" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O270" s="6"/>
     </row>
-    <row r="271" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="271" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O271" s="6"/>
     </row>
-    <row r="272" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="272" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O272" s="6"/>
     </row>
-    <row r="273" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="273" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O273" s="6"/>
     </row>
-    <row r="274" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="274" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O274" s="6"/>
     </row>
-    <row r="275" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="275" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O275" s="6"/>
     </row>
-    <row r="276" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="276" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O276" s="6"/>
     </row>
-    <row r="277" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="277" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O277" s="6"/>
     </row>
-    <row r="278" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="278" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O278" s="6"/>
     </row>
-    <row r="279" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="279" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O279" s="6"/>
     </row>
-    <row r="280" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="280" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O280" s="6"/>
     </row>
-    <row r="281" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="281" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O281" s="6"/>
     </row>
-    <row r="282" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="282" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O282" s="6"/>
     </row>
-    <row r="283" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="283" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O283" s="6"/>
     </row>
-    <row r="284" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="284" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O284" s="6"/>
     </row>
-    <row r="285" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="285" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O285" s="6"/>
     </row>
-    <row r="286" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="286" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O286" s="6"/>
     </row>
-    <row r="287" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="287" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O287" s="6"/>
     </row>
-    <row r="288" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="288" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O288" s="6"/>
     </row>
-    <row r="289" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="289" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O289" s="6"/>
     </row>
-    <row r="290" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="290" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O290" s="6"/>
     </row>
-    <row r="291" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="291" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O291" s="6"/>
     </row>
-    <row r="292" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="292" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O292" s="6"/>
     </row>
-    <row r="293" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="293" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O293" s="6"/>
     </row>
-    <row r="294" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="294" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O294" s="6"/>
     </row>
-    <row r="295" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="295" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O295" s="6"/>
     </row>
-    <row r="296" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="296" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O296" s="6"/>
     </row>
-    <row r="297" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="297" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O297" s="6"/>
     </row>
-    <row r="298" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="298" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O298" s="6"/>
     </row>
-    <row r="299" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="299" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O299" s="6"/>
     </row>
-    <row r="300" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="300" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O300" s="6"/>
     </row>
-    <row r="301" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="301" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O301" s="6"/>
     </row>
-    <row r="302" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="302" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O302" s="6"/>
     </row>
-    <row r="303" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="303" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O303" s="6"/>
     </row>
-    <row r="304" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="304" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O304" s="6"/>
     </row>
-    <row r="305" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="305" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O305" s="6"/>
     </row>
-    <row r="306" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="306" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O306" s="6"/>
     </row>
-    <row r="307" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="307" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O307" s="6"/>
     </row>
-    <row r="308" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="308" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O308" s="6"/>
     </row>
-    <row r="309" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="309" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O309" s="6"/>
     </row>
-    <row r="310" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="310" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O310" s="6"/>
     </row>
-    <row r="311" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="311" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O311" s="6"/>
     </row>
-    <row r="312" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="312" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O312" s="6"/>
     </row>
-    <row r="313" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="313" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O313" s="6"/>
     </row>
-    <row r="314" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="314" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O314" s="6"/>
     </row>
-    <row r="315" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="315" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O315" s="6"/>
     </row>
-    <row r="316" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="316" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O316" s="6"/>
     </row>
-    <row r="317" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="317" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O317" s="6"/>
     </row>
-    <row r="318" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="318" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O318" s="6"/>
     </row>
-    <row r="319" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="319" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O319" s="6"/>
     </row>
-    <row r="320" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="320" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O320" s="6"/>
     </row>
-    <row r="321" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="321" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O321" s="6"/>
     </row>
-    <row r="322" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="322" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O322" s="6"/>
     </row>
-    <row r="323" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="323" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O323" s="6"/>
     </row>
-    <row r="324" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="324" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O324" s="6"/>
     </row>
-    <row r="325" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="325" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O325" s="6"/>
     </row>
-    <row r="326" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="326" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O326" s="6"/>
     </row>
-    <row r="327" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="327" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O327" s="6"/>
     </row>
-    <row r="328" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="328" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O328" s="6"/>
     </row>
-    <row r="329" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="329" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O329" s="6"/>
     </row>
-    <row r="330" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="330" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O330" s="6"/>
     </row>
-    <row r="331" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="331" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O331" s="6"/>
     </row>
-    <row r="332" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="332" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O332" s="6"/>
     </row>
-    <row r="333" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="333" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O333" s="6"/>
     </row>
-    <row r="334" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="334" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O334" s="6"/>
     </row>
-    <row r="335" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="335" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O335" s="6"/>
     </row>
-    <row r="336" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="336" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O336" s="6"/>
     </row>
-    <row r="337" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="337" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O337" s="6"/>
     </row>
-    <row r="338" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="338" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O338" s="6"/>
     </row>
-    <row r="339" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="339" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O339" s="6"/>
     </row>
-    <row r="340" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="340" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O340" s="6"/>
     </row>
-    <row r="341" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="341" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O341" s="6"/>
     </row>
-    <row r="342" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="342" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O342" s="6"/>
     </row>
-    <row r="343" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="343" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O343" s="6"/>
     </row>
-    <row r="344" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="344" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O344" s="6"/>
     </row>
-    <row r="345" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="345" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O345" s="6"/>
     </row>
-    <row r="346" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="346" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O346" s="6"/>
     </row>
-    <row r="347" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="347" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O347" s="6"/>
     </row>
-    <row r="348" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="348" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O348" s="6"/>
     </row>
-    <row r="349" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="349" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O349" s="6"/>
     </row>
-    <row r="350" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="350" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O350" s="6"/>
     </row>
-    <row r="351" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="351" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O351" s="6"/>
     </row>
-    <row r="352" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="352" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O352" s="6"/>
     </row>
-    <row r="353" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="353" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O353" s="6"/>
     </row>
-    <row r="354" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="354" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O354" s="6"/>
     </row>
-    <row r="355" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="355" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O355" s="6"/>
     </row>
-    <row r="356" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="356" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O356" s="6"/>
     </row>
-    <row r="357" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="357" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O357" s="6"/>
     </row>
-    <row r="358" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="358" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O358" s="6"/>
     </row>
-    <row r="359" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="359" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O359" s="6"/>
     </row>
-    <row r="360" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="360" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O360" s="6"/>
     </row>
-    <row r="361" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="361" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O361" s="6"/>
     </row>
-    <row r="362" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="362" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O362" s="6"/>
     </row>
-    <row r="363" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="363" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O363" s="6"/>
     </row>
-    <row r="364" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="364" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O364" s="6"/>
     </row>
-    <row r="365" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="365" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O365" s="6"/>
     </row>
-    <row r="366" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="366" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O366" s="6"/>
     </row>
-    <row r="367" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="367" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O367" s="6"/>
     </row>
-    <row r="368" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="368" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O368" s="6"/>
     </row>
-    <row r="369" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="369" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O369" s="6"/>
     </row>
-    <row r="370" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="370" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O370" s="6"/>
     </row>
-    <row r="371" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="371" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O371" s="6"/>
     </row>
-    <row r="372" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="372" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O372" s="6"/>
     </row>
-    <row r="373" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="373" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O373" s="6"/>
     </row>
-    <row r="374" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="374" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O374" s="6"/>
     </row>
-    <row r="375" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="375" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O375" s="6"/>
     </row>
-    <row r="376" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="376" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O376" s="6"/>
     </row>
-    <row r="377" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="377" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O377" s="6"/>
     </row>
-    <row r="378" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="378" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O378" s="6"/>
     </row>
-    <row r="379" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="379" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O379" s="6"/>
     </row>
-    <row r="380" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="380" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O380" s="6"/>
     </row>
-    <row r="381" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="381" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O381" s="6"/>
     </row>
-    <row r="382" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="382" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O382" s="6"/>
     </row>
-    <row r="383" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="383" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O383" s="6"/>
     </row>
-    <row r="384" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="384" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O384" s="6"/>
     </row>
-    <row r="385" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="385" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O385" s="6"/>
     </row>
-    <row r="386" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="386" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O386" s="6"/>
     </row>
-    <row r="387" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="387" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O387" s="6"/>
     </row>
-    <row r="388" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="388" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O388" s="6"/>
     </row>
-    <row r="389" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="389" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O389" s="6"/>
     </row>
-    <row r="390" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="390" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O390" s="6"/>
     </row>
-    <row r="391" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="391" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O391" s="6"/>
     </row>
-    <row r="392" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="392" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O392" s="6"/>
     </row>
-    <row r="393" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="393" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O393" s="6"/>
     </row>
-    <row r="394" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="394" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O394" s="6"/>
     </row>
-    <row r="395" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="395" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O395" s="6"/>
     </row>
-    <row r="396" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="396" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O396" s="6"/>
     </row>
-    <row r="397" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="397" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O397" s="6"/>
     </row>
-    <row r="398" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="398" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O398" s="6"/>
     </row>
-    <row r="399" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="399" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O399" s="6"/>
     </row>
-    <row r="400" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="400" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O400" s="6"/>
     </row>
-    <row r="401" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="401" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O401" s="6"/>
     </row>
-    <row r="402" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="402" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O402" s="6"/>
     </row>
-    <row r="403" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="403" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O403" s="6"/>
     </row>
-    <row r="404" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="404" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O404" s="6"/>
     </row>
-    <row r="405" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="405" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O405" s="6"/>
     </row>
-    <row r="406" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="406" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O406" s="6"/>
     </row>
-    <row r="407" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="407" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O407" s="6"/>
     </row>
-    <row r="408" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="408" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O408" s="6"/>
     </row>
-    <row r="409" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="409" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O409" s="6"/>
     </row>
-    <row r="410" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="410" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O410" s="6"/>
     </row>
-    <row r="411" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="411" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O411" s="6"/>
     </row>
-    <row r="412" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="412" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O412" s="6"/>
     </row>
-    <row r="413" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="413" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O413" s="6"/>
     </row>
-    <row r="414" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="414" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O414" s="6"/>
     </row>
-    <row r="415" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="415" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O415" s="6"/>
     </row>
-    <row r="416" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="416" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O416" s="6"/>
     </row>
-    <row r="417" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="417" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O417" s="6"/>
     </row>
-    <row r="418" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="418" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O418" s="6"/>
     </row>
-    <row r="419" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="419" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O419" s="6"/>
     </row>
-    <row r="420" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="420" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O420" s="6"/>
     </row>
-    <row r="421" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="421" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O421" s="6"/>
     </row>
-    <row r="422" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="422" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O422" s="6"/>
     </row>
-    <row r="423" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="423" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O423" s="6"/>
     </row>
-    <row r="424" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="424" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O424" s="6"/>
     </row>
-    <row r="425" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="425" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O425" s="6"/>
     </row>
-    <row r="426" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="426" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O426" s="6"/>
     </row>
-    <row r="427" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="427" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O427" s="6"/>
     </row>
-    <row r="428" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="428" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O428" s="6"/>
     </row>
-    <row r="429" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="429" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O429" s="6"/>
     </row>
-    <row r="430" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="430" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O430" s="6"/>
     </row>
-    <row r="431" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="431" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O431" s="6"/>
     </row>
-    <row r="432" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="432" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O432" s="6"/>
     </row>
-    <row r="433" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="433" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O433" s="6"/>
     </row>
   </sheetData>

--- a/아이템 도감.xlsx
+++ b/아이템 도감.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hcw97\Desktop\CapstoneProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5F3C5D-CAFB-420B-8770-80F5DD9B8503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E30B7037-B868-4A5D-BE2D-3EEBADD802D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1600" yWindow="4860" windowWidth="28800" windowHeight="15370" xr2:uid="{AEFF7BDA-CB51-4C25-A75C-46A97EA8EBD6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{AEFF7BDA-CB51-4C25-A75C-46A97EA8EBD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,21 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="251">
   <si>
     <t>item_id</t>
   </si>
@@ -787,6 +778,78 @@
   <si>
     <t>Equip_ghostspray</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>C_Bottle_Cap</t>
+  </si>
+  <si>
+    <t>C_Brick</t>
+  </si>
+  <si>
+    <t>C_Broken_Clock</t>
+  </si>
+  <si>
+    <t>C_Broken_Washing_Machine</t>
+  </si>
+  <si>
+    <t>C_Cracked_Plate</t>
+  </si>
+  <si>
+    <t>C_Empty_Bottle</t>
+  </si>
+  <si>
+    <t>C_Empty_Can</t>
+  </si>
+  <si>
+    <t>C_Fish_Bone</t>
+  </si>
+  <si>
+    <t>C_Glass_Marble</t>
+  </si>
+  <si>
+    <t>C_Old_Boot</t>
+  </si>
+  <si>
+    <t>C_Old_Spoon</t>
+  </si>
+  <si>
+    <t>C_Paper_Plane</t>
+  </si>
+  <si>
+    <t>C_Rusty_Coin</t>
+  </si>
+  <si>
+    <t>C_Scrap_Map</t>
+  </si>
+  <si>
+    <t>C_Seashell</t>
+  </si>
+  <si>
+    <t>C_Tennis_Ball</t>
+  </si>
+  <si>
+    <t>C_Wooden_Button</t>
+  </si>
+  <si>
+    <t>C_Wooden_Doll</t>
+  </si>
+  <si>
+    <t>U_Ancient_Clay_Tablet</t>
+  </si>
+  <si>
+    <t>U_Brass_Canddlestick</t>
+  </si>
+  <si>
+    <t>U_Bronze_Mirror</t>
+  </si>
+  <si>
+    <t>U_Copper_Ring</t>
+  </si>
+  <si>
+    <t>U_Pearl_Earring</t>
+  </si>
+  <si>
+    <t>U_Silk_Handkerchief</t>
   </si>
 </sst>
 </file>
@@ -4217,7 +4280,9 @@
       <c r="N63" t="b">
         <v>1</v>
       </c>
-      <c r="O63" s="6"/>
+      <c r="O63" s="6" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A64">
@@ -4259,7 +4324,9 @@
       <c r="N64" t="b">
         <v>1</v>
       </c>
-      <c r="O64" s="6"/>
+      <c r="O64" s="6" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A65">
@@ -4301,7 +4368,9 @@
       <c r="N65" t="b">
         <v>1</v>
       </c>
-      <c r="O65" s="6"/>
+      <c r="O65" s="6" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A66">
@@ -4343,7 +4412,9 @@
       <c r="N66" t="b">
         <v>1</v>
       </c>
-      <c r="O66" s="6"/>
+      <c r="O66" s="6" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A67">
@@ -4385,7 +4456,9 @@
       <c r="N67" t="b">
         <v>1</v>
       </c>
-      <c r="O67" s="6"/>
+      <c r="O67" s="6" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A68">
@@ -4427,7 +4500,9 @@
       <c r="N68" t="b">
         <v>1</v>
       </c>
-      <c r="O68" s="6"/>
+      <c r="O68" s="6" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A69">
@@ -4469,7 +4544,9 @@
       <c r="N69" t="b">
         <v>1</v>
       </c>
-      <c r="O69" s="6"/>
+      <c r="O69" s="6" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A70">
@@ -4511,7 +4588,9 @@
       <c r="N70" t="b">
         <v>1</v>
       </c>
-      <c r="O70" s="6"/>
+      <c r="O70" s="6" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A71">
@@ -4553,7 +4632,9 @@
       <c r="N71" t="b">
         <v>1</v>
       </c>
-      <c r="O71" s="6"/>
+      <c r="O71" s="6" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A72">
@@ -4595,7 +4676,9 @@
       <c r="N72" t="b">
         <v>1</v>
       </c>
-      <c r="O72" s="6"/>
+      <c r="O72" s="6" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A73">
@@ -4637,7 +4720,9 @@
       <c r="N73" t="b">
         <v>1</v>
       </c>
-      <c r="O73" s="6"/>
+      <c r="O73" s="6" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A74">
@@ -4721,7 +4806,9 @@
       <c r="N75" t="b">
         <v>1</v>
       </c>
-      <c r="O75" s="6"/>
+      <c r="O75" s="6" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A76">
@@ -4763,7 +4850,9 @@
       <c r="N76" t="b">
         <v>1</v>
       </c>
-      <c r="O76" s="6"/>
+      <c r="O76" s="6" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A77">
@@ -4805,7 +4894,9 @@
       <c r="N77" t="b">
         <v>1</v>
       </c>
-      <c r="O77" s="6"/>
+      <c r="O77" s="6" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A78">
@@ -4847,7 +4938,9 @@
       <c r="N78" t="b">
         <v>1</v>
       </c>
-      <c r="O78" s="6"/>
+      <c r="O78" s="6" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A79">
@@ -4889,7 +4982,9 @@
       <c r="N79" t="b">
         <v>1</v>
       </c>
-      <c r="O79" s="6"/>
+      <c r="O79" s="6" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A80">
@@ -4931,7 +5026,9 @@
       <c r="N80" t="b">
         <v>1</v>
       </c>
-      <c r="O80" s="6"/>
+      <c r="O80" s="6" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A81">
@@ -4973,7 +5070,9 @@
       <c r="N81" t="b">
         <v>1</v>
       </c>
-      <c r="O81" s="6"/>
+      <c r="O81" s="6" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A82">
@@ -5015,7 +5114,9 @@
       <c r="N82" t="b">
         <v>1</v>
       </c>
-      <c r="O82" s="6"/>
+      <c r="O82" s="6" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A83">
@@ -5057,7 +5158,9 @@
       <c r="N83" t="b">
         <v>1</v>
       </c>
-      <c r="O83" s="6"/>
+      <c r="O83" s="6" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A84">
@@ -5099,7 +5202,9 @@
       <c r="N84" t="b">
         <v>1</v>
       </c>
-      <c r="O84" s="6"/>
+      <c r="O84" s="6" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A85">
@@ -5141,7 +5246,9 @@
       <c r="N85" t="b">
         <v>1</v>
       </c>
-      <c r="O85" s="6"/>
+      <c r="O85" s="6" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A86">
@@ -5225,7 +5332,9 @@
       <c r="N87" t="b">
         <v>1</v>
       </c>
-      <c r="O87" s="6"/>
+      <c r="O87" s="6" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A88">
@@ -5267,7 +5376,9 @@
       <c r="N88" t="b">
         <v>1</v>
       </c>
-      <c r="O88" s="6"/>
+      <c r="O88" s="6" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A89">

--- a/아이템 도감.xlsx
+++ b/아이템 도감.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\CapstoneProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hcw97\Desktop\CapstoneProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F2D1722-D18B-4DC1-9CB2-DCB4FCEA20DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD7D294-B879-4F37-A27E-110878FD21E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{AEFF7BDA-CB51-4C25-A75C-46A97EA8EBD6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{AEFF7BDA-CB51-4C25-A75C-46A97EA8EBD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="262">
   <si>
     <t>item_id</t>
   </si>
@@ -347,9 +347,6 @@
     <t>은 반지</t>
   </si>
   <si>
-    <t>에메랄드 귀걸이</t>
-  </si>
-  <si>
     <t>수정 해골</t>
   </si>
   <si>
@@ -785,6 +782,118 @@
   <si>
     <t>황금 주사위</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>C_Rusty_Coin</t>
+  </si>
+  <si>
+    <t>C_Glass_Marble</t>
+  </si>
+  <si>
+    <t>C_Old_Spoon</t>
+  </si>
+  <si>
+    <t>C_Empty_Bottle</t>
+  </si>
+  <si>
+    <t>C_Seashell</t>
+  </si>
+  <si>
+    <t>C_Scrap_Map</t>
+  </si>
+  <si>
+    <t>C_Wooden_Doll</t>
+  </si>
+  <si>
+    <t>C_Paper_Plane</t>
+  </si>
+  <si>
+    <t>C_Bottle_Cap</t>
+  </si>
+  <si>
+    <t>C_Tennis_Ball</t>
+  </si>
+  <si>
+    <t>C_Broken_Washing_Machine</t>
+  </si>
+  <si>
+    <t>C_Fish_Bone</t>
+  </si>
+  <si>
+    <t>C_Wooden_Button</t>
+  </si>
+  <si>
+    <t>C_Empty_Can</t>
+  </si>
+  <si>
+    <t>C_Brick</t>
+  </si>
+  <si>
+    <t>C_Cracked_Plate</t>
+  </si>
+  <si>
+    <t>C_Old_Boot</t>
+  </si>
+  <si>
+    <t>C_Broken_Clock</t>
+  </si>
+  <si>
+    <t>U_Copper_Ring</t>
+  </si>
+  <si>
+    <t>U_Silk_Handkerchief</t>
+  </si>
+  <si>
+    <t>U_Pearl_Earring</t>
+  </si>
+  <si>
+    <t>U_Brass_Canddlestick</t>
+  </si>
+  <si>
+    <t>U_Ancient_Clay_Tablet</t>
+  </si>
+  <si>
+    <t>U_Bronze_Mirror</t>
+  </si>
+  <si>
+    <t>에메랄드 브로치</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>R_Crystal_Skull</t>
+  </si>
+  <si>
+    <t>R_Emerald_Brooch</t>
+  </si>
+  <si>
+    <t>R_Silver_Ring</t>
+  </si>
+  <si>
+    <t>R_Viking_Helmet</t>
+  </si>
+  <si>
+    <t>U_Amethyst_Shard</t>
+  </si>
+  <si>
+    <t>U_Boxing_Glove</t>
+  </si>
+  <si>
+    <t>U_Car_Key</t>
+  </si>
+  <si>
+    <t>U_Ceramic_Vase</t>
+  </si>
+  <si>
+    <t>U_Frill_Ribbon</t>
+  </si>
+  <si>
+    <t>U_Golden Dice</t>
+  </si>
+  <si>
+    <t>U_Leather_Belt</t>
+  </si>
+  <si>
+    <t>U_Luxury_Bag</t>
   </si>
 </sst>
 </file>
@@ -1055,9 +1164,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1095,7 +1204,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1201,7 +1310,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1343,7 +1452,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1352,27 +1461,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176CEBE0-28C6-4629-A760-C52146228B7D}">
   <dimension ref="A1:Q433"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.875" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="18.125" customWidth="1"/>
+    <col min="3" max="3" width="18.08203125" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
-    <col min="5" max="5" width="14.375" customWidth="1"/>
-    <col min="6" max="6" width="21.125" customWidth="1"/>
-    <col min="7" max="8" width="14.875" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" customWidth="1"/>
+    <col min="6" max="6" width="21.08203125" customWidth="1"/>
+    <col min="7" max="8" width="14.83203125" customWidth="1"/>
     <col min="9" max="9" width="14.25" customWidth="1"/>
-    <col min="10" max="10" width="12.875" customWidth="1"/>
-    <col min="11" max="11" width="15.625" customWidth="1"/>
-    <col min="12" max="12" width="19.125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="15.58203125" customWidth="1"/>
+    <col min="12" max="12" width="19.08203125" customWidth="1"/>
     <col min="13" max="13" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="54.625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="35.125" customWidth="1"/>
+    <col min="14" max="14" width="54.58203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="35.08203125" customWidth="1"/>
     <col min="16" max="16" width="56.25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="59.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="59.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1401,7 +1510,7 @@
         <v>6</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>7</v>
@@ -1416,13 +1525,13 @@
         <v>10</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P1" s="11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1466,13 +1575,13 @@
         <v>1</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1517,10 +1626,10 @@
       </c>
       <c r="O3" s="6"/>
       <c r="P3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1565,10 +1674,10 @@
       </c>
       <c r="O4" s="6"/>
       <c r="P4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1613,10 +1722,10 @@
       </c>
       <c r="O5" s="6"/>
       <c r="P5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1660,13 +1769,13 @@
         <v>1</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1711,10 +1820,10 @@
       </c>
       <c r="O7" s="6"/>
       <c r="P7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1759,10 +1868,10 @@
       </c>
       <c r="O8" s="6"/>
       <c r="P8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1807,10 +1916,10 @@
       </c>
       <c r="O9" s="6"/>
       <c r="P9" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1854,13 +1963,13 @@
         <v>1</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P10" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1905,10 +2014,10 @@
       </c>
       <c r="O11" s="6"/>
       <c r="P11" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1953,10 +2062,10 @@
       </c>
       <c r="O12" s="6"/>
       <c r="P12" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2001,10 +2110,10 @@
       </c>
       <c r="O13" s="6"/>
       <c r="P13" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2049,10 +2158,10 @@
       </c>
       <c r="O14" s="6"/>
       <c r="P14" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2063,7 +2172,7 @@
         <v>150</v>
       </c>
       <c r="D15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -2096,13 +2205,13 @@
         <v>1</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="P15" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2146,13 +2255,13 @@
         <v>1</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P16" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A17" s="13">
         <v>16</v>
       </c>
@@ -2163,7 +2272,7 @@
         <v>151</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -2196,13 +2305,13 @@
         <v>1</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P17" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2246,13 +2355,13 @@
         <v>1</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P18" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2297,10 +2406,10 @@
       </c>
       <c r="O19" s="6"/>
       <c r="P19" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2344,13 +2453,13 @@
         <v>1</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P20" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>20</v>
       </c>
@@ -2394,13 +2503,13 @@
         <v>1</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P24" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>21</v>
       </c>
@@ -2444,13 +2553,13 @@
         <v>1</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P25" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>22</v>
       </c>
@@ -2494,13 +2603,13 @@
         <v>1</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P26" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>23</v>
       </c>
@@ -2544,13 +2653,13 @@
         <v>1</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P27" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>24</v>
       </c>
@@ -2594,16 +2703,16 @@
         <v>1</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q28" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>25</v>
       </c>
@@ -2647,16 +2756,16 @@
         <v>1</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P29" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q29" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>26</v>
       </c>
@@ -2700,13 +2809,13 @@
         <v>1</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P30" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>27</v>
       </c>
@@ -2750,13 +2859,13 @@
         <v>1</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P31" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>28</v>
       </c>
@@ -2800,13 +2909,13 @@
         <v>1</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P32" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>29</v>
       </c>
@@ -2850,13 +2959,13 @@
         <v>1</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P33" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>30</v>
       </c>
@@ -2900,13 +3009,13 @@
         <v>1</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P34" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>31</v>
       </c>
@@ -2950,13 +3059,13 @@
         <v>1</v>
       </c>
       <c r="O35" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P35" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>32</v>
       </c>
@@ -3000,16 +3109,16 @@
         <v>1</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P36" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q36" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>33</v>
       </c>
@@ -3053,16 +3162,16 @@
         <v>1</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="P37" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q37" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>34</v>
       </c>
@@ -3073,7 +3182,7 @@
         <v>202</v>
       </c>
       <c r="D38" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -3106,13 +3215,13 @@
         <v>1</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P38" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>35</v>
       </c>
@@ -3156,13 +3265,13 @@
         <v>1</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P39" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>36</v>
       </c>
@@ -3206,16 +3315,16 @@
         <v>1</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q40" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>37</v>
       </c>
@@ -3259,13 +3368,13 @@
         <v>1</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P41" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>38</v>
       </c>
@@ -3309,13 +3418,13 @@
         <v>1</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P42" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>39</v>
       </c>
@@ -3359,13 +3468,13 @@
         <v>1</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P43" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>40</v>
       </c>
@@ -3409,13 +3518,13 @@
         <v>1</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P44" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>41</v>
       </c>
@@ -3459,16 +3568,16 @@
         <v>1</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P45" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q45" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>42</v>
       </c>
@@ -3512,13 +3621,13 @@
         <v>1</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P46" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>43</v>
       </c>
@@ -3562,13 +3671,13 @@
         <v>1</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P47" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>44</v>
       </c>
@@ -3612,13 +3721,13 @@
         <v>1</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P48" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>45</v>
       </c>
@@ -3662,16 +3771,16 @@
         <v>1</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.45">
       <c r="O51" s="6"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>46</v>
       </c>
@@ -3716,13 +3825,13 @@
       </c>
       <c r="O52" s="6"/>
       <c r="P52" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Q52" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>47</v>
       </c>
@@ -3767,13 +3876,13 @@
       </c>
       <c r="O53" s="6"/>
       <c r="P53" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q53" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>48</v>
       </c>
@@ -3818,13 +3927,13 @@
       </c>
       <c r="O54" s="6"/>
       <c r="P54" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q54" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>49</v>
       </c>
@@ -3869,13 +3978,13 @@
       </c>
       <c r="O55" s="6"/>
       <c r="P55" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q55" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>50</v>
       </c>
@@ -3920,10 +4029,10 @@
       </c>
       <c r="O56" s="6"/>
       <c r="P56" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>51</v>
       </c>
@@ -3968,10 +4077,10 @@
       </c>
       <c r="O57" s="6"/>
       <c r="P57" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>52</v>
       </c>
@@ -4016,10 +4125,10 @@
       </c>
       <c r="O58" s="6"/>
       <c r="P58" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>53</v>
       </c>
@@ -4064,13 +4173,13 @@
       </c>
       <c r="O59" s="6"/>
       <c r="P59" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q59" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>54</v>
       </c>
@@ -4115,13 +4224,13 @@
       </c>
       <c r="O60" s="6"/>
       <c r="P60" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q60" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>55</v>
       </c>
@@ -4166,16 +4275,16 @@
       </c>
       <c r="O61" s="6"/>
       <c r="P61" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q61" t="s">
         <v>163</v>
       </c>
-      <c r="Q61" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.45">
       <c r="O62" s="6"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>56</v>
       </c>
@@ -4215,9 +4324,11 @@
       <c r="N63" t="b">
         <v>1</v>
       </c>
-      <c r="O63" s="6"/>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O63" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>57</v>
       </c>
@@ -4257,9 +4368,11 @@
       <c r="N64" t="b">
         <v>1</v>
       </c>
-      <c r="O64" s="6"/>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O64" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>58</v>
       </c>
@@ -4299,9 +4412,11 @@
       <c r="N65" t="b">
         <v>1</v>
       </c>
-      <c r="O65" s="6"/>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O65" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>59</v>
       </c>
@@ -4341,9 +4456,11 @@
       <c r="N66" t="b">
         <v>1</v>
       </c>
-      <c r="O66" s="6"/>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O66" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>60</v>
       </c>
@@ -4383,9 +4500,11 @@
       <c r="N67" t="b">
         <v>1</v>
       </c>
-      <c r="O67" s="6"/>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O67" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>61</v>
       </c>
@@ -4425,9 +4544,11 @@
       <c r="N68" t="b">
         <v>1</v>
       </c>
-      <c r="O68" s="6"/>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O68" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>62</v>
       </c>
@@ -4467,9 +4588,11 @@
       <c r="N69" t="b">
         <v>1</v>
       </c>
-      <c r="O69" s="6"/>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O69" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>63</v>
       </c>
@@ -4509,9 +4632,11 @@
       <c r="N70" t="b">
         <v>1</v>
       </c>
-      <c r="O70" s="6"/>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O70" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>64</v>
       </c>
@@ -4551,9 +4676,11 @@
       <c r="N71" t="b">
         <v>1</v>
       </c>
-      <c r="O71" s="6"/>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O71" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>65</v>
       </c>
@@ -4593,9 +4720,11 @@
       <c r="N72" t="b">
         <v>1</v>
       </c>
-      <c r="O72" s="6"/>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O72" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>66</v>
       </c>
@@ -4635,9 +4764,11 @@
       <c r="N73" t="b">
         <v>1</v>
       </c>
-      <c r="O73" s="6"/>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O73" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>67</v>
       </c>
@@ -4677,9 +4808,8 @@
       <c r="N74" t="b">
         <v>1</v>
       </c>
-      <c r="O74" s="6"/>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>68</v>
       </c>
@@ -4719,9 +4849,11 @@
       <c r="N75" t="b">
         <v>1</v>
       </c>
-      <c r="O75" s="6"/>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O75" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>69</v>
       </c>
@@ -4761,9 +4893,11 @@
       <c r="N76" t="b">
         <v>1</v>
       </c>
-      <c r="O76" s="6"/>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O76" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>70</v>
       </c>
@@ -4803,9 +4937,11 @@
       <c r="N77" t="b">
         <v>1</v>
       </c>
-      <c r="O77" s="6"/>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O77" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>71</v>
       </c>
@@ -4845,9 +4981,11 @@
       <c r="N78" t="b">
         <v>1</v>
       </c>
-      <c r="O78" s="6"/>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O78" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>72</v>
       </c>
@@ -4887,9 +5025,11 @@
       <c r="N79" t="b">
         <v>1</v>
       </c>
-      <c r="O79" s="6"/>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O79" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>73</v>
       </c>
@@ -4929,9 +5069,11 @@
       <c r="N80" t="b">
         <v>1</v>
       </c>
-      <c r="O80" s="6"/>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O80" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>74</v>
       </c>
@@ -4971,9 +5113,11 @@
       <c r="N81" t="b">
         <v>1</v>
       </c>
-      <c r="O81" s="6"/>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O81" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>75</v>
       </c>
@@ -5013,9 +5157,11 @@
       <c r="N82" t="b">
         <v>1</v>
       </c>
-      <c r="O82" s="6"/>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O82" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>76</v>
       </c>
@@ -5055,9 +5201,11 @@
       <c r="N83" t="b">
         <v>1</v>
       </c>
-      <c r="O83" s="6"/>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O83" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>77</v>
       </c>
@@ -5097,9 +5245,11 @@
       <c r="N84" t="b">
         <v>1</v>
       </c>
-      <c r="O84" s="6"/>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O84" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>78</v>
       </c>
@@ -5139,9 +5289,11 @@
       <c r="N85" t="b">
         <v>1</v>
       </c>
-      <c r="O85" s="6"/>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O85" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>79</v>
       </c>
@@ -5181,9 +5333,11 @@
       <c r="N86" t="b">
         <v>1</v>
       </c>
-      <c r="O86" s="6"/>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O86" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>80</v>
       </c>
@@ -5223,9 +5377,11 @@
       <c r="N87" t="b">
         <v>1</v>
       </c>
-      <c r="O87" s="6"/>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O87" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>81</v>
       </c>
@@ -5265,9 +5421,11 @@
       <c r="N88" t="b">
         <v>1</v>
       </c>
-      <c r="O88" s="6"/>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O88" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>82</v>
       </c>
@@ -5307,9 +5465,11 @@
       <c r="N89" t="b">
         <v>1</v>
       </c>
-      <c r="O89" s="6"/>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O89" s="12" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>83</v>
       </c>
@@ -5349,9 +5509,11 @@
       <c r="N90" t="b">
         <v>1</v>
       </c>
-      <c r="O90" s="6"/>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O90" s="12" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>84</v>
       </c>
@@ -5391,9 +5553,11 @@
       <c r="N91" t="b">
         <v>1</v>
       </c>
-      <c r="O91" s="6"/>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O91" s="12" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>85</v>
       </c>
@@ -5401,7 +5565,7 @@
         <v>3</v>
       </c>
       <c r="D92" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E92">
         <v>30</v>
@@ -5433,9 +5597,11 @@
       <c r="N92" t="b">
         <v>1</v>
       </c>
-      <c r="O92" s="6"/>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O92" s="12" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>86</v>
       </c>
@@ -5475,9 +5641,11 @@
       <c r="N93" t="b">
         <v>1</v>
       </c>
-      <c r="O93" s="6"/>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O93" s="12" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>87</v>
       </c>
@@ -5517,9 +5685,11 @@
       <c r="N94" t="b">
         <v>1</v>
       </c>
-      <c r="O94" s="6"/>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O94" s="12" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>88</v>
       </c>
@@ -5559,9 +5729,11 @@
       <c r="N95" t="b">
         <v>1</v>
       </c>
-      <c r="O95" s="6"/>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O95" s="12" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>89</v>
       </c>
@@ -5601,9 +5773,11 @@
       <c r="N96" t="b">
         <v>1</v>
       </c>
-      <c r="O96" s="6"/>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O96" s="12" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>90</v>
       </c>
@@ -5611,7 +5785,7 @@
         <v>3</v>
       </c>
       <c r="D97" t="s">
-        <v>103</v>
+        <v>249</v>
       </c>
       <c r="E97">
         <v>3</v>
@@ -5643,9 +5817,11 @@
       <c r="N97" t="b">
         <v>1</v>
       </c>
-      <c r="O97" s="6"/>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O97" s="12" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>91</v>
       </c>
@@ -5653,7 +5829,7 @@
         <v>3</v>
       </c>
       <c r="D98" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E98">
         <v>30</v>
@@ -5685,9 +5861,11 @@
       <c r="N98" t="b">
         <v>1</v>
       </c>
-      <c r="O98" s="6"/>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O98" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>92</v>
       </c>
@@ -5695,7 +5873,7 @@
         <v>3</v>
       </c>
       <c r="D99" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E99">
         <v>20</v>
@@ -5727,9 +5905,11 @@
       <c r="N99" t="b">
         <v>1</v>
       </c>
-      <c r="O99" s="6"/>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O99" s="12" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>93</v>
       </c>
@@ -5737,7 +5917,7 @@
         <v>3</v>
       </c>
       <c r="D100" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E100">
         <v>18</v>
@@ -5769,9 +5949,9 @@
       <c r="N100" t="b">
         <v>1</v>
       </c>
-      <c r="O100" s="6"/>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O100" s="12"/>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>94</v>
       </c>
@@ -5779,7 +5959,7 @@
         <v>3</v>
       </c>
       <c r="D101" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E101">
         <v>8</v>
@@ -5811,9 +5991,9 @@
       <c r="N101" t="b">
         <v>1</v>
       </c>
-      <c r="O101" s="6"/>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O101" s="12"/>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A102">
         <v>95</v>
       </c>
@@ -5821,7 +6001,7 @@
         <v>3</v>
       </c>
       <c r="D102" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E102">
         <v>2</v>
@@ -5853,9 +6033,9 @@
       <c r="N102" t="b">
         <v>1</v>
       </c>
-      <c r="O102" s="6"/>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O102" s="12"/>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A103">
         <v>96</v>
       </c>
@@ -5863,7 +6043,7 @@
         <v>3</v>
       </c>
       <c r="D103" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E103">
         <v>40</v>
@@ -5895,9 +6075,9 @@
       <c r="N103" t="b">
         <v>1</v>
       </c>
-      <c r="O103" s="6"/>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O103" s="12"/>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A104">
         <v>97</v>
       </c>
@@ -5905,7 +6085,7 @@
         <v>3</v>
       </c>
       <c r="D104" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E104">
         <v>15</v>
@@ -5937,9 +6117,9 @@
       <c r="N104" t="b">
         <v>1</v>
       </c>
-      <c r="O104" s="6"/>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O104" s="12"/>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A105">
         <v>98</v>
       </c>
@@ -5947,7 +6127,7 @@
         <v>3</v>
       </c>
       <c r="D105" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E105">
         <v>5</v>
@@ -5979,9 +6159,9 @@
       <c r="N105" t="b">
         <v>1</v>
       </c>
-      <c r="O105" s="6"/>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O105" s="12"/>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A106">
         <v>99</v>
       </c>
@@ -5989,7 +6169,7 @@
         <v>3</v>
       </c>
       <c r="D106" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E106">
         <v>25</v>
@@ -6021,9 +6201,9 @@
       <c r="N106" t="b">
         <v>1</v>
       </c>
-      <c r="O106" s="6"/>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O106" s="12"/>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A107">
         <v>100</v>
       </c>
@@ -6031,7 +6211,7 @@
         <v>3</v>
       </c>
       <c r="D107" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E107">
         <v>30</v>
@@ -6063,9 +6243,9 @@
       <c r="N107" t="b">
         <v>1</v>
       </c>
-      <c r="O107" s="6"/>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O107" s="12"/>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A108">
         <v>101</v>
       </c>
@@ -6073,7 +6253,7 @@
         <v>3</v>
       </c>
       <c r="D108" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E108">
         <v>50</v>
@@ -6105,9 +6285,9 @@
       <c r="N108" t="b">
         <v>1</v>
       </c>
-      <c r="O108" s="6"/>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O108" s="12"/>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A109">
         <v>102</v>
       </c>
@@ -6115,7 +6295,7 @@
         <v>3</v>
       </c>
       <c r="D109" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E109">
         <v>45</v>
@@ -6147,9 +6327,9 @@
       <c r="N109" t="b">
         <v>1</v>
       </c>
-      <c r="O109" s="6"/>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O109" s="12"/>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A110">
         <v>103</v>
       </c>
@@ -6157,7 +6337,7 @@
         <v>3</v>
       </c>
       <c r="D110" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E110">
         <v>40</v>
@@ -6189,9 +6369,9 @@
       <c r="N110" t="b">
         <v>1</v>
       </c>
-      <c r="O110" s="6"/>
-    </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O110" s="12"/>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A111">
         <v>104</v>
       </c>
@@ -6199,7 +6379,7 @@
         <v>3</v>
       </c>
       <c r="D111" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E111">
         <v>80</v>
@@ -6231,9 +6411,9 @@
       <c r="N111" t="b">
         <v>1</v>
       </c>
-      <c r="O111" s="6"/>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O111" s="12"/>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A112">
         <v>105</v>
       </c>
@@ -6241,7 +6421,7 @@
         <v>3</v>
       </c>
       <c r="D112" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E112">
         <v>1</v>
@@ -6273,9 +6453,9 @@
       <c r="N112" t="b">
         <v>1</v>
       </c>
-      <c r="O112" s="6"/>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O112" s="12"/>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A113">
         <v>106</v>
       </c>
@@ -6283,7 +6463,7 @@
         <v>3</v>
       </c>
       <c r="D113" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E113">
         <v>70</v>
@@ -6315,9 +6495,9 @@
       <c r="N113" t="b">
         <v>1</v>
       </c>
-      <c r="O113" s="6"/>
-    </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O113" s="12"/>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A114">
         <v>107</v>
       </c>
@@ -6325,7 +6505,7 @@
         <v>3</v>
       </c>
       <c r="D114" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E114">
         <v>62</v>
@@ -6357,9 +6537,9 @@
       <c r="N114" t="b">
         <v>1</v>
       </c>
-      <c r="O114" s="6"/>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O114" s="12"/>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A115">
         <v>108</v>
       </c>
@@ -6367,7 +6547,7 @@
         <v>3</v>
       </c>
       <c r="D115" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E115">
         <v>150</v>
@@ -6399,9 +6579,9 @@
       <c r="N115" t="b">
         <v>1</v>
       </c>
-      <c r="O115" s="6"/>
-    </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O115" s="12"/>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A116">
         <v>109</v>
       </c>
@@ -6409,7 +6589,7 @@
         <v>3</v>
       </c>
       <c r="D116" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E116">
         <v>70</v>
@@ -6441,957 +6621,957 @@
       <c r="N116" t="b">
         <v>1</v>
       </c>
-      <c r="O116" s="6"/>
-    </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O116" s="12"/>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O117" s="6"/>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O118" s="6"/>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O119" s="6"/>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O120" s="6"/>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O121" s="6"/>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O122" s="6"/>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O123" s="6"/>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O124" s="6"/>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O125" s="6"/>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O126" s="6"/>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O127" s="6"/>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O128" s="6"/>
     </row>
-    <row r="129" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="129" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O129" s="6"/>
     </row>
-    <row r="130" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="130" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O130" s="6"/>
     </row>
-    <row r="131" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="131" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O131" s="6"/>
     </row>
-    <row r="132" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="132" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O132" s="6"/>
     </row>
-    <row r="133" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="133" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O133" s="6"/>
     </row>
-    <row r="134" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="134" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O134" s="6"/>
     </row>
-    <row r="135" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="135" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O135" s="6"/>
     </row>
-    <row r="136" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="136" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O136" s="6"/>
     </row>
-    <row r="137" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="137" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O137" s="6"/>
     </row>
-    <row r="138" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="138" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O138" s="6"/>
     </row>
-    <row r="139" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="139" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O139" s="6"/>
     </row>
-    <row r="140" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="140" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O140" s="6"/>
     </row>
-    <row r="141" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="141" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O141" s="6"/>
     </row>
-    <row r="142" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="142" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O142" s="6"/>
     </row>
-    <row r="143" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="143" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O143" s="6"/>
     </row>
-    <row r="144" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="144" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O144" s="6"/>
     </row>
-    <row r="145" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="145" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O145" s="6"/>
     </row>
-    <row r="146" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="146" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O146" s="6"/>
     </row>
-    <row r="147" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="147" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O147" s="6"/>
     </row>
-    <row r="148" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="148" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O148" s="6"/>
     </row>
-    <row r="149" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="149" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O149" s="6"/>
     </row>
-    <row r="150" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="150" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O150" s="6"/>
     </row>
-    <row r="151" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="151" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O151" s="6"/>
     </row>
-    <row r="152" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="152" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O152" s="6"/>
     </row>
-    <row r="153" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="153" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O153" s="6"/>
     </row>
-    <row r="154" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="154" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O154" s="6"/>
     </row>
-    <row r="155" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="155" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O155" s="6"/>
     </row>
-    <row r="156" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="156" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O156" s="6"/>
     </row>
-    <row r="157" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="157" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O157" s="6"/>
     </row>
-    <row r="158" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="158" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O158" s="6"/>
     </row>
-    <row r="159" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="159" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O159" s="6"/>
     </row>
-    <row r="160" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="160" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O160" s="6"/>
     </row>
-    <row r="161" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="161" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O161" s="6"/>
     </row>
-    <row r="162" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="162" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O162" s="6"/>
     </row>
-    <row r="163" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="163" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O163" s="6"/>
     </row>
-    <row r="164" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="164" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O164" s="6"/>
     </row>
-    <row r="165" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="165" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O165" s="6"/>
     </row>
-    <row r="166" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="166" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O166" s="6"/>
     </row>
-    <row r="167" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="167" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O167" s="6"/>
     </row>
-    <row r="168" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="168" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O168" s="6"/>
     </row>
-    <row r="169" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="169" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O169" s="6"/>
     </row>
-    <row r="170" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="170" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O170" s="6"/>
     </row>
-    <row r="171" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="171" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O171" s="6"/>
     </row>
-    <row r="172" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="172" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O172" s="6"/>
     </row>
-    <row r="173" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="173" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O173" s="6"/>
     </row>
-    <row r="174" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="174" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O174" s="6"/>
     </row>
-    <row r="175" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="175" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O175" s="6"/>
     </row>
-    <row r="176" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="176" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O176" s="6"/>
     </row>
-    <row r="177" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="177" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O177" s="6"/>
     </row>
-    <row r="178" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="178" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O178" s="6"/>
     </row>
-    <row r="179" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="179" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O179" s="6"/>
     </row>
-    <row r="180" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="180" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O180" s="6"/>
     </row>
-    <row r="181" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="181" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O181" s="6"/>
     </row>
-    <row r="182" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="182" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O182" s="6"/>
     </row>
-    <row r="183" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="183" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O183" s="6"/>
     </row>
-    <row r="184" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="184" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O184" s="6"/>
     </row>
-    <row r="185" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="185" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O185" s="6"/>
     </row>
-    <row r="186" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="186" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O186" s="6"/>
     </row>
-    <row r="187" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="187" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O187" s="6"/>
     </row>
-    <row r="188" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="188" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O188" s="6"/>
     </row>
-    <row r="189" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="189" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O189" s="6"/>
     </row>
-    <row r="190" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="190" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O190" s="6"/>
     </row>
-    <row r="191" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="191" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O191" s="6"/>
     </row>
-    <row r="192" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="192" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O192" s="6"/>
     </row>
-    <row r="193" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="193" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O193" s="6"/>
     </row>
-    <row r="194" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="194" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O194" s="6"/>
     </row>
-    <row r="195" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="195" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O195" s="6"/>
     </row>
-    <row r="196" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="196" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O196" s="6"/>
     </row>
-    <row r="197" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="197" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O197" s="6"/>
     </row>
-    <row r="198" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="198" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O198" s="6"/>
     </row>
-    <row r="199" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="199" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O199" s="6"/>
     </row>
-    <row r="200" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="200" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O200" s="6"/>
     </row>
-    <row r="201" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="201" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O201" s="6"/>
     </row>
-    <row r="202" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="202" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O202" s="6"/>
     </row>
-    <row r="203" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="203" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O203" s="6"/>
     </row>
-    <row r="204" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="204" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O204" s="6"/>
     </row>
-    <row r="205" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="205" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O205" s="6"/>
     </row>
-    <row r="206" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="206" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O206" s="6"/>
     </row>
-    <row r="207" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="207" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O207" s="6"/>
     </row>
-    <row r="208" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="208" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O208" s="6"/>
     </row>
-    <row r="209" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="209" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O209" s="6"/>
     </row>
-    <row r="210" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="210" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O210" s="6"/>
     </row>
-    <row r="211" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="211" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O211" s="6"/>
     </row>
-    <row r="212" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="212" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O212" s="6"/>
     </row>
-    <row r="213" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="213" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O213" s="6"/>
     </row>
-    <row r="214" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="214" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O214" s="6"/>
     </row>
-    <row r="215" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="215" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O215" s="6"/>
     </row>
-    <row r="216" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="216" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O216" s="6"/>
     </row>
-    <row r="217" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="217" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O217" s="6"/>
     </row>
-    <row r="218" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="218" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O218" s="6"/>
     </row>
-    <row r="219" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="219" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O219" s="6"/>
     </row>
-    <row r="220" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="220" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O220" s="6"/>
     </row>
-    <row r="221" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="221" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O221" s="6"/>
     </row>
-    <row r="222" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="222" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O222" s="6"/>
     </row>
-    <row r="223" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="223" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O223" s="6"/>
     </row>
-    <row r="224" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="224" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O224" s="6"/>
     </row>
-    <row r="225" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="225" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O225" s="6"/>
     </row>
-    <row r="226" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="226" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O226" s="6"/>
     </row>
-    <row r="227" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="227" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O227" s="6"/>
     </row>
-    <row r="228" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="228" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O228" s="6"/>
     </row>
-    <row r="229" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="229" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O229" s="6"/>
     </row>
-    <row r="230" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="230" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O230" s="6"/>
     </row>
-    <row r="231" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="231" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O231" s="6"/>
     </row>
-    <row r="232" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="232" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O232" s="6"/>
     </row>
-    <row r="233" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="233" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O233" s="6"/>
     </row>
-    <row r="234" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="234" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O234" s="6"/>
     </row>
-    <row r="235" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="235" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O235" s="6"/>
     </row>
-    <row r="236" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="236" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O236" s="6"/>
     </row>
-    <row r="237" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="237" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O237" s="6"/>
     </row>
-    <row r="238" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="238" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O238" s="6"/>
     </row>
-    <row r="239" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="239" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O239" s="6"/>
     </row>
-    <row r="240" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="240" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O240" s="6"/>
     </row>
-    <row r="241" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="241" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O241" s="6"/>
     </row>
-    <row r="242" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="242" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O242" s="6"/>
     </row>
-    <row r="243" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="243" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O243" s="6"/>
     </row>
-    <row r="244" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="244" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O244" s="6"/>
     </row>
-    <row r="245" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="245" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O245" s="6"/>
     </row>
-    <row r="246" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="246" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O246" s="6"/>
     </row>
-    <row r="247" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="247" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O247" s="6"/>
     </row>
-    <row r="248" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="248" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O248" s="6"/>
     </row>
-    <row r="249" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="249" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O249" s="6"/>
     </row>
-    <row r="250" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="250" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O250" s="6"/>
     </row>
-    <row r="251" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="251" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O251" s="6"/>
     </row>
-    <row r="252" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="252" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O252" s="6"/>
     </row>
-    <row r="253" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="253" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O253" s="6"/>
     </row>
-    <row r="254" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="254" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O254" s="6"/>
     </row>
-    <row r="255" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="255" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O255" s="6"/>
     </row>
-    <row r="256" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="256" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O256" s="6"/>
     </row>
-    <row r="257" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="257" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O257" s="6"/>
     </row>
-    <row r="258" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="258" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O258" s="6"/>
     </row>
-    <row r="259" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="259" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O259" s="6"/>
     </row>
-    <row r="260" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="260" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O260" s="6"/>
     </row>
-    <row r="261" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="261" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O261" s="6"/>
     </row>
-    <row r="262" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="262" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O262" s="6"/>
     </row>
-    <row r="263" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="263" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O263" s="6"/>
     </row>
-    <row r="264" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="264" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O264" s="6"/>
     </row>
-    <row r="265" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="265" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O265" s="6"/>
     </row>
-    <row r="266" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="266" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O266" s="6"/>
     </row>
-    <row r="267" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="267" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O267" s="6"/>
     </row>
-    <row r="268" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="268" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O268" s="6"/>
     </row>
-    <row r="269" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="269" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O269" s="6"/>
     </row>
-    <row r="270" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="270" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O270" s="6"/>
     </row>
-    <row r="271" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="271" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O271" s="6"/>
     </row>
-    <row r="272" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="272" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O272" s="6"/>
     </row>
-    <row r="273" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="273" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O273" s="6"/>
     </row>
-    <row r="274" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="274" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O274" s="6"/>
     </row>
-    <row r="275" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="275" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O275" s="6"/>
     </row>
-    <row r="276" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="276" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O276" s="6"/>
     </row>
-    <row r="277" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="277" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O277" s="6"/>
     </row>
-    <row r="278" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="278" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O278" s="6"/>
     </row>
-    <row r="279" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="279" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O279" s="6"/>
     </row>
-    <row r="280" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="280" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O280" s="6"/>
     </row>
-    <row r="281" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="281" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O281" s="6"/>
     </row>
-    <row r="282" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="282" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O282" s="6"/>
     </row>
-    <row r="283" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="283" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O283" s="6"/>
     </row>
-    <row r="284" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="284" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O284" s="6"/>
     </row>
-    <row r="285" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="285" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O285" s="6"/>
     </row>
-    <row r="286" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="286" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O286" s="6"/>
     </row>
-    <row r="287" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="287" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O287" s="6"/>
     </row>
-    <row r="288" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="288" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O288" s="6"/>
     </row>
-    <row r="289" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="289" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O289" s="6"/>
     </row>
-    <row r="290" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="290" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O290" s="6"/>
     </row>
-    <row r="291" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="291" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O291" s="6"/>
     </row>
-    <row r="292" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="292" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O292" s="6"/>
     </row>
-    <row r="293" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="293" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O293" s="6"/>
     </row>
-    <row r="294" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="294" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O294" s="6"/>
     </row>
-    <row r="295" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="295" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O295" s="6"/>
     </row>
-    <row r="296" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="296" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O296" s="6"/>
     </row>
-    <row r="297" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="297" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O297" s="6"/>
     </row>
-    <row r="298" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="298" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O298" s="6"/>
     </row>
-    <row r="299" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="299" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O299" s="6"/>
     </row>
-    <row r="300" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="300" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O300" s="6"/>
     </row>
-    <row r="301" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="301" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O301" s="6"/>
     </row>
-    <row r="302" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="302" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O302" s="6"/>
     </row>
-    <row r="303" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="303" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O303" s="6"/>
     </row>
-    <row r="304" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="304" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O304" s="6"/>
     </row>
-    <row r="305" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="305" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O305" s="6"/>
     </row>
-    <row r="306" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="306" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O306" s="6"/>
     </row>
-    <row r="307" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="307" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O307" s="6"/>
     </row>
-    <row r="308" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="308" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O308" s="6"/>
     </row>
-    <row r="309" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="309" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O309" s="6"/>
     </row>
-    <row r="310" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="310" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O310" s="6"/>
     </row>
-    <row r="311" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="311" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O311" s="6"/>
     </row>
-    <row r="312" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="312" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O312" s="6"/>
     </row>
-    <row r="313" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="313" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O313" s="6"/>
     </row>
-    <row r="314" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="314" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O314" s="6"/>
     </row>
-    <row r="315" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="315" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O315" s="6"/>
     </row>
-    <row r="316" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="316" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O316" s="6"/>
     </row>
-    <row r="317" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="317" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O317" s="6"/>
     </row>
-    <row r="318" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="318" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O318" s="6"/>
     </row>
-    <row r="319" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="319" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O319" s="6"/>
     </row>
-    <row r="320" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="320" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O320" s="6"/>
     </row>
-    <row r="321" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="321" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O321" s="6"/>
     </row>
-    <row r="322" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="322" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O322" s="6"/>
     </row>
-    <row r="323" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="323" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O323" s="6"/>
     </row>
-    <row r="324" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="324" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O324" s="6"/>
     </row>
-    <row r="325" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="325" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O325" s="6"/>
     </row>
-    <row r="326" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="326" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O326" s="6"/>
     </row>
-    <row r="327" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="327" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O327" s="6"/>
     </row>
-    <row r="328" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="328" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O328" s="6"/>
     </row>
-    <row r="329" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="329" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O329" s="6"/>
     </row>
-    <row r="330" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="330" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O330" s="6"/>
     </row>
-    <row r="331" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="331" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O331" s="6"/>
     </row>
-    <row r="332" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="332" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O332" s="6"/>
     </row>
-    <row r="333" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="333" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O333" s="6"/>
     </row>
-    <row r="334" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="334" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O334" s="6"/>
     </row>
-    <row r="335" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="335" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O335" s="6"/>
     </row>
-    <row r="336" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="336" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O336" s="6"/>
     </row>
-    <row r="337" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="337" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O337" s="6"/>
     </row>
-    <row r="338" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="338" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O338" s="6"/>
     </row>
-    <row r="339" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="339" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O339" s="6"/>
     </row>
-    <row r="340" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="340" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O340" s="6"/>
     </row>
-    <row r="341" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="341" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O341" s="6"/>
     </row>
-    <row r="342" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="342" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O342" s="6"/>
     </row>
-    <row r="343" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="343" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O343" s="6"/>
     </row>
-    <row r="344" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="344" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O344" s="6"/>
     </row>
-    <row r="345" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="345" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O345" s="6"/>
     </row>
-    <row r="346" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="346" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O346" s="6"/>
     </row>
-    <row r="347" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="347" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O347" s="6"/>
     </row>
-    <row r="348" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="348" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O348" s="6"/>
     </row>
-    <row r="349" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="349" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O349" s="6"/>
     </row>
-    <row r="350" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="350" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O350" s="6"/>
     </row>
-    <row r="351" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="351" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O351" s="6"/>
     </row>
-    <row r="352" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="352" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O352" s="6"/>
     </row>
-    <row r="353" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="353" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O353" s="6"/>
     </row>
-    <row r="354" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="354" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O354" s="6"/>
     </row>
-    <row r="355" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="355" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O355" s="6"/>
     </row>
-    <row r="356" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="356" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O356" s="6"/>
     </row>
-    <row r="357" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="357" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O357" s="6"/>
     </row>
-    <row r="358" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="358" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O358" s="6"/>
     </row>
-    <row r="359" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="359" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O359" s="6"/>
     </row>
-    <row r="360" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="360" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O360" s="6"/>
     </row>
-    <row r="361" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="361" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O361" s="6"/>
     </row>
-    <row r="362" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="362" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O362" s="6"/>
     </row>
-    <row r="363" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="363" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O363" s="6"/>
     </row>
-    <row r="364" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="364" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O364" s="6"/>
     </row>
-    <row r="365" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="365" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O365" s="6"/>
     </row>
-    <row r="366" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="366" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O366" s="6"/>
     </row>
-    <row r="367" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="367" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O367" s="6"/>
     </row>
-    <row r="368" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="368" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O368" s="6"/>
     </row>
-    <row r="369" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="369" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O369" s="6"/>
     </row>
-    <row r="370" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="370" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O370" s="6"/>
     </row>
-    <row r="371" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="371" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O371" s="6"/>
     </row>
-    <row r="372" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="372" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O372" s="6"/>
     </row>
-    <row r="373" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="373" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O373" s="6"/>
     </row>
-    <row r="374" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="374" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O374" s="6"/>
     </row>
-    <row r="375" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="375" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O375" s="6"/>
     </row>
-    <row r="376" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="376" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O376" s="6"/>
     </row>
-    <row r="377" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="377" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O377" s="6"/>
     </row>
-    <row r="378" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="378" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O378" s="6"/>
     </row>
-    <row r="379" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="379" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O379" s="6"/>
     </row>
-    <row r="380" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="380" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O380" s="6"/>
     </row>
-    <row r="381" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="381" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O381" s="6"/>
     </row>
-    <row r="382" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="382" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O382" s="6"/>
     </row>
-    <row r="383" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="383" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O383" s="6"/>
     </row>
-    <row r="384" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="384" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O384" s="6"/>
     </row>
-    <row r="385" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="385" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O385" s="6"/>
     </row>
-    <row r="386" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="386" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O386" s="6"/>
     </row>
-    <row r="387" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="387" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O387" s="6"/>
     </row>
-    <row r="388" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="388" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O388" s="6"/>
     </row>
-    <row r="389" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="389" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O389" s="6"/>
     </row>
-    <row r="390" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="390" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O390" s="6"/>
     </row>
-    <row r="391" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="391" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O391" s="6"/>
     </row>
-    <row r="392" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="392" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O392" s="6"/>
     </row>
-    <row r="393" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="393" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O393" s="6"/>
     </row>
-    <row r="394" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="394" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O394" s="6"/>
     </row>
-    <row r="395" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="395" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O395" s="6"/>
     </row>
-    <row r="396" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="396" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O396" s="6"/>
     </row>
-    <row r="397" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="397" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O397" s="6"/>
     </row>
-    <row r="398" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="398" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O398" s="6"/>
     </row>
-    <row r="399" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="399" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O399" s="6"/>
     </row>
-    <row r="400" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="400" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O400" s="6"/>
     </row>
-    <row r="401" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="401" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O401" s="6"/>
     </row>
-    <row r="402" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="402" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O402" s="6"/>
     </row>
-    <row r="403" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="403" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O403" s="6"/>
     </row>
-    <row r="404" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="404" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O404" s="6"/>
     </row>
-    <row r="405" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="405" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O405" s="6"/>
     </row>
-    <row r="406" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="406" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O406" s="6"/>
     </row>
-    <row r="407" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="407" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O407" s="6"/>
     </row>
-    <row r="408" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="408" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O408" s="6"/>
     </row>
-    <row r="409" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="409" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O409" s="6"/>
     </row>
-    <row r="410" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="410" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O410" s="6"/>
     </row>
-    <row r="411" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="411" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O411" s="6"/>
     </row>
-    <row r="412" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="412" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O412" s="6"/>
     </row>
-    <row r="413" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="413" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O413" s="6"/>
     </row>
-    <row r="414" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="414" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O414" s="6"/>
     </row>
-    <row r="415" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="415" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O415" s="6"/>
     </row>
-    <row r="416" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="416" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O416" s="6"/>
     </row>
-    <row r="417" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="417" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O417" s="6"/>
     </row>
-    <row r="418" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="418" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O418" s="6"/>
     </row>
-    <row r="419" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="419" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O419" s="6"/>
     </row>
-    <row r="420" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="420" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O420" s="6"/>
     </row>
-    <row r="421" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="421" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O421" s="6"/>
     </row>
-    <row r="422" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="422" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O422" s="6"/>
     </row>
-    <row r="423" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="423" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O423" s="6"/>
     </row>
-    <row r="424" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="424" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O424" s="6"/>
     </row>
-    <row r="425" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="425" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O425" s="6"/>
     </row>
-    <row r="426" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="426" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O426" s="6"/>
     </row>
-    <row r="427" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="427" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O427" s="6"/>
     </row>
-    <row r="428" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="428" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O428" s="6"/>
     </row>
-    <row r="429" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="429" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O429" s="6"/>
     </row>
-    <row r="430" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="430" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O430" s="6"/>
     </row>
-    <row r="431" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="431" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O431" s="6"/>
     </row>
-    <row r="432" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="432" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O432" s="6"/>
     </row>
-    <row r="433" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="433" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O433" s="6"/>
     </row>
   </sheetData>

--- a/아이템 도감.xlsx
+++ b/아이템 도감.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hcw97\Desktop\CapstoneProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\CapstoneProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD7D294-B879-4F37-A27E-110878FD21E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47933F88-6803-4CDF-AC2A-3C2444CD7B2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{AEFF7BDA-CB51-4C25-A75C-46A97EA8EBD6}"/>
+    <workbookView xWindow="17580" yWindow="2370" windowWidth="20535" windowHeight="18045" xr2:uid="{AEFF7BDA-CB51-4C25-A75C-46A97EA8EBD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="272">
   <si>
     <t>item_id</t>
   </si>
@@ -894,6 +894,45 @@
   </si>
   <si>
     <t>U_Luxury_Bag</t>
+  </si>
+  <si>
+    <t>Etc_balloon</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc_trap</t>
+  </si>
+  <si>
+    <t>Etc_bananapeel</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc_cobweb</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc_memo</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc_oldsocks</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc_pail</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc_piggybank</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc_slime</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc_vuvuzela</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1164,9 +1203,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1204,7 +1243,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1310,7 +1349,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1452,7 +1491,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1461,27 +1500,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176CEBE0-28C6-4629-A760-C52146228B7D}">
   <dimension ref="A1:Q433"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12.875" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="18.08203125" customWidth="1"/>
+    <col min="3" max="3" width="18.125" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" customWidth="1"/>
-    <col min="6" max="6" width="21.08203125" customWidth="1"/>
-    <col min="7" max="8" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.375" customWidth="1"/>
+    <col min="6" max="6" width="21.125" customWidth="1"/>
+    <col min="7" max="8" width="14.875" customWidth="1"/>
     <col min="9" max="9" width="14.25" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="15.58203125" customWidth="1"/>
-    <col min="12" max="12" width="19.08203125" customWidth="1"/>
+    <col min="10" max="10" width="12.875" customWidth="1"/>
+    <col min="11" max="11" width="15.625" customWidth="1"/>
+    <col min="12" max="12" width="19.125" customWidth="1"/>
     <col min="13" max="13" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="54.58203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="35.08203125" customWidth="1"/>
+    <col min="14" max="14" width="54.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="35.125" customWidth="1"/>
     <col min="16" max="16" width="56.25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="59.58203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="59.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1531,7 +1570,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1581,7 +1620,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1629,7 +1668,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1677,7 +1716,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1725,7 +1764,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1775,7 +1814,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1823,7 +1862,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1871,7 +1910,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1919,7 +1958,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1969,7 +2008,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2017,7 +2056,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2065,7 +2104,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2113,7 +2152,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2161,7 +2200,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2211,7 +2250,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2261,7 +2300,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
         <v>16</v>
       </c>
@@ -2311,7 +2350,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2361,7 +2400,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2409,7 +2448,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2459,7 +2498,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>20</v>
       </c>
@@ -2509,7 +2548,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>21</v>
       </c>
@@ -2559,7 +2598,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>22</v>
       </c>
@@ -2609,7 +2648,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>23</v>
       </c>
@@ -2659,7 +2698,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>24</v>
       </c>
@@ -2712,7 +2751,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>25</v>
       </c>
@@ -2765,7 +2804,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26</v>
       </c>
@@ -2815,7 +2854,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>27</v>
       </c>
@@ -2865,7 +2904,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>28</v>
       </c>
@@ -2915,7 +2954,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>29</v>
       </c>
@@ -2965,7 +3004,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>30</v>
       </c>
@@ -3015,7 +3054,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>31</v>
       </c>
@@ -3065,7 +3104,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>32</v>
       </c>
@@ -3118,7 +3157,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>33</v>
       </c>
@@ -3171,7 +3210,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>34</v>
       </c>
@@ -3221,7 +3260,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>35</v>
       </c>
@@ -3271,7 +3310,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>36</v>
       </c>
@@ -3324,7 +3363,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>37</v>
       </c>
@@ -3374,7 +3413,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>38</v>
       </c>
@@ -3424,7 +3463,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>39</v>
       </c>
@@ -3474,7 +3513,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>40</v>
       </c>
@@ -3524,7 +3563,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>41</v>
       </c>
@@ -3577,7 +3616,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>42</v>
       </c>
@@ -3627,7 +3666,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>43</v>
       </c>
@@ -3677,7 +3716,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>44</v>
       </c>
@@ -3727,7 +3766,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>45</v>
       </c>
@@ -3777,10 +3816,10 @@
         <v>146</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="O51" s="6"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>46</v>
       </c>
@@ -3823,7 +3862,9 @@
       <c r="N52" t="b">
         <v>1</v>
       </c>
-      <c r="O52" s="6"/>
+      <c r="O52" s="6" t="s">
+        <v>262</v>
+      </c>
       <c r="P52" t="s">
         <v>147</v>
       </c>
@@ -3831,7 +3872,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>47</v>
       </c>
@@ -3874,7 +3915,9 @@
       <c r="N53" t="b">
         <v>1</v>
       </c>
-      <c r="O53" s="6"/>
+      <c r="O53" s="6" t="s">
+        <v>271</v>
+      </c>
       <c r="P53" t="s">
         <v>154</v>
       </c>
@@ -3882,7 +3925,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>48</v>
       </c>
@@ -3925,7 +3968,9 @@
       <c r="N54" t="b">
         <v>1</v>
       </c>
-      <c r="O54" s="6"/>
+      <c r="O54" s="6" t="s">
+        <v>268</v>
+      </c>
       <c r="P54" t="s">
         <v>155</v>
       </c>
@@ -3933,7 +3978,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>49</v>
       </c>
@@ -3976,7 +4021,9 @@
       <c r="N55" t="b">
         <v>1</v>
       </c>
-      <c r="O55" s="6"/>
+      <c r="O55" s="6" t="s">
+        <v>264</v>
+      </c>
       <c r="P55" t="s">
         <v>156</v>
       </c>
@@ -3984,7 +4031,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>50</v>
       </c>
@@ -4027,12 +4074,14 @@
       <c r="N56" t="b">
         <v>1</v>
       </c>
-      <c r="O56" s="6"/>
+      <c r="O56" s="6" t="s">
+        <v>267</v>
+      </c>
       <c r="P56" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>51</v>
       </c>
@@ -4075,12 +4124,14 @@
       <c r="N57" t="b">
         <v>1</v>
       </c>
-      <c r="O57" s="6"/>
+      <c r="O57" s="6" t="s">
+        <v>270</v>
+      </c>
       <c r="P57" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>52</v>
       </c>
@@ -4123,12 +4174,14 @@
       <c r="N58" t="b">
         <v>1</v>
       </c>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6" t="s">
+        <v>269</v>
+      </c>
       <c r="P58" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>53</v>
       </c>
@@ -4171,7 +4224,9 @@
       <c r="N59" t="b">
         <v>1</v>
       </c>
-      <c r="O59" s="6"/>
+      <c r="O59" s="6" t="s">
+        <v>266</v>
+      </c>
       <c r="P59" t="s">
         <v>160</v>
       </c>
@@ -4179,7 +4234,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>54</v>
       </c>
@@ -4222,7 +4277,9 @@
       <c r="N60" t="b">
         <v>1</v>
       </c>
-      <c r="O60" s="6"/>
+      <c r="O60" s="6" t="s">
+        <v>265</v>
+      </c>
       <c r="P60" t="s">
         <v>161</v>
       </c>
@@ -4230,7 +4287,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>55</v>
       </c>
@@ -4273,7 +4330,9 @@
       <c r="N61" t="b">
         <v>1</v>
       </c>
-      <c r="O61" s="6"/>
+      <c r="O61" s="6" t="s">
+        <v>263</v>
+      </c>
       <c r="P61" s="9" t="s">
         <v>162</v>
       </c>
@@ -4281,10 +4340,10 @@
         <v>163</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="O62" s="6"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>56</v>
       </c>
@@ -4328,7 +4387,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>57</v>
       </c>
@@ -4372,7 +4431,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>58</v>
       </c>
@@ -4416,7 +4475,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>59</v>
       </c>
@@ -4460,7 +4519,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>60</v>
       </c>
@@ -4504,7 +4563,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>61</v>
       </c>
@@ -4548,7 +4607,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>62</v>
       </c>
@@ -4592,7 +4651,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>63</v>
       </c>
@@ -4636,7 +4695,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>64</v>
       </c>
@@ -4680,7 +4739,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>65</v>
       </c>
@@ -4724,7 +4783,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>66</v>
       </c>
@@ -4768,7 +4827,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>67</v>
       </c>
@@ -4809,7 +4868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>68</v>
       </c>
@@ -4853,7 +4912,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>69</v>
       </c>
@@ -4897,7 +4956,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>70</v>
       </c>
@@ -4941,7 +5000,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>71</v>
       </c>
@@ -4985,7 +5044,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>72</v>
       </c>
@@ -5029,7 +5088,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>73</v>
       </c>
@@ -5073,7 +5132,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>74</v>
       </c>
@@ -5117,7 +5176,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>75</v>
       </c>
@@ -5161,7 +5220,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>76</v>
       </c>
@@ -5205,7 +5264,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>77</v>
       </c>
@@ -5249,7 +5308,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>78</v>
       </c>
@@ -5293,7 +5352,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>79</v>
       </c>
@@ -5337,7 +5396,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>80</v>
       </c>
@@ -5381,7 +5440,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>81</v>
       </c>
@@ -5425,7 +5484,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>82</v>
       </c>
@@ -5469,7 +5528,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>83</v>
       </c>
@@ -5513,7 +5572,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>84</v>
       </c>
@@ -5557,7 +5616,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>85</v>
       </c>
@@ -5601,7 +5660,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>86</v>
       </c>
@@ -5645,7 +5704,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>87</v>
       </c>
@@ -5689,7 +5748,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>88</v>
       </c>
@@ -5733,7 +5792,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>89</v>
       </c>
@@ -5777,7 +5836,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>90</v>
       </c>
@@ -5821,7 +5880,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>91</v>
       </c>
@@ -5865,7 +5924,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>92</v>
       </c>
@@ -5909,7 +5968,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>93</v>
       </c>
@@ -5951,7 +6010,7 @@
       </c>
       <c r="O100" s="12"/>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>94</v>
       </c>
@@ -5993,7 +6052,7 @@
       </c>
       <c r="O101" s="12"/>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>95</v>
       </c>
@@ -6035,7 +6094,7 @@
       </c>
       <c r="O102" s="12"/>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>96</v>
       </c>
@@ -6077,7 +6136,7 @@
       </c>
       <c r="O103" s="12"/>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>97</v>
       </c>
@@ -6119,7 +6178,7 @@
       </c>
       <c r="O104" s="12"/>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>98</v>
       </c>
@@ -6161,7 +6220,7 @@
       </c>
       <c r="O105" s="12"/>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>99</v>
       </c>
@@ -6203,7 +6262,7 @@
       </c>
       <c r="O106" s="12"/>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>100</v>
       </c>
@@ -6245,7 +6304,7 @@
       </c>
       <c r="O107" s="12"/>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>101</v>
       </c>
@@ -6287,7 +6346,7 @@
       </c>
       <c r="O108" s="12"/>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>102</v>
       </c>
@@ -6329,7 +6388,7 @@
       </c>
       <c r="O109" s="12"/>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>103</v>
       </c>
@@ -6371,7 +6430,7 @@
       </c>
       <c r="O110" s="12"/>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>104</v>
       </c>
@@ -6413,7 +6472,7 @@
       </c>
       <c r="O111" s="12"/>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>105</v>
       </c>
@@ -6455,7 +6514,7 @@
       </c>
       <c r="O112" s="12"/>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>106</v>
       </c>
@@ -6497,7 +6556,7 @@
       </c>
       <c r="O113" s="12"/>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>107</v>
       </c>
@@ -6539,7 +6598,7 @@
       </c>
       <c r="O114" s="12"/>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>108</v>
       </c>
@@ -6581,7 +6640,7 @@
       </c>
       <c r="O115" s="12"/>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>109</v>
       </c>
@@ -6623,955 +6682,955 @@
       </c>
       <c r="O116" s="12"/>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O117" s="6"/>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O118" s="6"/>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O119" s="6"/>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O120" s="6"/>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O121" s="6"/>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O122" s="6"/>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O123" s="6"/>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O124" s="6"/>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O125" s="6"/>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O126" s="6"/>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O127" s="6"/>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O128" s="6"/>
     </row>
-    <row r="129" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="129" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O129" s="6"/>
     </row>
-    <row r="130" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="130" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O130" s="6"/>
     </row>
-    <row r="131" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="131" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O131" s="6"/>
     </row>
-    <row r="132" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="132" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O132" s="6"/>
     </row>
-    <row r="133" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="133" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O133" s="6"/>
     </row>
-    <row r="134" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="134" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O134" s="6"/>
     </row>
-    <row r="135" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="135" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O135" s="6"/>
     </row>
-    <row r="136" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="136" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O136" s="6"/>
     </row>
-    <row r="137" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="137" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O137" s="6"/>
     </row>
-    <row r="138" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="138" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O138" s="6"/>
     </row>
-    <row r="139" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="139" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O139" s="6"/>
     </row>
-    <row r="140" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="140" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O140" s="6"/>
     </row>
-    <row r="141" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="141" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O141" s="6"/>
     </row>
-    <row r="142" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="142" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O142" s="6"/>
     </row>
-    <row r="143" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="143" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O143" s="6"/>
     </row>
-    <row r="144" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="144" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O144" s="6"/>
     </row>
-    <row r="145" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="145" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O145" s="6"/>
     </row>
-    <row r="146" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="146" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O146" s="6"/>
     </row>
-    <row r="147" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="147" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O147" s="6"/>
     </row>
-    <row r="148" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="148" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O148" s="6"/>
     </row>
-    <row r="149" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="149" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O149" s="6"/>
     </row>
-    <row r="150" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="150" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O150" s="6"/>
     </row>
-    <row r="151" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="151" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O151" s="6"/>
     </row>
-    <row r="152" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="152" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O152" s="6"/>
     </row>
-    <row r="153" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="153" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O153" s="6"/>
     </row>
-    <row r="154" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="154" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O154" s="6"/>
     </row>
-    <row r="155" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="155" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O155" s="6"/>
     </row>
-    <row r="156" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="156" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O156" s="6"/>
     </row>
-    <row r="157" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="157" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O157" s="6"/>
     </row>
-    <row r="158" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="158" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O158" s="6"/>
     </row>
-    <row r="159" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="159" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O159" s="6"/>
     </row>
-    <row r="160" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="160" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O160" s="6"/>
     </row>
-    <row r="161" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="161" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O161" s="6"/>
     </row>
-    <row r="162" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="162" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O162" s="6"/>
     </row>
-    <row r="163" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="163" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O163" s="6"/>
     </row>
-    <row r="164" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="164" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O164" s="6"/>
     </row>
-    <row r="165" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="165" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O165" s="6"/>
     </row>
-    <row r="166" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="166" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O166" s="6"/>
     </row>
-    <row r="167" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="167" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O167" s="6"/>
     </row>
-    <row r="168" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="168" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O168" s="6"/>
     </row>
-    <row r="169" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="169" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O169" s="6"/>
     </row>
-    <row r="170" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="170" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O170" s="6"/>
     </row>
-    <row r="171" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="171" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O171" s="6"/>
     </row>
-    <row r="172" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="172" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O172" s="6"/>
     </row>
-    <row r="173" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="173" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O173" s="6"/>
     </row>
-    <row r="174" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="174" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O174" s="6"/>
     </row>
-    <row r="175" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="175" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O175" s="6"/>
     </row>
-    <row r="176" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="176" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O176" s="6"/>
     </row>
-    <row r="177" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="177" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O177" s="6"/>
     </row>
-    <row r="178" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="178" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O178" s="6"/>
     </row>
-    <row r="179" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="179" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O179" s="6"/>
     </row>
-    <row r="180" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="180" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O180" s="6"/>
     </row>
-    <row r="181" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="181" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O181" s="6"/>
     </row>
-    <row r="182" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="182" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O182" s="6"/>
     </row>
-    <row r="183" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="183" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O183" s="6"/>
     </row>
-    <row r="184" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="184" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O184" s="6"/>
     </row>
-    <row r="185" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="185" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O185" s="6"/>
     </row>
-    <row r="186" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="186" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O186" s="6"/>
     </row>
-    <row r="187" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="187" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O187" s="6"/>
     </row>
-    <row r="188" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="188" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O188" s="6"/>
     </row>
-    <row r="189" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="189" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O189" s="6"/>
     </row>
-    <row r="190" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="190" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O190" s="6"/>
     </row>
-    <row r="191" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="191" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O191" s="6"/>
     </row>
-    <row r="192" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="192" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O192" s="6"/>
     </row>
-    <row r="193" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="193" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O193" s="6"/>
     </row>
-    <row r="194" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="194" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O194" s="6"/>
     </row>
-    <row r="195" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="195" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O195" s="6"/>
     </row>
-    <row r="196" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="196" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O196" s="6"/>
     </row>
-    <row r="197" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="197" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O197" s="6"/>
     </row>
-    <row r="198" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="198" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O198" s="6"/>
     </row>
-    <row r="199" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="199" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O199" s="6"/>
     </row>
-    <row r="200" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="200" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O200" s="6"/>
     </row>
-    <row r="201" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="201" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O201" s="6"/>
     </row>
-    <row r="202" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="202" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O202" s="6"/>
     </row>
-    <row r="203" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="203" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O203" s="6"/>
     </row>
-    <row r="204" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="204" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O204" s="6"/>
     </row>
-    <row r="205" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="205" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O205" s="6"/>
     </row>
-    <row r="206" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="206" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O206" s="6"/>
     </row>
-    <row r="207" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="207" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O207" s="6"/>
     </row>
-    <row r="208" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="208" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O208" s="6"/>
     </row>
-    <row r="209" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="209" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O209" s="6"/>
     </row>
-    <row r="210" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="210" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O210" s="6"/>
     </row>
-    <row r="211" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="211" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O211" s="6"/>
     </row>
-    <row r="212" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="212" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O212" s="6"/>
     </row>
-    <row r="213" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="213" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O213" s="6"/>
     </row>
-    <row r="214" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="214" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O214" s="6"/>
     </row>
-    <row r="215" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="215" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O215" s="6"/>
     </row>
-    <row r="216" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="216" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O216" s="6"/>
     </row>
-    <row r="217" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="217" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O217" s="6"/>
     </row>
-    <row r="218" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="218" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O218" s="6"/>
     </row>
-    <row r="219" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="219" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O219" s="6"/>
     </row>
-    <row r="220" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="220" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O220" s="6"/>
     </row>
-    <row r="221" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="221" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O221" s="6"/>
     </row>
-    <row r="222" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="222" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O222" s="6"/>
     </row>
-    <row r="223" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="223" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O223" s="6"/>
     </row>
-    <row r="224" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="224" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O224" s="6"/>
     </row>
-    <row r="225" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="225" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O225" s="6"/>
     </row>
-    <row r="226" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="226" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O226" s="6"/>
     </row>
-    <row r="227" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="227" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O227" s="6"/>
     </row>
-    <row r="228" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="228" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O228" s="6"/>
     </row>
-    <row r="229" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="229" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O229" s="6"/>
     </row>
-    <row r="230" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="230" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O230" s="6"/>
     </row>
-    <row r="231" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="231" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O231" s="6"/>
     </row>
-    <row r="232" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="232" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O232" s="6"/>
     </row>
-    <row r="233" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="233" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O233" s="6"/>
     </row>
-    <row r="234" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="234" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O234" s="6"/>
     </row>
-    <row r="235" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="235" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O235" s="6"/>
     </row>
-    <row r="236" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="236" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O236" s="6"/>
     </row>
-    <row r="237" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="237" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O237" s="6"/>
     </row>
-    <row r="238" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="238" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O238" s="6"/>
     </row>
-    <row r="239" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="239" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O239" s="6"/>
     </row>
-    <row r="240" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="240" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O240" s="6"/>
     </row>
-    <row r="241" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="241" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O241" s="6"/>
     </row>
-    <row r="242" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="242" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O242" s="6"/>
     </row>
-    <row r="243" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="243" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O243" s="6"/>
     </row>
-    <row r="244" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="244" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O244" s="6"/>
     </row>
-    <row r="245" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="245" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O245" s="6"/>
     </row>
-    <row r="246" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="246" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O246" s="6"/>
     </row>
-    <row r="247" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="247" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O247" s="6"/>
     </row>
-    <row r="248" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="248" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O248" s="6"/>
     </row>
-    <row r="249" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="249" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O249" s="6"/>
     </row>
-    <row r="250" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="250" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O250" s="6"/>
     </row>
-    <row r="251" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="251" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O251" s="6"/>
     </row>
-    <row r="252" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="252" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O252" s="6"/>
     </row>
-    <row r="253" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="253" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O253" s="6"/>
     </row>
-    <row r="254" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="254" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O254" s="6"/>
     </row>
-    <row r="255" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="255" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O255" s="6"/>
     </row>
-    <row r="256" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="256" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O256" s="6"/>
     </row>
-    <row r="257" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="257" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O257" s="6"/>
     </row>
-    <row r="258" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="258" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O258" s="6"/>
     </row>
-    <row r="259" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="259" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O259" s="6"/>
     </row>
-    <row r="260" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="260" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O260" s="6"/>
     </row>
-    <row r="261" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="261" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O261" s="6"/>
     </row>
-    <row r="262" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="262" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O262" s="6"/>
     </row>
-    <row r="263" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="263" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O263" s="6"/>
     </row>
-    <row r="264" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="264" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O264" s="6"/>
     </row>
-    <row r="265" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="265" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O265" s="6"/>
     </row>
-    <row r="266" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="266" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O266" s="6"/>
     </row>
-    <row r="267" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="267" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O267" s="6"/>
     </row>
-    <row r="268" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="268" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O268" s="6"/>
     </row>
-    <row r="269" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="269" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O269" s="6"/>
     </row>
-    <row r="270" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="270" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O270" s="6"/>
     </row>
-    <row r="271" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="271" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O271" s="6"/>
     </row>
-    <row r="272" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="272" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O272" s="6"/>
     </row>
-    <row r="273" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="273" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O273" s="6"/>
     </row>
-    <row r="274" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="274" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O274" s="6"/>
     </row>
-    <row r="275" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="275" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O275" s="6"/>
     </row>
-    <row r="276" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="276" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O276" s="6"/>
     </row>
-    <row r="277" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="277" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O277" s="6"/>
     </row>
-    <row r="278" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="278" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O278" s="6"/>
     </row>
-    <row r="279" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="279" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O279" s="6"/>
     </row>
-    <row r="280" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="280" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O280" s="6"/>
     </row>
-    <row r="281" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="281" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O281" s="6"/>
     </row>
-    <row r="282" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="282" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O282" s="6"/>
     </row>
-    <row r="283" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="283" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O283" s="6"/>
     </row>
-    <row r="284" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="284" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O284" s="6"/>
     </row>
-    <row r="285" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="285" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O285" s="6"/>
     </row>
-    <row r="286" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="286" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O286" s="6"/>
     </row>
-    <row r="287" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="287" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O287" s="6"/>
     </row>
-    <row r="288" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="288" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O288" s="6"/>
     </row>
-    <row r="289" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="289" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O289" s="6"/>
     </row>
-    <row r="290" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="290" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O290" s="6"/>
     </row>
-    <row r="291" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="291" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O291" s="6"/>
     </row>
-    <row r="292" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="292" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O292" s="6"/>
     </row>
-    <row r="293" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="293" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O293" s="6"/>
     </row>
-    <row r="294" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="294" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O294" s="6"/>
     </row>
-    <row r="295" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="295" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O295" s="6"/>
     </row>
-    <row r="296" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="296" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O296" s="6"/>
     </row>
-    <row r="297" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="297" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O297" s="6"/>
     </row>
-    <row r="298" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="298" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O298" s="6"/>
     </row>
-    <row r="299" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="299" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O299" s="6"/>
     </row>
-    <row r="300" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="300" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O300" s="6"/>
     </row>
-    <row r="301" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="301" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O301" s="6"/>
     </row>
-    <row r="302" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="302" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O302" s="6"/>
     </row>
-    <row r="303" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="303" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O303" s="6"/>
     </row>
-    <row r="304" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="304" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O304" s="6"/>
     </row>
-    <row r="305" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="305" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O305" s="6"/>
     </row>
-    <row r="306" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="306" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O306" s="6"/>
     </row>
-    <row r="307" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="307" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O307" s="6"/>
     </row>
-    <row r="308" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="308" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O308" s="6"/>
     </row>
-    <row r="309" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="309" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O309" s="6"/>
     </row>
-    <row r="310" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="310" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O310" s="6"/>
     </row>
-    <row r="311" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="311" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O311" s="6"/>
     </row>
-    <row r="312" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="312" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O312" s="6"/>
     </row>
-    <row r="313" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="313" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O313" s="6"/>
     </row>
-    <row r="314" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="314" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O314" s="6"/>
     </row>
-    <row r="315" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="315" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O315" s="6"/>
     </row>
-    <row r="316" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="316" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O316" s="6"/>
     </row>
-    <row r="317" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="317" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O317" s="6"/>
     </row>
-    <row r="318" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="318" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O318" s="6"/>
     </row>
-    <row r="319" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="319" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O319" s="6"/>
     </row>
-    <row r="320" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="320" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O320" s="6"/>
     </row>
-    <row r="321" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="321" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O321" s="6"/>
     </row>
-    <row r="322" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="322" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O322" s="6"/>
     </row>
-    <row r="323" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="323" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O323" s="6"/>
     </row>
-    <row r="324" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="324" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O324" s="6"/>
     </row>
-    <row r="325" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="325" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O325" s="6"/>
     </row>
-    <row r="326" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="326" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O326" s="6"/>
     </row>
-    <row r="327" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="327" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O327" s="6"/>
     </row>
-    <row r="328" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="328" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O328" s="6"/>
     </row>
-    <row r="329" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="329" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O329" s="6"/>
     </row>
-    <row r="330" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="330" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O330" s="6"/>
     </row>
-    <row r="331" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="331" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O331" s="6"/>
     </row>
-    <row r="332" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="332" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O332" s="6"/>
     </row>
-    <row r="333" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="333" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O333" s="6"/>
     </row>
-    <row r="334" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="334" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O334" s="6"/>
     </row>
-    <row r="335" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="335" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O335" s="6"/>
     </row>
-    <row r="336" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="336" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O336" s="6"/>
     </row>
-    <row r="337" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="337" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O337" s="6"/>
     </row>
-    <row r="338" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="338" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O338" s="6"/>
     </row>
-    <row r="339" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="339" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O339" s="6"/>
     </row>
-    <row r="340" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="340" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O340" s="6"/>
     </row>
-    <row r="341" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="341" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O341" s="6"/>
     </row>
-    <row r="342" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="342" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O342" s="6"/>
     </row>
-    <row r="343" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="343" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O343" s="6"/>
     </row>
-    <row r="344" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="344" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O344" s="6"/>
     </row>
-    <row r="345" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="345" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O345" s="6"/>
     </row>
-    <row r="346" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="346" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O346" s="6"/>
     </row>
-    <row r="347" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="347" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O347" s="6"/>
     </row>
-    <row r="348" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="348" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O348" s="6"/>
     </row>
-    <row r="349" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="349" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O349" s="6"/>
     </row>
-    <row r="350" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="350" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O350" s="6"/>
     </row>
-    <row r="351" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="351" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O351" s="6"/>
     </row>
-    <row r="352" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="352" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O352" s="6"/>
     </row>
-    <row r="353" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="353" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O353" s="6"/>
     </row>
-    <row r="354" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="354" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O354" s="6"/>
     </row>
-    <row r="355" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="355" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O355" s="6"/>
     </row>
-    <row r="356" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="356" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O356" s="6"/>
     </row>
-    <row r="357" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="357" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O357" s="6"/>
     </row>
-    <row r="358" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="358" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O358" s="6"/>
     </row>
-    <row r="359" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="359" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O359" s="6"/>
     </row>
-    <row r="360" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="360" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O360" s="6"/>
     </row>
-    <row r="361" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="361" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O361" s="6"/>
     </row>
-    <row r="362" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="362" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O362" s="6"/>
     </row>
-    <row r="363" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="363" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O363" s="6"/>
     </row>
-    <row r="364" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="364" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O364" s="6"/>
     </row>
-    <row r="365" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="365" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O365" s="6"/>
     </row>
-    <row r="366" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="366" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O366" s="6"/>
     </row>
-    <row r="367" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="367" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O367" s="6"/>
     </row>
-    <row r="368" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="368" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O368" s="6"/>
     </row>
-    <row r="369" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="369" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O369" s="6"/>
     </row>
-    <row r="370" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="370" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O370" s="6"/>
     </row>
-    <row r="371" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="371" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O371" s="6"/>
     </row>
-    <row r="372" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="372" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O372" s="6"/>
     </row>
-    <row r="373" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="373" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O373" s="6"/>
     </row>
-    <row r="374" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="374" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O374" s="6"/>
     </row>
-    <row r="375" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="375" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O375" s="6"/>
     </row>
-    <row r="376" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="376" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O376" s="6"/>
     </row>
-    <row r="377" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="377" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O377" s="6"/>
     </row>
-    <row r="378" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="378" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O378" s="6"/>
     </row>
-    <row r="379" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="379" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O379" s="6"/>
     </row>
-    <row r="380" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="380" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O380" s="6"/>
     </row>
-    <row r="381" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="381" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O381" s="6"/>
     </row>
-    <row r="382" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="382" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O382" s="6"/>
     </row>
-    <row r="383" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="383" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O383" s="6"/>
     </row>
-    <row r="384" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="384" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O384" s="6"/>
     </row>
-    <row r="385" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="385" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O385" s="6"/>
     </row>
-    <row r="386" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="386" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O386" s="6"/>
     </row>
-    <row r="387" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="387" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O387" s="6"/>
     </row>
-    <row r="388" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="388" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O388" s="6"/>
     </row>
-    <row r="389" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="389" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O389" s="6"/>
     </row>
-    <row r="390" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="390" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O390" s="6"/>
     </row>
-    <row r="391" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="391" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O391" s="6"/>
     </row>
-    <row r="392" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="392" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O392" s="6"/>
     </row>
-    <row r="393" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="393" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O393" s="6"/>
     </row>
-    <row r="394" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="394" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O394" s="6"/>
     </row>
-    <row r="395" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="395" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O395" s="6"/>
     </row>
-    <row r="396" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="396" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O396" s="6"/>
     </row>
-    <row r="397" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="397" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O397" s="6"/>
     </row>
-    <row r="398" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="398" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O398" s="6"/>
     </row>
-    <row r="399" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="399" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O399" s="6"/>
     </row>
-    <row r="400" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="400" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O400" s="6"/>
     </row>
-    <row r="401" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="401" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O401" s="6"/>
     </row>
-    <row r="402" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="402" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O402" s="6"/>
     </row>
-    <row r="403" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="403" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O403" s="6"/>
     </row>
-    <row r="404" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="404" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O404" s="6"/>
     </row>
-    <row r="405" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="405" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O405" s="6"/>
     </row>
-    <row r="406" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="406" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O406" s="6"/>
     </row>
-    <row r="407" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="407" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O407" s="6"/>
     </row>
-    <row r="408" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="408" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O408" s="6"/>
     </row>
-    <row r="409" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="409" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O409" s="6"/>
     </row>
-    <row r="410" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="410" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O410" s="6"/>
     </row>
-    <row r="411" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="411" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O411" s="6"/>
     </row>
-    <row r="412" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="412" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O412" s="6"/>
     </row>
-    <row r="413" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="413" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O413" s="6"/>
     </row>
-    <row r="414" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="414" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O414" s="6"/>
     </row>
-    <row r="415" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="415" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O415" s="6"/>
     </row>
-    <row r="416" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="416" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O416" s="6"/>
     </row>
-    <row r="417" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="417" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O417" s="6"/>
     </row>
-    <row r="418" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="418" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O418" s="6"/>
     </row>
-    <row r="419" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="419" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O419" s="6"/>
     </row>
-    <row r="420" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="420" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O420" s="6"/>
     </row>
-    <row r="421" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="421" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O421" s="6"/>
     </row>
-    <row r="422" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="422" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O422" s="6"/>
     </row>
-    <row r="423" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="423" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O423" s="6"/>
     </row>
-    <row r="424" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="424" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O424" s="6"/>
     </row>
-    <row r="425" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="425" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O425" s="6"/>
     </row>
-    <row r="426" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="426" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O426" s="6"/>
     </row>
-    <row r="427" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="427" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O427" s="6"/>
     </row>
-    <row r="428" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="428" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O428" s="6"/>
     </row>
-    <row r="429" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="429" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O429" s="6"/>
     </row>
-    <row r="430" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="430" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O430" s="6"/>
     </row>
-    <row r="431" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="431" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O431" s="6"/>
     </row>
-    <row r="432" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="432" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O432" s="6"/>
     </row>
-    <row r="433" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="433" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O433" s="6"/>
     </row>
   </sheetData>

--- a/아이템 도감.xlsx
+++ b/아이템 도감.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\CapstoneProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hcw97\Desktop\CapstoneProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47933F88-6803-4CDF-AC2A-3C2444CD7B2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1C94CD-DB67-46C0-90A0-CAA85D661E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17580" yWindow="2370" windowWidth="20535" windowHeight="18045" xr2:uid="{AEFF7BDA-CB51-4C25-A75C-46A97EA8EBD6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{AEFF7BDA-CB51-4C25-A75C-46A97EA8EBD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -787,151 +787,152 @@
     <t>C_Rusty_Coin</t>
   </si>
   <si>
+    <t>C_Old_Spoon</t>
+  </si>
+  <si>
+    <t>C_Empty_Bottle</t>
+  </si>
+  <si>
+    <t>C_Seashell</t>
+  </si>
+  <si>
+    <t>C_Scrap_Map</t>
+  </si>
+  <si>
+    <t>C_Wooden_Doll</t>
+  </si>
+  <si>
+    <t>C_Paper_Plane</t>
+  </si>
+  <si>
+    <t>C_Bottle_Cap</t>
+  </si>
+  <si>
+    <t>C_Tennis_Ball</t>
+  </si>
+  <si>
+    <t>C_Broken_Washing_Machine</t>
+  </si>
+  <si>
+    <t>C_Fish_Bone</t>
+  </si>
+  <si>
+    <t>C_Wooden_Button</t>
+  </si>
+  <si>
+    <t>C_Empty_Can</t>
+  </si>
+  <si>
+    <t>C_Brick</t>
+  </si>
+  <si>
+    <t>C_Cracked_Plate</t>
+  </si>
+  <si>
+    <t>C_Old_Boot</t>
+  </si>
+  <si>
+    <t>C_Broken_Clock</t>
+  </si>
+  <si>
+    <t>U_Copper_Ring</t>
+  </si>
+  <si>
+    <t>U_Silk_Handkerchief</t>
+  </si>
+  <si>
+    <t>U_Pearl_Earring</t>
+  </si>
+  <si>
+    <t>U_Brass_Canddlestick</t>
+  </si>
+  <si>
+    <t>U_Ancient_Clay_Tablet</t>
+  </si>
+  <si>
+    <t>U_Bronze_Mirror</t>
+  </si>
+  <si>
+    <t>에메랄드 브로치</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>R_Crystal_Skull</t>
+  </si>
+  <si>
+    <t>R_Emerald_Brooch</t>
+  </si>
+  <si>
+    <t>R_Silver_Ring</t>
+  </si>
+  <si>
+    <t>R_Viking_Helmet</t>
+  </si>
+  <si>
+    <t>U_Amethyst_Shard</t>
+  </si>
+  <si>
+    <t>U_Boxing_Glove</t>
+  </si>
+  <si>
+    <t>U_Car_Key</t>
+  </si>
+  <si>
+    <t>U_Ceramic_Vase</t>
+  </si>
+  <si>
+    <t>U_Frill_Ribbon</t>
+  </si>
+  <si>
+    <t>U_Golden Dice</t>
+  </si>
+  <si>
+    <t>U_Leather_Belt</t>
+  </si>
+  <si>
+    <t>U_Luxury_Bag</t>
+  </si>
+  <si>
+    <t>Etc_balloon</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc_trap</t>
+  </si>
+  <si>
+    <t>Etc_bananapeel</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc_cobweb</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc_memo</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc_oldsocks</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc_pail</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc_piggybank</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc_slime</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc_vuvuzela</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>C_Glass_Marble</t>
-  </si>
-  <si>
-    <t>C_Old_Spoon</t>
-  </si>
-  <si>
-    <t>C_Empty_Bottle</t>
-  </si>
-  <si>
-    <t>C_Seashell</t>
-  </si>
-  <si>
-    <t>C_Scrap_Map</t>
-  </si>
-  <si>
-    <t>C_Wooden_Doll</t>
-  </si>
-  <si>
-    <t>C_Paper_Plane</t>
-  </si>
-  <si>
-    <t>C_Bottle_Cap</t>
-  </si>
-  <si>
-    <t>C_Tennis_Ball</t>
-  </si>
-  <si>
-    <t>C_Broken_Washing_Machine</t>
-  </si>
-  <si>
-    <t>C_Fish_Bone</t>
-  </si>
-  <si>
-    <t>C_Wooden_Button</t>
-  </si>
-  <si>
-    <t>C_Empty_Can</t>
-  </si>
-  <si>
-    <t>C_Brick</t>
-  </si>
-  <si>
-    <t>C_Cracked_Plate</t>
-  </si>
-  <si>
-    <t>C_Old_Boot</t>
-  </si>
-  <si>
-    <t>C_Broken_Clock</t>
-  </si>
-  <si>
-    <t>U_Copper_Ring</t>
-  </si>
-  <si>
-    <t>U_Silk_Handkerchief</t>
-  </si>
-  <si>
-    <t>U_Pearl_Earring</t>
-  </si>
-  <si>
-    <t>U_Brass_Canddlestick</t>
-  </si>
-  <si>
-    <t>U_Ancient_Clay_Tablet</t>
-  </si>
-  <si>
-    <t>U_Bronze_Mirror</t>
-  </si>
-  <si>
-    <t>에메랄드 브로치</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>R_Crystal_Skull</t>
-  </si>
-  <si>
-    <t>R_Emerald_Brooch</t>
-  </si>
-  <si>
-    <t>R_Silver_Ring</t>
-  </si>
-  <si>
-    <t>R_Viking_Helmet</t>
-  </si>
-  <si>
-    <t>U_Amethyst_Shard</t>
-  </si>
-  <si>
-    <t>U_Boxing_Glove</t>
-  </si>
-  <si>
-    <t>U_Car_Key</t>
-  </si>
-  <si>
-    <t>U_Ceramic_Vase</t>
-  </si>
-  <si>
-    <t>U_Frill_Ribbon</t>
-  </si>
-  <si>
-    <t>U_Golden Dice</t>
-  </si>
-  <si>
-    <t>U_Leather_Belt</t>
-  </si>
-  <si>
-    <t>U_Luxury_Bag</t>
-  </si>
-  <si>
-    <t>Etc_balloon</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Etc_trap</t>
-  </si>
-  <si>
-    <t>Etc_bananapeel</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Etc_cobweb</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Etc_memo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Etc_oldsocks</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Etc_pail</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Etc_piggybank</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Etc_slime</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Etc_vuvuzela</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1203,9 +1204,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1243,7 +1244,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1349,7 +1350,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1491,7 +1492,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1500,27 +1501,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176CEBE0-28C6-4629-A760-C52146228B7D}">
   <dimension ref="A1:Q433"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.875" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="18.125" customWidth="1"/>
+    <col min="3" max="3" width="18.08203125" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
-    <col min="5" max="5" width="14.375" customWidth="1"/>
-    <col min="6" max="6" width="21.125" customWidth="1"/>
-    <col min="7" max="8" width="14.875" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" customWidth="1"/>
+    <col min="6" max="6" width="21.08203125" customWidth="1"/>
+    <col min="7" max="8" width="14.83203125" customWidth="1"/>
     <col min="9" max="9" width="14.25" customWidth="1"/>
-    <col min="10" max="10" width="12.875" customWidth="1"/>
-    <col min="11" max="11" width="15.625" customWidth="1"/>
-    <col min="12" max="12" width="19.125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="15.58203125" customWidth="1"/>
+    <col min="12" max="12" width="19.08203125" customWidth="1"/>
     <col min="13" max="13" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="54.625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="35.125" customWidth="1"/>
+    <col min="14" max="14" width="54.58203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="35.08203125" customWidth="1"/>
     <col min="16" max="16" width="56.25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="59.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="59.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1570,7 +1571,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1620,7 +1621,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1668,7 +1669,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1716,7 +1717,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1764,7 +1765,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1814,7 +1815,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1862,7 +1863,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1910,7 +1911,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1958,7 +1959,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2008,7 +2009,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2056,7 +2057,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2104,7 +2105,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2152,7 +2153,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2200,7 +2201,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2250,7 +2251,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2300,7 +2301,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A17" s="13">
         <v>16</v>
       </c>
@@ -2350,7 +2351,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2400,7 +2401,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2448,7 +2449,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2498,7 +2499,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>20</v>
       </c>
@@ -2548,7 +2549,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>21</v>
       </c>
@@ -2598,7 +2599,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>22</v>
       </c>
@@ -2648,7 +2649,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>23</v>
       </c>
@@ -2698,7 +2699,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>24</v>
       </c>
@@ -2751,7 +2752,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>25</v>
       </c>
@@ -2804,7 +2805,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>26</v>
       </c>
@@ -2854,7 +2855,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>27</v>
       </c>
@@ -2904,7 +2905,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>28</v>
       </c>
@@ -2954,7 +2955,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>29</v>
       </c>
@@ -3004,7 +3005,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>30</v>
       </c>
@@ -3054,7 +3055,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>31</v>
       </c>
@@ -3104,7 +3105,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>32</v>
       </c>
@@ -3157,7 +3158,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>33</v>
       </c>
@@ -3210,7 +3211,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>34</v>
       </c>
@@ -3260,7 +3261,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>35</v>
       </c>
@@ -3310,7 +3311,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>36</v>
       </c>
@@ -3363,7 +3364,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>37</v>
       </c>
@@ -3413,7 +3414,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>38</v>
       </c>
@@ -3463,7 +3464,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>39</v>
       </c>
@@ -3513,7 +3514,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>40</v>
       </c>
@@ -3563,7 +3564,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>41</v>
       </c>
@@ -3616,7 +3617,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>42</v>
       </c>
@@ -3666,7 +3667,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>43</v>
       </c>
@@ -3716,7 +3717,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>44</v>
       </c>
@@ -3766,7 +3767,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>45</v>
       </c>
@@ -3816,10 +3817,10 @@
         <v>146</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.45">
       <c r="O51" s="6"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>46</v>
       </c>
@@ -3863,7 +3864,7 @@
         <v>1</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P52" t="s">
         <v>147</v>
@@ -3872,7 +3873,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>47</v>
       </c>
@@ -3916,7 +3917,7 @@
         <v>1</v>
       </c>
       <c r="O53" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P53" t="s">
         <v>154</v>
@@ -3925,7 +3926,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>48</v>
       </c>
@@ -3969,7 +3970,7 @@
         <v>1</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P54" t="s">
         <v>155</v>
@@ -3978,7 +3979,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>49</v>
       </c>
@@ -4022,7 +4023,7 @@
         <v>1</v>
       </c>
       <c r="O55" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P55" t="s">
         <v>156</v>
@@ -4031,7 +4032,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>50</v>
       </c>
@@ -4075,13 +4076,13 @@
         <v>1</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P56" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>51</v>
       </c>
@@ -4125,13 +4126,13 @@
         <v>1</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P57" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>52</v>
       </c>
@@ -4175,13 +4176,13 @@
         <v>1</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P58" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>53</v>
       </c>
@@ -4225,7 +4226,7 @@
         <v>1</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P59" t="s">
         <v>160</v>
@@ -4234,7 +4235,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>54</v>
       </c>
@@ -4278,7 +4279,7 @@
         <v>1</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="P60" t="s">
         <v>161</v>
@@ -4287,7 +4288,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>55</v>
       </c>
@@ -4331,7 +4332,7 @@
         <v>1</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>162</v>
@@ -4340,10 +4341,10 @@
         <v>163</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.45">
       <c r="O62" s="6"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>56</v>
       </c>
@@ -4383,11 +4384,11 @@
       <c r="N63" t="b">
         <v>1</v>
       </c>
-      <c r="O63" t="s">
+      <c r="O63" s="6" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>57</v>
       </c>
@@ -4427,11 +4428,11 @@
       <c r="N64" t="b">
         <v>1</v>
       </c>
-      <c r="O64" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O64" s="6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>58</v>
       </c>
@@ -4471,11 +4472,11 @@
       <c r="N65" t="b">
         <v>1</v>
       </c>
-      <c r="O65" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O65" s="6" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>59</v>
       </c>
@@ -4515,11 +4516,11 @@
       <c r="N66" t="b">
         <v>1</v>
       </c>
-      <c r="O66" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O66" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>60</v>
       </c>
@@ -4559,11 +4560,11 @@
       <c r="N67" t="b">
         <v>1</v>
       </c>
-      <c r="O67" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O67" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>61</v>
       </c>
@@ -4603,11 +4604,11 @@
       <c r="N68" t="b">
         <v>1</v>
       </c>
-      <c r="O68" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O68" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>62</v>
       </c>
@@ -4647,11 +4648,11 @@
       <c r="N69" t="b">
         <v>1</v>
       </c>
-      <c r="O69" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O69" s="6" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>63</v>
       </c>
@@ -4691,11 +4692,11 @@
       <c r="N70" t="b">
         <v>1</v>
       </c>
-      <c r="O70" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O70" s="6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>64</v>
       </c>
@@ -4735,11 +4736,11 @@
       <c r="N71" t="b">
         <v>1</v>
       </c>
-      <c r="O71" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O71" s="6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>65</v>
       </c>
@@ -4779,11 +4780,11 @@
       <c r="N72" t="b">
         <v>1</v>
       </c>
-      <c r="O72" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O72" s="6" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>66</v>
       </c>
@@ -4823,11 +4824,11 @@
       <c r="N73" t="b">
         <v>1</v>
       </c>
-      <c r="O73" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O73" s="6" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>67</v>
       </c>
@@ -4867,8 +4868,9 @@
       <c r="N74" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O74" s="6"/>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>68</v>
       </c>
@@ -4908,11 +4910,11 @@
       <c r="N75" t="b">
         <v>1</v>
       </c>
-      <c r="O75" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O75" s="6" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>69</v>
       </c>
@@ -4952,11 +4954,11 @@
       <c r="N76" t="b">
         <v>1</v>
       </c>
-      <c r="O76" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O76" s="6" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>70</v>
       </c>
@@ -4996,11 +4998,11 @@
       <c r="N77" t="b">
         <v>1</v>
       </c>
-      <c r="O77" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O77" s="6" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>71</v>
       </c>
@@ -5040,11 +5042,11 @@
       <c r="N78" t="b">
         <v>1</v>
       </c>
-      <c r="O78" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O78" s="6" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>72</v>
       </c>
@@ -5084,11 +5086,11 @@
       <c r="N79" t="b">
         <v>1</v>
       </c>
-      <c r="O79" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O79" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>73</v>
       </c>
@@ -5128,11 +5130,11 @@
       <c r="N80" t="b">
         <v>1</v>
       </c>
-      <c r="O80" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O80" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>74</v>
       </c>
@@ -5172,11 +5174,11 @@
       <c r="N81" t="b">
         <v>1</v>
       </c>
-      <c r="O81" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O81" s="6" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>75</v>
       </c>
@@ -5216,11 +5218,11 @@
       <c r="N82" t="b">
         <v>1</v>
       </c>
-      <c r="O82" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O82" s="6" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>76</v>
       </c>
@@ -5260,11 +5262,11 @@
       <c r="N83" t="b">
         <v>1</v>
       </c>
-      <c r="O83" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O83" s="6" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>77</v>
       </c>
@@ -5304,11 +5306,11 @@
       <c r="N84" t="b">
         <v>1</v>
       </c>
-      <c r="O84" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O84" s="6" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>78</v>
       </c>
@@ -5348,11 +5350,11 @@
       <c r="N85" t="b">
         <v>1</v>
       </c>
-      <c r="O85" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O85" s="6" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>79</v>
       </c>
@@ -5392,11 +5394,11 @@
       <c r="N86" t="b">
         <v>1</v>
       </c>
-      <c r="O86" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O86" s="6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>80</v>
       </c>
@@ -5436,11 +5438,11 @@
       <c r="N87" t="b">
         <v>1</v>
       </c>
-      <c r="O87" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O87" s="6" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>81</v>
       </c>
@@ -5480,11 +5482,11 @@
       <c r="N88" t="b">
         <v>1</v>
       </c>
-      <c r="O88" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O88" s="6" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>82</v>
       </c>
@@ -5524,11 +5526,11 @@
       <c r="N89" t="b">
         <v>1</v>
       </c>
-      <c r="O89" s="12" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O89" s="6" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>83</v>
       </c>
@@ -5568,11 +5570,11 @@
       <c r="N90" t="b">
         <v>1</v>
       </c>
-      <c r="O90" s="12" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O90" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>84</v>
       </c>
@@ -5612,11 +5614,11 @@
       <c r="N91" t="b">
         <v>1</v>
       </c>
-      <c r="O91" s="12" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O91" s="6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>85</v>
       </c>
@@ -5656,11 +5658,11 @@
       <c r="N92" t="b">
         <v>1</v>
       </c>
-      <c r="O92" s="12" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O92" s="6" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>86</v>
       </c>
@@ -5700,11 +5702,11 @@
       <c r="N93" t="b">
         <v>1</v>
       </c>
-      <c r="O93" s="12" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O93" s="6" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>87</v>
       </c>
@@ -5744,11 +5746,11 @@
       <c r="N94" t="b">
         <v>1</v>
       </c>
-      <c r="O94" s="12" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O94" s="6" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>88</v>
       </c>
@@ -5788,11 +5790,11 @@
       <c r="N95" t="b">
         <v>1</v>
       </c>
-      <c r="O95" s="12" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O95" s="6" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>89</v>
       </c>
@@ -5832,11 +5834,11 @@
       <c r="N96" t="b">
         <v>1</v>
       </c>
-      <c r="O96" s="12" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O96" s="6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>90</v>
       </c>
@@ -5844,7 +5846,7 @@
         <v>3</v>
       </c>
       <c r="D97" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E97">
         <v>3</v>
@@ -5876,11 +5878,11 @@
       <c r="N97" t="b">
         <v>1</v>
       </c>
-      <c r="O97" s="12" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O97" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>91</v>
       </c>
@@ -5920,11 +5922,11 @@
       <c r="N98" t="b">
         <v>1</v>
       </c>
-      <c r="O98" s="12" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O98" s="6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>92</v>
       </c>
@@ -5964,11 +5966,11 @@
       <c r="N99" t="b">
         <v>1</v>
       </c>
-      <c r="O99" s="12" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O99" s="6" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>93</v>
       </c>
@@ -6008,9 +6010,9 @@
       <c r="N100" t="b">
         <v>1</v>
       </c>
-      <c r="O100" s="12"/>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O100" s="6"/>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>94</v>
       </c>
@@ -6050,9 +6052,9 @@
       <c r="N101" t="b">
         <v>1</v>
       </c>
-      <c r="O101" s="12"/>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O101" s="6"/>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A102">
         <v>95</v>
       </c>
@@ -6092,9 +6094,9 @@
       <c r="N102" t="b">
         <v>1</v>
       </c>
-      <c r="O102" s="12"/>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O102" s="6"/>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A103">
         <v>96</v>
       </c>
@@ -6134,9 +6136,9 @@
       <c r="N103" t="b">
         <v>1</v>
       </c>
-      <c r="O103" s="12"/>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O103" s="6"/>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A104">
         <v>97</v>
       </c>
@@ -6176,9 +6178,9 @@
       <c r="N104" t="b">
         <v>1</v>
       </c>
-      <c r="O104" s="12"/>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O104" s="6"/>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A105">
         <v>98</v>
       </c>
@@ -6218,9 +6220,9 @@
       <c r="N105" t="b">
         <v>1</v>
       </c>
-      <c r="O105" s="12"/>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O105" s="6"/>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A106">
         <v>99</v>
       </c>
@@ -6260,9 +6262,9 @@
       <c r="N106" t="b">
         <v>1</v>
       </c>
-      <c r="O106" s="12"/>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O106" s="6"/>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A107">
         <v>100</v>
       </c>
@@ -6302,9 +6304,9 @@
       <c r="N107" t="b">
         <v>1</v>
       </c>
-      <c r="O107" s="12"/>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O107" s="6"/>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A108">
         <v>101</v>
       </c>
@@ -6344,9 +6346,9 @@
       <c r="N108" t="b">
         <v>1</v>
       </c>
-      <c r="O108" s="12"/>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O108" s="6"/>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A109">
         <v>102</v>
       </c>
@@ -6386,9 +6388,9 @@
       <c r="N109" t="b">
         <v>1</v>
       </c>
-      <c r="O109" s="12"/>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O109" s="6"/>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A110">
         <v>103</v>
       </c>
@@ -6428,9 +6430,9 @@
       <c r="N110" t="b">
         <v>1</v>
       </c>
-      <c r="O110" s="12"/>
-    </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O110" s="6"/>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A111">
         <v>104</v>
       </c>
@@ -6470,9 +6472,9 @@
       <c r="N111" t="b">
         <v>1</v>
       </c>
-      <c r="O111" s="12"/>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O111" s="6"/>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A112">
         <v>105</v>
       </c>
@@ -6512,9 +6514,9 @@
       <c r="N112" t="b">
         <v>1</v>
       </c>
-      <c r="O112" s="12"/>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O112" s="6"/>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A113">
         <v>106</v>
       </c>
@@ -6554,9 +6556,9 @@
       <c r="N113" t="b">
         <v>1</v>
       </c>
-      <c r="O113" s="12"/>
-    </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O113" s="6"/>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A114">
         <v>107</v>
       </c>
@@ -6596,9 +6598,9 @@
       <c r="N114" t="b">
         <v>1</v>
       </c>
-      <c r="O114" s="12"/>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O114" s="6"/>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A115">
         <v>108</v>
       </c>
@@ -6638,9 +6640,9 @@
       <c r="N115" t="b">
         <v>1</v>
       </c>
-      <c r="O115" s="12"/>
-    </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O115" s="6"/>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A116">
         <v>109</v>
       </c>
@@ -6680,957 +6682,957 @@
       <c r="N116" t="b">
         <v>1</v>
       </c>
-      <c r="O116" s="12"/>
-    </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O116" s="6"/>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O117" s="6"/>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O118" s="6"/>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O119" s="6"/>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O120" s="6"/>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O121" s="6"/>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O122" s="6"/>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O123" s="6"/>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O124" s="6"/>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O125" s="6"/>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O126" s="6"/>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O127" s="6"/>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.45">
       <c r="O128" s="6"/>
     </row>
-    <row r="129" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="129" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O129" s="6"/>
     </row>
-    <row r="130" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="130" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O130" s="6"/>
     </row>
-    <row r="131" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="131" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O131" s="6"/>
     </row>
-    <row r="132" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="132" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O132" s="6"/>
     </row>
-    <row r="133" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="133" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O133" s="6"/>
     </row>
-    <row r="134" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="134" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O134" s="6"/>
     </row>
-    <row r="135" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="135" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O135" s="6"/>
     </row>
-    <row r="136" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="136" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O136" s="6"/>
     </row>
-    <row r="137" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="137" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O137" s="6"/>
     </row>
-    <row r="138" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="138" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O138" s="6"/>
     </row>
-    <row r="139" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="139" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O139" s="6"/>
     </row>
-    <row r="140" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="140" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O140" s="6"/>
     </row>
-    <row r="141" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="141" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O141" s="6"/>
     </row>
-    <row r="142" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="142" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O142" s="6"/>
     </row>
-    <row r="143" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="143" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O143" s="6"/>
     </row>
-    <row r="144" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="144" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O144" s="6"/>
     </row>
-    <row r="145" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="145" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O145" s="6"/>
     </row>
-    <row r="146" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="146" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O146" s="6"/>
     </row>
-    <row r="147" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="147" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O147" s="6"/>
     </row>
-    <row r="148" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="148" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O148" s="6"/>
     </row>
-    <row r="149" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="149" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O149" s="6"/>
     </row>
-    <row r="150" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="150" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O150" s="6"/>
     </row>
-    <row r="151" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="151" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O151" s="6"/>
     </row>
-    <row r="152" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="152" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O152" s="6"/>
     </row>
-    <row r="153" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="153" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O153" s="6"/>
     </row>
-    <row r="154" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="154" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O154" s="6"/>
     </row>
-    <row r="155" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="155" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O155" s="6"/>
     </row>
-    <row r="156" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="156" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O156" s="6"/>
     </row>
-    <row r="157" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="157" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O157" s="6"/>
     </row>
-    <row r="158" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="158" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O158" s="6"/>
     </row>
-    <row r="159" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="159" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O159" s="6"/>
     </row>
-    <row r="160" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="160" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O160" s="6"/>
     </row>
-    <row r="161" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="161" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O161" s="6"/>
     </row>
-    <row r="162" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="162" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O162" s="6"/>
     </row>
-    <row r="163" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="163" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O163" s="6"/>
     </row>
-    <row r="164" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="164" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O164" s="6"/>
     </row>
-    <row r="165" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="165" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O165" s="6"/>
     </row>
-    <row r="166" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="166" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O166" s="6"/>
     </row>
-    <row r="167" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="167" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O167" s="6"/>
     </row>
-    <row r="168" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="168" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O168" s="6"/>
     </row>
-    <row r="169" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="169" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O169" s="6"/>
     </row>
-    <row r="170" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="170" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O170" s="6"/>
     </row>
-    <row r="171" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="171" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O171" s="6"/>
     </row>
-    <row r="172" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="172" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O172" s="6"/>
     </row>
-    <row r="173" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="173" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O173" s="6"/>
     </row>
-    <row r="174" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="174" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O174" s="6"/>
     </row>
-    <row r="175" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="175" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O175" s="6"/>
     </row>
-    <row r="176" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="176" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O176" s="6"/>
     </row>
-    <row r="177" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="177" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O177" s="6"/>
     </row>
-    <row r="178" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="178" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O178" s="6"/>
     </row>
-    <row r="179" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="179" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O179" s="6"/>
     </row>
-    <row r="180" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="180" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O180" s="6"/>
     </row>
-    <row r="181" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="181" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O181" s="6"/>
     </row>
-    <row r="182" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="182" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O182" s="6"/>
     </row>
-    <row r="183" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="183" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O183" s="6"/>
     </row>
-    <row r="184" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="184" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O184" s="6"/>
     </row>
-    <row r="185" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="185" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O185" s="6"/>
     </row>
-    <row r="186" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="186" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O186" s="6"/>
     </row>
-    <row r="187" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="187" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O187" s="6"/>
     </row>
-    <row r="188" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="188" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O188" s="6"/>
     </row>
-    <row r="189" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="189" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O189" s="6"/>
     </row>
-    <row r="190" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="190" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O190" s="6"/>
     </row>
-    <row r="191" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="191" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O191" s="6"/>
     </row>
-    <row r="192" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="192" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O192" s="6"/>
     </row>
-    <row r="193" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="193" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O193" s="6"/>
     </row>
-    <row r="194" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="194" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O194" s="6"/>
     </row>
-    <row r="195" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="195" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O195" s="6"/>
     </row>
-    <row r="196" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="196" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O196" s="6"/>
     </row>
-    <row r="197" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="197" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O197" s="6"/>
     </row>
-    <row r="198" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="198" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O198" s="6"/>
     </row>
-    <row r="199" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="199" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O199" s="6"/>
     </row>
-    <row r="200" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="200" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O200" s="6"/>
     </row>
-    <row r="201" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="201" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O201" s="6"/>
     </row>
-    <row r="202" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="202" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O202" s="6"/>
     </row>
-    <row r="203" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="203" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O203" s="6"/>
     </row>
-    <row r="204" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="204" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O204" s="6"/>
     </row>
-    <row r="205" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="205" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O205" s="6"/>
     </row>
-    <row r="206" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="206" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O206" s="6"/>
     </row>
-    <row r="207" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="207" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O207" s="6"/>
     </row>
-    <row r="208" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="208" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O208" s="6"/>
     </row>
-    <row r="209" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="209" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O209" s="6"/>
     </row>
-    <row r="210" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="210" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O210" s="6"/>
     </row>
-    <row r="211" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="211" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O211" s="6"/>
     </row>
-    <row r="212" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="212" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O212" s="6"/>
     </row>
-    <row r="213" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="213" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O213" s="6"/>
     </row>
-    <row r="214" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="214" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O214" s="6"/>
     </row>
-    <row r="215" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="215" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O215" s="6"/>
     </row>
-    <row r="216" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="216" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O216" s="6"/>
     </row>
-    <row r="217" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="217" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O217" s="6"/>
     </row>
-    <row r="218" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="218" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O218" s="6"/>
     </row>
-    <row r="219" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="219" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O219" s="6"/>
     </row>
-    <row r="220" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="220" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O220" s="6"/>
     </row>
-    <row r="221" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="221" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O221" s="6"/>
     </row>
-    <row r="222" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="222" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O222" s="6"/>
     </row>
-    <row r="223" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="223" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O223" s="6"/>
     </row>
-    <row r="224" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="224" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O224" s="6"/>
     </row>
-    <row r="225" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="225" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O225" s="6"/>
     </row>
-    <row r="226" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="226" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O226" s="6"/>
     </row>
-    <row r="227" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="227" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O227" s="6"/>
     </row>
-    <row r="228" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="228" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O228" s="6"/>
     </row>
-    <row r="229" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="229" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O229" s="6"/>
     </row>
-    <row r="230" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="230" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O230" s="6"/>
     </row>
-    <row r="231" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="231" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O231" s="6"/>
     </row>
-    <row r="232" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="232" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O232" s="6"/>
     </row>
-    <row r="233" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="233" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O233" s="6"/>
     </row>
-    <row r="234" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="234" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O234" s="6"/>
     </row>
-    <row r="235" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="235" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O235" s="6"/>
     </row>
-    <row r="236" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="236" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O236" s="6"/>
     </row>
-    <row r="237" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="237" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O237" s="6"/>
     </row>
-    <row r="238" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="238" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O238" s="6"/>
     </row>
-    <row r="239" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="239" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O239" s="6"/>
     </row>
-    <row r="240" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="240" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O240" s="6"/>
     </row>
-    <row r="241" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="241" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O241" s="6"/>
     </row>
-    <row r="242" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="242" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O242" s="6"/>
     </row>
-    <row r="243" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="243" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O243" s="6"/>
     </row>
-    <row r="244" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="244" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O244" s="6"/>
     </row>
-    <row r="245" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="245" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O245" s="6"/>
     </row>
-    <row r="246" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="246" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O246" s="6"/>
     </row>
-    <row r="247" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="247" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O247" s="6"/>
     </row>
-    <row r="248" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="248" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O248" s="6"/>
     </row>
-    <row r="249" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="249" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O249" s="6"/>
     </row>
-    <row r="250" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="250" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O250" s="6"/>
     </row>
-    <row r="251" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="251" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O251" s="6"/>
     </row>
-    <row r="252" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="252" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O252" s="6"/>
     </row>
-    <row r="253" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="253" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O253" s="6"/>
     </row>
-    <row r="254" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="254" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O254" s="6"/>
     </row>
-    <row r="255" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="255" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O255" s="6"/>
     </row>
-    <row r="256" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="256" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O256" s="6"/>
     </row>
-    <row r="257" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="257" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O257" s="6"/>
     </row>
-    <row r="258" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="258" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O258" s="6"/>
     </row>
-    <row r="259" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="259" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O259" s="6"/>
     </row>
-    <row r="260" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="260" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O260" s="6"/>
     </row>
-    <row r="261" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="261" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O261" s="6"/>
     </row>
-    <row r="262" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="262" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O262" s="6"/>
     </row>
-    <row r="263" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="263" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O263" s="6"/>
     </row>
-    <row r="264" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="264" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O264" s="6"/>
     </row>
-    <row r="265" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="265" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O265" s="6"/>
     </row>
-    <row r="266" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="266" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O266" s="6"/>
     </row>
-    <row r="267" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="267" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O267" s="6"/>
     </row>
-    <row r="268" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="268" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O268" s="6"/>
     </row>
-    <row r="269" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="269" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O269" s="6"/>
     </row>
-    <row r="270" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="270" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O270" s="6"/>
     </row>
-    <row r="271" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="271" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O271" s="6"/>
     </row>
-    <row r="272" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="272" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O272" s="6"/>
     </row>
-    <row r="273" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="273" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O273" s="6"/>
     </row>
-    <row r="274" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="274" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O274" s="6"/>
     </row>
-    <row r="275" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="275" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O275" s="6"/>
     </row>
-    <row r="276" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="276" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O276" s="6"/>
     </row>
-    <row r="277" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="277" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O277" s="6"/>
     </row>
-    <row r="278" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="278" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O278" s="6"/>
     </row>
-    <row r="279" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="279" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O279" s="6"/>
     </row>
-    <row r="280" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="280" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O280" s="6"/>
     </row>
-    <row r="281" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="281" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O281" s="6"/>
     </row>
-    <row r="282" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="282" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O282" s="6"/>
     </row>
-    <row r="283" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="283" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O283" s="6"/>
     </row>
-    <row r="284" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="284" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O284" s="6"/>
     </row>
-    <row r="285" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="285" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O285" s="6"/>
     </row>
-    <row r="286" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="286" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O286" s="6"/>
     </row>
-    <row r="287" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="287" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O287" s="6"/>
     </row>
-    <row r="288" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="288" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O288" s="6"/>
     </row>
-    <row r="289" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="289" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O289" s="6"/>
     </row>
-    <row r="290" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="290" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O290" s="6"/>
     </row>
-    <row r="291" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="291" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O291" s="6"/>
     </row>
-    <row r="292" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="292" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O292" s="6"/>
     </row>
-    <row r="293" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="293" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O293" s="6"/>
     </row>
-    <row r="294" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="294" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O294" s="6"/>
     </row>
-    <row r="295" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="295" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O295" s="6"/>
     </row>
-    <row r="296" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="296" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O296" s="6"/>
     </row>
-    <row r="297" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="297" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O297" s="6"/>
     </row>
-    <row r="298" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="298" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O298" s="6"/>
     </row>
-    <row r="299" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="299" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O299" s="6"/>
     </row>
-    <row r="300" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="300" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O300" s="6"/>
     </row>
-    <row r="301" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="301" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O301" s="6"/>
     </row>
-    <row r="302" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="302" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O302" s="6"/>
     </row>
-    <row r="303" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="303" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O303" s="6"/>
     </row>
-    <row r="304" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="304" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O304" s="6"/>
     </row>
-    <row r="305" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="305" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O305" s="6"/>
     </row>
-    <row r="306" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="306" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O306" s="6"/>
     </row>
-    <row r="307" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="307" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O307" s="6"/>
     </row>
-    <row r="308" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="308" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O308" s="6"/>
     </row>
-    <row r="309" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="309" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O309" s="6"/>
     </row>
-    <row r="310" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="310" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O310" s="6"/>
     </row>
-    <row r="311" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="311" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O311" s="6"/>
     </row>
-    <row r="312" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="312" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O312" s="6"/>
     </row>
-    <row r="313" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="313" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O313" s="6"/>
     </row>
-    <row r="314" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="314" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O314" s="6"/>
     </row>
-    <row r="315" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="315" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O315" s="6"/>
     </row>
-    <row r="316" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="316" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O316" s="6"/>
     </row>
-    <row r="317" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="317" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O317" s="6"/>
     </row>
-    <row r="318" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="318" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O318" s="6"/>
     </row>
-    <row r="319" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="319" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O319" s="6"/>
     </row>
-    <row r="320" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="320" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O320" s="6"/>
     </row>
-    <row r="321" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="321" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O321" s="6"/>
     </row>
-    <row r="322" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="322" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O322" s="6"/>
     </row>
-    <row r="323" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="323" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O323" s="6"/>
     </row>
-    <row r="324" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="324" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O324" s="6"/>
     </row>
-    <row r="325" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="325" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O325" s="6"/>
     </row>
-    <row r="326" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="326" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O326" s="6"/>
     </row>
-    <row r="327" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="327" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O327" s="6"/>
     </row>
-    <row r="328" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="328" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O328" s="6"/>
     </row>
-    <row r="329" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="329" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O329" s="6"/>
     </row>
-    <row r="330" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="330" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O330" s="6"/>
     </row>
-    <row r="331" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="331" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O331" s="6"/>
     </row>
-    <row r="332" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="332" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O332" s="6"/>
     </row>
-    <row r="333" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="333" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O333" s="6"/>
     </row>
-    <row r="334" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="334" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O334" s="6"/>
     </row>
-    <row r="335" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="335" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O335" s="6"/>
     </row>
-    <row r="336" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="336" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O336" s="6"/>
     </row>
-    <row r="337" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="337" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O337" s="6"/>
     </row>
-    <row r="338" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="338" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O338" s="6"/>
     </row>
-    <row r="339" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="339" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O339" s="6"/>
     </row>
-    <row r="340" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="340" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O340" s="6"/>
     </row>
-    <row r="341" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="341" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O341" s="6"/>
     </row>
-    <row r="342" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="342" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O342" s="6"/>
     </row>
-    <row r="343" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="343" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O343" s="6"/>
     </row>
-    <row r="344" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="344" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O344" s="6"/>
     </row>
-    <row r="345" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="345" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O345" s="6"/>
     </row>
-    <row r="346" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="346" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O346" s="6"/>
     </row>
-    <row r="347" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="347" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O347" s="6"/>
     </row>
-    <row r="348" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="348" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O348" s="6"/>
     </row>
-    <row r="349" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="349" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O349" s="6"/>
     </row>
-    <row r="350" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="350" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O350" s="6"/>
     </row>
-    <row r="351" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="351" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O351" s="6"/>
     </row>
-    <row r="352" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="352" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O352" s="6"/>
     </row>
-    <row r="353" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="353" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O353" s="6"/>
     </row>
-    <row r="354" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="354" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O354" s="6"/>
     </row>
-    <row r="355" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="355" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O355" s="6"/>
     </row>
-    <row r="356" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="356" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O356" s="6"/>
     </row>
-    <row r="357" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="357" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O357" s="6"/>
     </row>
-    <row r="358" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="358" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O358" s="6"/>
     </row>
-    <row r="359" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="359" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O359" s="6"/>
     </row>
-    <row r="360" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="360" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O360" s="6"/>
     </row>
-    <row r="361" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="361" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O361" s="6"/>
     </row>
-    <row r="362" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="362" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O362" s="6"/>
     </row>
-    <row r="363" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="363" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O363" s="6"/>
     </row>
-    <row r="364" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="364" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O364" s="6"/>
     </row>
-    <row r="365" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="365" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O365" s="6"/>
     </row>
-    <row r="366" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="366" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O366" s="6"/>
     </row>
-    <row r="367" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="367" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O367" s="6"/>
     </row>
-    <row r="368" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="368" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O368" s="6"/>
     </row>
-    <row r="369" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="369" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O369" s="6"/>
     </row>
-    <row r="370" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="370" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O370" s="6"/>
     </row>
-    <row r="371" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="371" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O371" s="6"/>
     </row>
-    <row r="372" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="372" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O372" s="6"/>
     </row>
-    <row r="373" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="373" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O373" s="6"/>
     </row>
-    <row r="374" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="374" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O374" s="6"/>
     </row>
-    <row r="375" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="375" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O375" s="6"/>
     </row>
-    <row r="376" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="376" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O376" s="6"/>
     </row>
-    <row r="377" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="377" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O377" s="6"/>
     </row>
-    <row r="378" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="378" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O378" s="6"/>
     </row>
-    <row r="379" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="379" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O379" s="6"/>
     </row>
-    <row r="380" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="380" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O380" s="6"/>
     </row>
-    <row r="381" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="381" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O381" s="6"/>
     </row>
-    <row r="382" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="382" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O382" s="6"/>
     </row>
-    <row r="383" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="383" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O383" s="6"/>
     </row>
-    <row r="384" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="384" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O384" s="6"/>
     </row>
-    <row r="385" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="385" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O385" s="6"/>
     </row>
-    <row r="386" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="386" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O386" s="6"/>
     </row>
-    <row r="387" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="387" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O387" s="6"/>
     </row>
-    <row r="388" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="388" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O388" s="6"/>
     </row>
-    <row r="389" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="389" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O389" s="6"/>
     </row>
-    <row r="390" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="390" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O390" s="6"/>
     </row>
-    <row r="391" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="391" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O391" s="6"/>
     </row>
-    <row r="392" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="392" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O392" s="6"/>
     </row>
-    <row r="393" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="393" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O393" s="6"/>
     </row>
-    <row r="394" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="394" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O394" s="6"/>
     </row>
-    <row r="395" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="395" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O395" s="6"/>
     </row>
-    <row r="396" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="396" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O396" s="6"/>
     </row>
-    <row r="397" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="397" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O397" s="6"/>
     </row>
-    <row r="398" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="398" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O398" s="6"/>
     </row>
-    <row r="399" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="399" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O399" s="6"/>
     </row>
-    <row r="400" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="400" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O400" s="6"/>
     </row>
-    <row r="401" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="401" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O401" s="6"/>
     </row>
-    <row r="402" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="402" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O402" s="6"/>
     </row>
-    <row r="403" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="403" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O403" s="6"/>
     </row>
-    <row r="404" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="404" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O404" s="6"/>
     </row>
-    <row r="405" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="405" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O405" s="6"/>
     </row>
-    <row r="406" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="406" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O406" s="6"/>
     </row>
-    <row r="407" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="407" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O407" s="6"/>
     </row>
-    <row r="408" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="408" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O408" s="6"/>
     </row>
-    <row r="409" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="409" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O409" s="6"/>
     </row>
-    <row r="410" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="410" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O410" s="6"/>
     </row>
-    <row r="411" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="411" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O411" s="6"/>
     </row>
-    <row r="412" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="412" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O412" s="6"/>
     </row>
-    <row r="413" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="413" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O413" s="6"/>
     </row>
-    <row r="414" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="414" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O414" s="6"/>
     </row>
-    <row r="415" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="415" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O415" s="6"/>
     </row>
-    <row r="416" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="416" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O416" s="6"/>
     </row>
-    <row r="417" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="417" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O417" s="6"/>
     </row>
-    <row r="418" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="418" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O418" s="6"/>
     </row>
-    <row r="419" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="419" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O419" s="6"/>
     </row>
-    <row r="420" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="420" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O420" s="6"/>
     </row>
-    <row r="421" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="421" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O421" s="6"/>
     </row>
-    <row r="422" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="422" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O422" s="6"/>
     </row>
-    <row r="423" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="423" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O423" s="6"/>
     </row>
-    <row r="424" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="424" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O424" s="6"/>
     </row>
-    <row r="425" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="425" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O425" s="6"/>
     </row>
-    <row r="426" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="426" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O426" s="6"/>
     </row>
-    <row r="427" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="427" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O427" s="6"/>
     </row>
-    <row r="428" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="428" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O428" s="6"/>
     </row>
-    <row r="429" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="429" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O429" s="6"/>
     </row>
-    <row r="430" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="430" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O430" s="6"/>
     </row>
-    <row r="431" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="431" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O431" s="6"/>
     </row>
-    <row r="432" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="432" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O432" s="6"/>
     </row>
-    <row r="433" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="433" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O433" s="6"/>
     </row>
   </sheetData>

--- a/아이템 도감.xlsx
+++ b/아이템 도감.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hcw97\Desktop\CapstoneProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\CapstoneProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1C94CD-DB67-46C0-90A0-CAA85D661E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A60576B-35F5-42A5-BAF1-F182CA587DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{AEFF7BDA-CB51-4C25-A75C-46A97EA8EBD6}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{AEFF7BDA-CB51-4C25-A75C-46A97EA8EBD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="288">
   <si>
     <t>item_id</t>
   </si>
@@ -281,9 +281,6 @@
     <t>고장난 세탁기</t>
   </si>
   <si>
-    <t>망가진 자전거</t>
-  </si>
-  <si>
     <t>생선 뼈</t>
   </si>
   <si>
@@ -386,9 +383,6 @@
     <t>저주받은 토템</t>
   </si>
   <si>
-    <t>금괴 상자</t>
-  </si>
-  <si>
     <t>불사조의 깃털</t>
   </si>
   <si>
@@ -398,9 +392,6 @@
     <t>엑스칼리버</t>
   </si>
   <si>
-    <t>황제의 옥좌</t>
-  </si>
-  <si>
     <t>현자의 돌</t>
   </si>
   <si>
@@ -934,6 +925,65 @@
   <si>
     <t>C_Glass_Marble</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>R_Samurai_Katana</t>
+  </si>
+  <si>
+    <t>R_Jade_Bangle</t>
+  </si>
+  <si>
+    <t>R_Treasure_Map</t>
+  </si>
+  <si>
+    <t>R_Knight_Armor</t>
+  </si>
+  <si>
+    <t>R_Antique_Typewriter</t>
+  </si>
+  <si>
+    <t>E_Diamond_Ring</t>
+  </si>
+  <si>
+    <t>E_Unicorn_Horn</t>
+  </si>
+  <si>
+    <t>E_Golden_Chalice</t>
+  </si>
+  <si>
+    <t>E_Dinosaur_Egg_Fossil</t>
+  </si>
+  <si>
+    <t>E_Meteorite_Shard</t>
+  </si>
+  <si>
+    <t>E_Cursed_Totem</t>
+  </si>
+  <si>
+    <t>E_Chest_of_Gold</t>
+  </si>
+  <si>
+    <t>금화 상자</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>L_Phoenix_Feather</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>L_Heart_of_Ocean</t>
+  </si>
+  <si>
+    <t>L_Excalibur</t>
+  </si>
+  <si>
+    <t>L_Imperial_crown</t>
+  </si>
+  <si>
+    <t>황제의 왕관</t>
+  </si>
+  <si>
+    <t>L_Philosopher_Stone</t>
   </si>
 </sst>
 </file>
@@ -1204,9 +1254,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1244,7 +1294,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1350,7 +1400,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1492,7 +1542,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1501,27 +1551,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176CEBE0-28C6-4629-A760-C52146228B7D}">
   <dimension ref="A1:Q433"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12.875" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="18.08203125" customWidth="1"/>
+    <col min="3" max="3" width="18.125" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" customWidth="1"/>
-    <col min="6" max="6" width="21.08203125" customWidth="1"/>
-    <col min="7" max="8" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.375" customWidth="1"/>
+    <col min="6" max="6" width="21.125" customWidth="1"/>
+    <col min="7" max="8" width="14.875" customWidth="1"/>
     <col min="9" max="9" width="14.25" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="15.58203125" customWidth="1"/>
-    <col min="12" max="12" width="19.08203125" customWidth="1"/>
+    <col min="10" max="10" width="12.875" customWidth="1"/>
+    <col min="11" max="11" width="15.625" customWidth="1"/>
+    <col min="12" max="12" width="19.125" customWidth="1"/>
     <col min="13" max="13" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="54.58203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="35.08203125" customWidth="1"/>
+    <col min="14" max="14" width="54.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="35.125" customWidth="1"/>
     <col min="16" max="16" width="56.25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="59.58203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="59.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1550,7 +1600,7 @@
         <v>6</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>7</v>
@@ -1565,13 +1615,13 @@
         <v>10</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="P1" s="11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1615,13 +1665,13 @@
         <v>1</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="P2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1666,10 +1716,10 @@
       </c>
       <c r="O3" s="6"/>
       <c r="P3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1714,10 +1764,10 @@
       </c>
       <c r="O4" s="6"/>
       <c r="P4" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1762,10 +1812,10 @@
       </c>
       <c r="O5" s="6"/>
       <c r="P5" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1809,13 +1859,13 @@
         <v>1</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="P6" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1860,10 +1910,10 @@
       </c>
       <c r="O7" s="6"/>
       <c r="P7" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1908,10 +1958,10 @@
       </c>
       <c r="O8" s="6"/>
       <c r="P8" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1956,10 +2006,10 @@
       </c>
       <c r="O9" s="6"/>
       <c r="P9" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2003,13 +2053,13 @@
         <v>1</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2054,10 +2104,10 @@
       </c>
       <c r="O11" s="6"/>
       <c r="P11" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2102,10 +2152,10 @@
       </c>
       <c r="O12" s="6"/>
       <c r="P12" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2150,10 +2200,10 @@
       </c>
       <c r="O13" s="6"/>
       <c r="P13" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2198,10 +2248,10 @@
       </c>
       <c r="O14" s="6"/>
       <c r="P14" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2212,7 +2262,7 @@
         <v>150</v>
       </c>
       <c r="D15" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -2245,13 +2295,13 @@
         <v>1</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="P15" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2295,13 +2345,13 @@
         <v>1</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P16" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.45">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
         <v>16</v>
       </c>
@@ -2312,7 +2362,7 @@
         <v>151</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -2345,13 +2395,13 @@
         <v>1</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P17" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.45">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2395,13 +2445,13 @@
         <v>1</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P18" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.45">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2446,10 +2496,10 @@
       </c>
       <c r="O19" s="6"/>
       <c r="P19" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.45">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2493,13 +2543,13 @@
         <v>1</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="P20" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>20</v>
       </c>
@@ -2543,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="P24" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.45">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>21</v>
       </c>
@@ -2593,13 +2643,13 @@
         <v>1</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="P25" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>22</v>
       </c>
@@ -2643,13 +2693,13 @@
         <v>1</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="P26" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.45">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>23</v>
       </c>
@@ -2693,13 +2743,13 @@
         <v>1</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P27" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.45">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>24</v>
       </c>
@@ -2743,16 +2793,16 @@
         <v>1</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="P28" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="Q28" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.45">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>25</v>
       </c>
@@ -2796,16 +2846,16 @@
         <v>1</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P29" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="Q29" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.45">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26</v>
       </c>
@@ -2849,13 +2899,13 @@
         <v>1</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="P30" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.45">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>27</v>
       </c>
@@ -2899,13 +2949,13 @@
         <v>1</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="P31" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.45">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>28</v>
       </c>
@@ -2949,13 +2999,13 @@
         <v>1</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="P32" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.45">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>29</v>
       </c>
@@ -2999,13 +3049,13 @@
         <v>1</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="P33" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.45">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>30</v>
       </c>
@@ -3049,13 +3099,13 @@
         <v>1</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="P34" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.45">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>31</v>
       </c>
@@ -3099,13 +3149,13 @@
         <v>1</v>
       </c>
       <c r="O35" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="P35" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.45">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>32</v>
       </c>
@@ -3149,16 +3199,16 @@
         <v>1</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="P36" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="Q36" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.45">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>33</v>
       </c>
@@ -3202,16 +3252,16 @@
         <v>1</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="P37" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="Q37" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>34</v>
       </c>
@@ -3222,7 +3272,7 @@
         <v>202</v>
       </c>
       <c r="D38" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -3255,13 +3305,13 @@
         <v>1</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P38" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.45">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>35</v>
       </c>
@@ -3305,13 +3355,13 @@
         <v>1</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P39" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.45">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>36</v>
       </c>
@@ -3355,16 +3405,16 @@
         <v>1</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="P40" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="Q40" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.45">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>37</v>
       </c>
@@ -3408,13 +3458,13 @@
         <v>1</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P41" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.45">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>38</v>
       </c>
@@ -3458,13 +3508,13 @@
         <v>1</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P42" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.45">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>39</v>
       </c>
@@ -3508,13 +3558,13 @@
         <v>1</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P43" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.45">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>40</v>
       </c>
@@ -3558,13 +3608,13 @@
         <v>1</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="P44" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.45">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>41</v>
       </c>
@@ -3608,16 +3658,16 @@
         <v>1</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="P45" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="Q45" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>42</v>
       </c>
@@ -3661,13 +3711,13 @@
         <v>1</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="P46" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.45">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>43</v>
       </c>
@@ -3711,13 +3761,13 @@
         <v>1</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="P47" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.45">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>44</v>
       </c>
@@ -3761,13 +3811,13 @@
         <v>1</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="P48" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.45">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>45</v>
       </c>
@@ -3811,16 +3861,16 @@
         <v>1</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.45">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="O51" s="6"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>46</v>
       </c>
@@ -3864,16 +3914,16 @@
         <v>1</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="P52" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="Q52" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.45">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>47</v>
       </c>
@@ -3917,16 +3967,16 @@
         <v>1</v>
       </c>
       <c r="O53" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="P53" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="Q53" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>48</v>
       </c>
@@ -3970,16 +4020,16 @@
         <v>1</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="P54" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="Q54" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>49</v>
       </c>
@@ -4023,16 +4073,16 @@
         <v>1</v>
       </c>
       <c r="O55" s="6" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="P55" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="Q55" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>50</v>
       </c>
@@ -4076,13 +4126,13 @@
         <v>1</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="P56" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.45">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>51</v>
       </c>
@@ -4126,13 +4176,13 @@
         <v>1</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="P57" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.45">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>52</v>
       </c>
@@ -4176,13 +4226,13 @@
         <v>1</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="P58" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.45">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>53</v>
       </c>
@@ -4226,16 +4276,16 @@
         <v>1</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="P59" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="Q59" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>54</v>
       </c>
@@ -4279,16 +4329,16 @@
         <v>1</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="P60" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q60" t="s">
         <v>161</v>
       </c>
-      <c r="Q60" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.45">
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>55</v>
       </c>
@@ -4332,19 +4382,19 @@
         <v>1</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Q61" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.45">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="O62" s="6"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>56</v>
       </c>
@@ -4385,10 +4435,10 @@
         <v>1</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.45">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>57</v>
       </c>
@@ -4429,10 +4479,10 @@
         <v>1</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.45">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>58</v>
       </c>
@@ -4473,10 +4523,10 @@
         <v>1</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.45">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>59</v>
       </c>
@@ -4517,10 +4567,10 @@
         <v>1</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.45">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>60</v>
       </c>
@@ -4561,10 +4611,10 @@
         <v>1</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.45">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>61</v>
       </c>
@@ -4605,10 +4655,10 @@
         <v>1</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.45">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>62</v>
       </c>
@@ -4649,10 +4699,10 @@
         <v>1</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.45">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>63</v>
       </c>
@@ -4693,10 +4743,10 @@
         <v>1</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.45">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>64</v>
       </c>
@@ -4737,10 +4787,10 @@
         <v>1</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.45">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>65</v>
       </c>
@@ -4781,10 +4831,10 @@
         <v>1</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.45">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>66</v>
       </c>
@@ -4825,10 +4875,10 @@
         <v>1</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.45">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>67</v>
       </c>
@@ -4839,7 +4889,7 @@
         <v>81</v>
       </c>
       <c r="E74">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="F74">
         <v>-1</v>
@@ -4860,7 +4910,7 @@
         <v>0</v>
       </c>
       <c r="L74">
-        <v>240</v>
+        <v>2</v>
       </c>
       <c r="M74">
         <v>1</v>
@@ -4868,9 +4918,11 @@
       <c r="N74" t="b">
         <v>1</v>
       </c>
-      <c r="O74" s="6"/>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="O74" s="6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>68</v>
       </c>
@@ -4881,7 +4933,7 @@
         <v>82</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75">
         <v>-1</v>
@@ -4902,7 +4954,7 @@
         <v>0</v>
       </c>
       <c r="L75">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M75">
         <v>1</v>
@@ -4911,10 +4963,10 @@
         <v>1</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.45">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>69</v>
       </c>
@@ -4925,7 +4977,7 @@
         <v>83</v>
       </c>
       <c r="E76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F76">
         <v>-1</v>
@@ -4946,7 +4998,7 @@
         <v>0</v>
       </c>
       <c r="L76">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M76">
         <v>1</v>
@@ -4955,10 +5007,10 @@
         <v>1</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.45">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>70</v>
       </c>
@@ -4969,7 +5021,7 @@
         <v>84</v>
       </c>
       <c r="E77">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="F77">
         <v>-1</v>
@@ -4990,7 +5042,7 @@
         <v>0</v>
       </c>
       <c r="L77">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="M77">
         <v>1</v>
@@ -4999,10 +5051,10 @@
         <v>1</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.45">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>71</v>
       </c>
@@ -5013,7 +5065,7 @@
         <v>85</v>
       </c>
       <c r="E78">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F78">
         <v>-1</v>
@@ -5034,7 +5086,7 @@
         <v>0</v>
       </c>
       <c r="L78">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="M78">
         <v>1</v>
@@ -5043,10 +5095,10 @@
         <v>1</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.45">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>72</v>
       </c>
@@ -5057,7 +5109,7 @@
         <v>86</v>
       </c>
       <c r="E79">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F79">
         <v>-1</v>
@@ -5078,7 +5130,7 @@
         <v>0</v>
       </c>
       <c r="L79">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="M79">
         <v>1</v>
@@ -5087,10 +5139,10 @@
         <v>1</v>
       </c>
       <c r="O79" s="6" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.45">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>73</v>
       </c>
@@ -5101,7 +5153,7 @@
         <v>87</v>
       </c>
       <c r="E80">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F80">
         <v>-1</v>
@@ -5122,7 +5174,7 @@
         <v>0</v>
       </c>
       <c r="L80">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="M80">
         <v>1</v>
@@ -5131,10 +5183,10 @@
         <v>1</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.45">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>74</v>
       </c>
@@ -5145,7 +5197,7 @@
         <v>88</v>
       </c>
       <c r="E81">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F81">
         <v>-1</v>
@@ -5163,10 +5215,10 @@
         <v>-1</v>
       </c>
       <c r="K81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="M81">
         <v>1</v>
@@ -5175,10 +5227,10 @@
         <v>1</v>
       </c>
       <c r="O81" s="6" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.45">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>75</v>
       </c>
@@ -5189,7 +5241,7 @@
         <v>89</v>
       </c>
       <c r="E82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F82">
         <v>-1</v>
@@ -5210,7 +5262,7 @@
         <v>1</v>
       </c>
       <c r="L82">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M82">
         <v>1</v>
@@ -5219,10 +5271,10 @@
         <v>1</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.45">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>76</v>
       </c>
@@ -5233,7 +5285,7 @@
         <v>90</v>
       </c>
       <c r="E83">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F83">
         <v>-1</v>
@@ -5254,7 +5306,7 @@
         <v>1</v>
       </c>
       <c r="L83">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M83">
         <v>1</v>
@@ -5263,10 +5315,10 @@
         <v>1</v>
       </c>
       <c r="O83" s="6" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.45">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>77</v>
       </c>
@@ -5277,7 +5329,7 @@
         <v>91</v>
       </c>
       <c r="E84">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F84">
         <v>-1</v>
@@ -5298,7 +5350,7 @@
         <v>1</v>
       </c>
       <c r="L84">
-        <v>150</v>
+        <v>620</v>
       </c>
       <c r="M84">
         <v>1</v>
@@ -5307,10 +5359,10 @@
         <v>1</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.45">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>78</v>
       </c>
@@ -5321,7 +5373,7 @@
         <v>92</v>
       </c>
       <c r="E85">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F85">
         <v>-1</v>
@@ -5342,7 +5394,7 @@
         <v>1</v>
       </c>
       <c r="L85">
-        <v>620</v>
+        <v>360</v>
       </c>
       <c r="M85">
         <v>1</v>
@@ -5351,10 +5403,10 @@
         <v>1</v>
       </c>
       <c r="O85" s="6" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.45">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>79</v>
       </c>
@@ -5365,7 +5417,7 @@
         <v>93</v>
       </c>
       <c r="E86">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F86">
         <v>-1</v>
@@ -5386,7 +5438,7 @@
         <v>1</v>
       </c>
       <c r="L86">
-        <v>360</v>
+        <v>500</v>
       </c>
       <c r="M86">
         <v>1</v>
@@ -5395,10 +5447,10 @@
         <v>1</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.45">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>80</v>
       </c>
@@ -5409,7 +5461,7 @@
         <v>94</v>
       </c>
       <c r="E87">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F87">
         <v>-1</v>
@@ -5430,7 +5482,7 @@
         <v>1</v>
       </c>
       <c r="L87">
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="M87">
         <v>1</v>
@@ -5439,10 +5491,10 @@
         <v>1</v>
       </c>
       <c r="O87" s="6" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.45">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>81</v>
       </c>
@@ -5453,7 +5505,7 @@
         <v>95</v>
       </c>
       <c r="E88">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F88">
         <v>-1</v>
@@ -5474,7 +5526,7 @@
         <v>1</v>
       </c>
       <c r="L88">
-        <v>440</v>
+        <v>170</v>
       </c>
       <c r="M88">
         <v>1</v>
@@ -5483,10 +5535,10 @@
         <v>1</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.45">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>82</v>
       </c>
@@ -5497,7 +5549,7 @@
         <v>96</v>
       </c>
       <c r="E89">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F89">
         <v>-1</v>
@@ -5518,7 +5570,7 @@
         <v>1</v>
       </c>
       <c r="L89">
-        <v>170</v>
+        <v>270</v>
       </c>
       <c r="M89">
         <v>1</v>
@@ -5527,10 +5579,10 @@
         <v>1</v>
       </c>
       <c r="O89" s="6" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.45">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>83</v>
       </c>
@@ -5541,7 +5593,7 @@
         <v>97</v>
       </c>
       <c r="E90">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F90">
         <v>-1</v>
@@ -5562,7 +5614,7 @@
         <v>1</v>
       </c>
       <c r="L90">
-        <v>270</v>
+        <v>530</v>
       </c>
       <c r="M90">
         <v>1</v>
@@ -5571,10 +5623,10 @@
         <v>1</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.45">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>84</v>
       </c>
@@ -5582,10 +5634,10 @@
         <v>3</v>
       </c>
       <c r="D91" t="s">
-        <v>98</v>
+        <v>221</v>
       </c>
       <c r="E91">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F91">
         <v>-1</v>
@@ -5606,7 +5658,7 @@
         <v>1</v>
       </c>
       <c r="L91">
-        <v>530</v>
+        <v>720</v>
       </c>
       <c r="M91">
         <v>1</v>
@@ -5615,10 +5667,10 @@
         <v>1</v>
       </c>
       <c r="O91" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.45">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>85</v>
       </c>
@@ -5626,10 +5678,10 @@
         <v>3</v>
       </c>
       <c r="D92" t="s">
-        <v>224</v>
+        <v>98</v>
       </c>
       <c r="E92">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F92">
         <v>-1</v>
@@ -5650,7 +5702,7 @@
         <v>1</v>
       </c>
       <c r="L92">
-        <v>720</v>
+        <v>300</v>
       </c>
       <c r="M92">
         <v>1</v>
@@ -5659,10 +5711,10 @@
         <v>1</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.45">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>86</v>
       </c>
@@ -5673,7 +5725,7 @@
         <v>99</v>
       </c>
       <c r="E93">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F93">
         <v>-1</v>
@@ -5694,7 +5746,7 @@
         <v>1</v>
       </c>
       <c r="L93">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="M93">
         <v>1</v>
@@ -5703,10 +5755,10 @@
         <v>1</v>
       </c>
       <c r="O93" s="6" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.45">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>87</v>
       </c>
@@ -5717,7 +5769,7 @@
         <v>100</v>
       </c>
       <c r="E94">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F94">
         <v>-1</v>
@@ -5738,7 +5790,7 @@
         <v>1</v>
       </c>
       <c r="L94">
-        <v>360</v>
+        <v>520</v>
       </c>
       <c r="M94">
         <v>1</v>
@@ -5747,10 +5799,10 @@
         <v>1</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.45">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>88</v>
       </c>
@@ -5761,7 +5813,7 @@
         <v>101</v>
       </c>
       <c r="E95">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F95">
         <v>-1</v>
@@ -5779,10 +5831,10 @@
         <v>-1</v>
       </c>
       <c r="K95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L95">
-        <v>520</v>
+        <v>300</v>
       </c>
       <c r="M95">
         <v>1</v>
@@ -5791,10 +5843,10 @@
         <v>1</v>
       </c>
       <c r="O95" s="6" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.45">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>89</v>
       </c>
@@ -5802,10 +5854,10 @@
         <v>3</v>
       </c>
       <c r="D96" t="s">
-        <v>102</v>
+        <v>245</v>
       </c>
       <c r="E96">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F96">
         <v>-1</v>
@@ -5826,7 +5878,7 @@
         <v>2</v>
       </c>
       <c r="L96">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="M96">
         <v>1</v>
@@ -5835,10 +5887,10 @@
         <v>1</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.45">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>90</v>
       </c>
@@ -5846,10 +5898,10 @@
         <v>3</v>
       </c>
       <c r="D97" t="s">
-        <v>248</v>
+        <v>102</v>
       </c>
       <c r="E97">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F97">
         <v>-1</v>
@@ -5870,7 +5922,7 @@
         <v>2</v>
       </c>
       <c r="L97">
-        <v>340</v>
+        <v>2400</v>
       </c>
       <c r="M97">
         <v>1</v>
@@ -5879,10 +5931,10 @@
         <v>1</v>
       </c>
       <c r="O97" s="6" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.45">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>91</v>
       </c>
@@ -5893,7 +5945,7 @@
         <v>103</v>
       </c>
       <c r="E98">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F98">
         <v>-1</v>
@@ -5914,7 +5966,7 @@
         <v>2</v>
       </c>
       <c r="L98">
-        <v>2400</v>
+        <v>1400</v>
       </c>
       <c r="M98">
         <v>1</v>
@@ -5926,7 +5978,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>92</v>
       </c>
@@ -5937,7 +5989,7 @@
         <v>104</v>
       </c>
       <c r="E99">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F99">
         <v>-1</v>
@@ -5958,7 +6010,7 @@
         <v>2</v>
       </c>
       <c r="L99">
-        <v>1400</v>
+        <v>1800</v>
       </c>
       <c r="M99">
         <v>1</v>
@@ -5967,10 +6019,10 @@
         <v>1</v>
       </c>
       <c r="O99" s="6" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.45">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>93</v>
       </c>
@@ -5981,7 +6033,7 @@
         <v>105</v>
       </c>
       <c r="E100">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F100">
         <v>-1</v>
@@ -6002,7 +6054,7 @@
         <v>2</v>
       </c>
       <c r="L100">
-        <v>1800</v>
+        <v>700</v>
       </c>
       <c r="M100">
         <v>1</v>
@@ -6010,9 +6062,11 @@
       <c r="N100" t="b">
         <v>1</v>
       </c>
-      <c r="O100" s="6"/>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="O100" s="6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>94</v>
       </c>
@@ -6023,7 +6077,7 @@
         <v>106</v>
       </c>
       <c r="E101">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F101">
         <v>-1</v>
@@ -6044,7 +6098,7 @@
         <v>2</v>
       </c>
       <c r="L101">
-        <v>700</v>
+        <v>240</v>
       </c>
       <c r="M101">
         <v>1</v>
@@ -6052,9 +6106,11 @@
       <c r="N101" t="b">
         <v>1</v>
       </c>
-      <c r="O101" s="6"/>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="O101" s="6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>95</v>
       </c>
@@ -6065,7 +6121,7 @@
         <v>107</v>
       </c>
       <c r="E102">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="F102">
         <v>-1</v>
@@ -6086,7 +6142,7 @@
         <v>2</v>
       </c>
       <c r="L102">
-        <v>240</v>
+        <v>2950</v>
       </c>
       <c r="M102">
         <v>1</v>
@@ -6094,9 +6150,11 @@
       <c r="N102" t="b">
         <v>1</v>
       </c>
-      <c r="O102" s="6"/>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="O102" s="6" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>96</v>
       </c>
@@ -6107,7 +6165,7 @@
         <v>108</v>
       </c>
       <c r="E103">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F103">
         <v>-1</v>
@@ -6128,7 +6186,7 @@
         <v>2</v>
       </c>
       <c r="L103">
-        <v>2950</v>
+        <v>1350</v>
       </c>
       <c r="M103">
         <v>1</v>
@@ -6136,9 +6194,11 @@
       <c r="N103" t="b">
         <v>1</v>
       </c>
-      <c r="O103" s="6"/>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="O103" s="6" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>97</v>
       </c>
@@ -6149,7 +6209,7 @@
         <v>109</v>
       </c>
       <c r="E104">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F104">
         <v>-1</v>
@@ -6167,10 +6227,10 @@
         <v>-1</v>
       </c>
       <c r="K104">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L104">
-        <v>1350</v>
+        <v>1500</v>
       </c>
       <c r="M104">
         <v>1</v>
@@ -6178,9 +6238,11 @@
       <c r="N104" t="b">
         <v>1</v>
       </c>
-      <c r="O104" s="6"/>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="O104" s="6" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>98</v>
       </c>
@@ -6191,7 +6253,7 @@
         <v>110</v>
       </c>
       <c r="E105">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F105">
         <v>-1</v>
@@ -6212,7 +6274,7 @@
         <v>3</v>
       </c>
       <c r="L105">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="M105">
         <v>1</v>
@@ -6220,9 +6282,11 @@
       <c r="N105" t="b">
         <v>1</v>
       </c>
-      <c r="O105" s="6"/>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="O105" s="6" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>99</v>
       </c>
@@ -6233,7 +6297,7 @@
         <v>111</v>
       </c>
       <c r="E106">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F106">
         <v>-1</v>
@@ -6254,7 +6318,7 @@
         <v>3</v>
       </c>
       <c r="L106">
-        <v>5000</v>
+        <v>4520</v>
       </c>
       <c r="M106">
         <v>1</v>
@@ -6262,9 +6326,11 @@
       <c r="N106" t="b">
         <v>1</v>
       </c>
-      <c r="O106" s="6"/>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="O106" s="6" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>100</v>
       </c>
@@ -6275,7 +6341,7 @@
         <v>112</v>
       </c>
       <c r="E107">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F107">
         <v>-1</v>
@@ -6296,7 +6362,7 @@
         <v>3</v>
       </c>
       <c r="L107">
-        <v>4520</v>
+        <v>9800</v>
       </c>
       <c r="M107">
         <v>1</v>
@@ -6304,9 +6370,11 @@
       <c r="N107" t="b">
         <v>1</v>
       </c>
-      <c r="O107" s="6"/>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="O107" s="6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>101</v>
       </c>
@@ -6317,7 +6385,7 @@
         <v>113</v>
       </c>
       <c r="E108">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F108">
         <v>-1</v>
@@ -6338,7 +6406,7 @@
         <v>3</v>
       </c>
       <c r="L108">
-        <v>9800</v>
+        <v>12000</v>
       </c>
       <c r="M108">
         <v>1</v>
@@ -6346,9 +6414,11 @@
       <c r="N108" t="b">
         <v>1</v>
       </c>
-      <c r="O108" s="6"/>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="O108" s="6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>102</v>
       </c>
@@ -6359,7 +6429,7 @@
         <v>114</v>
       </c>
       <c r="E109">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F109">
         <v>-1</v>
@@ -6380,7 +6450,7 @@
         <v>3</v>
       </c>
       <c r="L109">
-        <v>12000</v>
+        <v>7500</v>
       </c>
       <c r="M109">
         <v>1</v>
@@ -6388,9 +6458,11 @@
       <c r="N109" t="b">
         <v>1</v>
       </c>
-      <c r="O109" s="6"/>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="O109" s="6" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>103</v>
       </c>
@@ -6398,10 +6470,10 @@
         <v>3</v>
       </c>
       <c r="D110" t="s">
-        <v>115</v>
+        <v>281</v>
       </c>
       <c r="E110">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F110">
         <v>-1</v>
@@ -6422,7 +6494,7 @@
         <v>3</v>
       </c>
       <c r="L110">
-        <v>7500</v>
+        <v>19520</v>
       </c>
       <c r="M110">
         <v>1</v>
@@ -6430,9 +6502,11 @@
       <c r="N110" t="b">
         <v>1</v>
       </c>
-      <c r="O110" s="6"/>
-    </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="O110" s="6" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>104</v>
       </c>
@@ -6440,10 +6514,10 @@
         <v>3</v>
       </c>
       <c r="D111" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E111">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="F111">
         <v>-1</v>
@@ -6461,10 +6535,10 @@
         <v>-1</v>
       </c>
       <c r="K111">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L111">
-        <v>19520</v>
+        <v>1000</v>
       </c>
       <c r="M111">
         <v>1</v>
@@ -6472,9 +6546,11 @@
       <c r="N111" t="b">
         <v>1</v>
       </c>
-      <c r="O111" s="6"/>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="O111" s="6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>105</v>
       </c>
@@ -6482,10 +6558,10 @@
         <v>3</v>
       </c>
       <c r="D112" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E112">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="F112">
         <v>-1</v>
@@ -6506,7 +6582,7 @@
         <v>4</v>
       </c>
       <c r="L112">
-        <v>1000</v>
+        <v>37200</v>
       </c>
       <c r="M112">
         <v>1</v>
@@ -6514,9 +6590,11 @@
       <c r="N112" t="b">
         <v>1</v>
       </c>
-      <c r="O112" s="6"/>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="O112" s="6" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>106</v>
       </c>
@@ -6524,10 +6602,10 @@
         <v>3</v>
       </c>
       <c r="D113" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E113">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F113">
         <v>-1</v>
@@ -6548,7 +6626,7 @@
         <v>4</v>
       </c>
       <c r="L113">
-        <v>37200</v>
+        <v>42890</v>
       </c>
       <c r="M113">
         <v>1</v>
@@ -6556,9 +6634,11 @@
       <c r="N113" t="b">
         <v>1</v>
       </c>
-      <c r="O113" s="6"/>
-    </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="O113" s="6" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>107</v>
       </c>
@@ -6566,10 +6646,10 @@
         <v>3</v>
       </c>
       <c r="D114" t="s">
-        <v>119</v>
+        <v>286</v>
       </c>
       <c r="E114">
-        <v>62</v>
+        <v>150</v>
       </c>
       <c r="F114">
         <v>-1</v>
@@ -6590,7 +6670,7 @@
         <v>4</v>
       </c>
       <c r="L114">
-        <v>42890</v>
+        <v>132460</v>
       </c>
       <c r="M114">
         <v>1</v>
@@ -6598,9 +6678,11 @@
       <c r="N114" t="b">
         <v>1</v>
       </c>
-      <c r="O114" s="6"/>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="O114" s="6" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>108</v>
       </c>
@@ -6608,10 +6690,10 @@
         <v>3</v>
       </c>
       <c r="D115" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E115">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="F115">
         <v>-1</v>
@@ -6632,7 +6714,7 @@
         <v>4</v>
       </c>
       <c r="L115">
-        <v>132460</v>
+        <v>52520</v>
       </c>
       <c r="M115">
         <v>1</v>
@@ -6640,999 +6722,959 @@
       <c r="N115" t="b">
         <v>1</v>
       </c>
-      <c r="O115" s="6"/>
-    </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A116">
-        <v>109</v>
-      </c>
-      <c r="B116">
-        <v>3</v>
-      </c>
-      <c r="D116" t="s">
-        <v>121</v>
-      </c>
-      <c r="E116">
-        <v>70</v>
-      </c>
-      <c r="F116">
-        <v>-1</v>
-      </c>
-      <c r="G116">
-        <v>-1</v>
-      </c>
-      <c r="H116">
-        <v>-1</v>
-      </c>
-      <c r="I116">
-        <v>-1</v>
-      </c>
-      <c r="J116">
-        <v>-1</v>
-      </c>
-      <c r="K116">
-        <v>4</v>
-      </c>
-      <c r="L116">
-        <v>52520</v>
-      </c>
-      <c r="M116">
-        <v>1</v>
-      </c>
-      <c r="N116" t="b">
-        <v>1</v>
-      </c>
-      <c r="O116" s="6"/>
-    </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="O115" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O117" s="6"/>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O118" s="6"/>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O119" s="6"/>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O120" s="6"/>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O121" s="6"/>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O122" s="6"/>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O123" s="6"/>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O124" s="6"/>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O125" s="6"/>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O126" s="6"/>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O127" s="6"/>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O128" s="6"/>
     </row>
-    <row r="129" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="129" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O129" s="6"/>
     </row>
-    <row r="130" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="130" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O130" s="6"/>
     </row>
-    <row r="131" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="131" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O131" s="6"/>
     </row>
-    <row r="132" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="132" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O132" s="6"/>
     </row>
-    <row r="133" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="133" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O133" s="6"/>
     </row>
-    <row r="134" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="134" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O134" s="6"/>
     </row>
-    <row r="135" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="135" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O135" s="6"/>
     </row>
-    <row r="136" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="136" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O136" s="6"/>
     </row>
-    <row r="137" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="137" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O137" s="6"/>
     </row>
-    <row r="138" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="138" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O138" s="6"/>
     </row>
-    <row r="139" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="139" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O139" s="6"/>
     </row>
-    <row r="140" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="140" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O140" s="6"/>
     </row>
-    <row r="141" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="141" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O141" s="6"/>
     </row>
-    <row r="142" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="142" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O142" s="6"/>
     </row>
-    <row r="143" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="143" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O143" s="6"/>
     </row>
-    <row r="144" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="144" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O144" s="6"/>
     </row>
-    <row r="145" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="145" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O145" s="6"/>
     </row>
-    <row r="146" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="146" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O146" s="6"/>
     </row>
-    <row r="147" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="147" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O147" s="6"/>
     </row>
-    <row r="148" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="148" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O148" s="6"/>
     </row>
-    <row r="149" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="149" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O149" s="6"/>
     </row>
-    <row r="150" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="150" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O150" s="6"/>
     </row>
-    <row r="151" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="151" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O151" s="6"/>
     </row>
-    <row r="152" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="152" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O152" s="6"/>
     </row>
-    <row r="153" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="153" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O153" s="6"/>
     </row>
-    <row r="154" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="154" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O154" s="6"/>
     </row>
-    <row r="155" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="155" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O155" s="6"/>
     </row>
-    <row r="156" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="156" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O156" s="6"/>
     </row>
-    <row r="157" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="157" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O157" s="6"/>
     </row>
-    <row r="158" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="158" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O158" s="6"/>
     </row>
-    <row r="159" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="159" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O159" s="6"/>
     </row>
-    <row r="160" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="160" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O160" s="6"/>
     </row>
-    <row r="161" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="161" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O161" s="6"/>
     </row>
-    <row r="162" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="162" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O162" s="6"/>
     </row>
-    <row r="163" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="163" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O163" s="6"/>
     </row>
-    <row r="164" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="164" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O164" s="6"/>
     </row>
-    <row r="165" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="165" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O165" s="6"/>
     </row>
-    <row r="166" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="166" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O166" s="6"/>
     </row>
-    <row r="167" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="167" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O167" s="6"/>
     </row>
-    <row r="168" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="168" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O168" s="6"/>
     </row>
-    <row r="169" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="169" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O169" s="6"/>
     </row>
-    <row r="170" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="170" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O170" s="6"/>
     </row>
-    <row r="171" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="171" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O171" s="6"/>
     </row>
-    <row r="172" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="172" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O172" s="6"/>
     </row>
-    <row r="173" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="173" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O173" s="6"/>
     </row>
-    <row r="174" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="174" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O174" s="6"/>
     </row>
-    <row r="175" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="175" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O175" s="6"/>
     </row>
-    <row r="176" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="176" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O176" s="6"/>
     </row>
-    <row r="177" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="177" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O177" s="6"/>
     </row>
-    <row r="178" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="178" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O178" s="6"/>
     </row>
-    <row r="179" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="179" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O179" s="6"/>
     </row>
-    <row r="180" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="180" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O180" s="6"/>
     </row>
-    <row r="181" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="181" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O181" s="6"/>
     </row>
-    <row r="182" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="182" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O182" s="6"/>
     </row>
-    <row r="183" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="183" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O183" s="6"/>
     </row>
-    <row r="184" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="184" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O184" s="6"/>
     </row>
-    <row r="185" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="185" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O185" s="6"/>
     </row>
-    <row r="186" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="186" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O186" s="6"/>
     </row>
-    <row r="187" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="187" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O187" s="6"/>
     </row>
-    <row r="188" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="188" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O188" s="6"/>
     </row>
-    <row r="189" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="189" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O189" s="6"/>
     </row>
-    <row r="190" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="190" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O190" s="6"/>
     </row>
-    <row r="191" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="191" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O191" s="6"/>
     </row>
-    <row r="192" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="192" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O192" s="6"/>
     </row>
-    <row r="193" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="193" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O193" s="6"/>
     </row>
-    <row r="194" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="194" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O194" s="6"/>
     </row>
-    <row r="195" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="195" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O195" s="6"/>
     </row>
-    <row r="196" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="196" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O196" s="6"/>
     </row>
-    <row r="197" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="197" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O197" s="6"/>
     </row>
-    <row r="198" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="198" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O198" s="6"/>
     </row>
-    <row r="199" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="199" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O199" s="6"/>
     </row>
-    <row r="200" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="200" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O200" s="6"/>
     </row>
-    <row r="201" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="201" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O201" s="6"/>
     </row>
-    <row r="202" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="202" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O202" s="6"/>
     </row>
-    <row r="203" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="203" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O203" s="6"/>
     </row>
-    <row r="204" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="204" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O204" s="6"/>
     </row>
-    <row r="205" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="205" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O205" s="6"/>
     </row>
-    <row r="206" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="206" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O206" s="6"/>
     </row>
-    <row r="207" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="207" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O207" s="6"/>
     </row>
-    <row r="208" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="208" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O208" s="6"/>
     </row>
-    <row r="209" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="209" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O209" s="6"/>
     </row>
-    <row r="210" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="210" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O210" s="6"/>
     </row>
-    <row r="211" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="211" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O211" s="6"/>
     </row>
-    <row r="212" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="212" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O212" s="6"/>
     </row>
-    <row r="213" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="213" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O213" s="6"/>
     </row>
-    <row r="214" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="214" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O214" s="6"/>
     </row>
-    <row r="215" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="215" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O215" s="6"/>
     </row>
-    <row r="216" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="216" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O216" s="6"/>
     </row>
-    <row r="217" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="217" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O217" s="6"/>
     </row>
-    <row r="218" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="218" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O218" s="6"/>
     </row>
-    <row r="219" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="219" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O219" s="6"/>
     </row>
-    <row r="220" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="220" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O220" s="6"/>
     </row>
-    <row r="221" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="221" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O221" s="6"/>
     </row>
-    <row r="222" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="222" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O222" s="6"/>
     </row>
-    <row r="223" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="223" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O223" s="6"/>
     </row>
-    <row r="224" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="224" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O224" s="6"/>
     </row>
-    <row r="225" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="225" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O225" s="6"/>
     </row>
-    <row r="226" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="226" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O226" s="6"/>
     </row>
-    <row r="227" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="227" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O227" s="6"/>
     </row>
-    <row r="228" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="228" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O228" s="6"/>
     </row>
-    <row r="229" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="229" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O229" s="6"/>
     </row>
-    <row r="230" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="230" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O230" s="6"/>
     </row>
-    <row r="231" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="231" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O231" s="6"/>
     </row>
-    <row r="232" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="232" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O232" s="6"/>
     </row>
-    <row r="233" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="233" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O233" s="6"/>
     </row>
-    <row r="234" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="234" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O234" s="6"/>
     </row>
-    <row r="235" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="235" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O235" s="6"/>
     </row>
-    <row r="236" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="236" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O236" s="6"/>
     </row>
-    <row r="237" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="237" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O237" s="6"/>
     </row>
-    <row r="238" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="238" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O238" s="6"/>
     </row>
-    <row r="239" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="239" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O239" s="6"/>
     </row>
-    <row r="240" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="240" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O240" s="6"/>
     </row>
-    <row r="241" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="241" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O241" s="6"/>
     </row>
-    <row r="242" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="242" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O242" s="6"/>
     </row>
-    <row r="243" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="243" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O243" s="6"/>
     </row>
-    <row r="244" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="244" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O244" s="6"/>
     </row>
-    <row r="245" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="245" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O245" s="6"/>
     </row>
-    <row r="246" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="246" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O246" s="6"/>
     </row>
-    <row r="247" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="247" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O247" s="6"/>
     </row>
-    <row r="248" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="248" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O248" s="6"/>
     </row>
-    <row r="249" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="249" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O249" s="6"/>
     </row>
-    <row r="250" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="250" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O250" s="6"/>
     </row>
-    <row r="251" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="251" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O251" s="6"/>
     </row>
-    <row r="252" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="252" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O252" s="6"/>
     </row>
-    <row r="253" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="253" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O253" s="6"/>
     </row>
-    <row r="254" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="254" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O254" s="6"/>
     </row>
-    <row r="255" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="255" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O255" s="6"/>
     </row>
-    <row r="256" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="256" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O256" s="6"/>
     </row>
-    <row r="257" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="257" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O257" s="6"/>
     </row>
-    <row r="258" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="258" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O258" s="6"/>
     </row>
-    <row r="259" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="259" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O259" s="6"/>
     </row>
-    <row r="260" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="260" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O260" s="6"/>
     </row>
-    <row r="261" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="261" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O261" s="6"/>
     </row>
-    <row r="262" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="262" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O262" s="6"/>
     </row>
-    <row r="263" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="263" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O263" s="6"/>
     </row>
-    <row r="264" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="264" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O264" s="6"/>
     </row>
-    <row r="265" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="265" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O265" s="6"/>
     </row>
-    <row r="266" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="266" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O266" s="6"/>
     </row>
-    <row r="267" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="267" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O267" s="6"/>
     </row>
-    <row r="268" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="268" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O268" s="6"/>
     </row>
-    <row r="269" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="269" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O269" s="6"/>
     </row>
-    <row r="270" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="270" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O270" s="6"/>
     </row>
-    <row r="271" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="271" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O271" s="6"/>
     </row>
-    <row r="272" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="272" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O272" s="6"/>
     </row>
-    <row r="273" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="273" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O273" s="6"/>
     </row>
-    <row r="274" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="274" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O274" s="6"/>
     </row>
-    <row r="275" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="275" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O275" s="6"/>
     </row>
-    <row r="276" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="276" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O276" s="6"/>
     </row>
-    <row r="277" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="277" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O277" s="6"/>
     </row>
-    <row r="278" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="278" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O278" s="6"/>
     </row>
-    <row r="279" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="279" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O279" s="6"/>
     </row>
-    <row r="280" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="280" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O280" s="6"/>
     </row>
-    <row r="281" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="281" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O281" s="6"/>
     </row>
-    <row r="282" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="282" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O282" s="6"/>
     </row>
-    <row r="283" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="283" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O283" s="6"/>
     </row>
-    <row r="284" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="284" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O284" s="6"/>
     </row>
-    <row r="285" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="285" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O285" s="6"/>
     </row>
-    <row r="286" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="286" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O286" s="6"/>
     </row>
-    <row r="287" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="287" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O287" s="6"/>
     </row>
-    <row r="288" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="288" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O288" s="6"/>
     </row>
-    <row r="289" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="289" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O289" s="6"/>
     </row>
-    <row r="290" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="290" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O290" s="6"/>
     </row>
-    <row r="291" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="291" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O291" s="6"/>
     </row>
-    <row r="292" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="292" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O292" s="6"/>
     </row>
-    <row r="293" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="293" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O293" s="6"/>
     </row>
-    <row r="294" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="294" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O294" s="6"/>
     </row>
-    <row r="295" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="295" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O295" s="6"/>
     </row>
-    <row r="296" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="296" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O296" s="6"/>
     </row>
-    <row r="297" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="297" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O297" s="6"/>
     </row>
-    <row r="298" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="298" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O298" s="6"/>
     </row>
-    <row r="299" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="299" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O299" s="6"/>
     </row>
-    <row r="300" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="300" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O300" s="6"/>
     </row>
-    <row r="301" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="301" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O301" s="6"/>
     </row>
-    <row r="302" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="302" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O302" s="6"/>
     </row>
-    <row r="303" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="303" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O303" s="6"/>
     </row>
-    <row r="304" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="304" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O304" s="6"/>
     </row>
-    <row r="305" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="305" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O305" s="6"/>
     </row>
-    <row r="306" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="306" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O306" s="6"/>
     </row>
-    <row r="307" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="307" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O307" s="6"/>
     </row>
-    <row r="308" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="308" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O308" s="6"/>
     </row>
-    <row r="309" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="309" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O309" s="6"/>
     </row>
-    <row r="310" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="310" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O310" s="6"/>
     </row>
-    <row r="311" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="311" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O311" s="6"/>
     </row>
-    <row r="312" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="312" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O312" s="6"/>
     </row>
-    <row r="313" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="313" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O313" s="6"/>
     </row>
-    <row r="314" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="314" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O314" s="6"/>
     </row>
-    <row r="315" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="315" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O315" s="6"/>
     </row>
-    <row r="316" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="316" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O316" s="6"/>
     </row>
-    <row r="317" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="317" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O317" s="6"/>
     </row>
-    <row r="318" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="318" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O318" s="6"/>
     </row>
-    <row r="319" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="319" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O319" s="6"/>
     </row>
-    <row r="320" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="320" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O320" s="6"/>
     </row>
-    <row r="321" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="321" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O321" s="6"/>
     </row>
-    <row r="322" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="322" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O322" s="6"/>
     </row>
-    <row r="323" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="323" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O323" s="6"/>
     </row>
-    <row r="324" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="324" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O324" s="6"/>
     </row>
-    <row r="325" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="325" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O325" s="6"/>
     </row>
-    <row r="326" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="326" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O326" s="6"/>
     </row>
-    <row r="327" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="327" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O327" s="6"/>
     </row>
-    <row r="328" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="328" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O328" s="6"/>
     </row>
-    <row r="329" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="329" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O329" s="6"/>
     </row>
-    <row r="330" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="330" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O330" s="6"/>
     </row>
-    <row r="331" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="331" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O331" s="6"/>
     </row>
-    <row r="332" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="332" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O332" s="6"/>
     </row>
-    <row r="333" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="333" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O333" s="6"/>
     </row>
-    <row r="334" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="334" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O334" s="6"/>
     </row>
-    <row r="335" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="335" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O335" s="6"/>
     </row>
-    <row r="336" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="336" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O336" s="6"/>
     </row>
-    <row r="337" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="337" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O337" s="6"/>
     </row>
-    <row r="338" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="338" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O338" s="6"/>
     </row>
-    <row r="339" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="339" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O339" s="6"/>
     </row>
-    <row r="340" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="340" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O340" s="6"/>
     </row>
-    <row r="341" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="341" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O341" s="6"/>
     </row>
-    <row r="342" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="342" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O342" s="6"/>
     </row>
-    <row r="343" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="343" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O343" s="6"/>
     </row>
-    <row r="344" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="344" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O344" s="6"/>
     </row>
-    <row r="345" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="345" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O345" s="6"/>
     </row>
-    <row r="346" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="346" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O346" s="6"/>
     </row>
-    <row r="347" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="347" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O347" s="6"/>
     </row>
-    <row r="348" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="348" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O348" s="6"/>
     </row>
-    <row r="349" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="349" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O349" s="6"/>
     </row>
-    <row r="350" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="350" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O350" s="6"/>
     </row>
-    <row r="351" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="351" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O351" s="6"/>
     </row>
-    <row r="352" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="352" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O352" s="6"/>
     </row>
-    <row r="353" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="353" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O353" s="6"/>
     </row>
-    <row r="354" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="354" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O354" s="6"/>
     </row>
-    <row r="355" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="355" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O355" s="6"/>
     </row>
-    <row r="356" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="356" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O356" s="6"/>
     </row>
-    <row r="357" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="357" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O357" s="6"/>
     </row>
-    <row r="358" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="358" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O358" s="6"/>
     </row>
-    <row r="359" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="359" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O359" s="6"/>
     </row>
-    <row r="360" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="360" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O360" s="6"/>
     </row>
-    <row r="361" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="361" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O361" s="6"/>
     </row>
-    <row r="362" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="362" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O362" s="6"/>
     </row>
-    <row r="363" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="363" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O363" s="6"/>
     </row>
-    <row r="364" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="364" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O364" s="6"/>
     </row>
-    <row r="365" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="365" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O365" s="6"/>
     </row>
-    <row r="366" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="366" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O366" s="6"/>
     </row>
-    <row r="367" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="367" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O367" s="6"/>
     </row>
-    <row r="368" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="368" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O368" s="6"/>
     </row>
-    <row r="369" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="369" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O369" s="6"/>
     </row>
-    <row r="370" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="370" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O370" s="6"/>
     </row>
-    <row r="371" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="371" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O371" s="6"/>
     </row>
-    <row r="372" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="372" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O372" s="6"/>
     </row>
-    <row r="373" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="373" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O373" s="6"/>
     </row>
-    <row r="374" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="374" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O374" s="6"/>
     </row>
-    <row r="375" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="375" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O375" s="6"/>
     </row>
-    <row r="376" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="376" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O376" s="6"/>
     </row>
-    <row r="377" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="377" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O377" s="6"/>
     </row>
-    <row r="378" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="378" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O378" s="6"/>
     </row>
-    <row r="379" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="379" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O379" s="6"/>
     </row>
-    <row r="380" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="380" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O380" s="6"/>
     </row>
-    <row r="381" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="381" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O381" s="6"/>
     </row>
-    <row r="382" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="382" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O382" s="6"/>
     </row>
-    <row r="383" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="383" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O383" s="6"/>
     </row>
-    <row r="384" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="384" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O384" s="6"/>
     </row>
-    <row r="385" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="385" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O385" s="6"/>
     </row>
-    <row r="386" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="386" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O386" s="6"/>
     </row>
-    <row r="387" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="387" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O387" s="6"/>
     </row>
-    <row r="388" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="388" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O388" s="6"/>
     </row>
-    <row r="389" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="389" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O389" s="6"/>
     </row>
-    <row r="390" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="390" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O390" s="6"/>
     </row>
-    <row r="391" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="391" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O391" s="6"/>
     </row>
-    <row r="392" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="392" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O392" s="6"/>
     </row>
-    <row r="393" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="393" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O393" s="6"/>
     </row>
-    <row r="394" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="394" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O394" s="6"/>
     </row>
-    <row r="395" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="395" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O395" s="6"/>
     </row>
-    <row r="396" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="396" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O396" s="6"/>
     </row>
-    <row r="397" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="397" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O397" s="6"/>
     </row>
-    <row r="398" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="398" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O398" s="6"/>
     </row>
-    <row r="399" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="399" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O399" s="6"/>
     </row>
-    <row r="400" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="400" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O400" s="6"/>
     </row>
-    <row r="401" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="401" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O401" s="6"/>
     </row>
-    <row r="402" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="402" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O402" s="6"/>
     </row>
-    <row r="403" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="403" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O403" s="6"/>
     </row>
-    <row r="404" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="404" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O404" s="6"/>
     </row>
-    <row r="405" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="405" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O405" s="6"/>
     </row>
-    <row r="406" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="406" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O406" s="6"/>
     </row>
-    <row r="407" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="407" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O407" s="6"/>
     </row>
-    <row r="408" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="408" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O408" s="6"/>
     </row>
-    <row r="409" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="409" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O409" s="6"/>
     </row>
-    <row r="410" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="410" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O410" s="6"/>
     </row>
-    <row r="411" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="411" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O411" s="6"/>
     </row>
-    <row r="412" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="412" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O412" s="6"/>
     </row>
-    <row r="413" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="413" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O413" s="6"/>
     </row>
-    <row r="414" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="414" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O414" s="6"/>
     </row>
-    <row r="415" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="415" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O415" s="6"/>
     </row>
-    <row r="416" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="416" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O416" s="6"/>
     </row>
-    <row r="417" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="417" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O417" s="6"/>
     </row>
-    <row r="418" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="418" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O418" s="6"/>
     </row>
-    <row r="419" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="419" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O419" s="6"/>
     </row>
-    <row r="420" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="420" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O420" s="6"/>
     </row>
-    <row r="421" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="421" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O421" s="6"/>
     </row>
-    <row r="422" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="422" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O422" s="6"/>
     </row>
-    <row r="423" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="423" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O423" s="6"/>
     </row>
-    <row r="424" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="424" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O424" s="6"/>
     </row>
-    <row r="425" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="425" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O425" s="6"/>
     </row>
-    <row r="426" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="426" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O426" s="6"/>
     </row>
-    <row r="427" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="427" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O427" s="6"/>
     </row>
-    <row r="428" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="428" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O428" s="6"/>
     </row>
-    <row r="429" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="429" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O429" s="6"/>
     </row>
-    <row r="430" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="430" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O430" s="6"/>
     </row>
-    <row r="431" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="431" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O431" s="6"/>
     </row>
-    <row r="432" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="432" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O432" s="6"/>
     </row>
-    <row r="433" spans="15:15" x14ac:dyDescent="0.45">
+    <row r="433" spans="15:15" x14ac:dyDescent="0.3">
       <c r="O433" s="6"/>
     </row>
   </sheetData>

--- a/아이템 도감.xlsx
+++ b/아이템 도감.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\CapstoneProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hcw97\Desktop\CapstoneProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A60576B-35F5-42A5-BAF1-F182CA587DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97ADA58A-AACE-43DB-861F-BC4435306B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{AEFF7BDA-CB51-4C25-A75C-46A97EA8EBD6}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{AEFF7BDA-CB51-4C25-A75C-46A97EA8EBD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="289">
   <si>
     <t>item_id</t>
   </si>
@@ -51,939 +51,944 @@
     <t>weight</t>
   </si>
   <si>
+    <t>effect_value</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>grade</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>max_stack</t>
+  </si>
+  <si>
+    <t>is_throwable</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>heal_amount</t>
+  </si>
+  <si>
+    <t>energy_amount</t>
+  </si>
+  <si>
+    <t>낡은 삽</t>
+  </si>
+  <si>
+    <t>평범한 삽</t>
+  </si>
+  <si>
+    <t>예리한 삽</t>
+  </si>
+  <si>
+    <t>튼튼한 삽</t>
+  </si>
+  <si>
+    <t>낡은 도끼</t>
+  </si>
+  <si>
+    <t>평범한 도끼</t>
+  </si>
+  <si>
+    <t>예리한 도끼</t>
+  </si>
+  <si>
+    <t>튼튼한 도끼</t>
+  </si>
+  <si>
+    <t>낡은 곡괭이</t>
+  </si>
+  <si>
+    <t>평범한 곡괭이</t>
+  </si>
+  <si>
+    <t>예리한 곡괭이</t>
+  </si>
+  <si>
+    <t>튼튼한 곡괭이</t>
+  </si>
+  <si>
+    <t>드릴</t>
+  </si>
+  <si>
+    <t>뿅망치</t>
+  </si>
+  <si>
+    <t>마법 지팡이</t>
+  </si>
+  <si>
+    <t>비비탄 총</t>
+  </si>
+  <si>
+    <t>장난감 칼</t>
+  </si>
+  <si>
+    <t>싱싱한 고기</t>
+  </si>
+  <si>
+    <t>냉동 만두</t>
+  </si>
+  <si>
+    <t>브로콜리</t>
+  </si>
+  <si>
+    <t>두리안</t>
+  </si>
+  <si>
+    <t>바나나</t>
+  </si>
+  <si>
+    <t>과자</t>
+  </si>
+  <si>
+    <t>상한 귤</t>
+  </si>
+  <si>
+    <t>싹난 감자</t>
+  </si>
+  <si>
+    <t>초콜릿</t>
+  </si>
+  <si>
+    <t>눈알 사탕</t>
+  </si>
+  <si>
+    <t>오렌지 주스</t>
+  </si>
+  <si>
+    <t>추로스</t>
+  </si>
+  <si>
+    <t>솜사탕</t>
+  </si>
+  <si>
+    <t>아이스크림</t>
+  </si>
+  <si>
+    <t>먹다 남은 나쵸</t>
+  </si>
+  <si>
+    <t>젤리빈</t>
+  </si>
+  <si>
+    <t>상한닭다리</t>
+  </si>
+  <si>
+    <t>곰팡이 치즈</t>
+  </si>
+  <si>
+    <t>상한 요거트</t>
+  </si>
+  <si>
+    <t>남긴 핫초코</t>
+  </si>
+  <si>
+    <t>남긴 케이크</t>
+  </si>
+  <si>
+    <t>조금 남은 과자</t>
+  </si>
+  <si>
+    <t>피자 박스</t>
+  </si>
+  <si>
+    <t>상한 생선</t>
+  </si>
+  <si>
+    <t>남긴 도시락</t>
+  </si>
+  <si>
+    <t>풍선</t>
+  </si>
+  <si>
+    <t>부부젤라</t>
+  </si>
+  <si>
+    <t>적 몬스터가 최우선으로 반응</t>
+  </si>
+  <si>
+    <t>양동이</t>
+  </si>
+  <si>
+    <t>몬스터 머리에 씌워지며 시야 차단! (유령 몬스터에는 사용 불가!)</t>
+  </si>
+  <si>
+    <t>바나나 껍질</t>
+  </si>
+  <si>
+    <t>밟으면 미끄러지며 스턴(2초)</t>
+  </si>
+  <si>
+    <t>구멍난 양말</t>
+  </si>
+  <si>
+    <t>끈적 슬라임</t>
+  </si>
+  <si>
+    <t>저금통</t>
+  </si>
+  <si>
+    <t>메모지</t>
+  </si>
+  <si>
+    <t>랜덤한 메모를 출력한다.</t>
+  </si>
+  <si>
+    <t>거미줄</t>
+  </si>
+  <si>
+    <t>덫</t>
+  </si>
+  <si>
+    <t>녹슨 동전</t>
+  </si>
+  <si>
+    <t>유리 구슬</t>
+  </si>
+  <si>
+    <t>오래된 숟가락</t>
+  </si>
+  <si>
+    <t>빈 물병</t>
+  </si>
+  <si>
+    <t>조개 껍데기</t>
+  </si>
+  <si>
+    <t>지도 조각</t>
+  </si>
+  <si>
+    <t>목각 인형</t>
+  </si>
+  <si>
+    <t>종이 비행기</t>
+  </si>
+  <si>
+    <t>병뚜껑</t>
+  </si>
+  <si>
+    <t>테니스 공</t>
+  </si>
+  <si>
+    <t>고장난 세탁기</t>
+  </si>
+  <si>
+    <t>생선 뼈</t>
+  </si>
+  <si>
+    <t>나무 단추</t>
+  </si>
+  <si>
+    <t>빈 깡통</t>
+  </si>
+  <si>
+    <t>벽돌</t>
+  </si>
+  <si>
+    <t>금 간 접시</t>
+  </si>
+  <si>
+    <t>낡은 부츠</t>
+  </si>
+  <si>
+    <t>고장난 시계</t>
+  </si>
+  <si>
+    <t>구리 반지</t>
+  </si>
+  <si>
+    <t>비단 손수건</t>
+  </si>
+  <si>
+    <t>진주 귀걸이</t>
+  </si>
+  <si>
+    <t>황동 촛대</t>
+  </si>
+  <si>
+    <t>자수정 조각</t>
+  </si>
+  <si>
+    <t>고대 점토판</t>
+  </si>
+  <si>
+    <t>청동 거울</t>
+  </si>
+  <si>
+    <t>프릴 리본</t>
+  </si>
+  <si>
+    <t>가죽 벨트</t>
+  </si>
+  <si>
+    <t>도자기 화병</t>
+  </si>
+  <si>
+    <t>복싱 글러브</t>
+  </si>
+  <si>
+    <t>차 열쇠</t>
+  </si>
+  <si>
+    <t>명품 가방</t>
+  </si>
+  <si>
+    <t>은 반지</t>
+  </si>
+  <si>
+    <t>수정 해골</t>
+  </si>
+  <si>
+    <t>바이킹 투구</t>
+  </si>
+  <si>
+    <t>무사의 검</t>
+  </si>
+  <si>
+    <t>옥 팔찌</t>
+  </si>
+  <si>
+    <t>보물 지도</t>
+  </si>
+  <si>
+    <t>기사 갑옷</t>
+  </si>
+  <si>
+    <t>골동품 타자기</t>
+  </si>
+  <si>
+    <t>다이아몬드 반지</t>
+  </si>
+  <si>
+    <t>유니콘 뿔</t>
+  </si>
+  <si>
+    <t>황금 성배</t>
+  </si>
+  <si>
+    <t>공룡 알 화석</t>
+  </si>
+  <si>
+    <t>운석 파편</t>
+  </si>
+  <si>
+    <t>저주받은 토템</t>
+  </si>
+  <si>
+    <t>불사조의 깃털</t>
+  </si>
+  <si>
+    <t>바다의 심장</t>
+  </si>
+  <si>
+    <t>엑스칼리버</t>
+  </si>
+  <si>
+    <t>현자의 돌</t>
+  </si>
+  <si>
+    <t>익지 않은 생고기.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>차갑고 딱딱한 냉동 만두.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>신선한 브로콜리.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>썩 좋지 않은 냄새가 풍긴다….</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>잘 익은 바나나. 껍질은 아무 데나 버리지 말자.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>질소로 빵빵하게 포장된 감자칩 과자.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>하얗게 곰팡이가 피어 있다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>귀여운 새싹이 보인다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>딸기 맛.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>오렌지 과즙 100%</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>놀이공원에 온 기분이 든다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>후후 불면 날아가는 솜사탕. 몸이 가벼워질 것 같다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>누군가 먹다 남긴 치즈맛 나쵸.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>콩 모양 젤리. 먹으면 마법 같은 맛이 난다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>상한 치킨. 한입 먹힌 흔적이 있다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>곰팡이 핀 치즈.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>맛있어 보이는 요거트. 시큼한 냄새가 난다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>누군가 마시던 핫초코.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>누군가 먹다 남긴 조각 케이크! 발걸음이 빨라질 만큼 맛있다!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>과자… 조금 남았다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>한 조각 반이 들어 있다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>새것 같은 달콤한 초콜릿.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>머리가 아플 정도로 차디찬 아이스크림.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>상한 생선… 냄새가 끔찍하다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>유통기한 임박 할인' 스티커가 붙어 있다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>몸이 가벼워진다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>10초간 이동 속도 30% 증가</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>10초간 점프 높이 20% 증가</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용 시 펑 터지는 소리가 난다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용 시 바나나 껍질 아이템 획득</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>10초간 채굴 속도 50% 증가</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>낙하 속도 느려짐.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>요란한 소리를 낼 수 있다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>머리에 씌울 수 있을 것 같다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>밟고 미끄러지지 않게 조심!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>구멍이 뚫려서 버려진 걸까?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>끈적한 슬라임. 쓸데는 없다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>흔들면 짤랑짤랑 소리가 난다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>누군가 남긴 메모.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>끈적한 거미줄. 닿으면 느려질 것 같다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>**유령에게도 효과 있음**</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>덫에 걸리면 5초간 움직이지 못한다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>밟은 대상의 이동속도를 7초간 감소시킨다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>평범한 삽.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>오래 쓸 수 있을 것 같은 튼튼한 삽.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>무엇이든 파낼 수 있을 것 같은 예리한 삽.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용된 세월이 느껴지는 삽.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용된 세월이 느껴지는 도끼.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>사용된 세월이 느껴지는 곡괭이.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>평범한 도끼.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>무엇이든 베어낼 수 있을 것 같은 예리한 도끼.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>오래 쓸 수 있을 것 같은 튼튼한 도끼.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>평범한 곡괭이.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>무엇이든 캐낼 수 있을 것 같은 예리한 곡괭이.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>오래 쓸 수 있을 것 같은 튼튼한 곡괭이.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>쓸모가 많은 전동 드릴.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>공 말고 다른 것도 쳐낼 수 있다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>**뿅뿅**</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>살상 능력은 없는 장난감 총.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>날카롭지 않아 안전하다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>마법을 쓸 수 있는 지팡이.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>duration</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_path</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip_ax</t>
+  </si>
+  <si>
+    <t>야구 방망이</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip_bat</t>
+  </si>
+  <si>
+    <t>Equip_magicwand</t>
+  </si>
+  <si>
+    <t>Equip_pick</t>
+  </si>
+  <si>
+    <t>Equip_shovel</t>
+  </si>
+  <si>
+    <t>Equip_squeaky_hammer</t>
+  </si>
+  <si>
+    <t>Equip_toysword</t>
+  </si>
+  <si>
+    <t>Food_banana</t>
+  </si>
+  <si>
+    <t>Food_broccoli</t>
+  </si>
+  <si>
+    <t>Food_cake</t>
+  </si>
+  <si>
+    <t>Food_candy</t>
+  </si>
+  <si>
+    <t>Food_candyfluff</t>
+  </si>
+  <si>
+    <t>Food_chocolate</t>
+  </si>
+  <si>
+    <t>Food_churros</t>
+  </si>
+  <si>
+    <t>Food_durian</t>
+  </si>
+  <si>
+    <t>Food_fish</t>
+  </si>
+  <si>
+    <t>Food_frozen_dumplings</t>
+  </si>
+  <si>
+    <t>Food_icecream</t>
+  </si>
+  <si>
+    <t>Food_jellybean</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Food_lunch</t>
+  </si>
+  <si>
+    <t>Food_mandarin</t>
+  </si>
+  <si>
+    <t>Food_meat</t>
+  </si>
+  <si>
+    <t>Food_Nachos</t>
+  </si>
+  <si>
+    <t>Food_orange_juice</t>
+  </si>
+  <si>
+    <t>Food_pizza</t>
+  </si>
+  <si>
+    <t>Food_potato</t>
+  </si>
+  <si>
+    <t>Food_snack</t>
+  </si>
+  <si>
+    <t>Food_snackbox</t>
+  </si>
+  <si>
+    <t>Food_yogurt</t>
+  </si>
+  <si>
+    <t>Food_cheese</t>
+  </si>
+  <si>
+    <t>Food_cocoa</t>
+  </si>
+  <si>
+    <t>Food_drumstick</t>
+  </si>
+  <si>
+    <t>Food_melonpan</t>
+  </si>
+  <si>
+    <t>멜론 빵</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>귀여운 멜론 모양의 맛있는 빵.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>유령 퇴치 스프레이</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>유령을 퇴치하는 스프레이</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equip_ghostspray</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>황금 주사위</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>C_Rusty_Coin</t>
+  </si>
+  <si>
+    <t>C_Old_Spoon</t>
+  </si>
+  <si>
+    <t>C_Empty_Bottle</t>
+  </si>
+  <si>
+    <t>C_Seashell</t>
+  </si>
+  <si>
+    <t>C_Scrap_Map</t>
+  </si>
+  <si>
+    <t>C_Wooden_Doll</t>
+  </si>
+  <si>
+    <t>C_Paper_Plane</t>
+  </si>
+  <si>
+    <t>C_Bottle_Cap</t>
+  </si>
+  <si>
+    <t>C_Tennis_Ball</t>
+  </si>
+  <si>
+    <t>C_Broken_Washing_Machine</t>
+  </si>
+  <si>
+    <t>C_Fish_Bone</t>
+  </si>
+  <si>
+    <t>C_Wooden_Button</t>
+  </si>
+  <si>
+    <t>C_Empty_Can</t>
+  </si>
+  <si>
+    <t>C_Brick</t>
+  </si>
+  <si>
+    <t>C_Cracked_Plate</t>
+  </si>
+  <si>
+    <t>C_Old_Boot</t>
+  </si>
+  <si>
+    <t>C_Broken_Clock</t>
+  </si>
+  <si>
+    <t>U_Copper_Ring</t>
+  </si>
+  <si>
+    <t>U_Silk_Handkerchief</t>
+  </si>
+  <si>
+    <t>U_Pearl_Earring</t>
+  </si>
+  <si>
+    <t>U_Brass_Canddlestick</t>
+  </si>
+  <si>
+    <t>U_Ancient_Clay_Tablet</t>
+  </si>
+  <si>
+    <t>U_Bronze_Mirror</t>
+  </si>
+  <si>
+    <t>에메랄드 브로치</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>R_Crystal_Skull</t>
+  </si>
+  <si>
+    <t>R_Emerald_Brooch</t>
+  </si>
+  <si>
+    <t>R_Silver_Ring</t>
+  </si>
+  <si>
+    <t>R_Viking_Helmet</t>
+  </si>
+  <si>
+    <t>U_Amethyst_Shard</t>
+  </si>
+  <si>
+    <t>U_Boxing_Glove</t>
+  </si>
+  <si>
+    <t>U_Car_Key</t>
+  </si>
+  <si>
+    <t>U_Ceramic_Vase</t>
+  </si>
+  <si>
+    <t>U_Frill_Ribbon</t>
+  </si>
+  <si>
+    <t>U_Golden Dice</t>
+  </si>
+  <si>
+    <t>U_Leather_Belt</t>
+  </si>
+  <si>
+    <t>U_Luxury_Bag</t>
+  </si>
+  <si>
+    <t>Etc_balloon</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc_trap</t>
+  </si>
+  <si>
+    <t>Etc_bananapeel</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc_cobweb</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc_memo</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc_oldsocks</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc_pail</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc_piggybank</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc_slime</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Etc_vuvuzela</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>C_Glass_Marble</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>R_Samurai_Katana</t>
+  </si>
+  <si>
+    <t>R_Jade_Bangle</t>
+  </si>
+  <si>
+    <t>R_Treasure_Map</t>
+  </si>
+  <si>
+    <t>R_Knight_Armor</t>
+  </si>
+  <si>
+    <t>R_Antique_Typewriter</t>
+  </si>
+  <si>
+    <t>E_Diamond_Ring</t>
+  </si>
+  <si>
+    <t>E_Unicorn_Horn</t>
+  </si>
+  <si>
+    <t>E_Golden_Chalice</t>
+  </si>
+  <si>
+    <t>E_Dinosaur_Egg_Fossil</t>
+  </si>
+  <si>
+    <t>E_Meteorite_Shard</t>
+  </si>
+  <si>
+    <t>E_Cursed_Totem</t>
+  </si>
+  <si>
+    <t>E_Chest_of_Gold</t>
+  </si>
+  <si>
+    <t>금화 상자</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>L_Phoenix_Feather</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>L_Heart_of_Ocean</t>
+  </si>
+  <si>
+    <t>L_Excalibur</t>
+  </si>
+  <si>
+    <t>L_Imperial_crown</t>
+  </si>
+  <si>
+    <t>황제의 왕관</t>
+  </si>
+  <si>
+    <t>L_Philosopher_Stone</t>
+  </si>
+  <si>
+    <t>attack_power</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>max_durability</t>
-  </si>
-  <si>
-    <t>effect_value</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>grade</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>price</t>
-  </si>
-  <si>
-    <t>max_stack</t>
-  </si>
-  <si>
-    <t>is_throwable</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>heal_amount</t>
-  </si>
-  <si>
-    <t>energy_amount</t>
-  </si>
-  <si>
-    <t>낡은 삽</t>
-  </si>
-  <si>
-    <t>평범한 삽</t>
-  </si>
-  <si>
-    <t>예리한 삽</t>
-  </si>
-  <si>
-    <t>튼튼한 삽</t>
-  </si>
-  <si>
-    <t>낡은 도끼</t>
-  </si>
-  <si>
-    <t>평범한 도끼</t>
-  </si>
-  <si>
-    <t>예리한 도끼</t>
-  </si>
-  <si>
-    <t>튼튼한 도끼</t>
-  </si>
-  <si>
-    <t>낡은 곡괭이</t>
-  </si>
-  <si>
-    <t>평범한 곡괭이</t>
-  </si>
-  <si>
-    <t>예리한 곡괭이</t>
-  </si>
-  <si>
-    <t>튼튼한 곡괭이</t>
-  </si>
-  <si>
-    <t>드릴</t>
-  </si>
-  <si>
-    <t>뿅망치</t>
-  </si>
-  <si>
-    <t>마법 지팡이</t>
-  </si>
-  <si>
-    <t>비비탄 총</t>
-  </si>
-  <si>
-    <t>장난감 칼</t>
-  </si>
-  <si>
-    <t>싱싱한 고기</t>
-  </si>
-  <si>
-    <t>냉동 만두</t>
-  </si>
-  <si>
-    <t>브로콜리</t>
-  </si>
-  <si>
-    <t>두리안</t>
-  </si>
-  <si>
-    <t>바나나</t>
-  </si>
-  <si>
-    <t>과자</t>
-  </si>
-  <si>
-    <t>상한 귤</t>
-  </si>
-  <si>
-    <t>싹난 감자</t>
-  </si>
-  <si>
-    <t>초콜릿</t>
-  </si>
-  <si>
-    <t>눈알 사탕</t>
-  </si>
-  <si>
-    <t>오렌지 주스</t>
-  </si>
-  <si>
-    <t>추로스</t>
-  </si>
-  <si>
-    <t>솜사탕</t>
-  </si>
-  <si>
-    <t>아이스크림</t>
-  </si>
-  <si>
-    <t>먹다 남은 나쵸</t>
-  </si>
-  <si>
-    <t>젤리빈</t>
-  </si>
-  <si>
-    <t>상한닭다리</t>
-  </si>
-  <si>
-    <t>곰팡이 치즈</t>
-  </si>
-  <si>
-    <t>상한 요거트</t>
-  </si>
-  <si>
-    <t>남긴 핫초코</t>
-  </si>
-  <si>
-    <t>남긴 케이크</t>
-  </si>
-  <si>
-    <t>조금 남은 과자</t>
-  </si>
-  <si>
-    <t>피자 박스</t>
-  </si>
-  <si>
-    <t>상한 생선</t>
-  </si>
-  <si>
-    <t>남긴 도시락</t>
-  </si>
-  <si>
-    <t>풍선</t>
-  </si>
-  <si>
-    <t>부부젤라</t>
-  </si>
-  <si>
-    <t>적 몬스터가 최우선으로 반응</t>
-  </si>
-  <si>
-    <t>양동이</t>
-  </si>
-  <si>
-    <t>몬스터 머리에 씌워지며 시야 차단! (유령 몬스터에는 사용 불가!)</t>
-  </si>
-  <si>
-    <t>바나나 껍질</t>
-  </si>
-  <si>
-    <t>밟으면 미끄러지며 스턴(2초)</t>
-  </si>
-  <si>
-    <t>구멍난 양말</t>
-  </si>
-  <si>
-    <t>끈적 슬라임</t>
-  </si>
-  <si>
-    <t>저금통</t>
-  </si>
-  <si>
-    <t>메모지</t>
-  </si>
-  <si>
-    <t>랜덤한 메모를 출력한다.</t>
-  </si>
-  <si>
-    <t>거미줄</t>
-  </si>
-  <si>
-    <t>덫</t>
-  </si>
-  <si>
-    <t>녹슨 동전</t>
-  </si>
-  <si>
-    <t>유리 구슬</t>
-  </si>
-  <si>
-    <t>오래된 숟가락</t>
-  </si>
-  <si>
-    <t>빈 물병</t>
-  </si>
-  <si>
-    <t>조개 껍데기</t>
-  </si>
-  <si>
-    <t>지도 조각</t>
-  </si>
-  <si>
-    <t>목각 인형</t>
-  </si>
-  <si>
-    <t>종이 비행기</t>
-  </si>
-  <si>
-    <t>병뚜껑</t>
-  </si>
-  <si>
-    <t>테니스 공</t>
-  </si>
-  <si>
-    <t>고장난 세탁기</t>
-  </si>
-  <si>
-    <t>생선 뼈</t>
-  </si>
-  <si>
-    <t>나무 단추</t>
-  </si>
-  <si>
-    <t>빈 깡통</t>
-  </si>
-  <si>
-    <t>벽돌</t>
-  </si>
-  <si>
-    <t>금 간 접시</t>
-  </si>
-  <si>
-    <t>낡은 부츠</t>
-  </si>
-  <si>
-    <t>고장난 시계</t>
-  </si>
-  <si>
-    <t>구리 반지</t>
-  </si>
-  <si>
-    <t>비단 손수건</t>
-  </si>
-  <si>
-    <t>진주 귀걸이</t>
-  </si>
-  <si>
-    <t>황동 촛대</t>
-  </si>
-  <si>
-    <t>자수정 조각</t>
-  </si>
-  <si>
-    <t>고대 점토판</t>
-  </si>
-  <si>
-    <t>청동 거울</t>
-  </si>
-  <si>
-    <t>프릴 리본</t>
-  </si>
-  <si>
-    <t>가죽 벨트</t>
-  </si>
-  <si>
-    <t>도자기 화병</t>
-  </si>
-  <si>
-    <t>복싱 글러브</t>
-  </si>
-  <si>
-    <t>차 열쇠</t>
-  </si>
-  <si>
-    <t>명품 가방</t>
-  </si>
-  <si>
-    <t>은 반지</t>
-  </si>
-  <si>
-    <t>수정 해골</t>
-  </si>
-  <si>
-    <t>바이킹 투구</t>
-  </si>
-  <si>
-    <t>무사의 검</t>
-  </si>
-  <si>
-    <t>옥 팔찌</t>
-  </si>
-  <si>
-    <t>보물 지도</t>
-  </si>
-  <si>
-    <t>기사 갑옷</t>
-  </si>
-  <si>
-    <t>골동품 타자기</t>
-  </si>
-  <si>
-    <t>다이아몬드 반지</t>
-  </si>
-  <si>
-    <t>유니콘 뿔</t>
-  </si>
-  <si>
-    <t>황금 성배</t>
-  </si>
-  <si>
-    <t>공룡 알 화석</t>
-  </si>
-  <si>
-    <t>운석 파편</t>
-  </si>
-  <si>
-    <t>저주받은 토템</t>
-  </si>
-  <si>
-    <t>불사조의 깃털</t>
-  </si>
-  <si>
-    <t>바다의 심장</t>
-  </si>
-  <si>
-    <t>엑스칼리버</t>
-  </si>
-  <si>
-    <t>현자의 돌</t>
-  </si>
-  <si>
-    <t>익지 않은 생고기.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>차갑고 딱딱한 냉동 만두.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>신선한 브로콜리.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>썩 좋지 않은 냄새가 풍긴다….</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>잘 익은 바나나. 껍질은 아무 데나 버리지 말자.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>질소로 빵빵하게 포장된 감자칩 과자.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>하얗게 곰팡이가 피어 있다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>귀여운 새싹이 보인다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>딸기 맛.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>오렌지 과즙 100%</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>놀이공원에 온 기분이 든다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>후후 불면 날아가는 솜사탕. 몸이 가벼워질 것 같다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>누군가 먹다 남긴 치즈맛 나쵸.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>콩 모양 젤리. 먹으면 마법 같은 맛이 난다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>상한 치킨. 한입 먹힌 흔적이 있다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>곰팡이 핀 치즈.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>맛있어 보이는 요거트. 시큼한 냄새가 난다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>누군가 마시던 핫초코.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>누군가 먹다 남긴 조각 케이크! 발걸음이 빨라질 만큼 맛있다!</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>과자… 조금 남았다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>한 조각 반이 들어 있다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>새것 같은 달콤한 초콜릿.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>머리가 아플 정도로 차디찬 아이스크림.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>상한 생선… 냄새가 끔찍하다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>유통기한 임박 할인' 스티커가 붙어 있다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>몸이 가벼워진다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>10초간 이동 속도 30% 증가</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>10초간 점프 높이 20% 증가</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>사용 시 펑 터지는 소리가 난다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>사용 시 바나나 껍질 아이템 획득</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>10초간 채굴 속도 50% 증가</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>낙하 속도 느려짐.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>요란한 소리를 낼 수 있다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>머리에 씌울 수 있을 것 같다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>밟고 미끄러지지 않게 조심!</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>구멍이 뚫려서 버려진 걸까?</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>끈적한 슬라임. 쓸데는 없다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>흔들면 짤랑짤랑 소리가 난다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>누군가 남긴 메모.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>끈적한 거미줄. 닿으면 느려질 것 같다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>**유령에게도 효과 있음**</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>덫에 걸리면 5초간 움직이지 못한다</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>밟은 대상의 이동속도를 7초간 감소시킨다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>평범한 삽.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>오래 쓸 수 있을 것 같은 튼튼한 삽.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>무엇이든 파낼 수 있을 것 같은 예리한 삽.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>사용된 세월이 느껴지는 삽.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>사용된 세월이 느껴지는 도끼.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>사용된 세월이 느껴지는 곡괭이.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>평범한 도끼.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>무엇이든 베어낼 수 있을 것 같은 예리한 도끼.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>오래 쓸 수 있을 것 같은 튼튼한 도끼.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>평범한 곡괭이.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>무엇이든 캐낼 수 있을 것 같은 예리한 곡괭이.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>오래 쓸 수 있을 것 같은 튼튼한 곡괭이.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>쓸모가 많은 전동 드릴.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>공 말고 다른 것도 쳐낼 수 있다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>**뿅뿅**</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>살상 능력은 없는 장난감 총.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>날카롭지 않아 안전하다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>마법을 쓸 수 있는 지팡이.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>duration</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon_path</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equip_ax</t>
-  </si>
-  <si>
-    <t>야구 방망이</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equip_bat</t>
-  </si>
-  <si>
-    <t>Equip_magicwand</t>
-  </si>
-  <si>
-    <t>Equip_pick</t>
-  </si>
-  <si>
-    <t>Equip_shovel</t>
-  </si>
-  <si>
-    <t>Equip_squeaky_hammer</t>
-  </si>
-  <si>
-    <t>Equip_toysword</t>
-  </si>
-  <si>
-    <t>Food_banana</t>
-  </si>
-  <si>
-    <t>Food_broccoli</t>
-  </si>
-  <si>
-    <t>Food_cake</t>
-  </si>
-  <si>
-    <t>Food_candy</t>
-  </si>
-  <si>
-    <t>Food_candyfluff</t>
-  </si>
-  <si>
-    <t>Food_chocolate</t>
-  </si>
-  <si>
-    <t>Food_churros</t>
-  </si>
-  <si>
-    <t>Food_durian</t>
-  </si>
-  <si>
-    <t>Food_fish</t>
-  </si>
-  <si>
-    <t>Food_frozen_dumplings</t>
-  </si>
-  <si>
-    <t>Food_icecream</t>
-  </si>
-  <si>
-    <t>Food_jellybean</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Food_lunch</t>
-  </si>
-  <si>
-    <t>Food_mandarin</t>
-  </si>
-  <si>
-    <t>Food_meat</t>
-  </si>
-  <si>
-    <t>Food_Nachos</t>
-  </si>
-  <si>
-    <t>Food_orange_juice</t>
-  </si>
-  <si>
-    <t>Food_pizza</t>
-  </si>
-  <si>
-    <t>Food_potato</t>
-  </si>
-  <si>
-    <t>Food_snack</t>
-  </si>
-  <si>
-    <t>Food_snackbox</t>
-  </si>
-  <si>
-    <t>Food_yogurt</t>
-  </si>
-  <si>
-    <t>Food_cheese</t>
-  </si>
-  <si>
-    <t>Food_cocoa</t>
-  </si>
-  <si>
-    <t>Food_drumstick</t>
-  </si>
-  <si>
-    <t>Food_melonpan</t>
-  </si>
-  <si>
-    <t>멜론 빵</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>귀여운 멜론 모양의 맛있는 빵.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>유령 퇴치 스프레이</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>유령을 퇴치하는 스프레이</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equip_ghostspray</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>황금 주사위</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>C_Rusty_Coin</t>
-  </si>
-  <si>
-    <t>C_Old_Spoon</t>
-  </si>
-  <si>
-    <t>C_Empty_Bottle</t>
-  </si>
-  <si>
-    <t>C_Seashell</t>
-  </si>
-  <si>
-    <t>C_Scrap_Map</t>
-  </si>
-  <si>
-    <t>C_Wooden_Doll</t>
-  </si>
-  <si>
-    <t>C_Paper_Plane</t>
-  </si>
-  <si>
-    <t>C_Bottle_Cap</t>
-  </si>
-  <si>
-    <t>C_Tennis_Ball</t>
-  </si>
-  <si>
-    <t>C_Broken_Washing_Machine</t>
-  </si>
-  <si>
-    <t>C_Fish_Bone</t>
-  </si>
-  <si>
-    <t>C_Wooden_Button</t>
-  </si>
-  <si>
-    <t>C_Empty_Can</t>
-  </si>
-  <si>
-    <t>C_Brick</t>
-  </si>
-  <si>
-    <t>C_Cracked_Plate</t>
-  </si>
-  <si>
-    <t>C_Old_Boot</t>
-  </si>
-  <si>
-    <t>C_Broken_Clock</t>
-  </si>
-  <si>
-    <t>U_Copper_Ring</t>
-  </si>
-  <si>
-    <t>U_Silk_Handkerchief</t>
-  </si>
-  <si>
-    <t>U_Pearl_Earring</t>
-  </si>
-  <si>
-    <t>U_Brass_Canddlestick</t>
-  </si>
-  <si>
-    <t>U_Ancient_Clay_Tablet</t>
-  </si>
-  <si>
-    <t>U_Bronze_Mirror</t>
-  </si>
-  <si>
-    <t>에메랄드 브로치</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>R_Crystal_Skull</t>
-  </si>
-  <si>
-    <t>R_Emerald_Brooch</t>
-  </si>
-  <si>
-    <t>R_Silver_Ring</t>
-  </si>
-  <si>
-    <t>R_Viking_Helmet</t>
-  </si>
-  <si>
-    <t>U_Amethyst_Shard</t>
-  </si>
-  <si>
-    <t>U_Boxing_Glove</t>
-  </si>
-  <si>
-    <t>U_Car_Key</t>
-  </si>
-  <si>
-    <t>U_Ceramic_Vase</t>
-  </si>
-  <si>
-    <t>U_Frill_Ribbon</t>
-  </si>
-  <si>
-    <t>U_Golden Dice</t>
-  </si>
-  <si>
-    <t>U_Leather_Belt</t>
-  </si>
-  <si>
-    <t>U_Luxury_Bag</t>
-  </si>
-  <si>
-    <t>Etc_balloon</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Etc_trap</t>
-  </si>
-  <si>
-    <t>Etc_bananapeel</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Etc_cobweb</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Etc_memo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Etc_oldsocks</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Etc_pail</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Etc_piggybank</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Etc_slime</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Etc_vuvuzela</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>C_Glass_Marble</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>R_Samurai_Katana</t>
-  </si>
-  <si>
-    <t>R_Jade_Bangle</t>
-  </si>
-  <si>
-    <t>R_Treasure_Map</t>
-  </si>
-  <si>
-    <t>R_Knight_Armor</t>
-  </si>
-  <si>
-    <t>R_Antique_Typewriter</t>
-  </si>
-  <si>
-    <t>E_Diamond_Ring</t>
-  </si>
-  <si>
-    <t>E_Unicorn_Horn</t>
-  </si>
-  <si>
-    <t>E_Golden_Chalice</t>
-  </si>
-  <si>
-    <t>E_Dinosaur_Egg_Fossil</t>
-  </si>
-  <si>
-    <t>E_Meteorite_Shard</t>
-  </si>
-  <si>
-    <t>E_Cursed_Totem</t>
-  </si>
-  <si>
-    <t>E_Chest_of_Gold</t>
-  </si>
-  <si>
-    <t>금화 상자</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>L_Phoenix_Feather</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>L_Heart_of_Ocean</t>
-  </si>
-  <si>
-    <t>L_Excalibur</t>
-  </si>
-  <si>
-    <t>L_Imperial_crown</t>
-  </si>
-  <si>
-    <t>황제의 왕관</t>
-  </si>
-  <si>
-    <t>L_Philosopher_Stone</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1254,9 +1259,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1294,7 +1299,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1400,7 +1405,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1542,7 +1547,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1550,28 +1555,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176CEBE0-28C6-4629-A760-C52146228B7D}">
-  <dimension ref="A1:Q433"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:R433"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.875" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="18.125" customWidth="1"/>
+    <col min="3" max="3" width="18.08203125" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
-    <col min="5" max="5" width="14.375" customWidth="1"/>
-    <col min="6" max="6" width="21.125" customWidth="1"/>
-    <col min="7" max="8" width="14.875" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" customWidth="1"/>
+    <col min="6" max="6" width="21.08203125" customWidth="1"/>
+    <col min="7" max="8" width="14.83203125" customWidth="1"/>
     <col min="9" max="9" width="14.25" customWidth="1"/>
-    <col min="10" max="10" width="12.875" customWidth="1"/>
-    <col min="11" max="11" width="15.625" customWidth="1"/>
-    <col min="12" max="12" width="19.125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="15.58203125" customWidth="1"/>
+    <col min="12" max="12" width="19.08203125" customWidth="1"/>
     <col min="13" max="13" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="54.625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="35.125" customWidth="1"/>
+    <col min="14" max="14" width="54.58203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="35.08203125" customWidth="1"/>
     <col min="16" max="16" width="56.25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="59.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="59.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="18" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1588,40 +1593,43 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" s="4" t="s">
+      <c r="K1" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="L1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="M1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="N1" s="3" t="s">
+      <c r="Q1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="P1" s="11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1632,17 +1640,17 @@
         <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E2">
         <v>2</v>
       </c>
       <c r="F2">
+        <v>-1</v>
+      </c>
+      <c r="G2">
         <v>10</v>
       </c>
-      <c r="G2">
-        <v>-1</v>
-      </c>
       <c r="H2">
         <v>-1</v>
       </c>
@@ -1656,22 +1664,25 @@
         <v>-1</v>
       </c>
       <c r="L2">
+        <v>-1</v>
+      </c>
+      <c r="M2">
         <v>200</v>
       </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-      <c r="N2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="P2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1682,17 +1693,17 @@
         <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3">
+        <v>-1</v>
+      </c>
+      <c r="G3">
         <v>20</v>
       </c>
-      <c r="G3">
-        <v>-1</v>
-      </c>
       <c r="H3">
         <v>-1</v>
       </c>
@@ -1706,20 +1717,23 @@
         <v>-1</v>
       </c>
       <c r="L3">
+        <v>-1</v>
+      </c>
+      <c r="M3">
         <v>400</v>
       </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3" t="b">
-        <v>1</v>
-      </c>
-      <c r="O3" s="6"/>
-      <c r="P3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P3" s="6"/>
+      <c r="Q3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1730,17 +1744,17 @@
         <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4">
+        <v>-1</v>
+      </c>
+      <c r="G4">
         <v>30</v>
       </c>
-      <c r="G4">
-        <v>-1</v>
-      </c>
       <c r="H4">
         <v>-1</v>
       </c>
@@ -1754,20 +1768,23 @@
         <v>-1</v>
       </c>
       <c r="L4">
+        <v>-1</v>
+      </c>
+      <c r="M4">
         <v>600</v>
       </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-      <c r="N4" t="b">
-        <v>1</v>
-      </c>
-      <c r="O4" s="6"/>
-      <c r="P4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4" t="b">
+        <v>1</v>
+      </c>
+      <c r="P4" s="6"/>
+      <c r="Q4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1778,17 +1795,17 @@
         <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5">
+        <v>-1</v>
+      </c>
+      <c r="G5">
         <v>40</v>
       </c>
-      <c r="G5">
-        <v>-1</v>
-      </c>
       <c r="H5">
         <v>-1</v>
       </c>
@@ -1802,20 +1819,23 @@
         <v>-1</v>
       </c>
       <c r="L5">
+        <v>-1</v>
+      </c>
+      <c r="M5">
         <v>900</v>
       </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-      <c r="N5" t="b">
-        <v>1</v>
-      </c>
-      <c r="O5" s="6"/>
-      <c r="P5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5" t="b">
+        <v>1</v>
+      </c>
+      <c r="P5" s="6"/>
+      <c r="Q5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1826,17 +1846,17 @@
         <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
       <c r="F6">
+        <v>-1</v>
+      </c>
+      <c r="G6">
         <v>30</v>
       </c>
-      <c r="G6">
-        <v>-1</v>
-      </c>
       <c r="H6">
         <v>-1</v>
       </c>
@@ -1850,22 +1870,25 @@
         <v>-1</v>
       </c>
       <c r="L6">
+        <v>-1</v>
+      </c>
+      <c r="M6">
         <v>300</v>
       </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-      <c r="N6" t="b">
-        <v>1</v>
-      </c>
-      <c r="O6" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="P6" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6" t="b">
+        <v>1</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1876,17 +1899,17 @@
         <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7">
+        <v>-1</v>
+      </c>
+      <c r="G7">
         <v>50</v>
       </c>
-      <c r="G7">
-        <v>-1</v>
-      </c>
       <c r="H7">
         <v>-1</v>
       </c>
@@ -1900,20 +1923,23 @@
         <v>-1</v>
       </c>
       <c r="L7">
+        <v>-1</v>
+      </c>
+      <c r="M7">
         <v>500</v>
       </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-      <c r="N7" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" s="6"/>
-      <c r="P7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7" t="b">
+        <v>1</v>
+      </c>
+      <c r="P7" s="6"/>
+      <c r="Q7" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1924,17 +1950,17 @@
         <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8">
         <v>2</v>
       </c>
       <c r="F8">
+        <v>-1</v>
+      </c>
+      <c r="G8">
         <v>80</v>
       </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
       <c r="H8">
         <v>-1</v>
       </c>
@@ -1948,20 +1974,23 @@
         <v>-1</v>
       </c>
       <c r="L8">
+        <v>-1</v>
+      </c>
+      <c r="M8">
         <v>800</v>
       </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-      <c r="N8" t="b">
-        <v>1</v>
-      </c>
-      <c r="O8" s="6"/>
-      <c r="P8" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8" t="b">
+        <v>1</v>
+      </c>
+      <c r="P8" s="6"/>
+      <c r="Q8" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1972,17 +2001,17 @@
         <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E9">
         <v>2</v>
       </c>
       <c r="F9">
+        <v>-1</v>
+      </c>
+      <c r="G9">
         <v>120</v>
       </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
       <c r="H9">
         <v>-1</v>
       </c>
@@ -1996,20 +2025,23 @@
         <v>-1</v>
       </c>
       <c r="L9">
+        <v>-1</v>
+      </c>
+      <c r="M9">
         <v>1200</v>
       </c>
-      <c r="M9">
-        <v>1</v>
-      </c>
-      <c r="N9" t="b">
-        <v>1</v>
-      </c>
-      <c r="O9" s="6"/>
-      <c r="P9" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9" t="b">
+        <v>1</v>
+      </c>
+      <c r="P9" s="6"/>
+      <c r="Q9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2020,17 +2052,17 @@
         <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E10">
         <v>2</v>
       </c>
       <c r="F10">
+        <v>-1</v>
+      </c>
+      <c r="G10">
         <v>80</v>
       </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
       <c r="H10">
         <v>-1</v>
       </c>
@@ -2044,22 +2076,25 @@
         <v>-1</v>
       </c>
       <c r="L10">
+        <v>-1</v>
+      </c>
+      <c r="M10">
         <v>350</v>
       </c>
-      <c r="M10">
-        <v>1</v>
-      </c>
-      <c r="N10" t="b">
-        <v>1</v>
-      </c>
-      <c r="O10" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="P10" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10" t="b">
+        <v>1</v>
+      </c>
+      <c r="P10" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2070,17 +2105,17 @@
         <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E11">
         <v>2</v>
       </c>
       <c r="F11">
+        <v>-1</v>
+      </c>
+      <c r="G11">
         <v>100</v>
       </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
       <c r="H11">
         <v>-1</v>
       </c>
@@ -2094,20 +2129,23 @@
         <v>-1</v>
       </c>
       <c r="L11">
+        <v>-1</v>
+      </c>
+      <c r="M11">
         <v>600</v>
       </c>
-      <c r="M11">
-        <v>1</v>
-      </c>
-      <c r="N11" t="b">
-        <v>1</v>
-      </c>
-      <c r="O11" s="6"/>
-      <c r="P11" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11" t="b">
+        <v>1</v>
+      </c>
+      <c r="P11" s="6"/>
+      <c r="Q11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2118,17 +2156,17 @@
         <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E12">
         <v>2</v>
       </c>
       <c r="F12">
+        <v>-1</v>
+      </c>
+      <c r="G12">
         <v>130</v>
       </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
       <c r="H12">
         <v>-1</v>
       </c>
@@ -2142,20 +2180,23 @@
         <v>-1</v>
       </c>
       <c r="L12">
+        <v>-1</v>
+      </c>
+      <c r="M12">
         <v>1000</v>
       </c>
-      <c r="M12">
-        <v>1</v>
-      </c>
-      <c r="N12" t="b">
-        <v>1</v>
-      </c>
-      <c r="O12" s="6"/>
-      <c r="P12" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12" t="b">
+        <v>1</v>
+      </c>
+      <c r="P12" s="6"/>
+      <c r="Q12" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2166,17 +2207,17 @@
         <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E13">
         <v>2</v>
       </c>
       <c r="F13">
+        <v>-1</v>
+      </c>
+      <c r="G13">
         <v>170</v>
       </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
       <c r="H13">
         <v>-1</v>
       </c>
@@ -2190,20 +2231,23 @@
         <v>-1</v>
       </c>
       <c r="L13">
+        <v>-1</v>
+      </c>
+      <c r="M13">
         <v>1500</v>
       </c>
-      <c r="M13">
-        <v>1</v>
-      </c>
-      <c r="N13" t="b">
-        <v>1</v>
-      </c>
-      <c r="O13" s="6"/>
-      <c r="P13" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13" t="b">
+        <v>1</v>
+      </c>
+      <c r="P13" s="6"/>
+      <c r="Q13" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2214,17 +2258,17 @@
         <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E14">
         <v>2</v>
       </c>
       <c r="F14">
+        <v>-1</v>
+      </c>
+      <c r="G14">
         <v>300</v>
       </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
       <c r="H14">
         <v>-1</v>
       </c>
@@ -2238,20 +2282,23 @@
         <v>-1</v>
       </c>
       <c r="L14">
+        <v>-1</v>
+      </c>
+      <c r="M14">
         <v>100000</v>
       </c>
-      <c r="M14">
-        <v>1</v>
-      </c>
-      <c r="N14" t="b">
-        <v>1</v>
-      </c>
-      <c r="O14" s="6"/>
-      <c r="P14" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14" t="b">
+        <v>1</v>
+      </c>
+      <c r="P14" s="6"/>
+      <c r="Q14" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2262,13 +2309,13 @@
         <v>150</v>
       </c>
       <c r="D15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E15">
         <v>2</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="G15">
         <v>-1</v>
@@ -2286,22 +2333,25 @@
         <v>-1</v>
       </c>
       <c r="L15">
+        <v>-1</v>
+      </c>
+      <c r="M15">
         <v>300</v>
       </c>
-      <c r="M15">
-        <v>1</v>
-      </c>
-      <c r="N15" t="b">
-        <v>1</v>
-      </c>
-      <c r="O15" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="P15" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15" t="b">
+        <v>1</v>
+      </c>
+      <c r="P15" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2312,16 +2362,16 @@
         <v>150</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E16">
         <v>2</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="H16">
         <v>-1</v>
@@ -2336,22 +2386,25 @@
         <v>-1</v>
       </c>
       <c r="L16">
+        <v>-1</v>
+      </c>
+      <c r="M16">
         <v>500</v>
       </c>
-      <c r="M16">
-        <v>1</v>
-      </c>
-      <c r="N16" t="b">
-        <v>1</v>
-      </c>
-      <c r="O16" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="P16" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16" t="b">
+        <v>1</v>
+      </c>
+      <c r="P16" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A17" s="13">
         <v>16</v>
       </c>
@@ -2362,17 +2415,17 @@
         <v>151</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E17">
         <v>2</v>
       </c>
       <c r="F17">
+        <v>-1</v>
+      </c>
+      <c r="G17">
         <v>10</v>
       </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
       <c r="H17">
         <v>-1</v>
       </c>
@@ -2386,22 +2439,25 @@
         <v>-1</v>
       </c>
       <c r="L17">
+        <v>-1</v>
+      </c>
+      <c r="M17">
         <v>350</v>
       </c>
-      <c r="M17">
-        <v>1</v>
-      </c>
-      <c r="N17" t="b">
-        <v>1</v>
-      </c>
-      <c r="O17" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="P17" t="s">
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17" t="b">
+        <v>1</v>
+      </c>
+      <c r="P17" s="6" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q17" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2412,7 +2468,7 @@
         <v>151</v>
       </c>
       <c r="D18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -2436,22 +2492,25 @@
         <v>-1</v>
       </c>
       <c r="L18">
+        <v>-1</v>
+      </c>
+      <c r="M18">
         <v>350</v>
       </c>
-      <c r="M18">
-        <v>1</v>
-      </c>
-      <c r="N18" t="b">
-        <v>1</v>
-      </c>
-      <c r="O18" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="P18" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18" t="b">
+        <v>1</v>
+      </c>
+      <c r="P18" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2462,7 +2521,7 @@
         <v>151</v>
       </c>
       <c r="D19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E19">
         <v>2</v>
@@ -2486,20 +2545,23 @@
         <v>-1</v>
       </c>
       <c r="L19">
+        <v>-1</v>
+      </c>
+      <c r="M19">
         <v>400</v>
       </c>
-      <c r="M19">
-        <v>1</v>
-      </c>
-      <c r="N19" t="b">
-        <v>1</v>
-      </c>
-      <c r="O19" s="6"/>
-      <c r="P19" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19" t="b">
+        <v>1</v>
+      </c>
+      <c r="P19" s="6"/>
+      <c r="Q19" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2510,16 +2572,16 @@
         <v>150</v>
       </c>
       <c r="D20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E20">
         <v>2</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>40</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="H20">
         <v>-1</v>
@@ -2534,22 +2596,25 @@
         <v>-1</v>
       </c>
       <c r="L20">
+        <v>-1</v>
+      </c>
+      <c r="M20">
         <v>250</v>
       </c>
-      <c r="M20">
-        <v>1</v>
-      </c>
-      <c r="N20" t="b">
-        <v>1</v>
-      </c>
-      <c r="O20" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="P20" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20" t="b">
+        <v>1</v>
+      </c>
+      <c r="P20" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>20</v>
       </c>
@@ -2560,7 +2625,7 @@
         <v>201</v>
       </c>
       <c r="D24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -2569,37 +2634,40 @@
         <v>-1</v>
       </c>
       <c r="G24">
+        <v>-1</v>
+      </c>
+      <c r="H24">
         <v>0</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>30</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>0</v>
       </c>
-      <c r="J24">
-        <v>-1</v>
-      </c>
       <c r="K24">
         <v>-1</v>
       </c>
       <c r="L24">
+        <v>-1</v>
+      </c>
+      <c r="M24">
         <v>300</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>99</v>
       </c>
-      <c r="N24" t="b">
-        <v>1</v>
-      </c>
-      <c r="O24" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="P24" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O24" t="b">
+        <v>1</v>
+      </c>
+      <c r="P24" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>21</v>
       </c>
@@ -2610,7 +2678,7 @@
         <v>201</v>
       </c>
       <c r="D25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -2619,37 +2687,40 @@
         <v>-1</v>
       </c>
       <c r="G25">
+        <v>-1</v>
+      </c>
+      <c r="H25">
         <v>0</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>50</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>0</v>
       </c>
-      <c r="J25">
-        <v>-1</v>
-      </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
+        <v>-1</v>
+      </c>
+      <c r="M25">
         <v>200</v>
       </c>
-      <c r="M25">
+      <c r="N25">
         <v>99</v>
       </c>
-      <c r="N25" t="b">
-        <v>1</v>
-      </c>
-      <c r="O25" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="P25" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O25" t="b">
+        <v>1</v>
+      </c>
+      <c r="P25" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>22</v>
       </c>
@@ -2660,7 +2731,7 @@
         <v>201</v>
       </c>
       <c r="D26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -2669,37 +2740,40 @@
         <v>-1</v>
       </c>
       <c r="G26">
+        <v>-1</v>
+      </c>
+      <c r="H26">
         <v>0</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>10</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>0</v>
       </c>
-      <c r="J26">
-        <v>-1</v>
-      </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
+        <v>-1</v>
+      </c>
+      <c r="M26">
         <v>180</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>99</v>
       </c>
-      <c r="N26" t="b">
-        <v>1</v>
-      </c>
-      <c r="O26" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="P26" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O26" t="b">
+        <v>1</v>
+      </c>
+      <c r="P26" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>23</v>
       </c>
@@ -2710,7 +2784,7 @@
         <v>201</v>
       </c>
       <c r="D27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -2719,37 +2793,40 @@
         <v>-1</v>
       </c>
       <c r="G27">
+        <v>-1</v>
+      </c>
+      <c r="H27">
         <v>0</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>30</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>0</v>
       </c>
-      <c r="J27">
-        <v>-1</v>
-      </c>
       <c r="K27">
         <v>-1</v>
       </c>
       <c r="L27">
+        <v>-1</v>
+      </c>
+      <c r="M27">
         <v>250</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <v>99</v>
       </c>
-      <c r="N27" t="b">
-        <v>1</v>
-      </c>
-      <c r="O27" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="P27" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O27" t="b">
+        <v>1</v>
+      </c>
+      <c r="P27" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>24</v>
       </c>
@@ -2760,7 +2837,7 @@
         <v>201</v>
       </c>
       <c r="D28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -2769,40 +2846,43 @@
         <v>-1</v>
       </c>
       <c r="G28">
+        <v>-1</v>
+      </c>
+      <c r="H28">
         <v>0</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>15</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>0</v>
       </c>
-      <c r="J28">
-        <v>-1</v>
-      </c>
       <c r="K28">
         <v>-1</v>
       </c>
       <c r="L28">
+        <v>-1</v>
+      </c>
+      <c r="M28">
         <v>120</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>99</v>
       </c>
-      <c r="N28" t="b">
-        <v>1</v>
-      </c>
-      <c r="O28" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="P28" t="s">
-        <v>123</v>
+      <c r="O28" t="b">
+        <v>1</v>
+      </c>
+      <c r="P28" s="6" t="s">
+        <v>189</v>
       </c>
       <c r="Q28" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+      <c r="R28" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>25</v>
       </c>
@@ -2813,7 +2893,7 @@
         <v>202</v>
       </c>
       <c r="D29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -2822,40 +2902,43 @@
         <v>-1</v>
       </c>
       <c r="G29">
+        <v>-1</v>
+      </c>
+      <c r="H29">
         <v>25</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>20</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>0</v>
       </c>
-      <c r="J29">
-        <v>-1</v>
-      </c>
       <c r="K29">
         <v>-1</v>
       </c>
       <c r="L29">
+        <v>-1</v>
+      </c>
+      <c r="M29">
         <v>100</v>
       </c>
-      <c r="M29">
+      <c r="N29">
         <v>99</v>
       </c>
-      <c r="N29" t="b">
-        <v>1</v>
-      </c>
-      <c r="O29" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="P29" t="s">
-        <v>124</v>
+      <c r="O29" t="b">
+        <v>1</v>
+      </c>
+      <c r="P29" s="6" t="s">
+        <v>208</v>
       </c>
       <c r="Q29" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="R29" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>26</v>
       </c>
@@ -2866,7 +2949,7 @@
         <v>200</v>
       </c>
       <c r="D30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -2875,37 +2958,40 @@
         <v>-1</v>
       </c>
       <c r="G30">
+        <v>-1</v>
+      </c>
+      <c r="H30">
         <v>5</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
       </c>
       <c r="I30">
         <v>0</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K30">
         <v>-1</v>
       </c>
       <c r="L30">
+        <v>-1</v>
+      </c>
+      <c r="M30">
         <v>50</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>99</v>
       </c>
-      <c r="N30" t="b">
-        <v>1</v>
-      </c>
-      <c r="O30" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="P30" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O30" t="b">
+        <v>1</v>
+      </c>
+      <c r="P30" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>27</v>
       </c>
@@ -2916,7 +3002,7 @@
         <v>200</v>
       </c>
       <c r="D31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -2925,37 +3011,40 @@
         <v>-1</v>
       </c>
       <c r="G31">
+        <v>-1</v>
+      </c>
+      <c r="H31">
         <v>10</v>
-      </c>
-      <c r="H31">
-        <v>0</v>
       </c>
       <c r="I31">
         <v>0</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K31">
         <v>-1</v>
       </c>
       <c r="L31">
+        <v>-1</v>
+      </c>
+      <c r="M31">
         <v>80</v>
       </c>
-      <c r="M31">
+      <c r="N31">
         <v>99</v>
       </c>
-      <c r="N31" t="b">
-        <v>1</v>
-      </c>
-      <c r="O31" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="P31" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O31" t="b">
+        <v>1</v>
+      </c>
+      <c r="P31" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>28</v>
       </c>
@@ -2966,7 +3055,7 @@
         <v>202</v>
       </c>
       <c r="D32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -2975,37 +3064,40 @@
         <v>-1</v>
       </c>
       <c r="G32">
+        <v>-1</v>
+      </c>
+      <c r="H32">
         <v>20</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <v>10</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>0</v>
       </c>
-      <c r="J32">
-        <v>-1</v>
-      </c>
       <c r="K32">
         <v>-1</v>
       </c>
       <c r="L32">
+        <v>-1</v>
+      </c>
+      <c r="M32">
         <v>100</v>
       </c>
-      <c r="M32">
+      <c r="N32">
         <v>99</v>
       </c>
-      <c r="N32" t="b">
-        <v>1</v>
-      </c>
-      <c r="O32" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="P32" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O32" t="b">
+        <v>1</v>
+      </c>
+      <c r="P32" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>29</v>
       </c>
@@ -3016,7 +3108,7 @@
         <v>202</v>
       </c>
       <c r="D33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -3025,37 +3117,40 @@
         <v>-1</v>
       </c>
       <c r="G33">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="H33">
         <v>10</v>
       </c>
       <c r="I33">
+        <v>10</v>
+      </c>
+      <c r="J33">
         <v>0</v>
       </c>
-      <c r="J33">
-        <v>-1</v>
-      </c>
       <c r="K33">
         <v>-1</v>
       </c>
       <c r="L33">
+        <v>-1</v>
+      </c>
+      <c r="M33">
         <v>100</v>
       </c>
-      <c r="M33">
+      <c r="N33">
         <v>99</v>
       </c>
-      <c r="N33" t="b">
-        <v>1</v>
-      </c>
-      <c r="O33" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="P33" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O33" t="b">
+        <v>1</v>
+      </c>
+      <c r="P33" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>30</v>
       </c>
@@ -3066,7 +3161,7 @@
         <v>201</v>
       </c>
       <c r="D34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -3075,37 +3170,40 @@
         <v>-1</v>
       </c>
       <c r="G34">
+        <v>-1</v>
+      </c>
+      <c r="H34">
         <v>0</v>
       </c>
-      <c r="H34">
+      <c r="I34">
         <v>50</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>0</v>
       </c>
-      <c r="J34">
-        <v>-1</v>
-      </c>
       <c r="K34">
         <v>-1</v>
       </c>
       <c r="L34">
+        <v>-1</v>
+      </c>
+      <c r="M34">
         <v>100</v>
       </c>
-      <c r="M34">
+      <c r="N34">
         <v>99</v>
       </c>
-      <c r="N34" t="b">
-        <v>1</v>
-      </c>
-      <c r="O34" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="P34" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O34" t="b">
+        <v>1</v>
+      </c>
+      <c r="P34" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>31</v>
       </c>
@@ -3116,7 +3214,7 @@
         <v>202</v>
       </c>
       <c r="D35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -3125,37 +3223,40 @@
         <v>-1</v>
       </c>
       <c r="G35">
+        <v>-1</v>
+      </c>
+      <c r="H35">
         <v>20</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>10</v>
       </c>
-      <c r="I35">
+      <c r="J35">
         <v>0</v>
       </c>
-      <c r="J35">
-        <v>-1</v>
-      </c>
       <c r="K35">
         <v>-1</v>
       </c>
       <c r="L35">
+        <v>-1</v>
+      </c>
+      <c r="M35">
         <v>220</v>
       </c>
-      <c r="M35">
+      <c r="N35">
         <v>99</v>
       </c>
-      <c r="N35" t="b">
-        <v>1</v>
-      </c>
-      <c r="O35" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="P35" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O35" t="b">
+        <v>1</v>
+      </c>
+      <c r="P35" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>32</v>
       </c>
@@ -3166,7 +3267,7 @@
         <v>203</v>
       </c>
       <c r="D36" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E36">
         <v>1</v>
@@ -3175,40 +3276,43 @@
         <v>-1</v>
       </c>
       <c r="G36">
+        <v>-1</v>
+      </c>
+      <c r="H36">
         <v>10</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <v>15</v>
       </c>
-      <c r="I36">
+      <c r="J36">
         <v>30</v>
       </c>
-      <c r="J36">
+      <c r="K36">
         <v>10</v>
       </c>
-      <c r="K36">
-        <v>-1</v>
-      </c>
       <c r="L36">
+        <v>-1</v>
+      </c>
+      <c r="M36">
         <v>100</v>
       </c>
-      <c r="M36">
+      <c r="N36">
         <v>99</v>
       </c>
-      <c r="N36" t="b">
-        <v>1</v>
-      </c>
-      <c r="O36" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="P36" t="s">
-        <v>130</v>
+      <c r="O36" t="b">
+        <v>1</v>
+      </c>
+      <c r="P36" s="6" t="s">
+        <v>193</v>
       </c>
       <c r="Q36" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+      <c r="R36" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>33</v>
       </c>
@@ -3219,7 +3323,7 @@
         <v>203</v>
       </c>
       <c r="D37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E37">
         <v>1</v>
@@ -3228,40 +3332,43 @@
         <v>-1</v>
       </c>
       <c r="G37">
+        <v>-1</v>
+      </c>
+      <c r="H37">
         <v>10</v>
       </c>
-      <c r="H37">
+      <c r="I37">
         <v>25</v>
-      </c>
-      <c r="I37">
-        <v>10</v>
       </c>
       <c r="J37">
         <v>10</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L37">
+        <v>-1</v>
+      </c>
+      <c r="M37">
         <v>200</v>
       </c>
-      <c r="M37">
+      <c r="N37">
         <v>99</v>
       </c>
-      <c r="N37" t="b">
-        <v>1</v>
-      </c>
-      <c r="O37" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="P37" t="s">
-        <v>141</v>
+      <c r="O37" t="b">
+        <v>1</v>
+      </c>
+      <c r="P37" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="Q37" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+      <c r="R37" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>34</v>
       </c>
@@ -3272,46 +3379,49 @@
         <v>202</v>
       </c>
       <c r="D38" t="s">
+        <v>215</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38">
+        <v>-1</v>
+      </c>
+      <c r="G38">
+        <v>-1</v>
+      </c>
+      <c r="H38">
+        <v>50</v>
+      </c>
+      <c r="I38">
+        <v>10</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>-1</v>
+      </c>
+      <c r="L38">
+        <v>-1</v>
+      </c>
+      <c r="M38">
+        <v>200</v>
+      </c>
+      <c r="N38">
+        <v>99</v>
+      </c>
+      <c r="O38" t="b">
+        <v>1</v>
+      </c>
+      <c r="P38" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q38" t="s">
         <v>216</v>
       </c>
-      <c r="E38">
-        <v>1</v>
-      </c>
-      <c r="F38">
-        <v>-1</v>
-      </c>
-      <c r="G38">
-        <v>50</v>
-      </c>
-      <c r="H38">
-        <v>10</v>
-      </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38">
-        <v>-1</v>
-      </c>
-      <c r="K38">
-        <v>-1</v>
-      </c>
-      <c r="L38">
-        <v>200</v>
-      </c>
-      <c r="M38">
-        <v>99</v>
-      </c>
-      <c r="N38" t="b">
-        <v>1</v>
-      </c>
-      <c r="O38" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="P38" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>35</v>
       </c>
@@ -3322,7 +3432,7 @@
         <v>202</v>
       </c>
       <c r="D39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -3331,37 +3441,40 @@
         <v>-1</v>
       </c>
       <c r="G39">
+        <v>-1</v>
+      </c>
+      <c r="H39">
         <v>25</v>
       </c>
-      <c r="H39">
+      <c r="I39">
         <v>10</v>
       </c>
-      <c r="I39">
+      <c r="J39">
         <v>0</v>
       </c>
-      <c r="J39">
-        <v>-1</v>
-      </c>
       <c r="K39">
         <v>-1</v>
       </c>
       <c r="L39">
+        <v>-1</v>
+      </c>
+      <c r="M39">
         <v>200</v>
       </c>
-      <c r="M39">
+      <c r="N39">
         <v>99</v>
       </c>
-      <c r="N39" t="b">
-        <v>1</v>
-      </c>
-      <c r="O39" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="P39" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O39" t="b">
+        <v>1</v>
+      </c>
+      <c r="P39" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>36</v>
       </c>
@@ -3372,7 +3485,7 @@
         <v>203</v>
       </c>
       <c r="D40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -3381,40 +3494,43 @@
         <v>-1</v>
       </c>
       <c r="G40">
+        <v>-1</v>
+      </c>
+      <c r="H40">
         <v>5</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>10</v>
       </c>
-      <c r="I40">
+      <c r="J40">
         <v>5</v>
       </c>
-      <c r="J40">
+      <c r="K40">
         <v>10</v>
       </c>
-      <c r="K40">
-        <v>-1</v>
-      </c>
       <c r="L40">
+        <v>-1</v>
+      </c>
+      <c r="M40">
         <v>200</v>
       </c>
-      <c r="M40">
+      <c r="N40">
         <v>99</v>
       </c>
-      <c r="N40" t="b">
-        <v>1</v>
-      </c>
-      <c r="O40" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="P40" t="s">
-        <v>132</v>
+      <c r="O40" t="b">
+        <v>1</v>
+      </c>
+      <c r="P40" s="6" t="s">
+        <v>200</v>
       </c>
       <c r="Q40" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+      <c r="R40" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>37</v>
       </c>
@@ -3425,7 +3541,7 @@
         <v>202</v>
       </c>
       <c r="D41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -3434,37 +3550,40 @@
         <v>-1</v>
       </c>
       <c r="G41">
+        <v>-1</v>
+      </c>
+      <c r="H41">
         <v>40</v>
       </c>
-      <c r="H41">
+      <c r="I41">
         <v>10</v>
       </c>
-      <c r="I41">
+      <c r="J41">
         <v>0</v>
       </c>
-      <c r="J41">
-        <v>-1</v>
-      </c>
       <c r="K41">
         <v>-1</v>
       </c>
       <c r="L41">
+        <v>-1</v>
+      </c>
+      <c r="M41">
         <v>200</v>
       </c>
-      <c r="M41">
+      <c r="N41">
         <v>99</v>
       </c>
-      <c r="N41" t="b">
-        <v>1</v>
-      </c>
-      <c r="O41" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="P41" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O41" t="b">
+        <v>1</v>
+      </c>
+      <c r="P41" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>38</v>
       </c>
@@ -3475,7 +3594,7 @@
         <v>202</v>
       </c>
       <c r="D42" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E42">
         <v>1</v>
@@ -3484,37 +3603,40 @@
         <v>-1</v>
       </c>
       <c r="G42">
+        <v>-1</v>
+      </c>
+      <c r="H42">
         <v>20</v>
       </c>
-      <c r="H42">
+      <c r="I42">
         <v>5</v>
       </c>
-      <c r="I42">
+      <c r="J42">
         <v>0</v>
       </c>
-      <c r="J42">
-        <v>-1</v>
-      </c>
       <c r="K42">
         <v>-1</v>
       </c>
       <c r="L42">
+        <v>-1</v>
+      </c>
+      <c r="M42">
         <v>200</v>
       </c>
-      <c r="M42">
+      <c r="N42">
         <v>99</v>
       </c>
-      <c r="N42" t="b">
-        <v>1</v>
-      </c>
-      <c r="O42" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="P42" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O42" t="b">
+        <v>1</v>
+      </c>
+      <c r="P42" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>39</v>
       </c>
@@ -3525,7 +3647,7 @@
         <v>202</v>
       </c>
       <c r="D43" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E43">
         <v>1</v>
@@ -3534,37 +3656,40 @@
         <v>-1</v>
       </c>
       <c r="G43">
+        <v>-1</v>
+      </c>
+      <c r="H43">
         <v>15</v>
       </c>
-      <c r="H43">
+      <c r="I43">
         <v>5</v>
       </c>
-      <c r="I43">
+      <c r="J43">
         <v>0</v>
       </c>
-      <c r="J43">
-        <v>-1</v>
-      </c>
       <c r="K43">
         <v>-1</v>
       </c>
       <c r="L43">
+        <v>-1</v>
+      </c>
+      <c r="M43">
         <v>200</v>
       </c>
-      <c r="M43">
+      <c r="N43">
         <v>99</v>
       </c>
-      <c r="N43" t="b">
-        <v>1</v>
-      </c>
-      <c r="O43" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="P43" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O43" t="b">
+        <v>1</v>
+      </c>
+      <c r="P43" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>40</v>
       </c>
@@ -3575,7 +3700,7 @@
         <v>202</v>
       </c>
       <c r="D44" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -3584,37 +3709,40 @@
         <v>-1</v>
       </c>
       <c r="G44">
+        <v>-1</v>
+      </c>
+      <c r="H44">
         <v>0</v>
       </c>
-      <c r="H44">
+      <c r="I44">
         <v>20</v>
       </c>
-      <c r="I44">
+      <c r="J44">
         <v>0</v>
       </c>
-      <c r="J44">
-        <v>-1</v>
-      </c>
       <c r="K44">
         <v>-1</v>
       </c>
       <c r="L44">
+        <v>-1</v>
+      </c>
+      <c r="M44">
         <v>200</v>
       </c>
-      <c r="M44">
+      <c r="N44">
         <v>99</v>
       </c>
-      <c r="N44" t="b">
-        <v>1</v>
-      </c>
-      <c r="O44" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="P44" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O44" t="b">
+        <v>1</v>
+      </c>
+      <c r="P44" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>41</v>
       </c>
@@ -3625,7 +3753,7 @@
         <v>203</v>
       </c>
       <c r="D45" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E45">
         <v>1</v>
@@ -3634,40 +3762,43 @@
         <v>-1</v>
       </c>
       <c r="G45">
+        <v>-1</v>
+      </c>
+      <c r="H45">
         <v>0</v>
       </c>
-      <c r="H45">
+      <c r="I45">
         <v>50</v>
       </c>
-      <c r="I45">
+      <c r="J45">
         <v>10</v>
       </c>
-      <c r="J45">
-        <v>-1</v>
-      </c>
       <c r="K45">
         <v>-1</v>
       </c>
       <c r="L45">
+        <v>-1</v>
+      </c>
+      <c r="M45">
         <v>200</v>
       </c>
-      <c r="M45">
+      <c r="N45">
         <v>99</v>
       </c>
-      <c r="N45" t="b">
-        <v>1</v>
-      </c>
-      <c r="O45" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="P45" t="s">
-        <v>137</v>
+      <c r="O45" t="b">
+        <v>1</v>
+      </c>
+      <c r="P45" s="6" t="s">
+        <v>191</v>
       </c>
       <c r="Q45" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+      <c r="R45" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>42</v>
       </c>
@@ -3678,7 +3809,7 @@
         <v>202</v>
       </c>
       <c r="D46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E46">
         <v>1</v>
@@ -3687,37 +3818,40 @@
         <v>-1</v>
       </c>
       <c r="G46">
+        <v>-1</v>
+      </c>
+      <c r="H46">
         <v>5</v>
       </c>
-      <c r="H46">
+      <c r="I46">
         <v>15</v>
       </c>
-      <c r="I46">
+      <c r="J46">
         <v>0</v>
       </c>
-      <c r="J46">
-        <v>-1</v>
-      </c>
       <c r="K46">
         <v>-1</v>
       </c>
       <c r="L46">
+        <v>-1</v>
+      </c>
+      <c r="M46">
         <v>200</v>
       </c>
-      <c r="M46">
+      <c r="N46">
         <v>99</v>
       </c>
-      <c r="N46" t="b">
-        <v>1</v>
-      </c>
-      <c r="O46" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="P46" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O46" t="b">
+        <v>1</v>
+      </c>
+      <c r="P46" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>43</v>
       </c>
@@ -3728,7 +3862,7 @@
         <v>202</v>
       </c>
       <c r="D47" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E47">
         <v>1</v>
@@ -3737,37 +3871,40 @@
         <v>-1</v>
       </c>
       <c r="G47">
-        <v>30</v>
+        <v>-1</v>
       </c>
       <c r="H47">
         <v>30</v>
       </c>
       <c r="I47">
+        <v>30</v>
+      </c>
+      <c r="J47">
         <v>0</v>
       </c>
-      <c r="J47">
-        <v>-1</v>
-      </c>
       <c r="K47">
         <v>-1</v>
       </c>
       <c r="L47">
+        <v>-1</v>
+      </c>
+      <c r="M47">
         <v>200</v>
       </c>
-      <c r="M47">
+      <c r="N47">
         <v>99</v>
       </c>
-      <c r="N47" t="b">
-        <v>1</v>
-      </c>
-      <c r="O47" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="P47" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O47" t="b">
+        <v>1</v>
+      </c>
+      <c r="P47" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>44</v>
       </c>
@@ -3778,7 +3915,7 @@
         <v>202</v>
       </c>
       <c r="D48" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3787,37 +3924,40 @@
         <v>-1</v>
       </c>
       <c r="G48">
+        <v>-1</v>
+      </c>
+      <c r="H48">
         <v>20</v>
       </c>
-      <c r="H48">
+      <c r="I48">
         <v>10</v>
       </c>
-      <c r="I48">
+      <c r="J48">
         <v>0</v>
       </c>
-      <c r="J48">
-        <v>-1</v>
-      </c>
       <c r="K48">
         <v>-1</v>
       </c>
       <c r="L48">
+        <v>-1</v>
+      </c>
+      <c r="M48">
         <v>200</v>
       </c>
-      <c r="M48">
+      <c r="N48">
         <v>99</v>
       </c>
-      <c r="N48" t="b">
-        <v>1</v>
-      </c>
-      <c r="O48" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="P48" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O48" t="b">
+        <v>1</v>
+      </c>
+      <c r="P48" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>45</v>
       </c>
@@ -3828,7 +3968,7 @@
         <v>202</v>
       </c>
       <c r="D49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E49">
         <v>1</v>
@@ -3837,40 +3977,43 @@
         <v>-1</v>
       </c>
       <c r="G49">
+        <v>-1</v>
+      </c>
+      <c r="H49">
         <v>25</v>
       </c>
-      <c r="H49">
+      <c r="I49">
         <v>30</v>
       </c>
-      <c r="I49">
+      <c r="J49">
         <v>0</v>
       </c>
-      <c r="J49">
-        <v>-1</v>
-      </c>
       <c r="K49">
         <v>-1</v>
       </c>
       <c r="L49">
+        <v>-1</v>
+      </c>
+      <c r="M49">
         <v>200</v>
       </c>
-      <c r="M49">
+      <c r="N49">
         <v>99</v>
       </c>
-      <c r="N49" t="b">
-        <v>1</v>
-      </c>
-      <c r="O49" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="P49" s="9" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="O51" s="6"/>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O49" t="b">
+        <v>1</v>
+      </c>
+      <c r="P49" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q49" s="9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P51" s="6"/>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>46</v>
       </c>
@@ -3881,7 +4024,7 @@
         <v>302</v>
       </c>
       <c r="D52" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E52">
         <v>1</v>
@@ -3905,25 +4048,28 @@
         <v>-1</v>
       </c>
       <c r="L52">
+        <v>-1</v>
+      </c>
+      <c r="M52">
         <v>80</v>
       </c>
-      <c r="M52">
+      <c r="N52">
         <v>99</v>
       </c>
-      <c r="N52" t="b">
-        <v>1</v>
-      </c>
-      <c r="O52" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="P52" t="s">
-        <v>144</v>
+      <c r="O52" t="b">
+        <v>1</v>
+      </c>
+      <c r="P52" s="6" t="s">
+        <v>257</v>
       </c>
       <c r="Q52" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+      <c r="R52" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>47</v>
       </c>
@@ -3934,49 +4080,52 @@
         <v>301</v>
       </c>
       <c r="D53" t="s">
+        <v>56</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+      <c r="F53">
+        <v>-1</v>
+      </c>
+      <c r="G53">
+        <v>-1</v>
+      </c>
+      <c r="H53">
+        <v>-1</v>
+      </c>
+      <c r="I53">
+        <v>-1</v>
+      </c>
+      <c r="J53">
+        <v>-1</v>
+      </c>
+      <c r="K53">
+        <v>-1</v>
+      </c>
+      <c r="L53">
+        <v>-1</v>
+      </c>
+      <c r="M53">
+        <v>150</v>
+      </c>
+      <c r="N53">
+        <v>99</v>
+      </c>
+      <c r="O53" t="b">
+        <v>1</v>
+      </c>
+      <c r="P53" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>150</v>
+      </c>
+      <c r="R53" t="s">
         <v>57</v>
       </c>
-      <c r="E53">
-        <v>1</v>
-      </c>
-      <c r="F53">
-        <v>-1</v>
-      </c>
-      <c r="G53">
-        <v>-1</v>
-      </c>
-      <c r="H53">
-        <v>-1</v>
-      </c>
-      <c r="I53">
-        <v>-1</v>
-      </c>
-      <c r="J53">
-        <v>-1</v>
-      </c>
-      <c r="K53">
-        <v>-1</v>
-      </c>
-      <c r="L53">
-        <v>150</v>
-      </c>
-      <c r="M53">
-        <v>99</v>
-      </c>
-      <c r="N53" t="b">
-        <v>1</v>
-      </c>
-      <c r="O53" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="P53" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q53" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>48</v>
       </c>
@@ -3987,49 +4136,52 @@
         <v>301</v>
       </c>
       <c r="D54" t="s">
+        <v>58</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+      <c r="F54">
+        <v>-1</v>
+      </c>
+      <c r="G54">
+        <v>-1</v>
+      </c>
+      <c r="H54">
+        <v>-1</v>
+      </c>
+      <c r="I54">
+        <v>-1</v>
+      </c>
+      <c r="J54">
+        <v>-1</v>
+      </c>
+      <c r="K54">
+        <v>-1</v>
+      </c>
+      <c r="L54">
+        <v>-1</v>
+      </c>
+      <c r="M54">
+        <v>100</v>
+      </c>
+      <c r="N54">
+        <v>99</v>
+      </c>
+      <c r="O54" t="b">
+        <v>1</v>
+      </c>
+      <c r="P54" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>151</v>
+      </c>
+      <c r="R54" t="s">
         <v>59</v>
       </c>
-      <c r="E54">
-        <v>1</v>
-      </c>
-      <c r="F54">
-        <v>-1</v>
-      </c>
-      <c r="G54">
-        <v>-1</v>
-      </c>
-      <c r="H54">
-        <v>-1</v>
-      </c>
-      <c r="I54">
-        <v>-1</v>
-      </c>
-      <c r="J54">
-        <v>-1</v>
-      </c>
-      <c r="K54">
-        <v>-1</v>
-      </c>
-      <c r="L54">
-        <v>100</v>
-      </c>
-      <c r="M54">
-        <v>99</v>
-      </c>
-      <c r="N54" t="b">
-        <v>1</v>
-      </c>
-      <c r="O54" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="P54" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>49</v>
       </c>
@@ -4040,49 +4192,52 @@
         <v>303</v>
       </c>
       <c r="D55" t="s">
+        <v>60</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+      <c r="F55">
+        <v>-1</v>
+      </c>
+      <c r="G55">
+        <v>-1</v>
+      </c>
+      <c r="H55">
+        <v>-1</v>
+      </c>
+      <c r="I55">
+        <v>-1</v>
+      </c>
+      <c r="J55">
+        <v>-1</v>
+      </c>
+      <c r="K55">
+        <v>-1</v>
+      </c>
+      <c r="L55">
+        <v>-1</v>
+      </c>
+      <c r="M55">
+        <v>60</v>
+      </c>
+      <c r="N55">
+        <v>99</v>
+      </c>
+      <c r="O55" t="b">
+        <v>1</v>
+      </c>
+      <c r="P55" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>152</v>
+      </c>
+      <c r="R55" t="s">
         <v>61</v>
       </c>
-      <c r="E55">
-        <v>1</v>
-      </c>
-      <c r="F55">
-        <v>-1</v>
-      </c>
-      <c r="G55">
-        <v>-1</v>
-      </c>
-      <c r="H55">
-        <v>-1</v>
-      </c>
-      <c r="I55">
-        <v>-1</v>
-      </c>
-      <c r="J55">
-        <v>-1</v>
-      </c>
-      <c r="K55">
-        <v>-1</v>
-      </c>
-      <c r="L55">
-        <v>60</v>
-      </c>
-      <c r="M55">
-        <v>99</v>
-      </c>
-      <c r="N55" t="b">
-        <v>1</v>
-      </c>
-      <c r="O55" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="P55" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q55" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>50</v>
       </c>
@@ -4093,7 +4248,7 @@
         <v>300</v>
       </c>
       <c r="D56" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E56">
         <v>1</v>
@@ -4117,22 +4272,25 @@
         <v>-1</v>
       </c>
       <c r="L56">
+        <v>-1</v>
+      </c>
+      <c r="M56">
         <v>40</v>
       </c>
-      <c r="M56">
+      <c r="N56">
         <v>99</v>
       </c>
-      <c r="N56" t="b">
-        <v>1</v>
-      </c>
-      <c r="O56" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="P56" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O56" t="b">
+        <v>1</v>
+      </c>
+      <c r="P56" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>51</v>
       </c>
@@ -4143,7 +4301,7 @@
         <v>300</v>
       </c>
       <c r="D57" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E57">
         <v>1</v>
@@ -4167,22 +4325,25 @@
         <v>-1</v>
       </c>
       <c r="L57">
+        <v>-1</v>
+      </c>
+      <c r="M57">
         <v>90</v>
       </c>
-      <c r="M57">
+      <c r="N57">
         <v>99</v>
       </c>
-      <c r="N57" t="b">
-        <v>1</v>
-      </c>
-      <c r="O57" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="P57" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O57" t="b">
+        <v>1</v>
+      </c>
+      <c r="P57" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>52</v>
       </c>
@@ -4193,7 +4354,7 @@
         <v>300</v>
       </c>
       <c r="D58" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E58">
         <v>1</v>
@@ -4217,22 +4378,25 @@
         <v>-1</v>
       </c>
       <c r="L58">
+        <v>-1</v>
+      </c>
+      <c r="M58">
         <v>200</v>
       </c>
-      <c r="M58">
+      <c r="N58">
         <v>99</v>
       </c>
-      <c r="N58" t="b">
-        <v>1</v>
-      </c>
-      <c r="O58" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="P58" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O58" t="b">
+        <v>1</v>
+      </c>
+      <c r="P58" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>53</v>
       </c>
@@ -4243,49 +4407,52 @@
         <v>300</v>
       </c>
       <c r="D59" t="s">
+        <v>65</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="F59">
+        <v>-1</v>
+      </c>
+      <c r="G59">
+        <v>-1</v>
+      </c>
+      <c r="H59">
+        <v>-1</v>
+      </c>
+      <c r="I59">
+        <v>-1</v>
+      </c>
+      <c r="J59">
+        <v>-1</v>
+      </c>
+      <c r="K59">
+        <v>-1</v>
+      </c>
+      <c r="L59">
+        <v>-1</v>
+      </c>
+      <c r="M59">
+        <v>30</v>
+      </c>
+      <c r="N59">
+        <v>99</v>
+      </c>
+      <c r="O59" t="b">
+        <v>1</v>
+      </c>
+      <c r="P59" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>156</v>
+      </c>
+      <c r="R59" t="s">
         <v>66</v>
       </c>
-      <c r="E59">
-        <v>1</v>
-      </c>
-      <c r="F59">
-        <v>-1</v>
-      </c>
-      <c r="G59">
-        <v>-1</v>
-      </c>
-      <c r="H59">
-        <v>-1</v>
-      </c>
-      <c r="I59">
-        <v>-1</v>
-      </c>
-      <c r="J59">
-        <v>-1</v>
-      </c>
-      <c r="K59">
-        <v>-1</v>
-      </c>
-      <c r="L59">
-        <v>30</v>
-      </c>
-      <c r="M59">
-        <v>99</v>
-      </c>
-      <c r="N59" t="b">
-        <v>1</v>
-      </c>
-      <c r="O59" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="P59" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q59" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>54</v>
       </c>
@@ -4296,7 +4463,7 @@
         <v>303</v>
       </c>
       <c r="D60" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -4320,25 +4487,28 @@
         <v>-1</v>
       </c>
       <c r="L60">
+        <v>-1</v>
+      </c>
+      <c r="M60">
         <v>80</v>
       </c>
-      <c r="M60">
+      <c r="N60">
         <v>99</v>
       </c>
-      <c r="N60" t="b">
-        <v>1</v>
-      </c>
-      <c r="O60" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="P60" t="s">
-        <v>158</v>
+      <c r="O60" t="b">
+        <v>1</v>
+      </c>
+      <c r="P60" s="6" t="s">
+        <v>260</v>
       </c>
       <c r="Q60" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+      <c r="R60" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>55</v>
       </c>
@@ -4349,7 +4519,7 @@
         <v>303</v>
       </c>
       <c r="D61" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E61">
         <v>1</v>
@@ -4364,37 +4534,40 @@
         <v>-1</v>
       </c>
       <c r="I61">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="J61">
         <v>5</v>
       </c>
       <c r="K61">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L61">
+        <v>-1</v>
+      </c>
+      <c r="M61">
         <v>150</v>
       </c>
-      <c r="M61">
+      <c r="N61">
         <v>99</v>
       </c>
-      <c r="N61" t="b">
-        <v>1</v>
-      </c>
-      <c r="O61" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="P61" s="9" t="s">
+      <c r="O61" t="b">
+        <v>1</v>
+      </c>
+      <c r="P61" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q61" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="R61" t="s">
         <v>159</v>
       </c>
-      <c r="Q61" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="O62" s="6"/>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P62" s="6"/>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>56</v>
       </c>
@@ -4402,7 +4575,7 @@
         <v>3</v>
       </c>
       <c r="D63" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E63">
         <v>2</v>
@@ -4423,22 +4596,25 @@
         <v>-1</v>
       </c>
       <c r="K63">
+        <v>-1</v>
+      </c>
+      <c r="L63">
         <v>0</v>
       </c>
-      <c r="L63">
+      <c r="M63">
         <v>10</v>
       </c>
-      <c r="M63">
-        <v>1</v>
-      </c>
-      <c r="N63" t="b">
-        <v>1</v>
-      </c>
-      <c r="O63" s="6" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="N63">
+        <v>1</v>
+      </c>
+      <c r="O63" t="b">
+        <v>1</v>
+      </c>
+      <c r="P63" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>57</v>
       </c>
@@ -4446,7 +4622,7 @@
         <v>3</v>
       </c>
       <c r="D64" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E64">
         <v>3</v>
@@ -4467,22 +4643,25 @@
         <v>-1</v>
       </c>
       <c r="K64">
+        <v>-1</v>
+      </c>
+      <c r="L64">
         <v>0</v>
       </c>
-      <c r="L64">
+      <c r="M64">
         <v>18</v>
       </c>
-      <c r="M64">
-        <v>1</v>
-      </c>
-      <c r="N64" t="b">
-        <v>1</v>
-      </c>
-      <c r="O64" s="6" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N64">
+        <v>1</v>
+      </c>
+      <c r="O64" t="b">
+        <v>1</v>
+      </c>
+      <c r="P64" s="6" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>58</v>
       </c>
@@ -4490,7 +4669,7 @@
         <v>3</v>
       </c>
       <c r="D65" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E65">
         <v>4</v>
@@ -4511,22 +4690,25 @@
         <v>-1</v>
       </c>
       <c r="K65">
+        <v>-1</v>
+      </c>
+      <c r="L65">
         <v>0</v>
       </c>
-      <c r="L65">
+      <c r="M65">
         <v>26</v>
       </c>
-      <c r="M65">
-        <v>1</v>
-      </c>
-      <c r="N65" t="b">
-        <v>1</v>
-      </c>
-      <c r="O65" s="6" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N65">
+        <v>1</v>
+      </c>
+      <c r="O65" t="b">
+        <v>1</v>
+      </c>
+      <c r="P65" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>59</v>
       </c>
@@ -4534,7 +4716,7 @@
         <v>3</v>
       </c>
       <c r="D66" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E66">
         <v>3</v>
@@ -4555,22 +4737,25 @@
         <v>-1</v>
       </c>
       <c r="K66">
+        <v>-1</v>
+      </c>
+      <c r="L66">
         <v>0</v>
       </c>
-      <c r="L66">
+      <c r="M66">
         <v>17</v>
       </c>
-      <c r="M66">
-        <v>1</v>
-      </c>
-      <c r="N66" t="b">
-        <v>1</v>
-      </c>
-      <c r="O66" s="6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N66">
+        <v>1</v>
+      </c>
+      <c r="O66" t="b">
+        <v>1</v>
+      </c>
+      <c r="P66" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>60</v>
       </c>
@@ -4578,7 +4763,7 @@
         <v>3</v>
       </c>
       <c r="D67" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E67">
         <v>4</v>
@@ -4599,22 +4784,25 @@
         <v>-1</v>
       </c>
       <c r="K67">
+        <v>-1</v>
+      </c>
+      <c r="L67">
         <v>0</v>
       </c>
-      <c r="L67">
+      <c r="M67">
         <v>25</v>
       </c>
-      <c r="M67">
-        <v>1</v>
-      </c>
-      <c r="N67" t="b">
-        <v>1</v>
-      </c>
-      <c r="O67" s="6" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N67">
+        <v>1</v>
+      </c>
+      <c r="O67" t="b">
+        <v>1</v>
+      </c>
+      <c r="P67" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>61</v>
       </c>
@@ -4622,7 +4810,7 @@
         <v>3</v>
       </c>
       <c r="D68" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E68">
         <v>1</v>
@@ -4643,22 +4831,25 @@
         <v>-1</v>
       </c>
       <c r="K68">
+        <v>-1</v>
+      </c>
+      <c r="L68">
         <v>0</v>
       </c>
-      <c r="L68">
+      <c r="M68">
         <v>20</v>
       </c>
-      <c r="M68">
-        <v>1</v>
-      </c>
-      <c r="N68" t="b">
-        <v>1</v>
-      </c>
-      <c r="O68" s="6" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N68">
+        <v>1</v>
+      </c>
+      <c r="O68" t="b">
+        <v>1</v>
+      </c>
+      <c r="P68" s="6" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>62</v>
       </c>
@@ -4666,7 +4857,7 @@
         <v>3</v>
       </c>
       <c r="D69" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E69">
         <v>10</v>
@@ -4687,22 +4878,25 @@
         <v>-1</v>
       </c>
       <c r="K69">
+        <v>-1</v>
+      </c>
+      <c r="L69">
         <v>0</v>
       </c>
-      <c r="L69">
+      <c r="M69">
         <v>120</v>
       </c>
-      <c r="M69">
-        <v>1</v>
-      </c>
-      <c r="N69" t="b">
-        <v>1</v>
-      </c>
-      <c r="O69" s="6" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N69">
+        <v>1</v>
+      </c>
+      <c r="O69" t="b">
+        <v>1</v>
+      </c>
+      <c r="P69" s="6" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>63</v>
       </c>
@@ -4710,7 +4904,7 @@
         <v>3</v>
       </c>
       <c r="D70" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E70">
         <v>1</v>
@@ -4731,22 +4925,25 @@
         <v>-1</v>
       </c>
       <c r="K70">
+        <v>-1</v>
+      </c>
+      <c r="L70">
         <v>0</v>
       </c>
-      <c r="L70">
+      <c r="M70">
         <v>3</v>
       </c>
-      <c r="M70">
-        <v>1</v>
-      </c>
-      <c r="N70" t="b">
-        <v>1</v>
-      </c>
-      <c r="O70" s="6" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N70">
+        <v>1</v>
+      </c>
+      <c r="O70" t="b">
+        <v>1</v>
+      </c>
+      <c r="P70" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>64</v>
       </c>
@@ -4754,7 +4951,7 @@
         <v>3</v>
       </c>
       <c r="D71" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E71">
         <v>2</v>
@@ -4775,22 +4972,25 @@
         <v>-1</v>
       </c>
       <c r="K71">
+        <v>-1</v>
+      </c>
+      <c r="L71">
         <v>0</v>
       </c>
-      <c r="L71">
+      <c r="M71">
         <v>16</v>
       </c>
-      <c r="M71">
-        <v>1</v>
-      </c>
-      <c r="N71" t="b">
-        <v>1</v>
-      </c>
-      <c r="O71" s="6" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N71">
+        <v>1</v>
+      </c>
+      <c r="O71" t="b">
+        <v>1</v>
+      </c>
+      <c r="P71" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>65</v>
       </c>
@@ -4798,7 +4998,7 @@
         <v>3</v>
       </c>
       <c r="D72" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E72">
         <v>5</v>
@@ -4819,22 +5019,25 @@
         <v>-1</v>
       </c>
       <c r="K72">
+        <v>-1</v>
+      </c>
+      <c r="L72">
         <v>0</v>
       </c>
-      <c r="L72">
+      <c r="M72">
         <v>26</v>
       </c>
-      <c r="M72">
-        <v>1</v>
-      </c>
-      <c r="N72" t="b">
-        <v>1</v>
-      </c>
-      <c r="O72" s="6" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N72">
+        <v>1</v>
+      </c>
+      <c r="O72" t="b">
+        <v>1</v>
+      </c>
+      <c r="P72" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>66</v>
       </c>
@@ -4842,7 +5045,7 @@
         <v>3</v>
       </c>
       <c r="D73" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E73">
         <v>40</v>
@@ -4863,22 +5066,25 @@
         <v>-1</v>
       </c>
       <c r="K73">
+        <v>-1</v>
+      </c>
+      <c r="L73">
         <v>0</v>
       </c>
-      <c r="L73">
+      <c r="M73">
         <v>350</v>
       </c>
-      <c r="M73">
-        <v>1</v>
-      </c>
-      <c r="N73" t="b">
-        <v>1</v>
-      </c>
-      <c r="O73" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N73">
+        <v>1</v>
+      </c>
+      <c r="O73" t="b">
+        <v>1</v>
+      </c>
+      <c r="P73" s="6" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>67</v>
       </c>
@@ -4886,7 +5092,7 @@
         <v>3</v>
       </c>
       <c r="D74" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E74">
         <v>1</v>
@@ -4907,22 +5113,25 @@
         <v>-1</v>
       </c>
       <c r="K74">
+        <v>-1</v>
+      </c>
+      <c r="L74">
         <v>0</v>
       </c>
-      <c r="L74">
+      <c r="M74">
         <v>2</v>
       </c>
-      <c r="M74">
-        <v>1</v>
-      </c>
-      <c r="N74" t="b">
-        <v>1</v>
-      </c>
-      <c r="O74" s="6" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N74">
+        <v>1</v>
+      </c>
+      <c r="O74" t="b">
+        <v>1</v>
+      </c>
+      <c r="P74" s="6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>68</v>
       </c>
@@ -4930,7 +5139,7 @@
         <v>3</v>
       </c>
       <c r="D75" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E75">
         <v>2</v>
@@ -4951,22 +5160,25 @@
         <v>-1</v>
       </c>
       <c r="K75">
+        <v>-1</v>
+      </c>
+      <c r="L75">
         <v>0</v>
       </c>
-      <c r="L75">
+      <c r="M75">
         <v>8</v>
       </c>
-      <c r="M75">
-        <v>1</v>
-      </c>
-      <c r="N75" t="b">
-        <v>1</v>
-      </c>
-      <c r="O75" s="6" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N75">
+        <v>1</v>
+      </c>
+      <c r="O75" t="b">
+        <v>1</v>
+      </c>
+      <c r="P75" s="6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>69</v>
       </c>
@@ -4974,7 +5186,7 @@
         <v>3</v>
       </c>
       <c r="D76" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E76">
         <v>3</v>
@@ -4995,22 +5207,25 @@
         <v>-1</v>
       </c>
       <c r="K76">
+        <v>-1</v>
+      </c>
+      <c r="L76">
         <v>0</v>
       </c>
-      <c r="L76">
+      <c r="M76">
         <v>7</v>
       </c>
-      <c r="M76">
-        <v>1</v>
-      </c>
-      <c r="N76" t="b">
-        <v>1</v>
-      </c>
-      <c r="O76" s="6" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N76">
+        <v>1</v>
+      </c>
+      <c r="O76" t="b">
+        <v>1</v>
+      </c>
+      <c r="P76" s="6" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>70</v>
       </c>
@@ -5018,7 +5233,7 @@
         <v>3</v>
       </c>
       <c r="D77" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E77">
         <v>15</v>
@@ -5039,22 +5254,25 @@
         <v>-1</v>
       </c>
       <c r="K77">
+        <v>-1</v>
+      </c>
+      <c r="L77">
         <v>0</v>
       </c>
-      <c r="L77">
+      <c r="M77">
         <v>50</v>
       </c>
-      <c r="M77">
-        <v>1</v>
-      </c>
-      <c r="N77" t="b">
-        <v>1</v>
-      </c>
-      <c r="O77" s="6" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N77">
+        <v>1</v>
+      </c>
+      <c r="O77" t="b">
+        <v>1</v>
+      </c>
+      <c r="P77" s="6" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>71</v>
       </c>
@@ -5062,7 +5280,7 @@
         <v>3</v>
       </c>
       <c r="D78" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E78">
         <v>6</v>
@@ -5083,22 +5301,25 @@
         <v>-1</v>
       </c>
       <c r="K78">
+        <v>-1</v>
+      </c>
+      <c r="L78">
         <v>0</v>
       </c>
-      <c r="L78">
+      <c r="M78">
         <v>35</v>
       </c>
-      <c r="M78">
-        <v>1</v>
-      </c>
-      <c r="N78" t="b">
-        <v>1</v>
-      </c>
-      <c r="O78" s="6" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N78">
+        <v>1</v>
+      </c>
+      <c r="O78" t="b">
+        <v>1</v>
+      </c>
+      <c r="P78" s="6" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>72</v>
       </c>
@@ -5106,7 +5327,7 @@
         <v>3</v>
       </c>
       <c r="D79" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E79">
         <v>8</v>
@@ -5127,22 +5348,25 @@
         <v>-1</v>
       </c>
       <c r="K79">
+        <v>-1</v>
+      </c>
+      <c r="L79">
         <v>0</v>
       </c>
-      <c r="L79">
+      <c r="M79">
         <v>25</v>
       </c>
-      <c r="M79">
-        <v>1</v>
-      </c>
-      <c r="N79" t="b">
-        <v>1</v>
-      </c>
-      <c r="O79" s="6" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N79">
+        <v>1</v>
+      </c>
+      <c r="O79" t="b">
+        <v>1</v>
+      </c>
+      <c r="P79" s="6" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>73</v>
       </c>
@@ -5150,7 +5374,7 @@
         <v>3</v>
       </c>
       <c r="D80" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E80">
         <v>20</v>
@@ -5171,22 +5395,25 @@
         <v>-1</v>
       </c>
       <c r="K80">
+        <v>-1</v>
+      </c>
+      <c r="L80">
         <v>0</v>
       </c>
-      <c r="L80">
+      <c r="M80">
         <v>150</v>
       </c>
-      <c r="M80">
-        <v>1</v>
-      </c>
-      <c r="N80" t="b">
-        <v>1</v>
-      </c>
-      <c r="O80" s="6" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N80">
+        <v>1</v>
+      </c>
+      <c r="O80" t="b">
+        <v>1</v>
+      </c>
+      <c r="P80" s="6" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>74</v>
       </c>
@@ -5194,7 +5421,7 @@
         <v>3</v>
       </c>
       <c r="D81" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E81">
         <v>5</v>
@@ -5215,22 +5442,25 @@
         <v>-1</v>
       </c>
       <c r="K81">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L81">
+        <v>1</v>
+      </c>
+      <c r="M81">
         <v>120</v>
       </c>
-      <c r="M81">
-        <v>1</v>
-      </c>
-      <c r="N81" t="b">
-        <v>1</v>
-      </c>
-      <c r="O81" s="6" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N81">
+        <v>1</v>
+      </c>
+      <c r="O81" t="b">
+        <v>1</v>
+      </c>
+      <c r="P81" s="6" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>75</v>
       </c>
@@ -5238,7 +5468,7 @@
         <v>3</v>
       </c>
       <c r="D82" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E82">
         <v>4</v>
@@ -5259,22 +5489,25 @@
         <v>-1</v>
       </c>
       <c r="K82">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L82">
+        <v>1</v>
+      </c>
+      <c r="M82">
         <v>100</v>
       </c>
-      <c r="M82">
-        <v>1</v>
-      </c>
-      <c r="N82" t="b">
-        <v>1</v>
-      </c>
-      <c r="O82" s="6" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N82">
+        <v>1</v>
+      </c>
+      <c r="O82" t="b">
+        <v>1</v>
+      </c>
+      <c r="P82" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>76</v>
       </c>
@@ -5282,7 +5515,7 @@
         <v>3</v>
       </c>
       <c r="D83" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E83">
         <v>3</v>
@@ -5303,22 +5536,25 @@
         <v>-1</v>
       </c>
       <c r="K83">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L83">
+        <v>1</v>
+      </c>
+      <c r="M83">
         <v>150</v>
       </c>
-      <c r="M83">
-        <v>1</v>
-      </c>
-      <c r="N83" t="b">
-        <v>1</v>
-      </c>
-      <c r="O83" s="6" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N83">
+        <v>1</v>
+      </c>
+      <c r="O83" t="b">
+        <v>1</v>
+      </c>
+      <c r="P83" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>77</v>
       </c>
@@ -5326,7 +5562,7 @@
         <v>3</v>
       </c>
       <c r="D84" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E84">
         <v>20</v>
@@ -5347,22 +5583,25 @@
         <v>-1</v>
       </c>
       <c r="K84">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L84">
+        <v>1</v>
+      </c>
+      <c r="M84">
         <v>620</v>
       </c>
-      <c r="M84">
-        <v>1</v>
-      </c>
-      <c r="N84" t="b">
-        <v>1</v>
-      </c>
-      <c r="O84" s="6" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N84">
+        <v>1</v>
+      </c>
+      <c r="O84" t="b">
+        <v>1</v>
+      </c>
+      <c r="P84" s="6" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>78</v>
       </c>
@@ -5370,7 +5609,7 @@
         <v>3</v>
       </c>
       <c r="D85" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E85">
         <v>10</v>
@@ -5391,22 +5630,25 @@
         <v>-1</v>
       </c>
       <c r="K85">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L85">
+        <v>1</v>
+      </c>
+      <c r="M85">
         <v>360</v>
       </c>
-      <c r="M85">
-        <v>1</v>
-      </c>
-      <c r="N85" t="b">
-        <v>1</v>
-      </c>
-      <c r="O85" s="6" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N85">
+        <v>1</v>
+      </c>
+      <c r="O85" t="b">
+        <v>1</v>
+      </c>
+      <c r="P85" s="6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>79</v>
       </c>
@@ -5414,7 +5656,7 @@
         <v>3</v>
       </c>
       <c r="D86" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E86">
         <v>12</v>
@@ -5435,22 +5677,25 @@
         <v>-1</v>
       </c>
       <c r="K86">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L86">
+        <v>1</v>
+      </c>
+      <c r="M86">
         <v>500</v>
       </c>
-      <c r="M86">
-        <v>1</v>
-      </c>
-      <c r="N86" t="b">
-        <v>1</v>
-      </c>
-      <c r="O86" s="6" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N86">
+        <v>1</v>
+      </c>
+      <c r="O86" t="b">
+        <v>1</v>
+      </c>
+      <c r="P86" s="6" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>80</v>
       </c>
@@ -5458,7 +5703,7 @@
         <v>3</v>
       </c>
       <c r="D87" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E87">
         <v>17</v>
@@ -5479,22 +5724,25 @@
         <v>-1</v>
       </c>
       <c r="K87">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L87">
+        <v>1</v>
+      </c>
+      <c r="M87">
         <v>440</v>
       </c>
-      <c r="M87">
-        <v>1</v>
-      </c>
-      <c r="N87" t="b">
-        <v>1</v>
-      </c>
-      <c r="O87" s="6" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N87">
+        <v>1</v>
+      </c>
+      <c r="O87" t="b">
+        <v>1</v>
+      </c>
+      <c r="P87" s="6" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>81</v>
       </c>
@@ -5502,7 +5750,7 @@
         <v>3</v>
       </c>
       <c r="D88" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E88">
         <v>8</v>
@@ -5523,22 +5771,25 @@
         <v>-1</v>
       </c>
       <c r="K88">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L88">
+        <v>1</v>
+      </c>
+      <c r="M88">
         <v>170</v>
       </c>
-      <c r="M88">
-        <v>1</v>
-      </c>
-      <c r="N88" t="b">
-        <v>1</v>
-      </c>
-      <c r="O88" s="6" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N88">
+        <v>1</v>
+      </c>
+      <c r="O88" t="b">
+        <v>1</v>
+      </c>
+      <c r="P88" s="6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>82</v>
       </c>
@@ -5546,7 +5797,7 @@
         <v>3</v>
       </c>
       <c r="D89" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E89">
         <v>10</v>
@@ -5567,22 +5818,25 @@
         <v>-1</v>
       </c>
       <c r="K89">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L89">
+        <v>1</v>
+      </c>
+      <c r="M89">
         <v>270</v>
       </c>
-      <c r="M89">
-        <v>1</v>
-      </c>
-      <c r="N89" t="b">
-        <v>1</v>
-      </c>
-      <c r="O89" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N89">
+        <v>1</v>
+      </c>
+      <c r="O89" t="b">
+        <v>1</v>
+      </c>
+      <c r="P89" s="6" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>83</v>
       </c>
@@ -5590,7 +5844,7 @@
         <v>3</v>
       </c>
       <c r="D90" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E90">
         <v>17</v>
@@ -5611,22 +5865,25 @@
         <v>-1</v>
       </c>
       <c r="K90">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L90">
+        <v>1</v>
+      </c>
+      <c r="M90">
         <v>530</v>
       </c>
-      <c r="M90">
-        <v>1</v>
-      </c>
-      <c r="N90" t="b">
-        <v>1</v>
-      </c>
-      <c r="O90" s="6" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N90">
+        <v>1</v>
+      </c>
+      <c r="O90" t="b">
+        <v>1</v>
+      </c>
+      <c r="P90" s="6" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>84</v>
       </c>
@@ -5634,7 +5891,7 @@
         <v>3</v>
       </c>
       <c r="D91" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E91">
         <v>30</v>
@@ -5655,22 +5912,25 @@
         <v>-1</v>
       </c>
       <c r="K91">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L91">
+        <v>1</v>
+      </c>
+      <c r="M91">
         <v>720</v>
       </c>
-      <c r="M91">
-        <v>1</v>
-      </c>
-      <c r="N91" t="b">
-        <v>1</v>
-      </c>
-      <c r="O91" s="6" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N91">
+        <v>1</v>
+      </c>
+      <c r="O91" t="b">
+        <v>1</v>
+      </c>
+      <c r="P91" s="6" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>85</v>
       </c>
@@ -5678,7 +5938,7 @@
         <v>3</v>
       </c>
       <c r="D92" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E92">
         <v>14</v>
@@ -5699,22 +5959,25 @@
         <v>-1</v>
       </c>
       <c r="K92">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L92">
+        <v>1</v>
+      </c>
+      <c r="M92">
         <v>300</v>
       </c>
-      <c r="M92">
-        <v>1</v>
-      </c>
-      <c r="N92" t="b">
-        <v>1</v>
-      </c>
-      <c r="O92" s="6" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N92">
+        <v>1</v>
+      </c>
+      <c r="O92" t="b">
+        <v>1</v>
+      </c>
+      <c r="P92" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>86</v>
       </c>
@@ -5722,7 +5985,7 @@
         <v>3</v>
       </c>
       <c r="D93" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E93">
         <v>8</v>
@@ -5743,22 +6006,25 @@
         <v>-1</v>
       </c>
       <c r="K93">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L93">
+        <v>1</v>
+      </c>
+      <c r="M93">
         <v>360</v>
       </c>
-      <c r="M93">
-        <v>1</v>
-      </c>
-      <c r="N93" t="b">
-        <v>1</v>
-      </c>
-      <c r="O93" s="6" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N93">
+        <v>1</v>
+      </c>
+      <c r="O93" t="b">
+        <v>1</v>
+      </c>
+      <c r="P93" s="6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>87</v>
       </c>
@@ -5766,7 +6032,7 @@
         <v>3</v>
       </c>
       <c r="D94" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E94">
         <v>15</v>
@@ -5787,22 +6053,25 @@
         <v>-1</v>
       </c>
       <c r="K94">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L94">
+        <v>1</v>
+      </c>
+      <c r="M94">
         <v>520</v>
       </c>
-      <c r="M94">
-        <v>1</v>
-      </c>
-      <c r="N94" t="b">
-        <v>1</v>
-      </c>
-      <c r="O94" s="6" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N94">
+        <v>1</v>
+      </c>
+      <c r="O94" t="b">
+        <v>1</v>
+      </c>
+      <c r="P94" s="6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>88</v>
       </c>
@@ -5810,7 +6079,7 @@
         <v>3</v>
       </c>
       <c r="D95" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E95">
         <v>5</v>
@@ -5831,22 +6100,25 @@
         <v>-1</v>
       </c>
       <c r="K95">
+        <v>-1</v>
+      </c>
+      <c r="L95">
         <v>2</v>
       </c>
-      <c r="L95">
+      <c r="M95">
         <v>300</v>
       </c>
-      <c r="M95">
-        <v>1</v>
-      </c>
-      <c r="N95" t="b">
-        <v>1</v>
-      </c>
-      <c r="O95" s="6" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N95">
+        <v>1</v>
+      </c>
+      <c r="O95" t="b">
+        <v>1</v>
+      </c>
+      <c r="P95" s="6" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>89</v>
       </c>
@@ -5854,7 +6126,7 @@
         <v>3</v>
       </c>
       <c r="D96" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E96">
         <v>3</v>
@@ -5875,22 +6147,25 @@
         <v>-1</v>
       </c>
       <c r="K96">
+        <v>-1</v>
+      </c>
+      <c r="L96">
         <v>2</v>
       </c>
-      <c r="L96">
+      <c r="M96">
         <v>340</v>
       </c>
-      <c r="M96">
-        <v>1</v>
-      </c>
-      <c r="N96" t="b">
-        <v>1</v>
-      </c>
-      <c r="O96" s="6" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N96">
+        <v>1</v>
+      </c>
+      <c r="O96" t="b">
+        <v>1</v>
+      </c>
+      <c r="P96" s="6" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>90</v>
       </c>
@@ -5898,7 +6173,7 @@
         <v>3</v>
       </c>
       <c r="D97" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E97">
         <v>30</v>
@@ -5919,22 +6194,25 @@
         <v>-1</v>
       </c>
       <c r="K97">
+        <v>-1</v>
+      </c>
+      <c r="L97">
         <v>2</v>
       </c>
-      <c r="L97">
+      <c r="M97">
         <v>2400</v>
       </c>
-      <c r="M97">
-        <v>1</v>
-      </c>
-      <c r="N97" t="b">
-        <v>1</v>
-      </c>
-      <c r="O97" s="6" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N97">
+        <v>1</v>
+      </c>
+      <c r="O97" t="b">
+        <v>1</v>
+      </c>
+      <c r="P97" s="6" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>91</v>
       </c>
@@ -5942,7 +6220,7 @@
         <v>3</v>
       </c>
       <c r="D98" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E98">
         <v>20</v>
@@ -5963,22 +6241,25 @@
         <v>-1</v>
       </c>
       <c r="K98">
+        <v>-1</v>
+      </c>
+      <c r="L98">
         <v>2</v>
       </c>
-      <c r="L98">
+      <c r="M98">
         <v>1400</v>
       </c>
-      <c r="M98">
-        <v>1</v>
-      </c>
-      <c r="N98" t="b">
-        <v>1</v>
-      </c>
-      <c r="O98" s="6" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N98">
+        <v>1</v>
+      </c>
+      <c r="O98" t="b">
+        <v>1</v>
+      </c>
+      <c r="P98" s="6" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>92</v>
       </c>
@@ -5986,7 +6267,7 @@
         <v>3</v>
       </c>
       <c r="D99" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E99">
         <v>18</v>
@@ -6007,22 +6288,25 @@
         <v>-1</v>
       </c>
       <c r="K99">
+        <v>-1</v>
+      </c>
+      <c r="L99">
         <v>2</v>
       </c>
-      <c r="L99">
+      <c r="M99">
         <v>1800</v>
       </c>
-      <c r="M99">
-        <v>1</v>
-      </c>
-      <c r="N99" t="b">
-        <v>1</v>
-      </c>
-      <c r="O99" s="6" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N99">
+        <v>1</v>
+      </c>
+      <c r="O99" t="b">
+        <v>1</v>
+      </c>
+      <c r="P99" s="6" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>93</v>
       </c>
@@ -6030,7 +6314,7 @@
         <v>3</v>
       </c>
       <c r="D100" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E100">
         <v>8</v>
@@ -6051,22 +6335,25 @@
         <v>-1</v>
       </c>
       <c r="K100">
+        <v>-1</v>
+      </c>
+      <c r="L100">
         <v>2</v>
       </c>
-      <c r="L100">
+      <c r="M100">
         <v>700</v>
       </c>
-      <c r="M100">
-        <v>1</v>
-      </c>
-      <c r="N100" t="b">
-        <v>1</v>
-      </c>
-      <c r="O100" s="6" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N100">
+        <v>1</v>
+      </c>
+      <c r="O100" t="b">
+        <v>1</v>
+      </c>
+      <c r="P100" s="6" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>94</v>
       </c>
@@ -6074,7 +6361,7 @@
         <v>3</v>
       </c>
       <c r="D101" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E101">
         <v>2</v>
@@ -6095,22 +6382,25 @@
         <v>-1</v>
       </c>
       <c r="K101">
+        <v>-1</v>
+      </c>
+      <c r="L101">
         <v>2</v>
       </c>
-      <c r="L101">
+      <c r="M101">
         <v>240</v>
       </c>
-      <c r="M101">
-        <v>1</v>
-      </c>
-      <c r="N101" t="b">
-        <v>1</v>
-      </c>
-      <c r="O101" s="6" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N101">
+        <v>1</v>
+      </c>
+      <c r="O101" t="b">
+        <v>1</v>
+      </c>
+      <c r="P101" s="6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A102">
         <v>95</v>
       </c>
@@ -6118,7 +6408,7 @@
         <v>3</v>
       </c>
       <c r="D102" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E102">
         <v>40</v>
@@ -6139,22 +6429,25 @@
         <v>-1</v>
       </c>
       <c r="K102">
+        <v>-1</v>
+      </c>
+      <c r="L102">
         <v>2</v>
       </c>
-      <c r="L102">
+      <c r="M102">
         <v>2950</v>
       </c>
-      <c r="M102">
-        <v>1</v>
-      </c>
-      <c r="N102" t="b">
-        <v>1</v>
-      </c>
-      <c r="O102" s="6" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N102">
+        <v>1</v>
+      </c>
+      <c r="O102" t="b">
+        <v>1</v>
+      </c>
+      <c r="P102" s="6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A103">
         <v>96</v>
       </c>
@@ -6162,7 +6455,7 @@
         <v>3</v>
       </c>
       <c r="D103" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E103">
         <v>15</v>
@@ -6183,22 +6476,25 @@
         <v>-1</v>
       </c>
       <c r="K103">
+        <v>-1</v>
+      </c>
+      <c r="L103">
         <v>2</v>
       </c>
-      <c r="L103">
+      <c r="M103">
         <v>1350</v>
       </c>
-      <c r="M103">
-        <v>1</v>
-      </c>
-      <c r="N103" t="b">
-        <v>1</v>
-      </c>
-      <c r="O103" s="6" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N103">
+        <v>1</v>
+      </c>
+      <c r="O103" t="b">
+        <v>1</v>
+      </c>
+      <c r="P103" s="6" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A104">
         <v>97</v>
       </c>
@@ -6206,7 +6502,7 @@
         <v>3</v>
       </c>
       <c r="D104" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E104">
         <v>5</v>
@@ -6227,22 +6523,25 @@
         <v>-1</v>
       </c>
       <c r="K104">
+        <v>-1</v>
+      </c>
+      <c r="L104">
         <v>3</v>
       </c>
-      <c r="L104">
+      <c r="M104">
         <v>1500</v>
       </c>
-      <c r="M104">
-        <v>1</v>
-      </c>
-      <c r="N104" t="b">
-        <v>1</v>
-      </c>
-      <c r="O104" s="6" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N104">
+        <v>1</v>
+      </c>
+      <c r="O104" t="b">
+        <v>1</v>
+      </c>
+      <c r="P104" s="6" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A105">
         <v>98</v>
       </c>
@@ -6250,7 +6549,7 @@
         <v>3</v>
       </c>
       <c r="D105" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E105">
         <v>25</v>
@@ -6271,22 +6570,25 @@
         <v>-1</v>
       </c>
       <c r="K105">
+        <v>-1</v>
+      </c>
+      <c r="L105">
         <v>3</v>
       </c>
-      <c r="L105">
+      <c r="M105">
         <v>5000</v>
       </c>
-      <c r="M105">
-        <v>1</v>
-      </c>
-      <c r="N105" t="b">
-        <v>1</v>
-      </c>
-      <c r="O105" s="6" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N105">
+        <v>1</v>
+      </c>
+      <c r="O105" t="b">
+        <v>1</v>
+      </c>
+      <c r="P105" s="6" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A106">
         <v>99</v>
       </c>
@@ -6294,7 +6596,7 @@
         <v>3</v>
       </c>
       <c r="D106" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E106">
         <v>30</v>
@@ -6315,22 +6617,25 @@
         <v>-1</v>
       </c>
       <c r="K106">
+        <v>-1</v>
+      </c>
+      <c r="L106">
         <v>3</v>
       </c>
-      <c r="L106">
+      <c r="M106">
         <v>4520</v>
       </c>
-      <c r="M106">
-        <v>1</v>
-      </c>
-      <c r="N106" t="b">
-        <v>1</v>
-      </c>
-      <c r="O106" s="6" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N106">
+        <v>1</v>
+      </c>
+      <c r="O106" t="b">
+        <v>1</v>
+      </c>
+      <c r="P106" s="6" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A107">
         <v>100</v>
       </c>
@@ -6338,7 +6643,7 @@
         <v>3</v>
       </c>
       <c r="D107" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E107">
         <v>50</v>
@@ -6359,22 +6664,25 @@
         <v>-1</v>
       </c>
       <c r="K107">
+        <v>-1</v>
+      </c>
+      <c r="L107">
         <v>3</v>
       </c>
-      <c r="L107">
+      <c r="M107">
         <v>9800</v>
       </c>
-      <c r="M107">
-        <v>1</v>
-      </c>
-      <c r="N107" t="b">
-        <v>1</v>
-      </c>
-      <c r="O107" s="6" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N107">
+        <v>1</v>
+      </c>
+      <c r="O107" t="b">
+        <v>1</v>
+      </c>
+      <c r="P107" s="6" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A108">
         <v>101</v>
       </c>
@@ -6382,7 +6690,7 @@
         <v>3</v>
       </c>
       <c r="D108" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E108">
         <v>45</v>
@@ -6403,22 +6711,25 @@
         <v>-1</v>
       </c>
       <c r="K108">
+        <v>-1</v>
+      </c>
+      <c r="L108">
         <v>3</v>
       </c>
-      <c r="L108">
+      <c r="M108">
         <v>12000</v>
       </c>
-      <c r="M108">
-        <v>1</v>
-      </c>
-      <c r="N108" t="b">
-        <v>1</v>
-      </c>
-      <c r="O108" s="6" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N108">
+        <v>1</v>
+      </c>
+      <c r="O108" t="b">
+        <v>1</v>
+      </c>
+      <c r="P108" s="6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A109">
         <v>102</v>
       </c>
@@ -6426,7 +6737,7 @@
         <v>3</v>
       </c>
       <c r="D109" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E109">
         <v>40</v>
@@ -6447,22 +6758,25 @@
         <v>-1</v>
       </c>
       <c r="K109">
+        <v>-1</v>
+      </c>
+      <c r="L109">
         <v>3</v>
       </c>
-      <c r="L109">
+      <c r="M109">
         <v>7500</v>
       </c>
-      <c r="M109">
-        <v>1</v>
-      </c>
-      <c r="N109" t="b">
-        <v>1</v>
-      </c>
-      <c r="O109" s="6" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N109">
+        <v>1</v>
+      </c>
+      <c r="O109" t="b">
+        <v>1</v>
+      </c>
+      <c r="P109" s="6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A110">
         <v>103</v>
       </c>
@@ -6470,7 +6784,7 @@
         <v>3</v>
       </c>
       <c r="D110" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E110">
         <v>80</v>
@@ -6491,22 +6805,25 @@
         <v>-1</v>
       </c>
       <c r="K110">
+        <v>-1</v>
+      </c>
+      <c r="L110">
         <v>3</v>
       </c>
-      <c r="L110">
+      <c r="M110">
         <v>19520</v>
       </c>
-      <c r="M110">
-        <v>1</v>
-      </c>
-      <c r="N110" t="b">
-        <v>1</v>
-      </c>
-      <c r="O110" s="6" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N110">
+        <v>1</v>
+      </c>
+      <c r="O110" t="b">
+        <v>1</v>
+      </c>
+      <c r="P110" s="6" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A111">
         <v>104</v>
       </c>
@@ -6514,7 +6831,7 @@
         <v>3</v>
       </c>
       <c r="D111" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E111">
         <v>1</v>
@@ -6535,22 +6852,25 @@
         <v>-1</v>
       </c>
       <c r="K111">
+        <v>-1</v>
+      </c>
+      <c r="L111">
         <v>4</v>
       </c>
-      <c r="L111">
+      <c r="M111">
         <v>1000</v>
       </c>
-      <c r="M111">
-        <v>1</v>
-      </c>
-      <c r="N111" t="b">
-        <v>1</v>
-      </c>
-      <c r="O111" s="6" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N111">
+        <v>1</v>
+      </c>
+      <c r="O111" t="b">
+        <v>1</v>
+      </c>
+      <c r="P111" s="6" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A112">
         <v>105</v>
       </c>
@@ -6558,7 +6878,7 @@
         <v>3</v>
       </c>
       <c r="D112" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E112">
         <v>70</v>
@@ -6579,22 +6899,25 @@
         <v>-1</v>
       </c>
       <c r="K112">
+        <v>-1</v>
+      </c>
+      <c r="L112">
         <v>4</v>
       </c>
-      <c r="L112">
+      <c r="M112">
         <v>37200</v>
       </c>
-      <c r="M112">
-        <v>1</v>
-      </c>
-      <c r="N112" t="b">
-        <v>1</v>
-      </c>
-      <c r="O112" s="6" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N112">
+        <v>1</v>
+      </c>
+      <c r="O112" t="b">
+        <v>1</v>
+      </c>
+      <c r="P112" s="6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A113">
         <v>106</v>
       </c>
@@ -6602,7 +6925,7 @@
         <v>3</v>
       </c>
       <c r="D113" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E113">
         <v>62</v>
@@ -6623,22 +6946,25 @@
         <v>-1</v>
       </c>
       <c r="K113">
+        <v>-1</v>
+      </c>
+      <c r="L113">
         <v>4</v>
       </c>
-      <c r="L113">
+      <c r="M113">
         <v>42890</v>
       </c>
-      <c r="M113">
-        <v>1</v>
-      </c>
-      <c r="N113" t="b">
-        <v>1</v>
-      </c>
-      <c r="O113" s="6" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N113">
+        <v>1</v>
+      </c>
+      <c r="O113" t="b">
+        <v>1</v>
+      </c>
+      <c r="P113" s="6" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A114">
         <v>107</v>
       </c>
@@ -6646,7 +6972,7 @@
         <v>3</v>
       </c>
       <c r="D114" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E114">
         <v>150</v>
@@ -6667,22 +6993,25 @@
         <v>-1</v>
       </c>
       <c r="K114">
+        <v>-1</v>
+      </c>
+      <c r="L114">
         <v>4</v>
       </c>
-      <c r="L114">
+      <c r="M114">
         <v>132460</v>
       </c>
-      <c r="M114">
-        <v>1</v>
-      </c>
-      <c r="N114" t="b">
-        <v>1</v>
-      </c>
-      <c r="O114" s="6" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N114">
+        <v>1</v>
+      </c>
+      <c r="O114" t="b">
+        <v>1</v>
+      </c>
+      <c r="P114" s="6" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A115">
         <v>108</v>
       </c>
@@ -6690,7 +7019,7 @@
         <v>3</v>
       </c>
       <c r="D115" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E115">
         <v>70</v>
@@ -6711,970 +7040,973 @@
         <v>-1</v>
       </c>
       <c r="K115">
+        <v>-1</v>
+      </c>
+      <c r="L115">
         <v>4</v>
       </c>
-      <c r="L115">
+      <c r="M115">
         <v>52520</v>
       </c>
-      <c r="M115">
-        <v>1</v>
-      </c>
-      <c r="N115" t="b">
-        <v>1</v>
-      </c>
-      <c r="O115" s="6" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N115">
+        <v>1</v>
+      </c>
+      <c r="O115" t="b">
+        <v>1</v>
+      </c>
+      <c r="P115" s="6" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.45">
       <c r="O117" s="6"/>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.45">
       <c r="O118" s="6"/>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.45">
       <c r="O119" s="6"/>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.45">
       <c r="O120" s="6"/>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.45">
       <c r="O121" s="6"/>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.45">
       <c r="O122" s="6"/>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.45">
       <c r="O123" s="6"/>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.45">
       <c r="O124" s="6"/>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.45">
       <c r="O125" s="6"/>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.45">
       <c r="O126" s="6"/>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.45">
       <c r="O127" s="6"/>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.45">
       <c r="O128" s="6"/>
     </row>
-    <row r="129" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="129" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O129" s="6"/>
     </row>
-    <row r="130" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="130" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O130" s="6"/>
     </row>
-    <row r="131" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="131" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O131" s="6"/>
     </row>
-    <row r="132" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="132" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O132" s="6"/>
     </row>
-    <row r="133" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="133" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O133" s="6"/>
     </row>
-    <row r="134" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="134" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O134" s="6"/>
     </row>
-    <row r="135" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="135" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O135" s="6"/>
     </row>
-    <row r="136" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="136" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O136" s="6"/>
     </row>
-    <row r="137" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="137" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O137" s="6"/>
     </row>
-    <row r="138" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="138" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O138" s="6"/>
     </row>
-    <row r="139" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="139" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O139" s="6"/>
     </row>
-    <row r="140" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="140" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O140" s="6"/>
     </row>
-    <row r="141" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="141" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O141" s="6"/>
     </row>
-    <row r="142" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="142" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O142" s="6"/>
     </row>
-    <row r="143" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="143" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O143" s="6"/>
     </row>
-    <row r="144" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="144" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O144" s="6"/>
     </row>
-    <row r="145" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="145" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O145" s="6"/>
     </row>
-    <row r="146" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="146" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O146" s="6"/>
     </row>
-    <row r="147" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="147" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O147" s="6"/>
     </row>
-    <row r="148" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="148" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O148" s="6"/>
     </row>
-    <row r="149" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="149" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O149" s="6"/>
     </row>
-    <row r="150" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="150" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O150" s="6"/>
     </row>
-    <row r="151" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="151" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O151" s="6"/>
     </row>
-    <row r="152" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="152" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O152" s="6"/>
     </row>
-    <row r="153" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="153" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O153" s="6"/>
     </row>
-    <row r="154" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="154" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O154" s="6"/>
     </row>
-    <row r="155" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="155" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O155" s="6"/>
     </row>
-    <row r="156" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="156" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O156" s="6"/>
     </row>
-    <row r="157" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="157" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O157" s="6"/>
     </row>
-    <row r="158" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="158" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O158" s="6"/>
     </row>
-    <row r="159" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="159" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O159" s="6"/>
     </row>
-    <row r="160" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="160" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O160" s="6"/>
     </row>
-    <row r="161" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="161" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O161" s="6"/>
     </row>
-    <row r="162" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="162" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O162" s="6"/>
     </row>
-    <row r="163" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="163" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O163" s="6"/>
     </row>
-    <row r="164" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="164" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O164" s="6"/>
     </row>
-    <row r="165" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="165" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O165" s="6"/>
     </row>
-    <row r="166" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="166" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O166" s="6"/>
     </row>
-    <row r="167" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="167" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O167" s="6"/>
     </row>
-    <row r="168" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="168" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O168" s="6"/>
     </row>
-    <row r="169" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="169" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O169" s="6"/>
     </row>
-    <row r="170" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="170" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O170" s="6"/>
     </row>
-    <row r="171" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="171" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O171" s="6"/>
     </row>
-    <row r="172" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="172" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O172" s="6"/>
     </row>
-    <row r="173" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="173" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O173" s="6"/>
     </row>
-    <row r="174" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="174" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O174" s="6"/>
     </row>
-    <row r="175" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="175" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O175" s="6"/>
     </row>
-    <row r="176" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="176" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O176" s="6"/>
     </row>
-    <row r="177" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="177" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O177" s="6"/>
     </row>
-    <row r="178" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="178" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O178" s="6"/>
     </row>
-    <row r="179" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="179" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O179" s="6"/>
     </row>
-    <row r="180" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="180" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O180" s="6"/>
     </row>
-    <row r="181" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="181" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O181" s="6"/>
     </row>
-    <row r="182" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="182" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O182" s="6"/>
     </row>
-    <row r="183" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="183" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O183" s="6"/>
     </row>
-    <row r="184" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="184" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O184" s="6"/>
     </row>
-    <row r="185" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="185" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O185" s="6"/>
     </row>
-    <row r="186" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="186" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O186" s="6"/>
     </row>
-    <row r="187" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="187" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O187" s="6"/>
     </row>
-    <row r="188" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="188" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O188" s="6"/>
     </row>
-    <row r="189" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="189" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O189" s="6"/>
     </row>
-    <row r="190" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="190" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O190" s="6"/>
     </row>
-    <row r="191" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="191" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O191" s="6"/>
     </row>
-    <row r="192" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="192" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O192" s="6"/>
     </row>
-    <row r="193" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="193" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O193" s="6"/>
     </row>
-    <row r="194" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="194" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O194" s="6"/>
     </row>
-    <row r="195" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="195" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O195" s="6"/>
     </row>
-    <row r="196" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="196" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O196" s="6"/>
     </row>
-    <row r="197" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="197" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O197" s="6"/>
     </row>
-    <row r="198" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="198" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O198" s="6"/>
     </row>
-    <row r="199" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="199" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O199" s="6"/>
     </row>
-    <row r="200" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="200" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O200" s="6"/>
     </row>
-    <row r="201" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="201" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O201" s="6"/>
     </row>
-    <row r="202" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="202" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O202" s="6"/>
     </row>
-    <row r="203" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="203" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O203" s="6"/>
     </row>
-    <row r="204" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="204" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O204" s="6"/>
     </row>
-    <row r="205" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="205" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O205" s="6"/>
     </row>
-    <row r="206" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="206" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O206" s="6"/>
     </row>
-    <row r="207" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="207" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O207" s="6"/>
     </row>
-    <row r="208" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="208" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O208" s="6"/>
     </row>
-    <row r="209" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="209" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O209" s="6"/>
     </row>
-    <row r="210" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="210" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O210" s="6"/>
     </row>
-    <row r="211" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="211" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O211" s="6"/>
     </row>
-    <row r="212" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="212" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O212" s="6"/>
     </row>
-    <row r="213" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="213" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O213" s="6"/>
     </row>
-    <row r="214" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="214" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O214" s="6"/>
     </row>
-    <row r="215" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="215" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O215" s="6"/>
     </row>
-    <row r="216" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="216" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O216" s="6"/>
     </row>
-    <row r="217" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="217" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O217" s="6"/>
     </row>
-    <row r="218" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="218" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O218" s="6"/>
     </row>
-    <row r="219" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="219" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O219" s="6"/>
     </row>
-    <row r="220" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="220" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O220" s="6"/>
     </row>
-    <row r="221" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="221" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O221" s="6"/>
     </row>
-    <row r="222" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="222" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O222" s="6"/>
     </row>
-    <row r="223" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="223" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O223" s="6"/>
     </row>
-    <row r="224" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="224" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O224" s="6"/>
     </row>
-    <row r="225" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="225" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O225" s="6"/>
     </row>
-    <row r="226" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="226" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O226" s="6"/>
     </row>
-    <row r="227" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="227" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O227" s="6"/>
     </row>
-    <row r="228" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="228" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O228" s="6"/>
     </row>
-    <row r="229" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="229" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O229" s="6"/>
     </row>
-    <row r="230" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="230" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O230" s="6"/>
     </row>
-    <row r="231" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="231" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O231" s="6"/>
     </row>
-    <row r="232" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="232" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O232" s="6"/>
     </row>
-    <row r="233" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="233" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O233" s="6"/>
     </row>
-    <row r="234" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="234" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O234" s="6"/>
     </row>
-    <row r="235" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="235" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O235" s="6"/>
     </row>
-    <row r="236" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="236" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O236" s="6"/>
     </row>
-    <row r="237" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="237" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O237" s="6"/>
     </row>
-    <row r="238" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="238" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O238" s="6"/>
     </row>
-    <row r="239" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="239" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O239" s="6"/>
     </row>
-    <row r="240" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="240" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O240" s="6"/>
     </row>
-    <row r="241" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="241" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O241" s="6"/>
     </row>
-    <row r="242" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="242" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O242" s="6"/>
     </row>
-    <row r="243" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="243" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O243" s="6"/>
     </row>
-    <row r="244" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="244" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O244" s="6"/>
     </row>
-    <row r="245" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="245" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O245" s="6"/>
     </row>
-    <row r="246" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="246" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O246" s="6"/>
     </row>
-    <row r="247" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="247" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O247" s="6"/>
     </row>
-    <row r="248" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="248" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O248" s="6"/>
     </row>
-    <row r="249" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="249" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O249" s="6"/>
     </row>
-    <row r="250" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="250" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O250" s="6"/>
     </row>
-    <row r="251" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="251" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O251" s="6"/>
     </row>
-    <row r="252" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="252" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O252" s="6"/>
     </row>
-    <row r="253" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="253" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O253" s="6"/>
     </row>
-    <row r="254" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="254" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O254" s="6"/>
     </row>
-    <row r="255" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="255" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O255" s="6"/>
     </row>
-    <row r="256" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="256" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O256" s="6"/>
     </row>
-    <row r="257" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="257" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O257" s="6"/>
     </row>
-    <row r="258" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="258" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O258" s="6"/>
     </row>
-    <row r="259" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="259" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O259" s="6"/>
     </row>
-    <row r="260" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="260" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O260" s="6"/>
     </row>
-    <row r="261" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="261" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O261" s="6"/>
     </row>
-    <row r="262" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="262" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O262" s="6"/>
     </row>
-    <row r="263" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="263" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O263" s="6"/>
     </row>
-    <row r="264" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="264" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O264" s="6"/>
     </row>
-    <row r="265" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="265" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O265" s="6"/>
     </row>
-    <row r="266" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="266" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O266" s="6"/>
     </row>
-    <row r="267" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="267" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O267" s="6"/>
     </row>
-    <row r="268" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="268" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O268" s="6"/>
     </row>
-    <row r="269" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="269" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O269" s="6"/>
     </row>
-    <row r="270" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="270" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O270" s="6"/>
     </row>
-    <row r="271" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="271" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O271" s="6"/>
     </row>
-    <row r="272" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="272" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O272" s="6"/>
     </row>
-    <row r="273" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="273" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O273" s="6"/>
     </row>
-    <row r="274" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="274" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O274" s="6"/>
     </row>
-    <row r="275" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="275" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O275" s="6"/>
     </row>
-    <row r="276" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="276" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O276" s="6"/>
     </row>
-    <row r="277" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="277" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O277" s="6"/>
     </row>
-    <row r="278" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="278" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O278" s="6"/>
     </row>
-    <row r="279" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="279" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O279" s="6"/>
     </row>
-    <row r="280" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="280" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O280" s="6"/>
     </row>
-    <row r="281" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="281" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O281" s="6"/>
     </row>
-    <row r="282" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="282" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O282" s="6"/>
     </row>
-    <row r="283" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="283" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O283" s="6"/>
     </row>
-    <row r="284" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="284" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O284" s="6"/>
     </row>
-    <row r="285" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="285" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O285" s="6"/>
     </row>
-    <row r="286" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="286" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O286" s="6"/>
     </row>
-    <row r="287" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="287" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O287" s="6"/>
     </row>
-    <row r="288" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="288" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O288" s="6"/>
     </row>
-    <row r="289" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="289" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O289" s="6"/>
     </row>
-    <row r="290" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="290" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O290" s="6"/>
     </row>
-    <row r="291" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="291" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O291" s="6"/>
     </row>
-    <row r="292" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="292" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O292" s="6"/>
     </row>
-    <row r="293" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="293" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O293" s="6"/>
     </row>
-    <row r="294" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="294" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O294" s="6"/>
     </row>
-    <row r="295" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="295" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O295" s="6"/>
     </row>
-    <row r="296" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="296" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O296" s="6"/>
     </row>
-    <row r="297" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="297" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O297" s="6"/>
     </row>
-    <row r="298" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="298" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O298" s="6"/>
     </row>
-    <row r="299" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="299" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O299" s="6"/>
     </row>
-    <row r="300" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="300" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O300" s="6"/>
     </row>
-    <row r="301" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="301" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O301" s="6"/>
     </row>
-    <row r="302" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="302" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O302" s="6"/>
     </row>
-    <row r="303" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="303" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O303" s="6"/>
     </row>
-    <row r="304" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="304" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O304" s="6"/>
     </row>
-    <row r="305" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="305" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O305" s="6"/>
     </row>
-    <row r="306" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="306" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O306" s="6"/>
     </row>
-    <row r="307" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="307" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O307" s="6"/>
     </row>
-    <row r="308" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="308" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O308" s="6"/>
     </row>
-    <row r="309" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="309" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O309" s="6"/>
     </row>
-    <row r="310" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="310" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O310" s="6"/>
     </row>
-    <row r="311" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="311" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O311" s="6"/>
     </row>
-    <row r="312" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="312" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O312" s="6"/>
     </row>
-    <row r="313" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="313" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O313" s="6"/>
     </row>
-    <row r="314" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="314" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O314" s="6"/>
     </row>
-    <row r="315" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="315" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O315" s="6"/>
     </row>
-    <row r="316" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="316" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O316" s="6"/>
     </row>
-    <row r="317" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="317" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O317" s="6"/>
     </row>
-    <row r="318" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="318" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O318" s="6"/>
     </row>
-    <row r="319" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="319" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O319" s="6"/>
     </row>
-    <row r="320" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="320" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O320" s="6"/>
     </row>
-    <row r="321" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="321" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O321" s="6"/>
     </row>
-    <row r="322" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="322" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O322" s="6"/>
     </row>
-    <row r="323" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="323" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O323" s="6"/>
     </row>
-    <row r="324" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="324" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O324" s="6"/>
     </row>
-    <row r="325" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="325" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O325" s="6"/>
     </row>
-    <row r="326" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="326" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O326" s="6"/>
     </row>
-    <row r="327" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="327" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O327" s="6"/>
     </row>
-    <row r="328" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="328" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O328" s="6"/>
     </row>
-    <row r="329" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="329" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O329" s="6"/>
     </row>
-    <row r="330" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="330" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O330" s="6"/>
     </row>
-    <row r="331" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="331" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O331" s="6"/>
     </row>
-    <row r="332" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="332" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O332" s="6"/>
     </row>
-    <row r="333" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="333" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O333" s="6"/>
     </row>
-    <row r="334" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="334" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O334" s="6"/>
     </row>
-    <row r="335" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="335" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O335" s="6"/>
     </row>
-    <row r="336" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="336" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O336" s="6"/>
     </row>
-    <row r="337" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="337" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O337" s="6"/>
     </row>
-    <row r="338" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="338" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O338" s="6"/>
     </row>
-    <row r="339" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="339" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O339" s="6"/>
     </row>
-    <row r="340" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="340" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O340" s="6"/>
     </row>
-    <row r="341" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="341" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O341" s="6"/>
     </row>
-    <row r="342" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="342" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O342" s="6"/>
     </row>
-    <row r="343" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="343" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O343" s="6"/>
     </row>
-    <row r="344" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="344" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O344" s="6"/>
     </row>
-    <row r="345" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="345" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O345" s="6"/>
     </row>
-    <row r="346" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="346" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O346" s="6"/>
     </row>
-    <row r="347" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="347" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O347" s="6"/>
     </row>
-    <row r="348" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="348" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O348" s="6"/>
     </row>
-    <row r="349" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="349" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O349" s="6"/>
     </row>
-    <row r="350" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="350" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O350" s="6"/>
     </row>
-    <row r="351" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="351" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O351" s="6"/>
     </row>
-    <row r="352" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="352" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O352" s="6"/>
     </row>
-    <row r="353" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="353" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O353" s="6"/>
     </row>
-    <row r="354" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="354" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O354" s="6"/>
     </row>
-    <row r="355" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="355" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O355" s="6"/>
     </row>
-    <row r="356" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="356" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O356" s="6"/>
     </row>
-    <row r="357" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="357" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O357" s="6"/>
     </row>
-    <row r="358" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="358" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O358" s="6"/>
     </row>
-    <row r="359" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="359" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O359" s="6"/>
     </row>
-    <row r="360" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="360" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O360" s="6"/>
     </row>
-    <row r="361" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="361" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O361" s="6"/>
     </row>
-    <row r="362" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="362" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O362" s="6"/>
     </row>
-    <row r="363" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="363" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O363" s="6"/>
     </row>
-    <row r="364" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="364" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O364" s="6"/>
     </row>
-    <row r="365" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="365" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O365" s="6"/>
     </row>
-    <row r="366" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="366" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O366" s="6"/>
     </row>
-    <row r="367" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="367" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O367" s="6"/>
     </row>
-    <row r="368" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="368" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O368" s="6"/>
     </row>
-    <row r="369" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="369" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O369" s="6"/>
     </row>
-    <row r="370" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="370" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O370" s="6"/>
     </row>
-    <row r="371" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="371" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O371" s="6"/>
     </row>
-    <row r="372" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="372" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O372" s="6"/>
     </row>
-    <row r="373" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="373" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O373" s="6"/>
     </row>
-    <row r="374" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="374" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O374" s="6"/>
     </row>
-    <row r="375" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="375" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O375" s="6"/>
     </row>
-    <row r="376" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="376" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O376" s="6"/>
     </row>
-    <row r="377" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="377" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O377" s="6"/>
     </row>
-    <row r="378" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="378" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O378" s="6"/>
     </row>
-    <row r="379" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="379" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O379" s="6"/>
     </row>
-    <row r="380" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="380" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O380" s="6"/>
     </row>
-    <row r="381" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="381" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O381" s="6"/>
     </row>
-    <row r="382" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="382" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O382" s="6"/>
     </row>
-    <row r="383" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="383" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O383" s="6"/>
     </row>
-    <row r="384" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="384" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O384" s="6"/>
     </row>
-    <row r="385" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="385" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O385" s="6"/>
     </row>
-    <row r="386" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="386" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O386" s="6"/>
     </row>
-    <row r="387" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="387" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O387" s="6"/>
     </row>
-    <row r="388" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="388" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O388" s="6"/>
     </row>
-    <row r="389" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="389" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O389" s="6"/>
     </row>
-    <row r="390" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="390" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O390" s="6"/>
     </row>
-    <row r="391" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="391" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O391" s="6"/>
     </row>
-    <row r="392" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="392" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O392" s="6"/>
     </row>
-    <row r="393" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="393" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O393" s="6"/>
     </row>
-    <row r="394" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="394" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O394" s="6"/>
     </row>
-    <row r="395" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="395" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O395" s="6"/>
     </row>
-    <row r="396" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="396" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O396" s="6"/>
     </row>
-    <row r="397" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="397" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O397" s="6"/>
     </row>
-    <row r="398" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="398" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O398" s="6"/>
     </row>
-    <row r="399" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="399" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O399" s="6"/>
     </row>
-    <row r="400" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="400" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O400" s="6"/>
     </row>
-    <row r="401" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="401" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O401" s="6"/>
     </row>
-    <row r="402" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="402" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O402" s="6"/>
     </row>
-    <row r="403" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="403" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O403" s="6"/>
     </row>
-    <row r="404" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="404" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O404" s="6"/>
     </row>
-    <row r="405" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="405" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O405" s="6"/>
     </row>
-    <row r="406" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="406" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O406" s="6"/>
     </row>
-    <row r="407" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="407" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O407" s="6"/>
     </row>
-    <row r="408" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="408" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O408" s="6"/>
     </row>
-    <row r="409" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="409" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O409" s="6"/>
     </row>
-    <row r="410" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="410" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O410" s="6"/>
     </row>
-    <row r="411" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="411" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O411" s="6"/>
     </row>
-    <row r="412" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="412" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O412" s="6"/>
     </row>
-    <row r="413" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="413" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O413" s="6"/>
     </row>
-    <row r="414" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="414" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O414" s="6"/>
     </row>
-    <row r="415" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="415" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O415" s="6"/>
     </row>
-    <row r="416" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="416" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O416" s="6"/>
     </row>
-    <row r="417" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="417" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O417" s="6"/>
     </row>
-    <row r="418" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="418" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O418" s="6"/>
     </row>
-    <row r="419" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="419" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O419" s="6"/>
     </row>
-    <row r="420" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="420" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O420" s="6"/>
     </row>
-    <row r="421" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="421" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O421" s="6"/>
     </row>
-    <row r="422" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="422" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O422" s="6"/>
     </row>
-    <row r="423" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="423" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O423" s="6"/>
     </row>
-    <row r="424" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="424" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O424" s="6"/>
     </row>
-    <row r="425" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="425" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O425" s="6"/>
     </row>
-    <row r="426" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="426" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O426" s="6"/>
     </row>
-    <row r="427" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="427" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O427" s="6"/>
     </row>
-    <row r="428" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="428" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O428" s="6"/>
     </row>
-    <row r="429" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="429" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O429" s="6"/>
     </row>
-    <row r="430" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="430" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O430" s="6"/>
     </row>
-    <row r="431" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="431" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O431" s="6"/>
     </row>
-    <row r="432" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="432" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O432" s="6"/>
     </row>
-    <row r="433" spans="15:15" x14ac:dyDescent="0.3">
+    <row r="433" spans="15:15" x14ac:dyDescent="0.45">
       <c r="O433" s="6"/>
     </row>
   </sheetData>

--- a/아이템 도감.xlsx
+++ b/아이템 도감.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hcw97\Desktop\CapstoneProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97ADA58A-AACE-43DB-861F-BC4435306B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38591FD7-74D7-49E0-932A-1DDFF31B4557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{AEFF7BDA-CB51-4C25-A75C-46A97EA8EBD6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{AEFF7BDA-CB51-4C25-A75C-46A97EA8EBD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -194,9 +194,6 @@
     <t>조금 남은 과자</t>
   </si>
   <si>
-    <t>피자 박스</t>
-  </si>
-  <si>
     <t>상한 생선</t>
   </si>
   <si>
@@ -472,10 +469,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>한 조각 반이 들어 있다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>새것 같은 달콤한 초콜릿.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -488,10 +481,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>유통기한 임박 할인' 스티커가 붙어 있다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>몸이 가벼워진다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -988,6 +977,18 @@
   </si>
   <si>
     <t>max_durability</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>조각 피자</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>유통기한 임박 할인 스티커가 붙어 있다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>치즈가 길게 늘어나는 맛있는 피자</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1593,10 +1594,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>11</v>
@@ -1608,7 +1609,7 @@
         <v>5</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>6</v>
@@ -1623,7 +1624,7 @@
         <v>9</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="Q1" s="11" t="s">
         <v>10</v>
@@ -1676,10 +1677,10 @@
         <v>1</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="Q2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.45">
@@ -1730,7 +1731,7 @@
       </c>
       <c r="P3" s="6"/>
       <c r="Q3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.45">
@@ -1781,7 +1782,7 @@
       </c>
       <c r="P4" s="6"/>
       <c r="Q4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.45">
@@ -1832,7 +1833,7 @@
       </c>
       <c r="P5" s="6"/>
       <c r="Q5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.45">
@@ -1882,10 +1883,10 @@
         <v>1</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="Q6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.45">
@@ -1936,7 +1937,7 @@
       </c>
       <c r="P7" s="6"/>
       <c r="Q7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.45">
@@ -1987,7 +1988,7 @@
       </c>
       <c r="P8" s="6"/>
       <c r="Q8" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.45">
@@ -2038,7 +2039,7 @@
       </c>
       <c r="P9" s="6"/>
       <c r="Q9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.45">
@@ -2088,10 +2089,10 @@
         <v>1</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="Q10" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.45">
@@ -2142,7 +2143,7 @@
       </c>
       <c r="P11" s="6"/>
       <c r="Q11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.45">
@@ -2193,7 +2194,7 @@
       </c>
       <c r="P12" s="6"/>
       <c r="Q12" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.45">
@@ -2244,7 +2245,7 @@
       </c>
       <c r="P13" s="6"/>
       <c r="Q13" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.45">
@@ -2295,7 +2296,7 @@
       </c>
       <c r="P14" s="6"/>
       <c r="Q14" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.45">
@@ -2309,7 +2310,7 @@
         <v>150</v>
       </c>
       <c r="D15" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -2345,10 +2346,10 @@
         <v>1</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="Q15" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.45">
@@ -2398,10 +2399,10 @@
         <v>1</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="Q16" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.45">
@@ -2415,7 +2416,7 @@
         <v>151</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -2451,10 +2452,10 @@
         <v>1</v>
       </c>
       <c r="P17" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Q17" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.45">
@@ -2504,10 +2505,10 @@
         <v>1</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="Q18" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.45">
@@ -2558,7 +2559,7 @@
       </c>
       <c r="P19" s="6"/>
       <c r="Q19" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.45">
@@ -2608,10 +2609,10 @@
         <v>1</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Q20" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.45">
@@ -2661,10 +2662,10 @@
         <v>1</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="Q24" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.45">
@@ -2714,10 +2715,10 @@
         <v>1</v>
       </c>
       <c r="P25" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="Q25" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.45">
@@ -2767,10 +2768,10 @@
         <v>1</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="Q26" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.45">
@@ -2820,10 +2821,10 @@
         <v>1</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="Q27" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.45">
@@ -2873,13 +2874,13 @@
         <v>1</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="Q28" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="R28" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.45">
@@ -2929,13 +2930,13 @@
         <v>1</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="Q29" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R29" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.45">
@@ -2985,10 +2986,10 @@
         <v>1</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="Q30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.45">
@@ -3038,10 +3039,10 @@
         <v>1</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="Q31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.45">
@@ -3091,10 +3092,10 @@
         <v>1</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="Q32" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.45">
@@ -3144,10 +3145,10 @@
         <v>1</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="Q33" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.45">
@@ -3197,10 +3198,10 @@
         <v>1</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="Q34" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.45">
@@ -3250,10 +3251,10 @@
         <v>1</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q35" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.45">
@@ -3303,13 +3304,13 @@
         <v>1</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="Q36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="R36" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.45">
@@ -3359,13 +3360,13 @@
         <v>1</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="Q37" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="R37" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.45">
@@ -3379,7 +3380,7 @@
         <v>202</v>
       </c>
       <c r="D38" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -3415,10 +3416,10 @@
         <v>1</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q38" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.45">
@@ -3468,10 +3469,10 @@
         <v>1</v>
       </c>
       <c r="P39" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="Q39" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.45">
@@ -3521,13 +3522,13 @@
         <v>1</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="Q40" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R40" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.45">
@@ -3577,10 +3578,10 @@
         <v>1</v>
       </c>
       <c r="P41" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="Q41" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.45">
@@ -3630,10 +3631,10 @@
         <v>1</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="Q42" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.45">
@@ -3683,10 +3684,10 @@
         <v>1</v>
       </c>
       <c r="P43" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="Q43" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.45">
@@ -3736,10 +3737,10 @@
         <v>1</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="Q44" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.45">
@@ -3789,13 +3790,13 @@
         <v>1</v>
       </c>
       <c r="P45" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q45" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="R45" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.45">
@@ -3845,10 +3846,10 @@
         <v>1</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="Q46" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.45">
@@ -3862,7 +3863,7 @@
         <v>202</v>
       </c>
       <c r="D47" t="s">
-        <v>52</v>
+        <v>286</v>
       </c>
       <c r="E47">
         <v>1</v>
@@ -3898,10 +3899,10 @@
         <v>1</v>
       </c>
       <c r="P47" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="Q47" t="s">
-        <v>138</v>
+        <v>288</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.45">
@@ -3915,7 +3916,7 @@
         <v>202</v>
       </c>
       <c r="D48" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E48">
         <v>1</v>
@@ -3951,10 +3952,10 @@
         <v>1</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="Q48" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.45">
@@ -3968,7 +3969,7 @@
         <v>202</v>
       </c>
       <c r="D49" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E49">
         <v>1</v>
@@ -4004,10 +4005,10 @@
         <v>1</v>
       </c>
       <c r="P49" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="Q49" s="9" t="s">
-        <v>142</v>
+        <v>287</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.45">
@@ -4024,7 +4025,7 @@
         <v>302</v>
       </c>
       <c r="D52" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E52">
         <v>1</v>
@@ -4060,13 +4061,13 @@
         <v>1</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="Q52" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="R52" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.45">
@@ -4080,7 +4081,7 @@
         <v>301</v>
       </c>
       <c r="D53" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -4116,13 +4117,13 @@
         <v>1</v>
       </c>
       <c r="P53" s="6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="Q53" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="R53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.45">
@@ -4136,7 +4137,7 @@
         <v>301</v>
       </c>
       <c r="D54" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E54">
         <v>1</v>
@@ -4172,13 +4173,13 @@
         <v>1</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="Q54" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="R54" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.45">
@@ -4192,7 +4193,7 @@
         <v>303</v>
       </c>
       <c r="D55" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E55">
         <v>1</v>
@@ -4228,13 +4229,13 @@
         <v>1</v>
       </c>
       <c r="P55" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="Q55" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="R55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.45">
@@ -4248,7 +4249,7 @@
         <v>300</v>
       </c>
       <c r="D56" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E56">
         <v>1</v>
@@ -4284,10 +4285,10 @@
         <v>1</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="Q56" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.45">
@@ -4301,7 +4302,7 @@
         <v>300</v>
       </c>
       <c r="D57" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E57">
         <v>1</v>
@@ -4337,10 +4338,10 @@
         <v>1</v>
       </c>
       <c r="P57" s="6" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="Q57" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.45">
@@ -4354,7 +4355,7 @@
         <v>300</v>
       </c>
       <c r="D58" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E58">
         <v>1</v>
@@ -4390,10 +4391,10 @@
         <v>1</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="Q58" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.45">
@@ -4407,7 +4408,7 @@
         <v>300</v>
       </c>
       <c r="D59" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E59">
         <v>1</v>
@@ -4443,13 +4444,13 @@
         <v>1</v>
       </c>
       <c r="P59" s="6" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="Q59" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="R59" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.45">
@@ -4463,7 +4464,7 @@
         <v>303</v>
       </c>
       <c r="D60" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -4499,13 +4500,13 @@
         <v>1</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="Q60" t="s">
+        <v>154</v>
+      </c>
+      <c r="R60" t="s">
         <v>157</v>
-      </c>
-      <c r="R60" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.45">
@@ -4519,7 +4520,7 @@
         <v>303</v>
       </c>
       <c r="D61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E61">
         <v>1</v>
@@ -4555,13 +4556,13 @@
         <v>1</v>
       </c>
       <c r="P61" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="Q61" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="R61" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.45">
@@ -4575,7 +4576,7 @@
         <v>3</v>
       </c>
       <c r="D63" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E63">
         <v>2</v>
@@ -4611,7 +4612,7 @@
         <v>1</v>
       </c>
       <c r="P63" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.45">
@@ -4622,7 +4623,7 @@
         <v>3</v>
       </c>
       <c r="D64" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E64">
         <v>3</v>
@@ -4658,7 +4659,7 @@
         <v>1</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.45">
@@ -4669,7 +4670,7 @@
         <v>3</v>
       </c>
       <c r="D65" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E65">
         <v>4</v>
@@ -4705,7 +4706,7 @@
         <v>1</v>
       </c>
       <c r="P65" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.45">
@@ -4716,7 +4717,7 @@
         <v>3</v>
       </c>
       <c r="D66" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E66">
         <v>3</v>
@@ -4752,7 +4753,7 @@
         <v>1</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.45">
@@ -4763,7 +4764,7 @@
         <v>3</v>
       </c>
       <c r="D67" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E67">
         <v>4</v>
@@ -4799,7 +4800,7 @@
         <v>1</v>
       </c>
       <c r="P67" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.45">
@@ -4810,7 +4811,7 @@
         <v>3</v>
       </c>
       <c r="D68" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E68">
         <v>1</v>
@@ -4846,7 +4847,7 @@
         <v>1</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.45">
@@ -4857,7 +4858,7 @@
         <v>3</v>
       </c>
       <c r="D69" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E69">
         <v>10</v>
@@ -4893,7 +4894,7 @@
         <v>1</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.45">
@@ -4904,7 +4905,7 @@
         <v>3</v>
       </c>
       <c r="D70" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E70">
         <v>1</v>
@@ -4940,7 +4941,7 @@
         <v>1</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.45">
@@ -4951,7 +4952,7 @@
         <v>3</v>
       </c>
       <c r="D71" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E71">
         <v>2</v>
@@ -4987,7 +4988,7 @@
         <v>1</v>
       </c>
       <c r="P71" s="6" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.45">
@@ -4998,7 +4999,7 @@
         <v>3</v>
       </c>
       <c r="D72" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E72">
         <v>5</v>
@@ -5034,7 +5035,7 @@
         <v>1</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.45">
@@ -5045,7 +5046,7 @@
         <v>3</v>
       </c>
       <c r="D73" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E73">
         <v>40</v>
@@ -5081,7 +5082,7 @@
         <v>1</v>
       </c>
       <c r="P73" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.45">
@@ -5092,7 +5093,7 @@
         <v>3</v>
       </c>
       <c r="D74" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E74">
         <v>1</v>
@@ -5128,7 +5129,7 @@
         <v>1</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.45">
@@ -5139,7 +5140,7 @@
         <v>3</v>
       </c>
       <c r="D75" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E75">
         <v>2</v>
@@ -5175,7 +5176,7 @@
         <v>1</v>
       </c>
       <c r="P75" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.45">
@@ -5186,7 +5187,7 @@
         <v>3</v>
       </c>
       <c r="D76" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E76">
         <v>3</v>
@@ -5222,7 +5223,7 @@
         <v>1</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.45">
@@ -5233,7 +5234,7 @@
         <v>3</v>
       </c>
       <c r="D77" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E77">
         <v>15</v>
@@ -5269,7 +5270,7 @@
         <v>1</v>
       </c>
       <c r="P77" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.45">
@@ -5280,7 +5281,7 @@
         <v>3</v>
       </c>
       <c r="D78" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E78">
         <v>6</v>
@@ -5316,7 +5317,7 @@
         <v>1</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.45">
@@ -5327,7 +5328,7 @@
         <v>3</v>
       </c>
       <c r="D79" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E79">
         <v>8</v>
@@ -5363,7 +5364,7 @@
         <v>1</v>
       </c>
       <c r="P79" s="6" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.45">
@@ -5374,7 +5375,7 @@
         <v>3</v>
       </c>
       <c r="D80" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E80">
         <v>20</v>
@@ -5410,7 +5411,7 @@
         <v>1</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.45">
@@ -5421,7 +5422,7 @@
         <v>3</v>
       </c>
       <c r="D81" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E81">
         <v>5</v>
@@ -5457,7 +5458,7 @@
         <v>1</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.45">
@@ -5468,7 +5469,7 @@
         <v>3</v>
       </c>
       <c r="D82" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E82">
         <v>4</v>
@@ -5504,7 +5505,7 @@
         <v>1</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.45">
@@ -5515,7 +5516,7 @@
         <v>3</v>
       </c>
       <c r="D83" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E83">
         <v>3</v>
@@ -5551,7 +5552,7 @@
         <v>1</v>
       </c>
       <c r="P83" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.45">
@@ -5562,7 +5563,7 @@
         <v>3</v>
       </c>
       <c r="D84" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E84">
         <v>20</v>
@@ -5598,7 +5599,7 @@
         <v>1</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.45">
@@ -5609,7 +5610,7 @@
         <v>3</v>
       </c>
       <c r="D85" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E85">
         <v>10</v>
@@ -5645,7 +5646,7 @@
         <v>1</v>
       </c>
       <c r="P85" s="6" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.45">
@@ -5656,7 +5657,7 @@
         <v>3</v>
       </c>
       <c r="D86" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E86">
         <v>12</v>
@@ -5692,7 +5693,7 @@
         <v>1</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.45">
@@ -5703,7 +5704,7 @@
         <v>3</v>
       </c>
       <c r="D87" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E87">
         <v>17</v>
@@ -5739,7 +5740,7 @@
         <v>1</v>
       </c>
       <c r="P87" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.45">
@@ -5750,7 +5751,7 @@
         <v>3</v>
       </c>
       <c r="D88" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E88">
         <v>8</v>
@@ -5786,7 +5787,7 @@
         <v>1</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.45">
@@ -5797,7 +5798,7 @@
         <v>3</v>
       </c>
       <c r="D89" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E89">
         <v>10</v>
@@ -5833,7 +5834,7 @@
         <v>1</v>
       </c>
       <c r="P89" s="6" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.45">
@@ -5844,7 +5845,7 @@
         <v>3</v>
       </c>
       <c r="D90" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E90">
         <v>17</v>
@@ -5880,7 +5881,7 @@
         <v>1</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.45">
@@ -5891,7 +5892,7 @@
         <v>3</v>
       </c>
       <c r="D91" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E91">
         <v>30</v>
@@ -5927,7 +5928,7 @@
         <v>1</v>
       </c>
       <c r="P91" s="6" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.45">
@@ -5938,7 +5939,7 @@
         <v>3</v>
       </c>
       <c r="D92" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E92">
         <v>14</v>
@@ -5974,7 +5975,7 @@
         <v>1</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.45">
@@ -5985,7 +5986,7 @@
         <v>3</v>
       </c>
       <c r="D93" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E93">
         <v>8</v>
@@ -6021,7 +6022,7 @@
         <v>1</v>
       </c>
       <c r="P93" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.45">
@@ -6032,7 +6033,7 @@
         <v>3</v>
       </c>
       <c r="D94" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E94">
         <v>15</v>
@@ -6068,7 +6069,7 @@
         <v>1</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.45">
@@ -6079,7 +6080,7 @@
         <v>3</v>
       </c>
       <c r="D95" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E95">
         <v>5</v>
@@ -6115,7 +6116,7 @@
         <v>1</v>
       </c>
       <c r="P95" s="6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.45">
@@ -6126,7 +6127,7 @@
         <v>3</v>
       </c>
       <c r="D96" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E96">
         <v>3</v>
@@ -6162,7 +6163,7 @@
         <v>1</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.45">
@@ -6173,7 +6174,7 @@
         <v>3</v>
       </c>
       <c r="D97" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E97">
         <v>30</v>
@@ -6209,7 +6210,7 @@
         <v>1</v>
       </c>
       <c r="P97" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.45">
@@ -6220,7 +6221,7 @@
         <v>3</v>
       </c>
       <c r="D98" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E98">
         <v>20</v>
@@ -6256,7 +6257,7 @@
         <v>1</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.45">
@@ -6267,7 +6268,7 @@
         <v>3</v>
       </c>
       <c r="D99" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E99">
         <v>18</v>
@@ -6303,7 +6304,7 @@
         <v>1</v>
       </c>
       <c r="P99" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.45">
@@ -6314,7 +6315,7 @@
         <v>3</v>
       </c>
       <c r="D100" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E100">
         <v>8</v>
@@ -6350,7 +6351,7 @@
         <v>1</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.45">
@@ -6361,7 +6362,7 @@
         <v>3</v>
       </c>
       <c r="D101" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E101">
         <v>2</v>
@@ -6397,7 +6398,7 @@
         <v>1</v>
       </c>
       <c r="P101" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.45">
@@ -6408,7 +6409,7 @@
         <v>3</v>
       </c>
       <c r="D102" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E102">
         <v>40</v>
@@ -6444,7 +6445,7 @@
         <v>1</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.45">
@@ -6455,7 +6456,7 @@
         <v>3</v>
       </c>
       <c r="D103" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E103">
         <v>15</v>
@@ -6491,7 +6492,7 @@
         <v>1</v>
       </c>
       <c r="P103" s="6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.45">
@@ -6502,7 +6503,7 @@
         <v>3</v>
       </c>
       <c r="D104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E104">
         <v>5</v>
@@ -6538,7 +6539,7 @@
         <v>1</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.45">
@@ -6549,7 +6550,7 @@
         <v>3</v>
       </c>
       <c r="D105" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E105">
         <v>25</v>
@@ -6585,7 +6586,7 @@
         <v>1</v>
       </c>
       <c r="P105" s="6" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.45">
@@ -6596,7 +6597,7 @@
         <v>3</v>
       </c>
       <c r="D106" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E106">
         <v>30</v>
@@ -6632,7 +6633,7 @@
         <v>1</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.45">
@@ -6643,7 +6644,7 @@
         <v>3</v>
       </c>
       <c r="D107" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E107">
         <v>50</v>
@@ -6679,7 +6680,7 @@
         <v>1</v>
       </c>
       <c r="P107" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.45">
@@ -6690,7 +6691,7 @@
         <v>3</v>
       </c>
       <c r="D108" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E108">
         <v>45</v>
@@ -6726,7 +6727,7 @@
         <v>1</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.45">
@@ -6737,7 +6738,7 @@
         <v>3</v>
       </c>
       <c r="D109" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E109">
         <v>40</v>
@@ -6773,7 +6774,7 @@
         <v>1</v>
       </c>
       <c r="P109" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.45">
@@ -6784,7 +6785,7 @@
         <v>3</v>
       </c>
       <c r="D110" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E110">
         <v>80</v>
@@ -6820,7 +6821,7 @@
         <v>1</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.45">
@@ -6831,7 +6832,7 @@
         <v>3</v>
       </c>
       <c r="D111" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E111">
         <v>1</v>
@@ -6867,7 +6868,7 @@
         <v>1</v>
       </c>
       <c r="P111" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.45">
@@ -6878,7 +6879,7 @@
         <v>3</v>
       </c>
       <c r="D112" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E112">
         <v>70</v>
@@ -6914,7 +6915,7 @@
         <v>1</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.45">
@@ -6925,7 +6926,7 @@
         <v>3</v>
       </c>
       <c r="D113" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E113">
         <v>62</v>
@@ -6961,7 +6962,7 @@
         <v>1</v>
       </c>
       <c r="P113" s="6" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.45">
@@ -6972,7 +6973,7 @@
         <v>3</v>
       </c>
       <c r="D114" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E114">
         <v>150</v>
@@ -7008,7 +7009,7 @@
         <v>1</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.45">
@@ -7019,7 +7020,7 @@
         <v>3</v>
       </c>
       <c r="D115" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E115">
         <v>70</v>
@@ -7055,7 +7056,7 @@
         <v>1</v>
       </c>
       <c r="P115" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.45">
